--- a/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
+++ b/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F6C471-EBE9-4AFB-AA74-4F5ECB625FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64F0989-431A-48DD-96C9-AA825C29A2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="543">
   <si>
     <t>Component list</t>
   </si>
@@ -82,15 +82,9 @@
     <t>C2</t>
   </si>
   <si>
-    <t>C3, C8, C11, C14, C19, C45, C59</t>
-  </si>
-  <si>
     <t>C5, C7, C12, C13, C16</t>
   </si>
   <si>
-    <t>C6, C10, C15, C18, C22, C25, C26, C27, C28, C29, C30, C33, C36, C37, C38, C39, C40, C41, C44, C46, C47, C48, C49, C51, C52, C55, C57, C60, C62, C64, C66, C68, C69, C73, C76</t>
-  </si>
-  <si>
     <t>C9</t>
   </si>
   <si>
@@ -103,24 +97,12 @@
     <t>C34, C35</t>
   </si>
   <si>
-    <t>C42, C79</t>
-  </si>
-  <si>
-    <t>C50, C54</t>
-  </si>
-  <si>
-    <t>C53, C78</t>
-  </si>
-  <si>
     <t>C56</t>
   </si>
   <si>
     <t>C70</t>
   </si>
   <si>
-    <t>C71, C72</t>
-  </si>
-  <si>
     <t>C74</t>
   </si>
   <si>
@@ -253,54 +235,27 @@
     <t>R3</t>
   </si>
   <si>
-    <t>R4, R6, R9, R27, R54, R55, R68, R69, R70, R72, R73, R74, R75, R82, R101, R102, R104</t>
-  </si>
-  <si>
-    <t>R5, R8, R16, R18, R19, R20, R21, R22, R37, R39, R66, R78, R80</t>
-  </si>
-  <si>
     <t>R7, R10</t>
   </si>
   <si>
     <t>R11</t>
   </si>
   <si>
-    <t>R12, R110, R114</t>
-  </si>
-  <si>
     <t>R13</t>
   </si>
   <si>
     <t>R14, R15, R17</t>
   </si>
   <si>
-    <t>R23, R35, R36, R38, R76, R77, R79</t>
-  </si>
-  <si>
     <t>R24, R25</t>
   </si>
   <si>
-    <t>R26, R34, R40, R41, R50, R51, R60, R61, R67, R71, R85</t>
-  </si>
-  <si>
-    <t>R28, R31, R33, R42, R43, R44, R45, R46, R47, R48, R49, R52, R53, R56, R63, R86, R87, R88, R106, R108, R109</t>
-  </si>
-  <si>
-    <t>R29, R107</t>
-  </si>
-  <si>
     <t>R30</t>
   </si>
   <si>
     <t>R32</t>
   </si>
   <si>
-    <t>R57</t>
-  </si>
-  <si>
-    <t>R58, R59, R62</t>
-  </si>
-  <si>
     <t>R64</t>
   </si>
   <si>
@@ -313,9 +268,6 @@
     <t>R83, R84</t>
   </si>
   <si>
-    <t>R89, R90, R99, R100</t>
-  </si>
-  <si>
     <t>R91, R92</t>
   </si>
   <si>
@@ -331,24 +283,12 @@
     <t>R103</t>
   </si>
   <si>
-    <t>R105</t>
-  </si>
-  <si>
-    <t>R111, R115</t>
-  </si>
-  <si>
     <t>R112</t>
   </si>
   <si>
-    <t>R113</t>
-  </si>
-  <si>
     <t>R116</t>
   </si>
   <si>
-    <t>R117, R118</t>
-  </si>
-  <si>
     <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB31, SB32, SB33, SB34, SB35, SB36, SB37, SB38, SB39, SB40, SB41, SB42</t>
   </si>
   <si>
@@ -427,9 +367,6 @@
     <t>CAP 30pF NP0 0603 50 V ±5 % SMD</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 100V X7R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 20PF 50V C0G/NPO 0603</t>
   </si>
   <si>
@@ -565,9 +502,6 @@
     <t>±1% 1/10W Thick Film Resistors 75V ±600ppm/℃ -55℃~+155℃ 0.33Ω 0603 Chip Resistor - Surface Mount ROHS</t>
   </si>
   <si>
-    <t>RES SMD 10K OHM 5% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES 2.2K OHM 1% 1/10W 0603, RES SMD 2.2K OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -595,12 +529,6 @@
     <t>RES SMD 1K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES SMD 4.7K OHM 5% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES SMD 1K 0.1W 0603  75 V, Thick Film</t>
-  </si>
-  <si>
     <t>RES SMD 20K OHM 0.1% 1/10W 0603</t>
   </si>
   <si>
@@ -628,39 +556,21 @@
     <t>RES 100K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>Res SMD 0603 1M Ohm 1% 1/10W ±100ppm/°C Molded SMD Paper T/R</t>
-  </si>
-  <si>
     <t>RES  SMD 330R 100 mW 0603</t>
   </si>
   <si>
     <t>RES SMD 50K ±0.5% ±25ppm/℃ 0805</t>
   </si>
   <si>
-    <t>Res SMD 0603 150K Ohm 1% 0.1W(1/10W) ±100ppm/C Pad SMD T/R</t>
-  </si>
-  <si>
     <t>RES 150 OHM 0.5% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES SMD 100K OHM 5% 1/5W 0603</t>
-  </si>
-  <si>
-    <t>RES 2.2K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES SMD 7.5K OHM 0.1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES 3.3K OHM 0.5% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES 20K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES 0 OHM JUMPER 1/10W 0603</t>
-  </si>
-  <si>
     <t>Solder Bridge ON</t>
   </si>
   <si>
@@ -727,9 +637,6 @@
     <t>CAP-CASE A</t>
   </si>
   <si>
-    <t>Cap-0603</t>
-  </si>
-  <si>
     <t>SMA</t>
   </si>
   <si>
@@ -832,9 +739,6 @@
     <t>RES 0805</t>
   </si>
   <si>
-    <t>Res0603</t>
-  </si>
-  <si>
     <t>Solder Bridge</t>
   </si>
   <si>
@@ -895,9 +799,6 @@
     <t>CC0603JRNPO9BN300</t>
   </si>
   <si>
-    <t>CC0603KRX7R0BB104</t>
-  </si>
-  <si>
     <t>CC0603JRNPO9BN200</t>
   </si>
   <si>
@@ -988,9 +889,6 @@
     <t>RC0603FR-071K2L</t>
   </si>
   <si>
-    <t>AC0603JR-0710KL</t>
-  </si>
-  <si>
     <t>RC0603FR-072K2L</t>
   </si>
   <si>
@@ -1018,12 +916,6 @@
     <t>RC0603FR-071KL</t>
   </si>
   <si>
-    <t>RC0603JR-074K7L</t>
-  </si>
-  <si>
-    <t>RC0603JR-071KL</t>
-  </si>
-  <si>
     <t>RT0603BRD0720KL</t>
   </si>
   <si>
@@ -1063,21 +955,12 @@
     <t>RC0603DR-07150RL</t>
   </si>
   <si>
-    <t>CRGH0603J100K</t>
-  </si>
-  <si>
     <t>RT0603BRD077K5L</t>
   </si>
   <si>
-    <t>RC0603DR-073K3L</t>
-  </si>
-  <si>
     <t>RC0603FR-0720KL</t>
   </si>
   <si>
-    <t>RC0603JR-070RL</t>
-  </si>
-  <si>
     <t>ACS723LLCTR-20AU-T</t>
   </si>
   <si>
@@ -1210,9 +1093,6 @@
     <t>RALEC</t>
   </si>
   <si>
-    <t>Yageo, Yageo Phycomp</t>
-  </si>
-  <si>
     <t>UNI-ROYAL</t>
   </si>
   <si>
@@ -1222,9 +1102,6 @@
     <t>Viking Tech</t>
   </si>
   <si>
-    <t>TE Connectivity</t>
-  </si>
-  <si>
     <t>E-Switch</t>
   </si>
   <si>
@@ -1291,12 +1168,6 @@
     <t>C98220</t>
   </si>
   <si>
-    <t>C105428</t>
-  </si>
-  <si>
-    <t>C14676</t>
-  </si>
-  <si>
     <t>C96346</t>
   </si>
   <si>
@@ -1523,6 +1394,262 @@
   </si>
   <si>
     <t>Buzzer</t>
+  </si>
+  <si>
+    <t>C3, C8, C11, C14, C19, C42, C45, C59, C79</t>
+  </si>
+  <si>
+    <t>C6, C10, C15, C18, C22, C25, C26, C27, C28, C29, C30, C33, C36, C37, C38, C39, C40, C41, C44, C46, C47, C48, C49, C50, C51, C52, C54, C55, C57, C60, C62, C64, C66, C68, C69, C73, C76</t>
+  </si>
+  <si>
+    <t>R4, R6, R9, R12, R27, R54, R55, R68, R69, R70, R72, R73, R74, R75, R82, R101, R102, R104, R110, R114</t>
+  </si>
+  <si>
+    <t>R28, R31, R33, R42, R43, R44, R45, R46, R47, R48, R49, R52, R53, R56, R58, R59, R62, R63, R86, R87, R88, R106, R108, R109</t>
+  </si>
+  <si>
+    <t>R26, R29, R34, R40, R41, R50, R51, R60, R61, R67, R71, R85, R107</t>
+  </si>
+  <si>
+    <t>R57, R117, R118</t>
+  </si>
+  <si>
+    <t>R89, R90, R99, R100, R105</t>
+  </si>
+  <si>
+    <t>R23, R35, R36, R38, R76, R77, R79, R113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                          </t>
+  </si>
+  <si>
+    <t>R5, R8, R16, R18, R19, R20, R21, R22, R37, R39, R66, R78, R80, R111, R115</t>
+  </si>
+  <si>
+    <t>C72484</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>C191227</t>
+  </si>
+  <si>
+    <t>C106221</t>
+  </si>
+  <si>
+    <t>C125982</t>
+  </si>
+  <si>
+    <t>C107092</t>
+  </si>
+  <si>
+    <t>C123716</t>
+  </si>
+  <si>
+    <t>C113797</t>
+  </si>
+  <si>
+    <t>C92847</t>
+  </si>
+  <si>
+    <t>C53, C78, C71, C72</t>
+  </si>
+  <si>
+    <t>C281768</t>
+  </si>
+  <si>
+    <t>C268016</t>
+  </si>
+  <si>
+    <t>C1639</t>
+  </si>
+  <si>
+    <t>C3035843</t>
+  </si>
+  <si>
+    <t>C128848</t>
+  </si>
+  <si>
+    <t>C908809</t>
+  </si>
+  <si>
+    <t>C309982</t>
+  </si>
+  <si>
+    <t>C3011128</t>
+  </si>
+  <si>
+    <t>KF2EDGRC-5.08-2P</t>
+  </si>
+  <si>
+    <t>KF2EDGRC-5.08-3P</t>
+  </si>
+  <si>
+    <t>KF2EDGRC-5.08-4P</t>
+  </si>
+  <si>
+    <t>C441236</t>
+  </si>
+  <si>
+    <t>C441237</t>
+  </si>
+  <si>
+    <t>C441238</t>
+  </si>
+  <si>
+    <t>C1509209</t>
+  </si>
+  <si>
+    <t>C2935994</t>
+  </si>
+  <si>
+    <t>C281113</t>
+  </si>
+  <si>
+    <t>C93225</t>
+  </si>
+  <si>
+    <t>C269823</t>
+  </si>
+  <si>
+    <t>C251779</t>
+  </si>
+  <si>
+    <t>C130719</t>
+  </si>
+  <si>
+    <t>C146233</t>
+  </si>
+  <si>
+    <t>C409828</t>
+  </si>
+  <si>
+    <t>C492405</t>
+  </si>
+  <si>
+    <t>C30734</t>
+  </si>
+  <si>
+    <t>C492401</t>
+  </si>
+  <si>
+    <t>C2935910</t>
+  </si>
+  <si>
+    <t>C156273</t>
+  </si>
+  <si>
+    <t>C558174</t>
+  </si>
+  <si>
+    <t>C558180</t>
+  </si>
+  <si>
+    <t>NCD0402R1</t>
+  </si>
+  <si>
+    <t>PZ254V-11-06P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ254V-11-02P
+</t>
+  </si>
+  <si>
+    <t>DZ254R-11-04-63</t>
+  </si>
+  <si>
+    <t>C49257</t>
+  </si>
+  <si>
+    <t>C57668</t>
+  </si>
+  <si>
+    <t>C8666</t>
+  </si>
+  <si>
+    <t>C41095</t>
+  </si>
+  <si>
+    <t>C181990</t>
+  </si>
+  <si>
+    <t>C144660</t>
+  </si>
+  <si>
+    <t>C114605</t>
+  </si>
+  <si>
+    <t>C103893</t>
+  </si>
+  <si>
+    <t>C144601</t>
+  </si>
+  <si>
+    <t>C422956</t>
+  </si>
+  <si>
+    <t>C112310</t>
+  </si>
+  <si>
+    <t>C108078</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t>C100044</t>
+  </si>
+  <si>
+    <t>C99782</t>
+  </si>
+  <si>
+    <t>C14675</t>
+  </si>
+  <si>
+    <t>C2828840</t>
+  </si>
+  <si>
+    <t>ARG05DTC5002</t>
+  </si>
+  <si>
+    <t>C114660</t>
+  </si>
+  <si>
+    <t>RES 150K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>C273516</t>
+  </si>
+  <si>
+    <t>C100023</t>
+  </si>
+  <si>
+    <t>C201952</t>
+  </si>
+  <si>
+    <t>C713240</t>
+  </si>
+  <si>
+    <t>C67112</t>
+  </si>
+  <si>
+    <t>C100024</t>
+  </si>
+  <si>
+    <t>C33002</t>
+  </si>
+  <si>
+    <t>C219772</t>
+  </si>
+  <si>
+    <t>C90465</t>
+  </si>
+  <si>
+    <t>C2905353</t>
+  </si>
+  <si>
+    <t>C620155</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1661,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1686,8 +1813,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1715,30 +1858,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1976,10 +2095,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2143,6 +2263,18 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2175,71 +2307,24 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2579,23 +2664,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S118"/>
+  <dimension ref="A1:S108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.5703125" customWidth="1"/>
     <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5703125" customWidth="1"/>
     <col min="16" max="16" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -2613,15 +2698,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="62"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="66"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2671,7 +2756,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="63"/>
+      <c r="S3" s="67"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2696,7 +2781,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="64"/>
+      <c r="S4" s="68"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2721,7 +2806,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="64"/>
+      <c r="S5" s="68"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2742,7 +2827,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="64"/>
+      <c r="S6" s="68"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2763,7 +2848,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="64"/>
+      <c r="S7" s="68"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2784,7 +2869,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="64"/>
+      <c r="S8" s="68"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2798,49 +2883,49 @@
         <v>17</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="F9" s="74" t="s">
-        <v>229</v>
+        <v>105</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>199</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>284</v>
-      </c>
-      <c r="H9" s="75" t="s">
-        <v>361</v>
+        <v>252</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>322</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>481</v>
+        <v>438</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>412</v>
+        <v>371</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>482</v>
+        <v>439</v>
       </c>
       <c r="L9" s="31" t="s">
-        <v>478</v>
+        <v>435</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>483</v>
+        <v>440</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>484</v>
+        <v>441</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>485</v>
+        <v>442</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>486</v>
+        <v>443</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>487</v>
+        <v>444</v>
       </c>
       <c r="R9" s="31" t="s">
-        <v>488</v>
+        <v>445</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>489</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2849,28 +2934,32 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="61" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="38" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>479</v>
+        <v>436</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>362</v>
-      </c>
-      <c r="I10" s="38"/>
-      <c r="J10" s="39"/>
+        <v>323</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J10" s="38" t="s">
+        <v>468</v>
+      </c>
       <c r="K10" s="38" t="s">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="L10" s="39">
         <v>13</v>
@@ -2879,12 +2968,18 @@
         <f>L10*5</f>
         <v>65</v>
       </c>
-      <c r="N10" s="39"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="53"/>
+      <c r="N10" s="38">
+        <v>80</v>
+      </c>
+      <c r="O10" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P10" s="42">
+        <v>2.4500000000000001E-2</v>
+      </c>
       <c r="Q10" s="42">
         <f>P10*N10</f>
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R10" s="39"/>
       <c r="S10" s="44"/>
@@ -2892,33 +2987,33 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="52">
-        <f t="shared" ref="B11:B115" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B105" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="79" t="s">
+      <c r="D11" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="79" t="s">
-        <v>127</v>
-      </c>
-      <c r="F11" s="80" t="s">
-        <v>230</v>
-      </c>
-      <c r="G11" s="79" t="s">
-        <v>285</v>
-      </c>
-      <c r="H11" s="80" t="s">
-        <v>363</v>
-      </c>
-      <c r="I11" s="79"/>
-      <c r="J11" s="80" t="s">
-        <v>413</v>
-      </c>
-      <c r="K11" s="79" t="s">
-        <v>433</v>
+      <c r="E11" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="I11" s="40"/>
+      <c r="J11" s="41" t="s">
+        <v>372</v>
+      </c>
+      <c r="K11" s="40" t="s">
+        <v>390</v>
       </c>
       <c r="L11" s="41">
         <v>1</v>
@@ -2928,7 +3023,7 @@
         <v>5</v>
       </c>
       <c r="N11" s="41"/>
-      <c r="O11" s="40"/>
+      <c r="O11" s="77"/>
       <c r="P11" s="54"/>
       <c r="Q11" s="43">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
@@ -2943,42 +3038,52 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="61" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>128</v>
+        <v>458</v>
+      </c>
+      <c r="E12" s="75" t="s">
+        <v>108</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39"/>
+        <v>324</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>373</v>
+      </c>
       <c r="K12" s="38" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="L12" s="39">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M12" s="38">
         <f>L12*5</f>
-        <v>35</v>
-      </c>
-      <c r="N12" s="39"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="53"/>
+        <v>45</v>
+      </c>
+      <c r="N12" s="38">
+        <v>100</v>
+      </c>
+      <c r="O12" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P12" s="53">
+        <v>4.7000000000000002E-3</v>
+      </c>
       <c r="Q12" s="42">
         <f>P12*N12</f>
-        <v>0</v>
+        <v>0.47000000000000003</v>
       </c>
       <c r="R12" s="39"/>
       <c r="S12" s="38"/>
@@ -2989,28 +3094,30 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="62" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>364</v>
+        <v>325</v>
       </c>
       <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
+      <c r="J13" s="41" t="s">
+        <v>470</v>
+      </c>
       <c r="K13" s="40" t="s">
-        <v>435</v>
+        <v>392</v>
       </c>
       <c r="L13" s="41">
         <v>5</v>
@@ -3019,12 +3126,18 @@
         <f t="shared" ref="M13" si="3">L13*5</f>
         <v>25</v>
       </c>
-      <c r="N13" s="41"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="54"/>
+      <c r="N13" s="41">
+        <v>27</v>
+      </c>
+      <c r="O13" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P13" s="54">
+        <v>0.28799999999999998</v>
+      </c>
       <c r="Q13" s="43">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
-        <v>0</v>
+        <v>7.7759999999999998</v>
       </c>
       <c r="R13" s="41"/>
       <c r="S13" s="40"/>
@@ -3035,42 +3148,52 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="82" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="82" t="s">
-        <v>130</v>
-      </c>
-      <c r="F14" s="83" t="s">
-        <v>231</v>
-      </c>
-      <c r="G14" s="82" t="s">
-        <v>287</v>
-      </c>
-      <c r="H14" s="83" t="s">
-        <v>363</v>
-      </c>
-      <c r="I14" s="82"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="82" t="s">
-        <v>433</v>
+      <c r="D14" s="38" t="s">
+        <v>459</v>
+      </c>
+      <c r="E14" s="75" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J14" s="39" t="s">
+        <v>471</v>
+      </c>
+      <c r="K14" s="38" t="s">
+        <v>390</v>
       </c>
       <c r="L14" s="39">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M14" s="38">
         <f>L14*5</f>
-        <v>175</v>
-      </c>
-      <c r="N14" s="39"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="53"/>
+        <v>185</v>
+      </c>
+      <c r="N14" s="38">
+        <v>200</v>
+      </c>
+      <c r="O14" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P14" s="53">
+        <v>2.7000000000000001E-3</v>
+      </c>
       <c r="Q14" s="42">
         <f>P14*N14</f>
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="R14" s="39"/>
       <c r="S14" s="38"/>
@@ -3081,28 +3204,32 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="62" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>365</v>
-      </c>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
+        <v>326</v>
+      </c>
+      <c r="I15" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>472</v>
+      </c>
       <c r="K15" s="40" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="L15" s="41">
         <v>1</v>
@@ -3111,12 +3238,18 @@
         <f t="shared" ref="M15" si="5">L15*5</f>
         <v>5</v>
       </c>
-      <c r="N15" s="41"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="54"/>
+      <c r="N15" s="41">
+        <v>10</v>
+      </c>
+      <c r="O15" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P15" s="54">
+        <v>0.13789999999999999</v>
+      </c>
       <c r="Q15" s="43">
         <f t="shared" ref="Q15" si="6">P15*N15</f>
-        <v>0</v>
+        <v>1.379</v>
       </c>
       <c r="R15" s="41"/>
       <c r="S15" s="40"/>
@@ -3127,28 +3260,32 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="61" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>132</v>
+        <v>22</v>
+      </c>
+      <c r="E16" s="75" t="s">
+        <v>112</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39"/>
+        <v>324</v>
+      </c>
+      <c r="I16" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J16" s="39" t="s">
+        <v>473</v>
+      </c>
       <c r="K16" s="38" t="s">
-        <v>437</v>
+        <v>394</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -3157,12 +3294,18 @@
         <f>L16*5</f>
         <v>5</v>
       </c>
-      <c r="N16" s="39"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="53"/>
+      <c r="N16" s="38">
+        <v>100</v>
+      </c>
+      <c r="O16" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P16" s="53">
+        <v>2.5000000000000001E-3</v>
+      </c>
       <c r="Q16" s="42">
         <f>P16*N16</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R16" s="39"/>
       <c r="S16" s="38"/>
@@ -3173,28 +3316,32 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="62" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="H17" s="41" t="s">
-        <v>366</v>
-      </c>
-      <c r="I17" s="40"/>
-      <c r="J17" s="41"/>
+        <v>327</v>
+      </c>
+      <c r="I17" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J17" s="41" t="s">
+        <v>474</v>
+      </c>
       <c r="K17" s="40" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="L17" s="41">
         <v>1</v>
@@ -3203,12 +3350,18 @@
         <f t="shared" ref="M17" si="7">L17*5</f>
         <v>5</v>
       </c>
-      <c r="N17" s="41"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="54"/>
+      <c r="N17" s="41">
+        <v>6</v>
+      </c>
+      <c r="O17" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P17" s="54">
+        <v>0.19359999999999999</v>
+      </c>
       <c r="Q17" s="43">
         <f t="shared" ref="Q17" si="8">P17*N17</f>
-        <v>0</v>
+        <v>1.1616</v>
       </c>
       <c r="R17" s="41"/>
       <c r="S17" s="40"/>
@@ -3219,28 +3372,32 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="61" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>134</v>
+        <v>24</v>
+      </c>
+      <c r="E18" s="75" t="s">
+        <v>114</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="I18" s="38"/>
-      <c r="J18" s="39"/>
+        <v>324</v>
+      </c>
+      <c r="I18" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>475</v>
+      </c>
       <c r="K18" s="38" t="s">
-        <v>438</v>
+        <v>395</v>
       </c>
       <c r="L18" s="39">
         <v>2</v>
@@ -3249,12 +3406,18 @@
         <f>L18*5</f>
         <v>10</v>
       </c>
-      <c r="N18" s="39"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="53"/>
+      <c r="N18" s="38">
+        <v>100</v>
+      </c>
+      <c r="O18" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P18" s="53">
+        <v>2.5999999999999999E-3</v>
+      </c>
       <c r="Q18" s="42">
         <f>P18*N18</f>
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="R18" s="39"/>
       <c r="S18" s="38"/>
@@ -3265,44 +3428,52 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="62" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>27</v>
+        <v>477</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="H19" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="I19" s="40"/>
+        <v>324</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J19" s="41" t="s">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="K19" s="40" t="s">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="L19" s="41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M19" s="40">
         <f t="shared" ref="M19" si="9">L19*5</f>
-        <v>10</v>
-      </c>
-      <c r="N19" s="41"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="54"/>
+        <v>20</v>
+      </c>
+      <c r="N19" s="41">
+        <v>100</v>
+      </c>
+      <c r="O19" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P19" s="54">
+        <v>2.8999999999999998E-3</v>
+      </c>
       <c r="Q19" s="43">
         <f t="shared" ref="Q19" si="10">P19*N19</f>
-        <v>0</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R19" s="41"/>
       <c r="S19" s="40"/>
@@ -3313,42 +3484,52 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="81" t="s">
+      <c r="C20" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="83" t="s">
-        <v>231</v>
-      </c>
-      <c r="G20" s="82" t="s">
-        <v>291</v>
-      </c>
-      <c r="H20" s="83" t="s">
-        <v>363</v>
-      </c>
-      <c r="I20" s="82"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="82" t="s">
-        <v>433</v>
+      <c r="D20" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="75" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J20" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="K20" s="38" t="s">
+        <v>397</v>
       </c>
       <c r="L20" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" s="38">
         <f>L20*5</f>
-        <v>10</v>
-      </c>
-      <c r="N20" s="39"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="53"/>
+        <v>5</v>
+      </c>
+      <c r="N20" s="38">
+        <v>20</v>
+      </c>
+      <c r="O20" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P20" s="53">
+        <v>3.5200000000000002E-2</v>
+      </c>
       <c r="Q20" s="42">
         <f>P20*N20</f>
-        <v>0</v>
+        <v>0.70400000000000007</v>
       </c>
       <c r="R20" s="39"/>
       <c r="S20" s="38"/>
@@ -3359,553 +3540,655 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="62" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="G21" s="40" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="I21" s="40"/>
-      <c r="J21" s="41"/>
+        <v>328</v>
+      </c>
+      <c r="I21" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J21" s="41" t="s">
+        <v>476</v>
+      </c>
       <c r="K21" s="40" t="s">
-        <v>439</v>
+        <v>398</v>
       </c>
       <c r="L21" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" s="40">
         <f t="shared" ref="M21" si="11">L21*5</f>
-        <v>10</v>
-      </c>
-      <c r="N21" s="41"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="54"/>
+        <v>5</v>
+      </c>
+      <c r="N21" s="41">
+        <v>20</v>
+      </c>
+      <c r="O21" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P21" s="54">
+        <v>3.04E-2</v>
+      </c>
       <c r="Q21" s="43">
         <f t="shared" ref="Q21" si="12">P21*N21</f>
-        <v>0</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="R21" s="41"/>
       <c r="S21" s="40"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="51">
-        <f>ROW(B22) - ROW($B$9)</f>
+      <c r="B22" s="52">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="71" t="s">
+      <c r="C22" s="61" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>137</v>
+        <v>27</v>
+      </c>
+      <c r="E22" s="75" t="s">
+        <v>118</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="I22" s="38"/>
+        <v>324</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J22" s="39" t="s">
-        <v>415</v>
+        <v>478</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>440</v>
+        <v>399</v>
       </c>
       <c r="L22" s="39">
         <v>1</v>
       </c>
       <c r="M22" s="38">
-        <f>L22*5</f>
+        <f t="shared" ref="M22" si="13">L22*5</f>
         <v>5</v>
       </c>
-      <c r="N22" s="39"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="53"/>
+      <c r="N22" s="38">
+        <v>100</v>
+      </c>
+      <c r="O22" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P22" s="53">
+        <v>3.3E-3</v>
+      </c>
       <c r="Q22" s="42">
-        <f>P22*N22</f>
-        <v>0</v>
+        <f t="shared" ref="Q22" si="14">P22*N22</f>
+        <v>0.33</v>
       </c>
       <c r="R22" s="39"/>
       <c r="S22" s="38"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="52">
-        <f t="shared" si="0"/>
+      <c r="B23" s="51">
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="62" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="H23" s="41" t="s">
-        <v>367</v>
-      </c>
-      <c r="I23" s="40"/>
-      <c r="J23" s="41"/>
+        <v>328</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J23" s="41" t="s">
+        <v>479</v>
+      </c>
       <c r="K23" s="40" t="s">
-        <v>441</v>
+        <v>400</v>
       </c>
       <c r="L23" s="41">
         <v>1</v>
       </c>
       <c r="M23" s="40">
-        <f t="shared" ref="M23" si="13">L23*5</f>
+        <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="41"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="54"/>
+      <c r="N23" s="41">
+        <v>20</v>
+      </c>
+      <c r="O23" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P23" s="54">
+        <v>2.9899999999999999E-2</v>
+      </c>
       <c r="Q23" s="43">
-        <f t="shared" ref="Q23" si="14">P23*N23</f>
-        <v>0</v>
+        <f>P23*N23</f>
+        <v>0.59799999999999998</v>
       </c>
       <c r="R23" s="41"/>
       <c r="S23" s="40"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="51">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="52">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="61" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>136</v>
+        <v>29</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>120</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="I24" s="38"/>
+        <v>324</v>
+      </c>
+      <c r="I24" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J24" s="39" t="s">
-        <v>416</v>
+        <v>480</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>439</v>
+        <v>401</v>
       </c>
       <c r="L24" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" s="38">
-        <f>L24*5</f>
-        <v>10</v>
-      </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="53"/>
+        <f t="shared" ref="M24" si="15">L24*5</f>
+        <v>5</v>
+      </c>
+      <c r="N24" s="38">
+        <v>100</v>
+      </c>
+      <c r="O24" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P24" s="53">
+        <v>3.0999999999999999E-3</v>
+      </c>
       <c r="Q24" s="42">
-        <f>P24*N24</f>
-        <v>0</v>
+        <f t="shared" ref="Q24" si="16">P24*N24</f>
+        <v>0.31</v>
       </c>
       <c r="R24" s="39"/>
       <c r="S24" s="38"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="52">
-        <f t="shared" si="0"/>
+      <c r="B25" s="51">
+        <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="72" t="s">
-        <v>11</v>
+      <c r="C25" s="62" t="s">
+        <v>12</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="G25" s="40" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="H25" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="I25" s="40"/>
-      <c r="J25" s="41"/>
+        <v>329</v>
+      </c>
+      <c r="I25" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J25" s="41" t="s">
+        <v>481</v>
+      </c>
       <c r="K25" s="40" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="L25" s="41">
         <v>1</v>
       </c>
       <c r="M25" s="40">
-        <f t="shared" ref="M25" si="15">L25*5</f>
+        <f>L25*5</f>
         <v>5</v>
       </c>
-      <c r="N25" s="41"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="54"/>
+      <c r="N25" s="41">
+        <v>20</v>
+      </c>
+      <c r="O25" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P25" s="54">
+        <v>3.2899999999999999E-2</v>
+      </c>
       <c r="Q25" s="43">
-        <f t="shared" ref="Q25" si="16">P25*N25</f>
-        <v>0</v>
+        <f>P25*N25</f>
+        <v>0.65799999999999992</v>
       </c>
       <c r="R25" s="41"/>
       <c r="S25" s="40"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="51">
-        <f>ROW(B26) - ROW($B$9)</f>
+      <c r="B26" s="52">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="71" t="s">
-        <v>11</v>
+      <c r="C26" s="61" t="s">
+        <v>12</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>140</v>
+        <v>31</v>
+      </c>
+      <c r="E26" s="75" t="s">
+        <v>122</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="I26" s="38"/>
-      <c r="J26" s="39"/>
+        <v>330</v>
+      </c>
+      <c r="I26" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J26" s="39" t="s">
+        <v>482</v>
+      </c>
       <c r="K26" s="38" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="L26" s="39">
         <v>1</v>
       </c>
       <c r="M26" s="38">
-        <f>L26*5</f>
+        <f t="shared" ref="M26" si="17">L26*5</f>
         <v>5</v>
       </c>
-      <c r="N26" s="39"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="53"/>
+      <c r="N26" s="38">
+        <v>6</v>
+      </c>
+      <c r="O26" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P26" s="53">
+        <v>0.49009999999999998</v>
+      </c>
       <c r="Q26" s="42">
-        <f>P26*N26</f>
-        <v>0</v>
+        <f t="shared" ref="Q26" si="18">P26*N26</f>
+        <v>2.9405999999999999</v>
       </c>
       <c r="R26" s="39"/>
       <c r="S26" s="38"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="52">
-        <f t="shared" si="0"/>
+      <c r="B27" s="51">
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="72" t="s">
-        <v>11</v>
+      <c r="C27" s="62" t="s">
+        <v>12</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="G27" s="40" t="s">
-        <v>297</v>
+        <v>206</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="I27" s="40"/>
-      <c r="J27" s="41"/>
+        <v>331</v>
+      </c>
+      <c r="I27" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J27" s="41" t="s">
+        <v>483</v>
+      </c>
       <c r="K27" s="40" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L27" s="41">
         <v>1</v>
       </c>
       <c r="M27" s="40">
-        <f t="shared" ref="M27" si="17">L27*5</f>
+        <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N27" s="41"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="54"/>
+      <c r="N27" s="41">
+        <v>20</v>
+      </c>
+      <c r="O27" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P27" s="54">
+        <v>3.1399999999999997E-2</v>
+      </c>
       <c r="Q27" s="43">
-        <f t="shared" ref="Q27" si="18">P27*N27</f>
-        <v>0</v>
+        <f>P27*N27</f>
+        <v>0.62799999999999989</v>
       </c>
       <c r="R27" s="41"/>
       <c r="S27" s="40"/>
     </row>
-    <row r="28" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="51">
-        <f>ROW(B28) - ROW($B$9)</f>
+      <c r="B28" s="52">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="61" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>142</v>
+        <v>33</v>
+      </c>
+      <c r="E28" s="75" t="s">
+        <v>124</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="H28" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="I28" s="38"/>
-      <c r="J28" s="39"/>
+        <v>332</v>
+      </c>
+      <c r="I28" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J28" s="39" t="s">
+        <v>376</v>
+      </c>
       <c r="K28" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L28" s="39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M28" s="38">
-        <f>L28*5</f>
-        <v>5</v>
-      </c>
-      <c r="N28" s="39"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="53"/>
+        <f t="shared" ref="M28" si="19">L28*5</f>
+        <v>25</v>
+      </c>
+      <c r="N28" s="38">
+        <v>40</v>
+      </c>
+      <c r="O28" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P28" s="53">
+        <v>2.0400000000000001E-2</v>
+      </c>
       <c r="Q28" s="42">
-        <f>P28*N28</f>
-        <v>0</v>
+        <f t="shared" ref="Q28" si="20">P28*N28</f>
+        <v>0.81600000000000006</v>
       </c>
       <c r="R28" s="39"/>
       <c r="S28" s="38"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="52">
-        <f t="shared" si="0"/>
+      <c r="B29" s="51">
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="62" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="G29" s="40" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>369</v>
-      </c>
-      <c r="I29" s="40"/>
-      <c r="J29" s="41"/>
+        <v>333</v>
+      </c>
+      <c r="I29" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J29" s="41" t="s">
+        <v>484</v>
+      </c>
       <c r="K29" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L29" s="41">
         <v>1</v>
       </c>
       <c r="M29" s="40">
-        <f t="shared" ref="M29" si="19">L29*5</f>
+        <f>L29*5</f>
         <v>5</v>
       </c>
-      <c r="N29" s="41"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="54"/>
+      <c r="N29" s="41">
+        <v>10</v>
+      </c>
+      <c r="O29" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P29" s="54">
+        <v>6.2700000000000006E-2</v>
+      </c>
       <c r="Q29" s="43">
-        <f t="shared" ref="Q29" si="20">P29*N29</f>
-        <v>0</v>
+        <f>P29*N29</f>
+        <v>0.627</v>
       </c>
       <c r="R29" s="41"/>
       <c r="S29" s="40"/>
     </row>
-    <row r="30" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="51">
-        <f>ROW(B30) - ROW($B$9)</f>
+      <c r="B30" s="52">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="76" t="s">
+      <c r="C30" s="61" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="38" t="s">
-        <v>144</v>
+        <v>35</v>
+      </c>
+      <c r="E30" s="75" t="s">
+        <v>126</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="I30" s="38"/>
-      <c r="J30" s="39"/>
+        <v>334</v>
+      </c>
+      <c r="I30" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J30" s="39" t="s">
+        <v>485</v>
+      </c>
       <c r="K30" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L30" s="39">
         <v>1</v>
       </c>
       <c r="M30" s="38">
-        <f>L30*5</f>
+        <f t="shared" ref="M30" si="21">L30*5</f>
         <v>5</v>
       </c>
-      <c r="N30" s="39"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="53"/>
+      <c r="N30" s="38">
+        <v>10</v>
+      </c>
+      <c r="O30" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P30" s="53">
+        <v>8.7099999999999997E-2</v>
+      </c>
       <c r="Q30" s="42">
-        <f>P30*N30</f>
-        <v>0</v>
+        <f t="shared" ref="Q30" si="22">P30*N30</f>
+        <v>0.871</v>
       </c>
       <c r="R30" s="39"/>
       <c r="S30" s="38"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="52">
-        <f t="shared" si="0"/>
+      <c r="B31" s="51">
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="77" t="s">
+      <c r="C31" s="62" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="H31" s="41" t="s">
-        <v>371</v>
-      </c>
-      <c r="I31" s="40"/>
+        <v>335</v>
+      </c>
+      <c r="I31" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J31" s="41" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="K31" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L31" s="41">
+        <v>1</v>
+      </c>
+      <c r="M31" s="40">
+        <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="M31" s="40">
-        <f t="shared" ref="M31" si="21">L31*5</f>
-        <v>25</v>
-      </c>
       <c r="N31" s="41"/>
-      <c r="O31" s="40"/>
+      <c r="O31" s="77"/>
       <c r="P31" s="54"/>
       <c r="Q31" s="43">
-        <f t="shared" ref="Q31" si="22">P31*N31</f>
+        <f>P31*N31</f>
         <v>0</v>
       </c>
       <c r="R31" s="41"/>
       <c r="S31" s="40"/>
     </row>
-    <row r="32" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="51">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="52">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="76" t="s">
-        <v>12</v>
+      <c r="C32" s="61" t="s">
+        <v>450</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>146</v>
+        <v>37</v>
+      </c>
+      <c r="E32" s="75" t="s">
+        <v>128</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>239</v>
+        <v>437</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="H32" s="39" t="s">
-        <v>372</v>
-      </c>
-      <c r="I32" s="38"/>
-      <c r="J32" s="39"/>
+        <v>336</v>
+      </c>
+      <c r="I32" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J32" s="39" t="s">
+        <v>448</v>
+      </c>
       <c r="K32" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L32" s="39">
         <v>1</v>
       </c>
       <c r="M32" s="38">
-        <f>L32*5</f>
+        <f t="shared" ref="M32" si="23">L32*5</f>
         <v>5</v>
       </c>
-      <c r="N32" s="39"/>
-      <c r="O32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="76"/>
       <c r="P32" s="53"/>
       <c r="Q32" s="42">
-        <f>P32*N32</f>
+        <f t="shared" ref="Q32" si="24">P32*N32</f>
         <v>0</v>
       </c>
       <c r="R32" s="39"/>
@@ -3913,632 +4196,762 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="52">
-        <f t="shared" si="0"/>
+      <c r="B33" s="51">
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="77" t="s">
-        <v>12</v>
+      <c r="C33" s="62" t="s">
+        <v>453</v>
       </c>
       <c r="D33" s="40" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>240</v>
-      </c>
-      <c r="G33" s="40" t="s">
-        <v>240</v>
+        <v>437</v>
+      </c>
+      <c r="G33" s="78" t="s">
+        <v>212</v>
       </c>
       <c r="H33" s="41" t="s">
-        <v>373</v>
-      </c>
-      <c r="I33" s="40"/>
-      <c r="J33" s="41"/>
+        <v>337</v>
+      </c>
+      <c r="I33" s="40" t="s">
+        <v>486</v>
+      </c>
+      <c r="J33" s="41" t="s">
+        <v>489</v>
+      </c>
       <c r="K33" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L33" s="41">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M33" s="40">
-        <f t="shared" ref="M33" si="23">L33*5</f>
-        <v>5</v>
-      </c>
-      <c r="N33" s="41"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="54"/>
+        <f>L33*5</f>
+        <v>45</v>
+      </c>
+      <c r="N33" s="41">
+        <v>50</v>
+      </c>
+      <c r="O33" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P33" s="54">
+        <v>7.1199999999999999E-2</v>
+      </c>
       <c r="Q33" s="43">
-        <f t="shared" ref="Q33" si="24">P33*N33</f>
-        <v>0</v>
+        <f>P33*N33</f>
+        <v>3.56</v>
       </c>
       <c r="R33" s="41"/>
       <c r="S33" s="40"/>
     </row>
-    <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="51">
-        <f>ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="52">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="76" t="s">
-        <v>12</v>
+      <c r="C34" s="61" t="s">
+        <v>453</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>148</v>
+        <v>39</v>
+      </c>
+      <c r="E34" s="75" t="s">
+        <v>129</v>
       </c>
       <c r="F34" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>302</v>
+        <v>437</v>
+      </c>
+      <c r="G34" s="79" t="s">
+        <v>213</v>
       </c>
       <c r="H34" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="I34" s="38"/>
-      <c r="J34" s="39"/>
+        <v>337</v>
+      </c>
+      <c r="I34" s="38" t="s">
+        <v>487</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>490</v>
+      </c>
       <c r="K34" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L34" s="39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M34" s="38">
-        <f>L34*5</f>
-        <v>5</v>
-      </c>
-      <c r="N34" s="39"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="53"/>
+        <f t="shared" ref="M34" si="25">L34*5</f>
+        <v>25</v>
+      </c>
+      <c r="N34" s="38">
+        <v>30</v>
+      </c>
+      <c r="O34" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P34" s="53">
+        <v>0.10539999999999999</v>
+      </c>
       <c r="Q34" s="42">
-        <f>P34*N34</f>
-        <v>0</v>
+        <f t="shared" ref="Q34" si="26">P34*N34</f>
+        <v>3.1619999999999999</v>
       </c>
       <c r="R34" s="39"/>
       <c r="S34" s="38"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="52">
-        <f t="shared" si="0"/>
+      <c r="B35" s="51">
+        <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="41" t="s">
-        <v>493</v>
+      <c r="C35" s="62" t="s">
+        <v>453</v>
       </c>
       <c r="D35" s="40" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>480</v>
-      </c>
-      <c r="G35" s="40" t="s">
-        <v>242</v>
+        <v>437</v>
+      </c>
+      <c r="G35" s="78" t="s">
+        <v>214</v>
       </c>
       <c r="H35" s="41" t="s">
-        <v>375</v>
-      </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41"/>
+        <v>337</v>
+      </c>
+      <c r="I35" s="40" t="s">
+        <v>488</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>491</v>
+      </c>
       <c r="K35" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L35" s="41">
         <v>1</v>
       </c>
       <c r="M35" s="40">
-        <f t="shared" ref="M35" si="25">L35*5</f>
+        <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="41"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="54"/>
+      <c r="N35" s="41">
+        <v>10</v>
+      </c>
+      <c r="O35" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P35" s="54">
+        <v>0.1114</v>
+      </c>
       <c r="Q35" s="43">
-        <f t="shared" ref="Q35" si="26">P35*N35</f>
-        <v>0</v>
+        <f>P35*N35</f>
+        <v>1.1139999999999999</v>
       </c>
       <c r="R35" s="41"/>
       <c r="S35" s="40"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="51">
-        <f>ROW(B36) - ROW($B$9)</f>
+      <c r="B36" s="52">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="39" t="s">
-        <v>496</v>
+      <c r="C36" s="61" t="s">
+        <v>454</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="38" t="s">
-        <v>150</v>
+        <v>41</v>
+      </c>
+      <c r="E36" s="75" t="s">
+        <v>130</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="H36" s="39" t="s">
-        <v>376</v>
-      </c>
-      <c r="I36" s="38"/>
-      <c r="J36" s="39"/>
+        <v>338</v>
+      </c>
+      <c r="I36" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J36" s="39" t="s">
+        <v>492</v>
+      </c>
       <c r="K36" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L36" s="39">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M36" s="38">
-        <f>L36*5</f>
-        <v>45</v>
-      </c>
-      <c r="N36" s="39"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="53"/>
+        <f t="shared" ref="M36" si="27">L36*5</f>
+        <v>5</v>
+      </c>
+      <c r="N36" s="38">
+        <v>6</v>
+      </c>
+      <c r="O36" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P36" s="53">
+        <v>0.75180000000000002</v>
+      </c>
       <c r="Q36" s="42">
-        <f>P36*N36</f>
-        <v>0</v>
+        <f t="shared" ref="Q36" si="28">P36*N36</f>
+        <v>4.5107999999999997</v>
       </c>
       <c r="R36" s="39"/>
       <c r="S36" s="38"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="52">
-        <f t="shared" si="0"/>
+      <c r="B37" s="51">
+        <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="41" t="s">
-        <v>496</v>
+      <c r="C37" s="62" t="s">
+        <v>450</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="G37" s="40" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="H37" s="41" t="s">
-        <v>376</v>
-      </c>
-      <c r="I37" s="40"/>
-      <c r="J37" s="41"/>
+        <v>339</v>
+      </c>
+      <c r="I37" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J37" s="41" t="s">
+        <v>493</v>
+      </c>
       <c r="K37" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L37" s="41">
+        <v>1</v>
+      </c>
+      <c r="M37" s="40">
+        <f>L37*5</f>
         <v>5</v>
       </c>
-      <c r="M37" s="40">
-        <f t="shared" ref="M37" si="27">L37*5</f>
-        <v>25</v>
-      </c>
-      <c r="N37" s="41"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="54"/>
+      <c r="N37" s="41">
+        <v>10</v>
+      </c>
+      <c r="O37" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P37" s="54">
+        <v>6.4299999999999996E-2</v>
+      </c>
       <c r="Q37" s="43">
-        <f t="shared" ref="Q37" si="28">P37*N37</f>
-        <v>0</v>
+        <f>P37*N37</f>
+        <v>0.64300000000000002</v>
       </c>
       <c r="R37" s="41"/>
       <c r="S37" s="40"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="51">
-        <f>ROW(B38) - ROW($B$9)</f>
+      <c r="B38" s="52">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="39" t="s">
-        <v>496</v>
+      <c r="C38" s="61" t="s">
+        <v>13</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>150</v>
+        <v>43</v>
+      </c>
+      <c r="E38" s="75" t="s">
+        <v>132</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="H38" s="39" t="s">
-        <v>376</v>
-      </c>
-      <c r="I38" s="38"/>
-      <c r="J38" s="39"/>
+        <v>340</v>
+      </c>
+      <c r="I38" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J38" s="39" t="s">
+        <v>377</v>
+      </c>
       <c r="K38" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L38" s="39">
         <v>1</v>
       </c>
       <c r="M38" s="38">
-        <f>L38*5</f>
+        <f t="shared" ref="M38" si="29">L38*5</f>
         <v>5</v>
       </c>
-      <c r="N38" s="39"/>
-      <c r="O38" s="38"/>
-      <c r="P38" s="53"/>
+      <c r="N38" s="38">
+        <v>6</v>
+      </c>
+      <c r="O38" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P38" s="53">
+        <v>0.22120000000000001</v>
+      </c>
       <c r="Q38" s="42">
-        <f>P38*N38</f>
-        <v>0</v>
+        <f t="shared" ref="Q38" si="30">P38*N38</f>
+        <v>1.3271999999999999</v>
       </c>
       <c r="R38" s="39"/>
       <c r="S38" s="38"/>
     </row>
     <row r="39" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="52">
-        <f t="shared" si="0"/>
+      <c r="B39" s="51">
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="41" t="s">
-        <v>497</v>
+      <c r="C39" s="62" t="s">
+        <v>14</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>480</v>
+        <v>217</v>
       </c>
       <c r="G39" s="40" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="H39" s="41" t="s">
-        <v>377</v>
-      </c>
-      <c r="I39" s="40"/>
-      <c r="J39" s="41"/>
+        <v>341</v>
+      </c>
+      <c r="I39" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J39" s="41" t="s">
+        <v>378</v>
+      </c>
       <c r="K39" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L39" s="41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M39" s="40">
-        <f t="shared" ref="M39" si="29">L39*5</f>
-        <v>5</v>
-      </c>
-      <c r="N39" s="41"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="54"/>
+        <f>L39*5</f>
+        <v>25</v>
+      </c>
+      <c r="N39" s="41">
+        <v>27</v>
+      </c>
+      <c r="O39" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P39" s="54">
+        <v>1.2012</v>
+      </c>
       <c r="Q39" s="43">
-        <f t="shared" ref="Q39" si="30">P39*N39</f>
-        <v>0</v>
+        <f>P39*N39</f>
+        <v>32.432400000000001</v>
       </c>
       <c r="R39" s="41"/>
       <c r="S39" s="40"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="51">
-        <f>ROW(B40) - ROW($B$9)</f>
+      <c r="B40" s="52">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="39" t="s">
-        <v>493</v>
+      <c r="C40" s="61" t="s">
+        <v>455</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>152</v>
+        <v>45</v>
+      </c>
+      <c r="E40" s="75" t="s">
+        <v>134</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>480</v>
+        <v>218</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="I40" s="38"/>
-      <c r="J40" s="39"/>
+        <v>342</v>
+      </c>
+      <c r="I40" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J40" s="39" t="s">
+        <v>494</v>
+      </c>
       <c r="K40" s="38" t="s">
-        <v>491</v>
+        <v>402</v>
       </c>
       <c r="L40" s="39">
         <v>1</v>
       </c>
       <c r="M40" s="38">
-        <f>L40*5</f>
+        <f t="shared" ref="M40" si="31">L40*5</f>
         <v>5</v>
       </c>
-      <c r="N40" s="39"/>
-      <c r="O40" s="38"/>
-      <c r="P40" s="53"/>
+      <c r="N40" s="38">
+        <v>10</v>
+      </c>
+      <c r="O40" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P40" s="53">
+        <v>4.0399999999999998E-2</v>
+      </c>
       <c r="Q40" s="42">
-        <f>P40*N40</f>
-        <v>0</v>
+        <f t="shared" ref="Q40" si="32">P40*N40</f>
+        <v>0.40399999999999997</v>
       </c>
       <c r="R40" s="39"/>
       <c r="S40" s="38"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="52">
-        <f t="shared" si="0"/>
+      <c r="B41" s="51">
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="41" t="s">
-        <v>13</v>
+      <c r="C41" s="62" t="s">
+        <v>455</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="G41" s="40" t="s">
-        <v>303</v>
+        <v>219</v>
       </c>
       <c r="H41" s="41" t="s">
-        <v>379</v>
-      </c>
-      <c r="I41" s="40"/>
+        <v>343</v>
+      </c>
+      <c r="I41" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J41" s="41" t="s">
-        <v>418</v>
+        <v>495</v>
       </c>
       <c r="K41" s="40" t="s">
-        <v>491</v>
+        <v>403</v>
       </c>
       <c r="L41" s="41">
         <v>1</v>
       </c>
       <c r="M41" s="40">
-        <f t="shared" ref="M41" si="31">L41*5</f>
+        <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="41"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="54"/>
+      <c r="N41" s="41">
+        <v>6</v>
+      </c>
+      <c r="O41" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P41" s="54">
+        <v>0.47249999999999998</v>
+      </c>
       <c r="Q41" s="43">
-        <f t="shared" ref="Q41" si="32">P41*N41</f>
-        <v>0</v>
+        <f>P41*N41</f>
+        <v>2.835</v>
       </c>
       <c r="R41" s="41"/>
       <c r="S41" s="40"/>
     </row>
-    <row r="42" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="51">
-        <f>ROW(B42) - ROW($B$9)</f>
+      <c r="B42" s="52">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="39" t="s">
-        <v>14</v>
+      <c r="C42" s="61" t="s">
+        <v>455</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>154</v>
+        <v>47</v>
+      </c>
+      <c r="E42" s="75" t="s">
+        <v>136</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="H42" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="I42" s="38"/>
+        <v>344</v>
+      </c>
+      <c r="I42" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J42" s="39" t="s">
-        <v>419</v>
+        <v>496</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>491</v>
+        <v>404</v>
       </c>
       <c r="L42" s="39">
+        <v>1</v>
+      </c>
+      <c r="M42" s="38">
+        <f t="shared" ref="M42" si="33">L42*5</f>
         <v>5</v>
       </c>
-      <c r="M42" s="38">
-        <f>L42*5</f>
-        <v>25</v>
-      </c>
-      <c r="N42" s="39"/>
-      <c r="O42" s="38"/>
-      <c r="P42" s="53"/>
+      <c r="N42" s="38">
+        <v>10</v>
+      </c>
+      <c r="O42" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P42" s="53">
+        <v>7.9100000000000004E-2</v>
+      </c>
       <c r="Q42" s="42">
-        <f>P42*N42</f>
-        <v>0</v>
+        <f t="shared" ref="Q42" si="34">P42*N42</f>
+        <v>0.79100000000000004</v>
       </c>
       <c r="R42" s="39"/>
       <c r="S42" s="38"/>
     </row>
-    <row r="43" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="52">
-        <f t="shared" si="0"/>
+      <c r="B43" s="51">
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="77" t="s">
-        <v>498</v>
+      <c r="C43" s="62" t="s">
+        <v>455</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F43" s="41" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="G43" s="40" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="H43" s="41" t="s">
-        <v>381</v>
-      </c>
-      <c r="I43" s="40"/>
-      <c r="J43" s="41"/>
+        <v>345</v>
+      </c>
+      <c r="I43" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J43" s="41" t="s">
+        <v>497</v>
+      </c>
       <c r="K43" s="40" t="s">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="L43" s="41">
         <v>1</v>
       </c>
       <c r="M43" s="40">
-        <f t="shared" ref="M43" si="33">L43*5</f>
+        <f>L43*5</f>
         <v>5</v>
       </c>
-      <c r="N43" s="41"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="54"/>
+      <c r="N43" s="41">
+        <v>10</v>
+      </c>
+      <c r="O43" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P43" s="54">
+        <v>8.5099999999999995E-2</v>
+      </c>
       <c r="Q43" s="43">
-        <f t="shared" ref="Q43" si="34">P43*N43</f>
-        <v>0</v>
+        <f>P43*N43</f>
+        <v>0.85099999999999998</v>
       </c>
       <c r="R43" s="41"/>
       <c r="S43" s="40"/>
     </row>
-    <row r="44" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="51">
-        <f>ROW(B44) - ROW($B$9)</f>
+      <c r="B44" s="52">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="61" t="s">
+        <v>456</v>
+      </c>
+      <c r="D44" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="G44" s="79" t="s">
+        <v>275</v>
+      </c>
+      <c r="H44" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="I44" s="38" t="s">
+        <v>508</v>
+      </c>
+      <c r="J44" s="39" t="s">
         <v>498</v>
       </c>
-      <c r="D44" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="E44" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="F44" s="39" t="s">
-        <v>480</v>
-      </c>
-      <c r="G44" s="38" t="s">
-        <v>250</v>
-      </c>
-      <c r="H44" s="39" t="s">
-        <v>382</v>
-      </c>
-      <c r="I44" s="38"/>
-      <c r="J44" s="39"/>
       <c r="K44" s="38" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L44" s="39">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M44" s="38">
-        <f>L44*5</f>
-        <v>5</v>
-      </c>
-      <c r="N44" s="39"/>
-      <c r="O44" s="38"/>
-      <c r="P44" s="53"/>
+        <f t="shared" ref="M44" si="35">L44*5</f>
+        <v>35</v>
+      </c>
+      <c r="N44" s="38">
+        <v>40</v>
+      </c>
+      <c r="O44" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P44" s="53">
+        <v>3.5400000000000001E-2</v>
+      </c>
       <c r="Q44" s="42">
-        <f>P44*N44</f>
-        <v>0</v>
+        <f t="shared" ref="Q44" si="36">P44*N44</f>
+        <v>1.4159999999999999</v>
       </c>
       <c r="R44" s="39"/>
       <c r="S44" s="38"/>
     </row>
-    <row r="45" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="52">
-        <f t="shared" si="0"/>
+      <c r="B45" s="51">
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="77" t="s">
-        <v>498</v>
+      <c r="C45" s="62" t="s">
+        <v>456</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>251</v>
+        <v>437</v>
       </c>
       <c r="G45" s="40" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="H45" s="41" t="s">
-        <v>383</v>
-      </c>
-      <c r="I45" s="40"/>
-      <c r="J45" s="41"/>
+        <v>347</v>
+      </c>
+      <c r="I45" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J45" s="41" t="s">
+        <v>499</v>
+      </c>
       <c r="K45" s="40" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L45" s="41">
         <v>1</v>
       </c>
       <c r="M45" s="40">
-        <f t="shared" ref="M45" si="35">L45*5</f>
+        <f>L45*5</f>
         <v>5</v>
       </c>
-      <c r="N45" s="41"/>
-      <c r="O45" s="40"/>
-      <c r="P45" s="54"/>
+      <c r="N45" s="41">
+        <v>10</v>
+      </c>
+      <c r="O45" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P45" s="54">
+        <v>0.1216</v>
+      </c>
       <c r="Q45" s="43">
-        <f t="shared" ref="Q45" si="36">P45*N45</f>
-        <v>0</v>
+        <f>P45*N45</f>
+        <v>1.216</v>
       </c>
       <c r="R45" s="41"/>
       <c r="S45" s="40"/>
     </row>
-    <row r="46" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="51">
-        <f>ROW(B46) - ROW($B$9)</f>
+      <c r="B46" s="52">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="76" t="s">
-        <v>498</v>
+      <c r="C46" s="61" t="s">
+        <v>457</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="38" t="s">
-        <v>158</v>
+        <v>51</v>
+      </c>
+      <c r="E46" s="75" t="s">
+        <v>140</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>252</v>
+        <v>437</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>307</v>
+        <v>223</v>
       </c>
       <c r="H46" s="39" t="s">
-        <v>384</v>
-      </c>
-      <c r="I46" s="38"/>
-      <c r="J46" s="39"/>
+        <v>348</v>
+      </c>
+      <c r="I46" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J46" s="39" t="s">
+        <v>500</v>
+      </c>
       <c r="K46" s="38" t="s">
         <v>448</v>
       </c>
@@ -4546,842 +4959,1013 @@
         <v>1</v>
       </c>
       <c r="M46" s="38">
-        <f>L46*5</f>
+        <f t="shared" ref="M46" si="37">L46*5</f>
         <v>5</v>
       </c>
-      <c r="N46" s="39"/>
-      <c r="O46" s="38"/>
-      <c r="P46" s="53"/>
+      <c r="N46" s="38">
+        <v>6</v>
+      </c>
+      <c r="O46" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P46" s="53">
+        <v>0.34010000000000001</v>
+      </c>
       <c r="Q46" s="42">
-        <f>P46*N46</f>
-        <v>0</v>
+        <f t="shared" ref="Q46" si="38">P46*N46</f>
+        <v>2.0406</v>
       </c>
       <c r="R46" s="39"/>
       <c r="S46" s="38"/>
     </row>
-    <row r="47" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="52">
-        <f t="shared" si="0"/>
+      <c r="B47" s="51">
+        <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="77" t="s">
-        <v>499</v>
+      <c r="C47" s="62" t="s">
+        <v>406</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="F47" s="41" t="s">
-        <v>253</v>
+        <v>437</v>
       </c>
       <c r="G47" s="40" t="s">
-        <v>308</v>
-      </c>
-      <c r="H47" s="41" t="s">
-        <v>385</v>
-      </c>
-      <c r="I47" s="40"/>
+        <v>224</v>
+      </c>
+      <c r="H47" s="41"/>
+      <c r="I47" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J47" s="41"/>
       <c r="K47" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L47" s="41">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M47" s="40">
-        <f t="shared" ref="M47" si="37">L47*5</f>
-        <v>35</v>
-      </c>
-      <c r="N47" s="41"/>
-      <c r="O47" s="40"/>
-      <c r="P47" s="54"/>
-      <c r="Q47" s="43">
-        <f t="shared" ref="Q47" si="38">P47*N47</f>
-        <v>0</v>
+        <f>L47*5</f>
+        <v>10</v>
+      </c>
+      <c r="N47" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="O47" s="77" t="s">
+        <v>448</v>
+      </c>
+      <c r="P47" s="54" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q47" s="43" t="s">
+        <v>448</v>
       </c>
       <c r="R47" s="41"/>
       <c r="S47" s="40"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="51">
-        <f>ROW(B48) - ROW($B$9)</f>
+      <c r="B48" s="52">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="76" t="s">
-        <v>499</v>
+      <c r="C48" s="61" t="s">
+        <v>450</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>160</v>
+        <v>53</v>
+      </c>
+      <c r="E48" s="75" t="s">
+        <v>142</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>480</v>
-      </c>
-      <c r="G48" s="38" t="s">
-        <v>309</v>
+        <v>225</v>
+      </c>
+      <c r="G48" s="79">
+        <v>61300311121</v>
       </c>
       <c r="H48" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="I48" s="38"/>
-      <c r="J48" s="39"/>
+        <v>349</v>
+      </c>
+      <c r="I48" s="38" t="s">
+        <v>512</v>
+      </c>
+      <c r="J48" s="39" t="s">
+        <v>512</v>
+      </c>
       <c r="K48" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L48" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48" s="38">
-        <f>L48*5</f>
-        <v>5</v>
-      </c>
-      <c r="N48" s="39"/>
-      <c r="O48" s="38"/>
-      <c r="P48" s="53"/>
+        <f t="shared" ref="M48" si="39">L48*5</f>
+        <v>10</v>
+      </c>
+      <c r="N48" s="38">
+        <v>50</v>
+      </c>
+      <c r="O48" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P48" s="53">
+        <v>1.44E-2</v>
+      </c>
       <c r="Q48" s="42">
-        <f>P48*N48</f>
-        <v>0</v>
+        <f t="shared" ref="Q48" si="40">P48*N48</f>
+        <v>0.72</v>
       </c>
       <c r="R48" s="39"/>
       <c r="S48" s="38"/>
     </row>
-    <row r="49" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="52">
-        <f t="shared" si="0"/>
+      <c r="B49" s="51">
+        <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="77" t="s">
-        <v>500</v>
+      <c r="C49" s="62" t="s">
+        <v>450</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="F49" s="41" t="s">
-        <v>480</v>
-      </c>
-      <c r="G49" s="40" t="s">
-        <v>254</v>
+        <v>226</v>
+      </c>
+      <c r="G49" s="78">
+        <v>61300611121</v>
       </c>
       <c r="H49" s="41" t="s">
-        <v>387</v>
-      </c>
-      <c r="I49" s="40"/>
-      <c r="J49" s="41"/>
+        <v>349</v>
+      </c>
+      <c r="I49" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="J49" s="41" t="s">
+        <v>501</v>
+      </c>
       <c r="K49" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L49" s="41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M49" s="40">
-        <f t="shared" ref="M49" si="39">L49*5</f>
-        <v>5</v>
-      </c>
-      <c r="N49" s="41"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="54"/>
+        <f>L49*5</f>
+        <v>20</v>
+      </c>
+      <c r="N49" s="41">
+        <v>40</v>
+      </c>
+      <c r="O49" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P49" s="54">
+        <v>2.9700000000000001E-2</v>
+      </c>
       <c r="Q49" s="43">
-        <f t="shared" ref="Q49" si="40">P49*N49</f>
-        <v>0</v>
+        <f>P49*N49</f>
+        <v>1.1879999999999999</v>
       </c>
       <c r="R49" s="41"/>
       <c r="S49" s="40"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="51">
-        <f>ROW(B50) - ROW($B$9)</f>
+      <c r="B50" s="52">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="76" t="s">
-        <v>449</v>
+      <c r="C50" s="61" t="s">
+        <v>450</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" s="38" t="s">
-        <v>162</v>
+        <v>55</v>
+      </c>
+      <c r="E50" s="75" t="s">
+        <v>144</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>480</v>
-      </c>
-      <c r="G50" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="H50" s="39"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="39"/>
+        <v>227</v>
+      </c>
+      <c r="G50" s="79" t="s">
+        <v>277</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="I50" s="38" t="s">
+        <v>502</v>
+      </c>
+      <c r="J50" s="39" t="s">
+        <v>502</v>
+      </c>
       <c r="K50" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L50" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" s="38">
-        <f>L50*5</f>
+        <f t="shared" ref="M50" si="41">L50*5</f>
+        <v>5</v>
+      </c>
+      <c r="N50" s="38">
         <v>10</v>
       </c>
-      <c r="N50" s="39"/>
-      <c r="O50" s="38"/>
-      <c r="P50" s="53"/>
+      <c r="O50" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P50" s="53">
+        <v>0.11509999999999999</v>
+      </c>
       <c r="Q50" s="42">
-        <f>P50*N50</f>
-        <v>0</v>
+        <f t="shared" ref="Q50" si="42">P50*N50</f>
+        <v>1.151</v>
       </c>
       <c r="R50" s="39"/>
       <c r="S50" s="38"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="52">
-        <f t="shared" si="0"/>
+      <c r="B51" s="51">
+        <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="77" t="s">
-        <v>493</v>
+      <c r="C51" s="62" t="s">
+        <v>450</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="F51" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="G51" s="40">
-        <v>61300311121</v>
+        <v>228</v>
+      </c>
+      <c r="G51" s="78">
+        <v>61300211121</v>
       </c>
       <c r="H51" s="41" t="s">
-        <v>388</v>
-      </c>
-      <c r="I51" s="40"/>
-      <c r="J51" s="41"/>
+        <v>349</v>
+      </c>
+      <c r="I51" s="40" t="s">
+        <v>510</v>
+      </c>
+      <c r="J51" s="41" t="s">
+        <v>503</v>
+      </c>
       <c r="K51" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L51" s="41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M51" s="40">
-        <f t="shared" ref="M51" si="41">L51*5</f>
-        <v>10</v>
-      </c>
-      <c r="N51" s="41"/>
-      <c r="O51" s="40"/>
-      <c r="P51" s="54"/>
+        <f>L51*5</f>
+        <v>15</v>
+      </c>
+      <c r="N51" s="41">
+        <v>50</v>
+      </c>
+      <c r="O51" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P51" s="54">
+        <v>1.3299999999999999E-2</v>
+      </c>
       <c r="Q51" s="43">
-        <f t="shared" ref="Q51" si="42">P51*N51</f>
-        <v>0</v>
+        <f>P51*N51</f>
+        <v>0.66499999999999992</v>
       </c>
       <c r="R51" s="41"/>
       <c r="S51" s="40"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="51">
-        <f>ROW(B52) - ROW($B$9)</f>
+      <c r="B52" s="52">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="76" t="s">
-        <v>493</v>
+      <c r="C52" s="61" t="s">
+        <v>450</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="38" t="s">
-        <v>164</v>
+        <v>57</v>
+      </c>
+      <c r="E52" s="75" t="s">
+        <v>146</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="G52" s="38">
-        <v>61300611121</v>
+        <v>229</v>
+      </c>
+      <c r="G52" s="79">
+        <v>61300411121</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>388</v>
-      </c>
-      <c r="I52" s="38"/>
-      <c r="J52" s="39"/>
+        <v>349</v>
+      </c>
+      <c r="I52" s="38" t="s">
+        <v>511</v>
+      </c>
+      <c r="J52" s="39" t="s">
+        <v>504</v>
+      </c>
       <c r="K52" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L52" s="39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M52" s="38">
-        <f>L52*5</f>
+        <f t="shared" ref="M52" si="43">L52*5</f>
+        <v>5</v>
+      </c>
+      <c r="N52" s="38">
         <v>20</v>
       </c>
-      <c r="N52" s="39"/>
-      <c r="O52" s="38"/>
-      <c r="P52" s="53"/>
+      <c r="O52" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P52" s="53">
+        <v>2.18E-2</v>
+      </c>
       <c r="Q52" s="42">
-        <f>P52*N52</f>
-        <v>0</v>
+        <f t="shared" ref="Q52" si="44">P52*N52</f>
+        <v>0.436</v>
       </c>
       <c r="R52" s="39"/>
       <c r="S52" s="38"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="52">
-        <f t="shared" si="0"/>
+      <c r="B53" s="51">
+        <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="77" t="s">
-        <v>493</v>
+      <c r="C53" s="62" t="s">
+        <v>15</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="F53" s="41" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="H53" s="41" t="s">
-        <v>389</v>
-      </c>
-      <c r="I53" s="40"/>
-      <c r="J53" s="41"/>
+        <v>332</v>
+      </c>
+      <c r="I53" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J53" s="41" t="s">
+        <v>505</v>
+      </c>
       <c r="K53" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L53" s="41">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M53" s="40">
-        <f t="shared" ref="M53" si="43">L53*5</f>
-        <v>5</v>
-      </c>
-      <c r="N53" s="41"/>
-      <c r="O53" s="40"/>
-      <c r="P53" s="54"/>
+        <f>L53*5</f>
+        <v>45</v>
+      </c>
+      <c r="N53" s="41">
+        <v>47</v>
+      </c>
+      <c r="O53" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P53" s="54">
+        <v>0.31269999999999998</v>
+      </c>
       <c r="Q53" s="43">
-        <f t="shared" ref="Q53" si="44">P53*N53</f>
-        <v>0</v>
+        <f>P53*N53</f>
+        <v>14.696899999999999</v>
       </c>
       <c r="R53" s="41"/>
       <c r="S53" s="40"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="51">
-        <f>ROW(B54) - ROW($B$9)</f>
+      <c r="B54" s="52">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="76" t="s">
-        <v>493</v>
+      <c r="C54" s="61" t="s">
+        <v>15</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" s="38" t="s">
-        <v>166</v>
+        <v>59</v>
+      </c>
+      <c r="E54" s="75" t="s">
+        <v>148</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="G54" s="38">
-        <v>61300211121</v>
+        <v>231</v>
+      </c>
+      <c r="G54" s="38" t="s">
+        <v>279</v>
       </c>
       <c r="H54" s="39" t="s">
-        <v>388</v>
-      </c>
-      <c r="I54" s="38"/>
-      <c r="J54" s="39"/>
+        <v>351</v>
+      </c>
+      <c r="I54" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J54" s="39" t="s">
+        <v>506</v>
+      </c>
       <c r="K54" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L54" s="39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M54" s="38">
-        <f>L54*5</f>
-        <v>15</v>
-      </c>
-      <c r="N54" s="39"/>
-      <c r="O54" s="38"/>
-      <c r="P54" s="53"/>
+        <f t="shared" ref="M54" si="45">L54*5</f>
+        <v>5</v>
+      </c>
+      <c r="N54" s="38">
+        <v>10</v>
+      </c>
+      <c r="O54" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P54" s="53">
+        <v>7.0800000000000002E-2</v>
+      </c>
       <c r="Q54" s="42">
-        <f>P54*N54</f>
-        <v>0</v>
+        <f t="shared" ref="Q54" si="46">P54*N54</f>
+        <v>0.70799999999999996</v>
       </c>
       <c r="R54" s="39"/>
       <c r="S54" s="38"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="52">
-        <f t="shared" si="0"/>
+      <c r="B55" s="51">
+        <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="77" t="s">
-        <v>493</v>
+      <c r="C55" s="62" t="s">
+        <v>15</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F55" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="G55" s="40">
-        <v>61300411121</v>
+        <v>232</v>
+      </c>
+      <c r="G55" s="40" t="s">
+        <v>280</v>
       </c>
       <c r="H55" s="41" t="s">
-        <v>388</v>
-      </c>
-      <c r="I55" s="40"/>
+        <v>352</v>
+      </c>
+      <c r="I55" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J55" s="41"/>
       <c r="K55" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L55" s="41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="40">
-        <f t="shared" ref="M55" si="45">L55*5</f>
-        <v>5</v>
-      </c>
-      <c r="N55" s="41"/>
-      <c r="O55" s="40"/>
+        <f>L55*5</f>
+        <v>10</v>
+      </c>
+      <c r="N55" s="41">
+        <v>12</v>
+      </c>
+      <c r="O55" s="77"/>
       <c r="P55" s="54"/>
       <c r="Q55" s="43">
-        <f t="shared" ref="Q55" si="46">P55*N55</f>
+        <f>P55*N55</f>
         <v>0</v>
       </c>
       <c r="R55" s="41"/>
       <c r="S55" s="40"/>
     </row>
-    <row r="56" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="51">
-        <f>ROW(B56) - ROW($B$9)</f>
+      <c r="B56" s="52">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="76" t="s">
+      <c r="C56" s="61" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E56" s="38" t="s">
-        <v>168</v>
+        <v>61</v>
+      </c>
+      <c r="E56" s="75" t="s">
+        <v>150</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="G56" s="38" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="H56" s="39" t="s">
-        <v>371</v>
-      </c>
-      <c r="I56" s="38"/>
-      <c r="J56" s="39"/>
+        <v>351</v>
+      </c>
+      <c r="I56" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J56" s="39" t="s">
+        <v>507</v>
+      </c>
       <c r="K56" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L56" s="39">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M56" s="38">
-        <f>L56*5</f>
-        <v>45</v>
-      </c>
-      <c r="N56" s="39"/>
-      <c r="O56" s="38"/>
-      <c r="P56" s="53"/>
+        <f t="shared" ref="M56" si="47">L56*5</f>
+        <v>10</v>
+      </c>
+      <c r="N56" s="38">
+        <v>15</v>
+      </c>
+      <c r="O56" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P56" s="53">
+        <v>0.1182</v>
+      </c>
       <c r="Q56" s="42">
-        <f>P56*N56</f>
-        <v>0</v>
+        <f t="shared" ref="Q56" si="48">P56*N56</f>
+        <v>1.7729999999999999</v>
       </c>
       <c r="R56" s="39"/>
       <c r="S56" s="38"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="52">
-        <f t="shared" si="0"/>
+      <c r="B57" s="51">
+        <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="77" t="s">
+      <c r="C57" s="62" t="s">
         <v>15</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F57" s="41" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="H57" s="41" t="s">
-        <v>390</v>
-      </c>
-      <c r="I57" s="40"/>
-      <c r="J57" s="41"/>
+        <v>332</v>
+      </c>
+      <c r="I57" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J57" s="41" t="s">
+        <v>379</v>
+      </c>
       <c r="K57" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L57" s="41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M57" s="40">
-        <f t="shared" ref="M57" si="47">L57*5</f>
-        <v>5</v>
-      </c>
-      <c r="N57" s="41"/>
-      <c r="O57" s="40"/>
-      <c r="P57" s="54"/>
+        <f>L57*5</f>
+        <v>30</v>
+      </c>
+      <c r="N57" s="41">
+        <v>20</v>
+      </c>
+      <c r="O57" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P57" s="54">
+        <v>3.3500000000000002E-2</v>
+      </c>
       <c r="Q57" s="43">
-        <f t="shared" ref="Q57" si="48">P57*N57</f>
-        <v>0</v>
+        <f>P57*N57</f>
+        <v>0.67</v>
       </c>
       <c r="R57" s="41"/>
       <c r="S57" s="40"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="51">
-        <f>ROW(B58) - ROW($B$9)</f>
+      <c r="B58" s="52">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="76" t="s">
+      <c r="C58" s="61" t="s">
         <v>15</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="E58" s="38" t="s">
-        <v>170</v>
+        <v>63</v>
+      </c>
+      <c r="E58" s="75" t="s">
+        <v>152</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="G58" s="38" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="H58" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="I58" s="38"/>
-      <c r="J58" s="39"/>
+        <v>353</v>
+      </c>
+      <c r="I58" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J58" s="39" t="s">
+        <v>513</v>
+      </c>
       <c r="K58" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L58" s="39">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M58" s="38">
-        <f>L58*5</f>
-        <v>10</v>
-      </c>
-      <c r="N58" s="39"/>
-      <c r="O58" s="38"/>
-      <c r="P58" s="53"/>
+        <f t="shared" ref="M58" si="49">L58*5</f>
+        <v>50</v>
+      </c>
+      <c r="N58" s="38">
+        <v>60</v>
+      </c>
+      <c r="O58" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P58" s="53">
+        <v>1.9099999999999999E-2</v>
+      </c>
       <c r="Q58" s="42">
-        <f>P58*N58</f>
-        <v>0</v>
+        <f t="shared" ref="Q58" si="50">P58*N58</f>
+        <v>1.1459999999999999</v>
       </c>
       <c r="R58" s="39"/>
       <c r="S58" s="38"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="52">
-        <f t="shared" si="0"/>
+      <c r="B59" s="51">
+        <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="77" t="s">
+      <c r="C59" s="62" t="s">
         <v>15</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="F59" s="41" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="H59" s="41" t="s">
-        <v>390</v>
-      </c>
-      <c r="I59" s="40"/>
-      <c r="J59" s="41"/>
+        <v>353</v>
+      </c>
+      <c r="I59" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J59" s="41" t="s">
+        <v>514</v>
+      </c>
       <c r="K59" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L59" s="41">
         <v>2</v>
       </c>
       <c r="M59" s="40">
-        <f t="shared" ref="M59" si="49">L59*5</f>
+        <f>L59*5</f>
         <v>10</v>
       </c>
-      <c r="N59" s="41"/>
-      <c r="O59" s="40"/>
-      <c r="P59" s="54"/>
+      <c r="N59" s="41">
+        <v>20</v>
+      </c>
+      <c r="O59" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P59" s="54">
+        <v>2.0299999999999999E-2</v>
+      </c>
       <c r="Q59" s="43">
-        <f t="shared" ref="Q59" si="50">P59*N59</f>
-        <v>0</v>
+        <f>P59*N59</f>
+        <v>0.40599999999999997</v>
       </c>
       <c r="R59" s="41"/>
       <c r="S59" s="40"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="51">
-        <f>ROW(B60) - ROW($B$9)</f>
+      <c r="B60" s="52">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="76" t="s">
+      <c r="C60" s="61" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E60" s="38" t="s">
-        <v>172</v>
+        <v>65</v>
+      </c>
+      <c r="E60" s="75" t="s">
+        <v>154</v>
       </c>
       <c r="F60" s="39" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="H60" s="39" t="s">
-        <v>371</v>
-      </c>
-      <c r="I60" s="38"/>
+        <v>330</v>
+      </c>
+      <c r="I60" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J60" s="39" t="s">
-        <v>420</v>
+        <v>515</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L60" s="39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M60" s="38">
-        <f>L60*5</f>
-        <v>30</v>
-      </c>
-      <c r="N60" s="39"/>
-      <c r="O60" s="38"/>
-      <c r="P60" s="53"/>
+        <f t="shared" ref="M60" si="51">L60*5</f>
+        <v>15</v>
+      </c>
+      <c r="N60" s="38">
+        <v>20</v>
+      </c>
+      <c r="O60" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P60" s="53">
+        <v>2.9899999999999999E-2</v>
+      </c>
       <c r="Q60" s="42">
-        <f>P60*N60</f>
-        <v>0</v>
+        <f t="shared" ref="Q60" si="52">P60*N60</f>
+        <v>0.59799999999999998</v>
       </c>
       <c r="R60" s="39"/>
       <c r="S60" s="38"/>
     </row>
     <row r="61" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="52">
-        <f t="shared" si="0"/>
+      <c r="B61" s="51">
+        <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="77" t="s">
-        <v>15</v>
+      <c r="C61" s="62" t="s">
+        <v>16</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F61" s="41" t="s">
-        <v>262</v>
+        <v>452</v>
       </c>
       <c r="G61" s="40" t="s">
-        <v>316</v>
+        <v>233</v>
       </c>
       <c r="H61" s="41" t="s">
-        <v>392</v>
-      </c>
-      <c r="I61" s="40"/>
-      <c r="J61" s="41"/>
+        <v>354</v>
+      </c>
+      <c r="I61" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J61" s="41" t="s">
+        <v>516</v>
+      </c>
       <c r="K61" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L61" s="41">
+        <v>1</v>
+      </c>
+      <c r="M61" s="40">
+        <f>L61*5</f>
+        <v>5</v>
+      </c>
+      <c r="N61" s="41">
         <v>10</v>
       </c>
-      <c r="M61" s="40">
-        <f t="shared" ref="M61" si="51">L61*5</f>
-        <v>50</v>
-      </c>
-      <c r="N61" s="41"/>
-      <c r="O61" s="40"/>
-      <c r="P61" s="54"/>
+      <c r="O61" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P61" s="54">
+        <v>0.3261</v>
+      </c>
       <c r="Q61" s="43">
-        <f t="shared" ref="Q61" si="52">P61*N61</f>
-        <v>0</v>
+        <f>P61*N61</f>
+        <v>3.2610000000000001</v>
       </c>
       <c r="R61" s="41"/>
       <c r="S61" s="40"/>
     </row>
-    <row r="62" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="51">
-        <f>ROW(B62) - ROW($B$9)</f>
+      <c r="B62" s="52">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="76" t="s">
-        <v>15</v>
+      <c r="C62" s="61" t="s">
+        <v>16</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="E62" s="38" t="s">
-        <v>174</v>
+        <v>67</v>
+      </c>
+      <c r="E62" s="75" t="s">
+        <v>156</v>
       </c>
       <c r="F62" s="39" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="G62" s="38" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="H62" s="39" t="s">
-        <v>392</v>
-      </c>
-      <c r="I62" s="38"/>
-      <c r="J62" s="39"/>
+        <v>355</v>
+      </c>
+      <c r="I62" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J62" s="39" t="s">
+        <v>380</v>
+      </c>
       <c r="K62" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L62" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="38">
-        <f>L62*5</f>
+        <f t="shared" ref="M62" si="53">L62*5</f>
+        <v>5</v>
+      </c>
+      <c r="N62" s="38">
         <v>10</v>
       </c>
-      <c r="N62" s="39"/>
-      <c r="O62" s="38"/>
-      <c r="P62" s="53"/>
+      <c r="O62" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P62" s="53">
+        <v>4.3700000000000003E-2</v>
+      </c>
       <c r="Q62" s="42">
-        <f>P62*N62</f>
-        <v>0</v>
+        <f t="shared" ref="Q62" si="54">P62*N62</f>
+        <v>0.43700000000000006</v>
       </c>
       <c r="R62" s="39"/>
       <c r="S62" s="38"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="52">
-        <f t="shared" si="0"/>
+      <c r="B63" s="51">
+        <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="77" t="s">
-        <v>15</v>
+      <c r="C63" s="62" t="s">
+        <v>16</v>
       </c>
       <c r="D63" s="40" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="F63" s="41" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="G63" s="40" t="s">
-        <v>318</v>
+        <v>287</v>
       </c>
       <c r="H63" s="41" t="s">
-        <v>369</v>
-      </c>
-      <c r="I63" s="40"/>
-      <c r="J63" s="41"/>
+        <v>324</v>
+      </c>
+      <c r="I63" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J63" s="41" t="s">
+        <v>517</v>
+      </c>
       <c r="K63" s="40" t="s">
-        <v>491</v>
+        <v>407</v>
       </c>
       <c r="L63" s="41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M63" s="40">
-        <f t="shared" ref="M63" si="53">L63*5</f>
-        <v>15</v>
-      </c>
-      <c r="N63" s="41"/>
-      <c r="O63" s="40"/>
+        <f>L63*5</f>
+        <v>5</v>
+      </c>
+      <c r="N63" s="41">
+        <v>100</v>
+      </c>
+      <c r="O63" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P63" s="54"/>
       <c r="Q63" s="43">
-        <f t="shared" ref="Q63" si="54">P63*N63</f>
+        <f>P63*N63</f>
         <v>0</v>
       </c>
       <c r="R63" s="41"/>
       <c r="S63" s="40"/>
     </row>
-    <row r="64" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="51">
-        <f>ROW(B64) - ROW($B$9)</f>
+      <c r="B64" s="52">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="76" t="s">
+      <c r="C64" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="E64" s="38" t="s">
-        <v>176</v>
+        <v>69</v>
+      </c>
+      <c r="E64" s="75" t="s">
+        <v>158</v>
       </c>
       <c r="F64" s="39" t="s">
-        <v>495</v>
+        <v>234</v>
       </c>
       <c r="G64" s="38" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="H64" s="39" t="s">
-        <v>393</v>
-      </c>
-      <c r="I64" s="38"/>
-      <c r="J64" s="39"/>
+        <v>324</v>
+      </c>
+      <c r="I64" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J64" s="39" t="s">
+        <v>518</v>
+      </c>
       <c r="K64" s="38" t="s">
-        <v>491</v>
+        <v>408</v>
       </c>
       <c r="L64" s="39">
         <v>1</v>
       </c>
       <c r="M64" s="38">
-        <f>L64*5</f>
+        <f t="shared" ref="M64" si="55">L64*5</f>
         <v>5</v>
       </c>
-      <c r="N64" s="39"/>
-      <c r="O64" s="38"/>
+      <c r="N64" s="38">
+        <v>100</v>
+      </c>
+      <c r="O64" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P64" s="53"/>
       <c r="Q64" s="42">
-        <f>P64*N64</f>
+        <f t="shared" ref="Q64" si="56">P64*N64</f>
         <v>0</v>
       </c>
       <c r="R64" s="39"/>
@@ -5389,90 +5973,102 @@
     </row>
     <row r="65" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="52">
-        <f t="shared" si="0"/>
+      <c r="B65" s="51">
+        <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="77" t="s">
+      <c r="C65" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="F65" s="41" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="G65" s="40" t="s">
-        <v>319</v>
+        <v>447</v>
       </c>
       <c r="H65" s="41" t="s">
-        <v>394</v>
-      </c>
-      <c r="I65" s="40"/>
+        <v>356</v>
+      </c>
+      <c r="I65" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J65" s="41" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="K65" s="40" t="s">
-        <v>491</v>
+        <v>409</v>
       </c>
       <c r="L65" s="41">
         <v>1</v>
       </c>
       <c r="M65" s="40">
-        <f t="shared" ref="M65" si="55">L65*5</f>
+        <f>L65*5</f>
         <v>5</v>
       </c>
-      <c r="N65" s="41"/>
-      <c r="O65" s="40"/>
+      <c r="N65" s="41">
+        <v>50</v>
+      </c>
+      <c r="O65" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P65" s="54"/>
       <c r="Q65" s="43">
-        <f t="shared" ref="Q65" si="56">P65*N65</f>
+        <f>P65*N65</f>
         <v>0</v>
       </c>
       <c r="R65" s="41"/>
       <c r="S65" s="40"/>
     </row>
-    <row r="66" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="51">
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="76" t="s">
+      <c r="C66" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="E66" s="38" t="s">
-        <v>178</v>
+        <v>467</v>
+      </c>
+      <c r="E66" s="75" t="s">
+        <v>160</v>
       </c>
       <c r="F66" s="39" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="H66" s="39" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I66" s="38"/>
-      <c r="J66" s="39"/>
+      <c r="J66" s="39" t="s">
+        <v>386</v>
+      </c>
       <c r="K66" s="38" t="s">
-        <v>450</v>
+        <v>411</v>
       </c>
       <c r="L66" s="39">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M66" s="38">
         <f>L66*5</f>
-        <v>5</v>
-      </c>
-      <c r="N66" s="39"/>
-      <c r="O66" s="38"/>
+        <v>75</v>
+      </c>
+      <c r="N66" s="38">
+        <v>100</v>
+      </c>
+      <c r="O66" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P66" s="53"/>
       <c r="Q66" s="42">
         <f>P66*N66</f>
@@ -5487,38 +6083,44 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="77" t="s">
+      <c r="C67" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F67" s="41" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="G67" s="40" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="H67" s="41" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I67" s="40"/>
-      <c r="J67" s="41"/>
+      <c r="J67" s="41" t="s">
+        <v>520</v>
+      </c>
       <c r="K67" s="40" t="s">
-        <v>451</v>
+        <v>412</v>
       </c>
       <c r="L67" s="41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" s="40">
         <f t="shared" ref="M67" si="57">L67*5</f>
-        <v>5</v>
-      </c>
-      <c r="N67" s="41"/>
-      <c r="O67" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="N67" s="41">
+        <v>100</v>
+      </c>
+      <c r="O67" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P67" s="54"/>
       <c r="Q67" s="43">
         <f t="shared" ref="Q67" si="58">P67*N67</f>
@@ -5533,28 +6135,30 @@
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="76" t="s">
+      <c r="C68" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="E68" s="38" t="s">
-        <v>180</v>
+        <v>72</v>
+      </c>
+      <c r="E68" s="75" t="s">
+        <v>162</v>
       </c>
       <c r="F68" s="39" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>490</v>
+        <v>291</v>
       </c>
       <c r="H68" s="39" t="s">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="I68" s="38"/>
-      <c r="J68" s="39"/>
+      <c r="J68" s="39" t="s">
+        <v>521</v>
+      </c>
       <c r="K68" s="38" t="s">
-        <v>452</v>
+        <v>413</v>
       </c>
       <c r="L68" s="39">
         <v>1</v>
@@ -5563,8 +6167,12 @@
         <f>L68*5</f>
         <v>5</v>
       </c>
-      <c r="N68" s="39"/>
-      <c r="O68" s="38"/>
+      <c r="N68" s="38">
+        <v>100</v>
+      </c>
+      <c r="O68" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P68" s="53"/>
       <c r="Q68" s="42">
         <f>P68*N68</f>
@@ -5579,84 +6187,92 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="77" t="s">
+      <c r="C69" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="D69" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E69" s="84" t="s">
-        <v>181</v>
-      </c>
-      <c r="F69" s="85" t="s">
-        <v>265</v>
-      </c>
-      <c r="G69" s="84" t="s">
-        <v>322</v>
-      </c>
-      <c r="H69" s="85" t="s">
-        <v>363</v>
-      </c>
-      <c r="I69" s="84"/>
-      <c r="J69" s="85"/>
-      <c r="K69" s="84" t="s">
-        <v>453</v>
+      <c r="D69" s="40" t="s">
+        <v>460</v>
+      </c>
+      <c r="E69" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F69" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="G69" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="H69" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="I69" s="40"/>
+      <c r="J69" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="K69" s="40" t="s">
+        <v>410</v>
       </c>
       <c r="L69" s="41">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M69" s="40">
         <f t="shared" ref="M69" si="59">L69*5</f>
-        <v>85</v>
-      </c>
-      <c r="N69" s="41"/>
-      <c r="O69" s="40"/>
-      <c r="P69" s="54"/>
+        <v>100</v>
+      </c>
+      <c r="N69" s="41">
+        <v>200</v>
+      </c>
+      <c r="O69" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P69" s="54">
+        <v>1E-3</v>
+      </c>
       <c r="Q69" s="43">
         <f t="shared" ref="Q69" si="60">P69*N69</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R69" s="41"/>
       <c r="S69" s="40"/>
     </row>
-    <row r="70" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="51">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="76" t="s">
+      <c r="C70" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" s="38" t="s">
-        <v>182</v>
+        <v>73</v>
+      </c>
+      <c r="E70" s="75" t="s">
+        <v>164</v>
       </c>
       <c r="F70" s="39" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="H70" s="39" t="s">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="I70" s="38"/>
       <c r="J70" s="39"/>
       <c r="K70" s="38" t="s">
-        <v>454</v>
+        <v>414</v>
       </c>
       <c r="L70" s="39">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M70" s="38">
         <f>L70*5</f>
-        <v>65</v>
-      </c>
-      <c r="N70" s="39"/>
-      <c r="O70" s="38"/>
+        <v>5</v>
+      </c>
+      <c r="N70" s="38"/>
+      <c r="O70" s="76"/>
       <c r="P70" s="53"/>
       <c r="Q70" s="42">
         <f>P70*N70</f>
@@ -5671,38 +6287,44 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="77" t="s">
+      <c r="C71" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="F71" s="41" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="G71" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="H71" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="H71" s="41" t="s">
-        <v>363</v>
-      </c>
       <c r="I71" s="40"/>
-      <c r="J71" s="41"/>
+      <c r="J71" s="41" t="s">
+        <v>522</v>
+      </c>
       <c r="K71" s="40" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="L71" s="41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M71" s="40">
         <f t="shared" ref="M71" si="61">L71*5</f>
-        <v>10</v>
-      </c>
-      <c r="N71" s="41"/>
-      <c r="O71" s="40"/>
+        <v>15</v>
+      </c>
+      <c r="N71" s="41">
+        <v>100</v>
+      </c>
+      <c r="O71" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P71" s="54"/>
       <c r="Q71" s="43">
         <f t="shared" ref="Q71" si="62">P71*N71</f>
@@ -5711,44 +6333,50 @@
       <c r="R71" s="41"/>
       <c r="S71" s="40"/>
     </row>
-    <row r="72" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="51">
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="76" t="s">
+      <c r="C72" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E72" s="38" t="s">
-        <v>184</v>
+        <v>465</v>
+      </c>
+      <c r="E72" s="75" t="s">
+        <v>166</v>
       </c>
       <c r="F72" s="39" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="H72" s="39" t="s">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="I72" s="38"/>
-      <c r="J72" s="39"/>
+      <c r="J72" s="39" t="s">
+        <v>523</v>
+      </c>
       <c r="K72" s="38" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="L72" s="39">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M72" s="38">
         <f>L72*5</f>
-        <v>5</v>
-      </c>
-      <c r="N72" s="39"/>
-      <c r="O72" s="38"/>
+        <v>40</v>
+      </c>
+      <c r="N72" s="38">
+        <v>100</v>
+      </c>
+      <c r="O72" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P72" s="53"/>
       <c r="Q72" s="42">
         <f>P72*N72</f>
@@ -5763,40 +6391,38 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="77" t="s">
+      <c r="C73" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="D73" s="84" t="s">
-        <v>81</v>
-      </c>
-      <c r="E73" s="84" t="s">
-        <v>185</v>
-      </c>
-      <c r="F73" s="85" t="s">
-        <v>266</v>
-      </c>
-      <c r="G73" s="84" t="s">
-        <v>326</v>
-      </c>
-      <c r="H73" s="85" t="s">
-        <v>363</v>
-      </c>
-      <c r="I73" s="84"/>
-      <c r="J73" s="85" t="s">
-        <v>422</v>
-      </c>
-      <c r="K73" s="84" t="s">
-        <v>453</v>
+      <c r="D73" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E73" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="F73" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="G73" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="H73" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="I73" s="40"/>
+      <c r="J73" s="41"/>
+      <c r="K73" s="40" t="s">
+        <v>417</v>
       </c>
       <c r="L73" s="41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M73" s="40">
         <f t="shared" ref="M73" si="63">L73*5</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N73" s="41"/>
-      <c r="O73" s="40"/>
+      <c r="O73" s="77"/>
       <c r="P73" s="54"/>
       <c r="Q73" s="43">
         <f t="shared" ref="Q73" si="64">P73*N73</f>
@@ -5805,44 +6431,50 @@
       <c r="R73" s="41"/>
       <c r="S73" s="40"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="51">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="76" t="s">
+      <c r="C74" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E74" s="38" t="s">
-        <v>186</v>
+        <v>462</v>
+      </c>
+      <c r="E74" s="75" t="s">
+        <v>168</v>
       </c>
       <c r="F74" s="39" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="H74" s="39" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I74" s="38"/>
-      <c r="J74" s="39"/>
+      <c r="J74" s="39" t="s">
+        <v>524</v>
+      </c>
       <c r="K74" s="38" t="s">
-        <v>457</v>
+        <v>418</v>
       </c>
       <c r="L74" s="39">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M74" s="38">
         <f>L74*5</f>
-        <v>5</v>
-      </c>
-      <c r="N74" s="39"/>
-      <c r="O74" s="38"/>
+        <v>65</v>
+      </c>
+      <c r="N74" s="38">
+        <v>100</v>
+      </c>
+      <c r="O74" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P74" s="53"/>
       <c r="Q74" s="42">
         <f>P74*N74</f>
@@ -5857,38 +6489,38 @@
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="77" t="s">
+      <c r="C75" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F75" s="41" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="H75" s="41" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I75" s="40"/>
       <c r="J75" s="41"/>
       <c r="K75" s="40" t="s">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="L75" s="41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M75" s="40">
         <f t="shared" ref="M75" si="65">L75*5</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N75" s="41"/>
-      <c r="O75" s="40"/>
+      <c r="O75" s="77"/>
       <c r="P75" s="54"/>
       <c r="Q75" s="43">
         <f t="shared" ref="Q75" si="66">P75*N75</f>
@@ -5903,38 +6535,38 @@
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="76" t="s">
+      <c r="C76" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E76" s="38" t="s">
-        <v>188</v>
+        <v>77</v>
+      </c>
+      <c r="E76" s="75" t="s">
+        <v>170</v>
       </c>
       <c r="F76" s="39" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="H76" s="39" t="s">
-        <v>398</v>
+        <v>324</v>
       </c>
       <c r="I76" s="38"/>
       <c r="J76" s="39"/>
       <c r="K76" s="38" t="s">
-        <v>459</v>
+        <v>421</v>
       </c>
       <c r="L76" s="39">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M76" s="38">
         <f>L76*5</f>
-        <v>35</v>
-      </c>
-      <c r="N76" s="39"/>
-      <c r="O76" s="38"/>
+        <v>5</v>
+      </c>
+      <c r="N76" s="38"/>
+      <c r="O76" s="76"/>
       <c r="P76" s="53"/>
       <c r="Q76" s="42">
         <f>P76*N76</f>
@@ -5949,38 +6581,44 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="77" t="s">
+      <c r="C77" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>85</v>
+        <v>463</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="F77" s="41" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="H77" s="41" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I77" s="40"/>
-      <c r="J77" s="41"/>
+      <c r="J77" s="41" t="s">
+        <v>525</v>
+      </c>
       <c r="K77" s="40" t="s">
-        <v>460</v>
+        <v>422</v>
       </c>
       <c r="L77" s="41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M77" s="40">
         <f t="shared" ref="M77" si="67">L77*5</f>
-        <v>10</v>
-      </c>
-      <c r="N77" s="41"/>
-      <c r="O77" s="40"/>
+        <v>15</v>
+      </c>
+      <c r="N77" s="41">
+        <v>100</v>
+      </c>
+      <c r="O77" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P77" s="54"/>
       <c r="Q77" s="43">
         <f t="shared" ref="Q77" si="68">P77*N77</f>
@@ -5989,44 +6627,50 @@
       <c r="R77" s="41"/>
       <c r="S77" s="40"/>
     </row>
-    <row r="78" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="51">
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
-      <c r="C78" s="76" t="s">
+      <c r="C78" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="E78" s="38" t="s">
-        <v>190</v>
+        <v>461</v>
+      </c>
+      <c r="E78" s="75" t="s">
+        <v>172</v>
       </c>
       <c r="F78" s="39" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="G78" s="38" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I78" s="38"/>
-      <c r="J78" s="39"/>
+      <c r="J78" s="39" t="s">
+        <v>526</v>
+      </c>
       <c r="K78" s="38" t="s">
-        <v>461</v>
+        <v>419</v>
       </c>
       <c r="L78" s="39">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="M78" s="38">
         <f>L78*5</f>
-        <v>55</v>
-      </c>
-      <c r="N78" s="39"/>
-      <c r="O78" s="38"/>
+        <v>120</v>
+      </c>
+      <c r="N78" s="38">
+        <v>200</v>
+      </c>
+      <c r="O78" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P78" s="53"/>
       <c r="Q78" s="42">
         <f>P78*N78</f>
@@ -6035,46 +6679,46 @@
       <c r="R78" s="39"/>
       <c r="S78" s="38"/>
     </row>
-    <row r="79" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="52">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="77" t="s">
+      <c r="C79" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="D79" s="88" t="s">
-        <v>87</v>
-      </c>
-      <c r="E79" s="88" t="s">
-        <v>191</v>
-      </c>
-      <c r="F79" s="89" t="s">
-        <v>266</v>
-      </c>
-      <c r="G79" s="88" t="s">
-        <v>332</v>
-      </c>
-      <c r="H79" s="89" t="s">
-        <v>363</v>
-      </c>
-      <c r="I79" s="88"/>
-      <c r="J79" s="89" t="s">
+      <c r="D79" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E79" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F79" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="G79" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="H79" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="I79" s="40"/>
+      <c r="J79" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="K79" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="K79" s="88" t="s">
-        <v>462</v>
-      </c>
       <c r="L79" s="41">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M79" s="40">
         <f t="shared" ref="M79" si="69">L79*5</f>
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="N79" s="41"/>
-      <c r="O79" s="40"/>
+      <c r="O79" s="77"/>
       <c r="P79" s="54"/>
       <c r="Q79" s="43">
         <f t="shared" ref="Q79" si="70">P79*N79</f>
@@ -6083,46 +6727,46 @@
       <c r="R79" s="41"/>
       <c r="S79" s="40"/>
     </row>
-    <row r="80" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="51">
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
-      <c r="C80" s="76" t="s">
+      <c r="C80" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="E80" s="38" t="s">
-        <v>192</v>
+        <v>79</v>
+      </c>
+      <c r="E80" s="75" t="s">
+        <v>174</v>
       </c>
       <c r="F80" s="39" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="G80" s="38" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="H80" s="39" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I80" s="38"/>
       <c r="J80" s="39" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="K80" s="38" t="s">
-        <v>461</v>
+        <v>418</v>
       </c>
       <c r="L80" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80" s="38">
         <f>L80*5</f>
-        <v>10</v>
-      </c>
-      <c r="N80" s="39"/>
-      <c r="O80" s="38"/>
+        <v>5</v>
+      </c>
+      <c r="N80" s="38"/>
+      <c r="O80" s="76"/>
       <c r="P80" s="53"/>
       <c r="Q80" s="42">
         <f>P80*N80</f>
@@ -6137,28 +6781,30 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="77" t="s">
+      <c r="C81" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="F81" s="41" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="G81" s="40" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="H81" s="41" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I81" s="40"/>
-      <c r="J81" s="41"/>
+      <c r="J81" s="41" t="s">
+        <v>384</v>
+      </c>
       <c r="K81" s="40" t="s">
-        <v>463</v>
+        <v>424</v>
       </c>
       <c r="L81" s="41">
         <v>1</v>
@@ -6168,7 +6814,7 @@
         <v>5</v>
       </c>
       <c r="N81" s="41"/>
-      <c r="O81" s="40"/>
+      <c r="O81" s="77"/>
       <c r="P81" s="54"/>
       <c r="Q81" s="43">
         <f t="shared" ref="Q81" si="72">P81*N81</f>
@@ -6183,38 +6829,38 @@
         <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
-      <c r="C82" s="76" t="s">
+      <c r="C82" s="61" t="s">
         <v>16</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="E82" s="38" t="s">
-        <v>194</v>
+        <v>81</v>
+      </c>
+      <c r="E82" s="75" t="s">
+        <v>176</v>
       </c>
       <c r="F82" s="39" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="G82" s="38" t="s">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="H82" s="39" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I82" s="38"/>
       <c r="J82" s="39"/>
       <c r="K82" s="38" t="s">
-        <v>464</v>
+        <v>425</v>
       </c>
       <c r="L82" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="38">
         <f>L82*5</f>
-        <v>5</v>
-      </c>
-      <c r="N82" s="39"/>
-      <c r="O82" s="38"/>
+        <v>10</v>
+      </c>
+      <c r="N82" s="38"/>
+      <c r="O82" s="76"/>
       <c r="P82" s="53"/>
       <c r="Q82" s="42">
         <f>P82*N82</f>
@@ -6229,38 +6875,46 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C83" s="77" t="s">
+      <c r="C83" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>91</v>
+        <v>464</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F83" s="41" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="G83" s="40" t="s">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="H83" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="I83" s="40"/>
-      <c r="J83" s="41"/>
+        <v>324</v>
+      </c>
+      <c r="I83" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J83" s="41" t="s">
+        <v>527</v>
+      </c>
       <c r="K83" s="40" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="L83" s="41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M83" s="40">
         <f t="shared" ref="M83" si="73">L83*5</f>
-        <v>5</v>
-      </c>
-      <c r="N83" s="41"/>
-      <c r="O83" s="40"/>
+        <v>25</v>
+      </c>
+      <c r="N83" s="41">
+        <v>100</v>
+      </c>
+      <c r="O83" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P83" s="54"/>
       <c r="Q83" s="43">
         <f t="shared" ref="Q83" si="74">P83*N83</f>
@@ -6275,38 +6929,36 @@
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
-      <c r="C84" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="90" t="s">
-        <v>92</v>
-      </c>
-      <c r="E84" s="90" t="s">
-        <v>196</v>
-      </c>
-      <c r="F84" s="91" t="s">
-        <v>265</v>
-      </c>
-      <c r="G84" s="90" t="s">
-        <v>337</v>
-      </c>
-      <c r="H84" s="91" t="s">
-        <v>363</v>
-      </c>
-      <c r="I84" s="90"/>
-      <c r="J84" s="91"/>
-      <c r="K84" s="90" t="s">
-        <v>462</v>
+      <c r="C84" s="61"/>
+      <c r="D84" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E84" s="75" t="s">
+        <v>466</v>
+      </c>
+      <c r="F84" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="G84" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="H84" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="I84" s="38"/>
+      <c r="J84" s="39"/>
+      <c r="K84" s="38" t="s">
+        <v>426</v>
       </c>
       <c r="L84" s="39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M84" s="38">
         <f>L84*5</f>
-        <v>15</v>
-      </c>
-      <c r="N84" s="39"/>
-      <c r="O84" s="38"/>
+        <v>10</v>
+      </c>
+      <c r="N84" s="38"/>
+      <c r="O84" s="76"/>
       <c r="P84" s="53"/>
       <c r="Q84" s="42">
         <f>P84*N84</f>
@@ -6321,40 +6973,38 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="D85" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="E85" s="86" t="s">
-        <v>197</v>
-      </c>
-      <c r="F85" s="87" t="s">
-        <v>267</v>
-      </c>
-      <c r="G85" s="86" t="s">
-        <v>338</v>
-      </c>
-      <c r="H85" s="87" t="s">
-        <v>363</v>
-      </c>
-      <c r="I85" s="86"/>
-      <c r="J85" s="87" t="s">
-        <v>425</v>
-      </c>
-      <c r="K85" s="86" t="s">
-        <v>466</v>
+      <c r="C85" s="62"/>
+      <c r="D85" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E85" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="F85" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="G85" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="H85" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="I85" s="40"/>
+      <c r="J85" s="41" t="s">
+        <v>385</v>
+      </c>
+      <c r="K85" s="40" t="s">
+        <v>427</v>
       </c>
       <c r="L85" s="41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" s="40">
         <f t="shared" ref="M85" si="75">L85*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N85" s="41"/>
-      <c r="O85" s="40"/>
+      <c r="O85" s="77"/>
       <c r="P85" s="54"/>
       <c r="Q85" s="43">
         <f t="shared" ref="Q85" si="76">P85*N85</f>
@@ -6369,44 +7019,50 @@
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="76" t="s">
-        <v>16</v>
-      </c>
+      <c r="C86" s="61"/>
       <c r="D86" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>198</v>
+        <v>84</v>
+      </c>
+      <c r="E86" s="75" t="s">
+        <v>179</v>
       </c>
       <c r="F86" s="39" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>339</v>
+        <v>529</v>
       </c>
       <c r="H86" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="I86" s="38"/>
+        <v>359</v>
+      </c>
+      <c r="I86" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J86" s="39" t="s">
-        <v>426</v>
+        <v>528</v>
       </c>
       <c r="K86" s="38" t="s">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="L86" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" s="38">
         <f>L86*5</f>
-        <v>5</v>
-      </c>
-      <c r="N86" s="39"/>
-      <c r="O86" s="38"/>
-      <c r="P86" s="53"/>
+        <v>10</v>
+      </c>
+      <c r="N86" s="38">
+        <v>50</v>
+      </c>
+      <c r="O86" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="P86" s="53">
+        <v>0.01</v>
+      </c>
       <c r="Q86" s="42">
         <f>P86*N86</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R86" s="39"/>
       <c r="S86" s="38"/>
@@ -6417,44 +7073,50 @@
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="77" t="s">
-        <v>16</v>
-      </c>
+      <c r="C87" s="62"/>
       <c r="D87" s="40" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>199</v>
+        <v>531</v>
       </c>
       <c r="F87" s="41" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="H87" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="I87" s="40"/>
+        <v>324</v>
+      </c>
+      <c r="I87" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J87" s="41" t="s">
-        <v>427</v>
+        <v>530</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>467</v>
+        <v>429</v>
       </c>
       <c r="L87" s="41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M87" s="40">
         <f t="shared" ref="M87" si="77">L87*5</f>
-        <v>5</v>
-      </c>
-      <c r="N87" s="41"/>
-      <c r="O87" s="40"/>
-      <c r="P87" s="54"/>
+        <v>10</v>
+      </c>
+      <c r="N87" s="41">
+        <v>100</v>
+      </c>
+      <c r="O87" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="P87" s="54">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q87" s="43">
         <f t="shared" ref="Q87" si="78">P87*N87</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R87" s="41"/>
       <c r="S87" s="40"/>
@@ -6465,38 +7127,36 @@
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="76" t="s">
-        <v>16</v>
-      </c>
+      <c r="C88" s="61"/>
       <c r="D88" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="E88" s="38" t="s">
-        <v>200</v>
+        <v>86</v>
+      </c>
+      <c r="E88" s="75" t="s">
+        <v>180</v>
       </c>
       <c r="F88" s="39" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="G88" s="38" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="H88" s="39" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I88" s="38"/>
       <c r="J88" s="39"/>
       <c r="K88" s="38" t="s">
-        <v>468</v>
+        <v>430</v>
       </c>
       <c r="L88" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M88" s="38">
         <f>L88*5</f>
-        <v>10</v>
-      </c>
-      <c r="N88" s="39"/>
-      <c r="O88" s="38"/>
+        <v>5</v>
+      </c>
+      <c r="N88" s="38"/>
+      <c r="O88" s="76"/>
       <c r="P88" s="53"/>
       <c r="Q88" s="42">
         <f>P88*N88</f>
@@ -6511,38 +7171,36 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C89" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="D89" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="E89" s="86" t="s">
-        <v>201</v>
-      </c>
-      <c r="F89" s="87" t="s">
-        <v>265</v>
-      </c>
-      <c r="G89" s="86" t="s">
-        <v>342</v>
-      </c>
-      <c r="H89" s="87" t="s">
-        <v>363</v>
-      </c>
-      <c r="I89" s="86"/>
-      <c r="J89" s="87"/>
-      <c r="K89" s="86" t="s">
-        <v>466</v>
+      <c r="C89" s="62"/>
+      <c r="D89" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="E89" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="F89" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="G89" s="40" t="s">
+        <v>311</v>
+      </c>
+      <c r="H89" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="I89" s="40"/>
+      <c r="J89" s="41"/>
+      <c r="K89" s="40" t="s">
+        <v>431</v>
       </c>
       <c r="L89" s="41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M89" s="40">
         <f t="shared" ref="M89" si="79">L89*5</f>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N89" s="41"/>
-      <c r="O89" s="40"/>
+      <c r="O89" s="77"/>
       <c r="P89" s="54"/>
       <c r="Q89" s="43">
         <f t="shared" ref="Q89" si="80">P89*N89</f>
@@ -6551,91 +7209,93 @@
       <c r="R89" s="41"/>
       <c r="S89" s="40"/>
     </row>
-    <row r="90" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
-      <c r="B90" s="51">
-        <f>ROW(B90) - ROW($B$9)</f>
+      <c r="B90" s="52">
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="C90" s="39"/>
+      <c r="C90" s="61"/>
       <c r="D90" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="E90" s="38" t="s">
-        <v>202</v>
+        <v>88</v>
+      </c>
+      <c r="E90" s="75" t="s">
+        <v>182</v>
       </c>
       <c r="F90" s="39" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="G90" s="38" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="H90" s="39" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="I90" s="38"/>
-      <c r="J90" s="39"/>
+      <c r="J90" s="39" t="s">
+        <v>387</v>
+      </c>
       <c r="K90" s="38" t="s">
-        <v>469</v>
+        <v>420</v>
       </c>
       <c r="L90" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="38">
-        <f>L90*5</f>
-        <v>10</v>
-      </c>
-      <c r="N90" s="39"/>
-      <c r="O90" s="38"/>
+        <f t="shared" ref="M90" si="81">L90*5</f>
+        <v>5</v>
+      </c>
+      <c r="N90" s="38"/>
+      <c r="O90" s="76"/>
       <c r="P90" s="53"/>
       <c r="Q90" s="42">
-        <f>P90*N90</f>
+        <f t="shared" ref="Q90" si="82">P90*N90</f>
         <v>0</v>
       </c>
       <c r="R90" s="39"/>
       <c r="S90" s="38"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" ht="84" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="52">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C91" s="41"/>
+      <c r="C91" s="62"/>
       <c r="D91" s="40" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F91" s="41" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="G91" s="40" t="s">
-        <v>344</v>
+        <v>239</v>
       </c>
       <c r="H91" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="I91" s="40"/>
-      <c r="J91" s="41" t="s">
-        <v>428</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="I91" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J91" s="41"/>
       <c r="K91" s="40" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="L91" s="41">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="M91" s="40">
-        <f t="shared" ref="M91" si="81">L91*5</f>
-        <v>10</v>
+        <f t="shared" ref="M91" si="83">L91*5</f>
+        <v>210</v>
       </c>
       <c r="N91" s="41"/>
-      <c r="O91" s="40"/>
+      <c r="O91" s="77"/>
       <c r="P91" s="54"/>
       <c r="Q91" s="43">
-        <f t="shared" ref="Q91" si="82">P91*N91</f>
+        <f t="shared" ref="Q91" si="84">P91*N91</f>
         <v>0</v>
       </c>
       <c r="R91" s="41"/>
@@ -6647,34 +7307,42 @@
         <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
-      <c r="C92" s="39"/>
+      <c r="C92" s="61"/>
       <c r="D92" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="E92" s="38" t="s">
-        <v>204</v>
+        <v>90</v>
+      </c>
+      <c r="E92" s="75" t="s">
+        <v>184</v>
       </c>
       <c r="F92" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="G92" s="38"/>
+        <v>437</v>
+      </c>
+      <c r="G92" s="38" t="s">
+        <v>240</v>
+      </c>
       <c r="H92" s="39" t="s">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="I92" s="38"/>
-      <c r="J92" s="39"/>
+      <c r="J92" s="39" t="s">
+        <v>532</v>
+      </c>
       <c r="K92" s="38" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
       <c r="L92" s="39">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M92" s="38">
         <f>L92*5</f>
-        <v>10</v>
-      </c>
-      <c r="N92" s="39"/>
-      <c r="O92" s="38"/>
+        <v>35</v>
+      </c>
+      <c r="N92" s="38">
+        <v>37</v>
+      </c>
+      <c r="O92" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P92" s="53"/>
       <c r="Q92" s="42">
         <f>P92*N92</f>
@@ -6683,76 +7351,84 @@
       <c r="R92" s="39"/>
       <c r="S92" s="38"/>
     </row>
-    <row r="93" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="52">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="C93" s="41"/>
+      <c r="C93" s="62"/>
       <c r="D93" s="40" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="F93" s="41" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="G93" s="40" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="H93" s="41" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I93" s="40"/>
-      <c r="J93" s="41"/>
+      <c r="J93" s="41" t="s">
+        <v>448</v>
+      </c>
       <c r="K93" s="40" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="L93" s="41">
         <v>2</v>
       </c>
       <c r="M93" s="40">
-        <f t="shared" ref="M93" si="83">L93*5</f>
+        <f t="shared" ref="M93" si="85">L93*5</f>
         <v>10</v>
       </c>
-      <c r="N93" s="41"/>
-      <c r="O93" s="40"/>
+      <c r="N93" s="41">
+        <v>12</v>
+      </c>
+      <c r="O93" s="77" t="s">
+        <v>437</v>
+      </c>
       <c r="P93" s="54"/>
       <c r="Q93" s="43">
-        <f t="shared" ref="Q93" si="84">P93*N93</f>
+        <f t="shared" ref="Q93" si="86">P93*N93</f>
         <v>0</v>
       </c>
       <c r="R93" s="41"/>
       <c r="S93" s="40"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="51">
         <f>ROW(B94) - ROW($B$9)</f>
         <v>85</v>
       </c>
-      <c r="C94" s="39"/>
+      <c r="C94" s="61"/>
       <c r="D94" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="E94" s="38" t="s">
-        <v>206</v>
+        <v>92</v>
+      </c>
+      <c r="E94" s="75" t="s">
+        <v>186</v>
       </c>
       <c r="F94" s="39" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="G94" s="38" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="H94" s="39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I94" s="38"/>
-      <c r="J94" s="39"/>
+      <c r="J94" s="39" t="s">
+        <v>533</v>
+      </c>
       <c r="K94" s="38" t="s">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="L94" s="39">
         <v>1</v>
@@ -6761,8 +7437,12 @@
         <f>L94*5</f>
         <v>5</v>
       </c>
-      <c r="N94" s="39"/>
-      <c r="O94" s="38"/>
+      <c r="N94" s="38">
+        <v>6</v>
+      </c>
+      <c r="O94" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P94" s="53"/>
       <c r="Q94" s="42">
         <f>P94*N94</f>
@@ -6777,39 +7457,45 @@
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="C95" s="41"/>
-      <c r="D95" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="E95" s="86" t="s">
-        <v>207</v>
-      </c>
-      <c r="F95" s="87" t="s">
-        <v>270</v>
-      </c>
-      <c r="G95" s="86" t="s">
-        <v>347</v>
-      </c>
-      <c r="H95" s="87" t="s">
-        <v>400</v>
-      </c>
-      <c r="I95" s="86"/>
-      <c r="J95" s="87"/>
-      <c r="K95" s="86" t="s">
-        <v>466</v>
+      <c r="C95" s="62"/>
+      <c r="D95" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E95" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="F95" s="41" t="s">
+        <v>242</v>
+      </c>
+      <c r="G95" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="H95" s="41" t="s">
+        <v>362</v>
+      </c>
+      <c r="I95" s="40"/>
+      <c r="J95" s="41" t="s">
+        <v>534</v>
+      </c>
+      <c r="K95" s="40" t="s">
+        <v>448</v>
       </c>
       <c r="L95" s="41">
         <v>1</v>
       </c>
       <c r="M95" s="40">
-        <f t="shared" ref="M95" si="85">L95*5</f>
+        <f t="shared" ref="M95" si="87">L95*5</f>
         <v>5</v>
       </c>
-      <c r="N95" s="41"/>
-      <c r="O95" s="40"/>
+      <c r="N95" s="41">
+        <v>6</v>
+      </c>
+      <c r="O95" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P95" s="54"/>
       <c r="Q95" s="43">
-        <f t="shared" ref="Q95" si="86">P95*N95</f>
+        <f t="shared" ref="Q95" si="88">P95*N95</f>
         <v>0</v>
       </c>
       <c r="R95" s="41"/>
@@ -6821,40 +7507,42 @@
         <f>ROW(B96) - ROW($B$9)</f>
         <v>87</v>
       </c>
-      <c r="C96" s="39" t="s">
-        <v>16</v>
-      </c>
+      <c r="C96" s="61"/>
       <c r="D96" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="E96" s="38" t="s">
-        <v>208</v>
+        <v>94</v>
+      </c>
+      <c r="E96" s="75" t="s">
+        <v>188</v>
       </c>
       <c r="F96" s="39" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="G96" s="38" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H96" s="39" t="s">
         <v>363</v>
       </c>
       <c r="I96" s="38"/>
       <c r="J96" s="39" t="s">
-        <v>429</v>
+        <v>535</v>
       </c>
       <c r="K96" s="38" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="L96" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M96" s="38">
         <f>L96*5</f>
-        <v>10</v>
-      </c>
-      <c r="N96" s="39"/>
-      <c r="O96" s="38"/>
+        <v>5</v>
+      </c>
+      <c r="N96" s="38">
+        <v>6</v>
+      </c>
+      <c r="O96" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P96" s="53"/>
       <c r="Q96" s="42">
         <f>P96*N96</f>
@@ -6863,76 +7551,84 @@
       <c r="R96" s="39"/>
       <c r="S96" s="38"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="52">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C97" s="41"/>
+      <c r="C97" s="62"/>
       <c r="D97" s="40" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E97" s="40" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="F97" s="41" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="G97" s="40" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="H97" s="41" t="s">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="I97" s="40"/>
-      <c r="J97" s="41"/>
+      <c r="J97" s="41" t="s">
+        <v>448</v>
+      </c>
       <c r="K97" s="40" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="L97" s="41">
         <v>1</v>
       </c>
       <c r="M97" s="40">
-        <f t="shared" ref="M97" si="87">L97*5</f>
+        <f t="shared" ref="M97" si="89">L97*5</f>
         <v>5</v>
       </c>
-      <c r="N97" s="41"/>
-      <c r="O97" s="40"/>
+      <c r="N97" s="41">
+        <v>6</v>
+      </c>
+      <c r="O97" s="77" t="s">
+        <v>437</v>
+      </c>
       <c r="P97" s="54"/>
       <c r="Q97" s="43">
-        <f t="shared" ref="Q97" si="88">P97*N97</f>
+        <f t="shared" ref="Q97" si="90">P97*N97</f>
         <v>0</v>
       </c>
       <c r="R97" s="41"/>
       <c r="S97" s="40"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="51">
         <f>ROW(B98) - ROW($B$9)</f>
         <v>89</v>
       </c>
-      <c r="C98" s="39"/>
+      <c r="C98" s="61"/>
       <c r="D98" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E98" s="38" t="s">
-        <v>210</v>
+        <v>96</v>
+      </c>
+      <c r="E98" s="75" t="s">
+        <v>190</v>
       </c>
       <c r="F98" s="39" t="s">
-        <v>266</v>
+        <v>451</v>
       </c>
       <c r="G98" s="38" t="s">
-        <v>349</v>
+        <v>244</v>
       </c>
       <c r="H98" s="39" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I98" s="38"/>
-      <c r="J98" s="39"/>
+      <c r="J98" s="39" t="s">
+        <v>448</v>
+      </c>
       <c r="K98" s="38" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="L98" s="39">
         <v>1</v>
@@ -6941,8 +7637,12 @@
         <f>L98*5</f>
         <v>5</v>
       </c>
-      <c r="N98" s="39"/>
-      <c r="O98" s="38"/>
+      <c r="N98" s="38">
+        <v>6</v>
+      </c>
+      <c r="O98" s="76" t="s">
+        <v>437</v>
+      </c>
       <c r="P98" s="53"/>
       <c r="Q98" s="42">
         <f>P98*N98</f>
@@ -6951,47 +7651,51 @@
       <c r="R98" s="39"/>
       <c r="S98" s="38"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="52">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C99" s="41"/>
+      <c r="C99" s="62"/>
       <c r="D99" s="40" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="F99" s="41" t="s">
-        <v>266</v>
+        <v>449</v>
       </c>
       <c r="G99" s="40" t="s">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="H99" s="41" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I99" s="40"/>
       <c r="J99" s="41" t="s">
-        <v>430</v>
+        <v>536</v>
       </c>
       <c r="K99" s="40" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="L99" s="41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M99" s="40">
-        <f t="shared" ref="M99" si="89">L99*5</f>
-        <v>5</v>
-      </c>
-      <c r="N99" s="41"/>
-      <c r="O99" s="40"/>
+        <f t="shared" ref="M99" si="91">L99*5</f>
+        <v>20</v>
+      </c>
+      <c r="N99" s="41">
+        <v>22</v>
+      </c>
+      <c r="O99" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P99" s="54"/>
       <c r="Q99" s="43">
-        <f t="shared" ref="Q99" si="90">P99*N99</f>
+        <f t="shared" ref="Q99" si="92">P99*N99</f>
         <v>0</v>
       </c>
       <c r="R99" s="41"/>
@@ -7003,36 +7707,42 @@
         <f>ROW(B100) - ROW($B$9)</f>
         <v>91</v>
       </c>
-      <c r="C100" s="39"/>
+      <c r="C100" s="61"/>
       <c r="D100" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="E100" s="38" t="s">
-        <v>212</v>
+        <v>98</v>
+      </c>
+      <c r="E100" s="75" t="s">
+        <v>192</v>
       </c>
       <c r="F100" s="39" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="G100" s="38" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="H100" s="39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I100" s="38"/>
-      <c r="J100" s="39"/>
+      <c r="J100" s="39" t="s">
+        <v>537</v>
+      </c>
       <c r="K100" s="38" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="L100" s="39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M100" s="38">
         <f>L100*5</f>
-        <v>10</v>
-      </c>
-      <c r="N100" s="39"/>
-      <c r="O100" s="38"/>
+        <v>15</v>
+      </c>
+      <c r="N100" s="38">
+        <v>17</v>
+      </c>
+      <c r="O100" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P100" s="53"/>
       <c r="Q100" s="42">
         <f>P100*N100</f>
@@ -7041,88 +7751,98 @@
       <c r="R100" s="39"/>
       <c r="S100" s="38"/>
     </row>
-    <row r="101" spans="1:19" ht="96" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="52">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="C101" s="41"/>
+      <c r="C101" s="62"/>
       <c r="D101" s="40" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="F101" s="41" t="s">
-        <v>480</v>
+        <v>247</v>
       </c>
       <c r="G101" s="40" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="H101" s="41" t="s">
-        <v>491</v>
-      </c>
-      <c r="I101" s="40" t="s">
-        <v>491</v>
-      </c>
-      <c r="J101" s="41"/>
+        <v>362</v>
+      </c>
+      <c r="I101" s="40"/>
+      <c r="J101" s="41" t="s">
+        <v>538</v>
+      </c>
       <c r="K101" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L101" s="41">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="M101" s="40">
-        <f t="shared" ref="M101" si="91">L101*5</f>
-        <v>210</v>
-      </c>
-      <c r="N101" s="41"/>
-      <c r="O101" s="40"/>
+        <f t="shared" ref="M101" si="93">L101*5</f>
+        <v>5</v>
+      </c>
+      <c r="N101" s="41">
+        <v>6</v>
+      </c>
+      <c r="O101" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P101" s="54"/>
       <c r="Q101" s="43">
-        <f t="shared" ref="Q101" si="92">P101*N101</f>
+        <f t="shared" ref="Q101" si="94">P101*N101</f>
         <v>0</v>
       </c>
       <c r="R101" s="41"/>
       <c r="S101" s="40"/>
     </row>
-    <row r="102" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="51">
         <f>ROW(B102) - ROW($B$9)</f>
         <v>93</v>
       </c>
-      <c r="C102" s="39"/>
+      <c r="C102" s="61"/>
       <c r="D102" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E102" s="38" t="s">
-        <v>214</v>
+        <v>100</v>
+      </c>
+      <c r="E102" s="75" t="s">
+        <v>194</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>480</v>
+        <v>248</v>
       </c>
       <c r="G102" s="38" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="H102" s="39" t="s">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="I102" s="38"/>
-      <c r="J102" s="39"/>
+      <c r="J102" s="39" t="s">
+        <v>539</v>
+      </c>
       <c r="K102" s="38" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L102" s="39">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M102" s="38">
         <f>L102*5</f>
-        <v>35</v>
-      </c>
-      <c r="N102" s="39"/>
-      <c r="O102" s="38"/>
+        <v>5</v>
+      </c>
+      <c r="N102" s="38">
+        <v>6</v>
+      </c>
+      <c r="O102" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P102" s="53"/>
       <c r="Q102" s="42">
         <f>P102*N102</f>
@@ -7137,39 +7857,45 @@
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="C103" s="41"/>
+      <c r="C103" s="62"/>
       <c r="D103" s="40" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="F103" s="41" t="s">
-        <v>273</v>
+        <v>437</v>
       </c>
       <c r="G103" s="40" t="s">
-        <v>352</v>
+        <v>249</v>
       </c>
       <c r="H103" s="41" t="s">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="I103" s="40"/>
-      <c r="J103" s="41"/>
+      <c r="J103" s="41" t="s">
+        <v>540</v>
+      </c>
       <c r="K103" s="40" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="L103" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M103" s="40">
-        <f t="shared" ref="M103" si="93">L103*5</f>
-        <v>10</v>
-      </c>
-      <c r="N103" s="41"/>
-      <c r="O103" s="40"/>
+        <f t="shared" ref="M103" si="95">L103*5</f>
+        <v>5</v>
+      </c>
+      <c r="N103" s="41">
+        <v>6</v>
+      </c>
+      <c r="O103" s="77" t="s">
+        <v>469</v>
+      </c>
       <c r="P103" s="54"/>
       <c r="Q103" s="43">
-        <f t="shared" ref="Q103" si="94">P103*N103</f>
+        <f t="shared" ref="Q103" si="96">P103*N103</f>
         <v>0</v>
       </c>
       <c r="R103" s="41"/>
@@ -7181,26 +7907,28 @@
         <f>ROW(B104) - ROW($B$9)</f>
         <v>95</v>
       </c>
-      <c r="C104" s="39"/>
+      <c r="C104" s="61"/>
       <c r="D104" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="E104" s="38" t="s">
-        <v>216</v>
+        <v>102</v>
+      </c>
+      <c r="E104" s="75" t="s">
+        <v>196</v>
       </c>
       <c r="F104" s="39" t="s">
-        <v>273</v>
+        <v>437</v>
       </c>
       <c r="G104" s="38" t="s">
-        <v>353</v>
+        <v>250</v>
       </c>
       <c r="H104" s="39" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="I104" s="38"/>
-      <c r="J104" s="39"/>
+      <c r="J104" s="39" t="s">
+        <v>541</v>
+      </c>
       <c r="K104" s="38" t="s">
-        <v>491</v>
+        <v>432</v>
       </c>
       <c r="L104" s="39">
         <v>1</v>
@@ -7209,8 +7937,12 @@
         <f>L104*5</f>
         <v>5</v>
       </c>
-      <c r="N104" s="39"/>
-      <c r="O104" s="38"/>
+      <c r="N104" s="38">
+        <v>6</v>
+      </c>
+      <c r="O104" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P104" s="53"/>
       <c r="Q104" s="42">
         <f>P104*N104</f>
@@ -7219,76 +7951,80 @@
       <c r="R104" s="39"/>
       <c r="S104" s="38"/>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="52">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="C105" s="41"/>
+      <c r="C105" s="62"/>
       <c r="D105" s="40" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E105" s="40" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="F105" s="41" t="s">
-        <v>274</v>
+        <v>437</v>
       </c>
       <c r="G105" s="40" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="H105" s="41" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="I105" s="40"/>
-      <c r="J105" s="41"/>
+      <c r="J105" s="41" t="s">
+        <v>388</v>
+      </c>
       <c r="K105" s="40" t="s">
-        <v>491</v>
+        <v>433</v>
       </c>
       <c r="L105" s="41">
         <v>1</v>
       </c>
       <c r="M105" s="40">
-        <f t="shared" ref="M105" si="95">L105*5</f>
+        <f t="shared" ref="M105" si="97">L105*5</f>
         <v>5</v>
       </c>
       <c r="N105" s="41"/>
-      <c r="O105" s="40"/>
+      <c r="O105" s="77"/>
       <c r="P105" s="54"/>
       <c r="Q105" s="43">
-        <f t="shared" ref="Q105" si="96">P105*N105</f>
+        <f t="shared" ref="Q105" si="98">P105*N105</f>
         <v>0</v>
       </c>
       <c r="R105" s="41"/>
       <c r="S105" s="40"/>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="51">
         <f>ROW(B106) - ROW($B$9)</f>
         <v>97</v>
       </c>
-      <c r="C106" s="39"/>
+      <c r="C106" s="61"/>
       <c r="D106" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="E106" s="38" t="s">
-        <v>218</v>
+        <v>104</v>
+      </c>
+      <c r="E106" s="75" t="s">
+        <v>198</v>
       </c>
       <c r="F106" s="39" t="s">
-        <v>275</v>
+        <v>437</v>
       </c>
       <c r="G106" s="38" t="s">
-        <v>355</v>
+        <v>251</v>
       </c>
       <c r="H106" s="39" t="s">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="I106" s="38"/>
-      <c r="J106" s="39"/>
+      <c r="J106" s="39" t="s">
+        <v>542</v>
+      </c>
       <c r="K106" s="38" t="s">
-        <v>491</v>
+        <v>434</v>
       </c>
       <c r="L106" s="39">
         <v>1</v>
@@ -7297,8 +8033,12 @@
         <f>L106*5</f>
         <v>5</v>
       </c>
-      <c r="N106" s="39"/>
-      <c r="O106" s="38"/>
+      <c r="N106" s="38">
+        <v>6</v>
+      </c>
+      <c r="O106" s="76" t="s">
+        <v>469</v>
+      </c>
       <c r="P106" s="53"/>
       <c r="Q106" s="42">
         <f>P106*N106</f>
@@ -7307,510 +8047,145 @@
       <c r="R106" s="39"/>
       <c r="S106" s="38"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
-      <c r="B107" s="52">
-        <f t="shared" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="C107" s="41"/>
-      <c r="D107" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="E107" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="F107" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="G107" s="40" t="s">
-        <v>356</v>
-      </c>
-      <c r="H107" s="41" t="s">
-        <v>369</v>
-      </c>
-      <c r="I107" s="40"/>
-      <c r="J107" s="41"/>
-      <c r="K107" s="40" t="s">
-        <v>491</v>
-      </c>
-      <c r="L107" s="41">
-        <v>1</v>
-      </c>
-      <c r="M107" s="40">
-        <f t="shared" ref="M107" si="97">L107*5</f>
+      <c r="B107" s="45"/>
+      <c r="C107" s="46"/>
+      <c r="D107" s="47"/>
+      <c r="E107" s="48"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="50"/>
+      <c r="H107" s="49"/>
+      <c r="I107" s="50"/>
+      <c r="J107" s="49"/>
+      <c r="K107" s="50"/>
+      <c r="L107" s="50"/>
+      <c r="M107" s="50"/>
+      <c r="N107" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="N107" s="41"/>
-      <c r="O107" s="40"/>
-      <c r="P107" s="54"/>
-      <c r="Q107" s="43">
-        <f t="shared" ref="Q107" si="98">P107*N107</f>
-        <v>0</v>
-      </c>
-      <c r="R107" s="41"/>
-      <c r="S107" s="40"/>
-    </row>
-    <row r="108" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A108" s="1"/>
-      <c r="B108" s="51">
-        <f>ROW(B108) - ROW($B$9)</f>
-        <v>99</v>
-      </c>
-      <c r="C108" s="39"/>
-      <c r="D108" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E108" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="F108" s="39" t="s">
-        <v>494</v>
-      </c>
-      <c r="G108" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="H108" s="39" t="s">
-        <v>405</v>
-      </c>
-      <c r="I108" s="38"/>
-      <c r="J108" s="39"/>
-      <c r="K108" s="38" t="s">
-        <v>491</v>
-      </c>
-      <c r="L108" s="39">
-        <v>1</v>
-      </c>
-      <c r="M108" s="38">
-        <f>L108*5</f>
-        <v>5</v>
-      </c>
-      <c r="N108" s="39"/>
-      <c r="O108" s="38"/>
-      <c r="P108" s="53"/>
-      <c r="Q108" s="42">
-        <f>P108*N108</f>
-        <v>0</v>
-      </c>
-      <c r="R108" s="39"/>
-      <c r="S108" s="38"/>
-    </row>
-    <row r="109" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A109" s="1"/>
-      <c r="B109" s="52">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C109" s="41"/>
-      <c r="D109" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="E109" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="F109" s="41" t="s">
-        <v>492</v>
-      </c>
-      <c r="G109" s="40" t="s">
-        <v>277</v>
-      </c>
-      <c r="H109" s="41" t="s">
-        <v>406</v>
-      </c>
-      <c r="I109" s="40"/>
-      <c r="J109" s="41"/>
-      <c r="K109" s="40" t="s">
-        <v>491</v>
-      </c>
-      <c r="L109" s="41">
-        <v>4</v>
-      </c>
-      <c r="M109" s="40">
-        <f t="shared" ref="M109" si="99">L109*5</f>
-        <v>20</v>
-      </c>
-      <c r="N109" s="41"/>
-      <c r="O109" s="40"/>
-      <c r="P109" s="54"/>
-      <c r="Q109" s="43">
-        <f t="shared" ref="Q109" si="100">P109*N109</f>
-        <v>0</v>
-      </c>
-      <c r="R109" s="41"/>
-      <c r="S109" s="40"/>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A110" s="1"/>
-      <c r="B110" s="51">
-        <f>ROW(B110) - ROW($B$9)</f>
-        <v>101</v>
-      </c>
-      <c r="C110" s="39"/>
-      <c r="D110" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="E110" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="F110" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="G110" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="H110" s="39" t="s">
-        <v>403</v>
-      </c>
-      <c r="I110" s="38"/>
-      <c r="J110" s="39"/>
-      <c r="K110" s="38" t="s">
-        <v>491</v>
-      </c>
-      <c r="L110" s="39">
-        <v>3</v>
-      </c>
-      <c r="M110" s="38">
-        <f>L110*5</f>
-        <v>15</v>
-      </c>
-      <c r="N110" s="39"/>
-      <c r="O110" s="38"/>
-      <c r="P110" s="53"/>
-      <c r="Q110" s="42">
-        <f>P110*N110</f>
-        <v>0</v>
-      </c>
-      <c r="R110" s="39"/>
-      <c r="S110" s="38"/>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A111" s="1"/>
-      <c r="B111" s="52">
-        <f t="shared" si="0"/>
-        <v>102</v>
-      </c>
-      <c r="C111" s="41"/>
-      <c r="D111" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="E111" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="F111" s="41" t="s">
-        <v>279</v>
-      </c>
-      <c r="G111" s="40" t="s">
-        <v>358</v>
-      </c>
-      <c r="H111" s="41" t="s">
-        <v>403</v>
-      </c>
-      <c r="I111" s="40"/>
-      <c r="J111" s="41"/>
-      <c r="K111" s="40" t="s">
-        <v>491</v>
-      </c>
-      <c r="L111" s="41">
-        <v>1</v>
-      </c>
-      <c r="M111" s="40">
-        <f t="shared" ref="M111" si="101">L111*5</f>
-        <v>5</v>
-      </c>
-      <c r="N111" s="41"/>
-      <c r="O111" s="40"/>
-      <c r="P111" s="54"/>
-      <c r="Q111" s="43">
-        <f t="shared" ref="Q111" si="102">P111*N111</f>
-        <v>0</v>
-      </c>
-      <c r="R111" s="41"/>
-      <c r="S111" s="40"/>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A112" s="1"/>
-      <c r="B112" s="51">
-        <f>ROW(B112) - ROW($B$9)</f>
-        <v>103</v>
-      </c>
-      <c r="C112" s="39"/>
-      <c r="D112" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="E112" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="F112" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="G112" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="H112" s="39" t="s">
-        <v>407</v>
-      </c>
-      <c r="I112" s="38"/>
-      <c r="J112" s="39"/>
-      <c r="K112" s="38" t="s">
-        <v>491</v>
-      </c>
-      <c r="L112" s="39">
-        <v>1</v>
-      </c>
-      <c r="M112" s="38">
-        <f>L112*5</f>
-        <v>5</v>
-      </c>
-      <c r="N112" s="39"/>
-      <c r="O112" s="38"/>
-      <c r="P112" s="53"/>
-      <c r="Q112" s="42">
-        <f>P112*N112</f>
-        <v>0</v>
-      </c>
-      <c r="R112" s="39"/>
-      <c r="S112" s="38"/>
-    </row>
-    <row r="113" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A113" s="1"/>
-      <c r="B113" s="52">
-        <f t="shared" si="0"/>
-        <v>104</v>
-      </c>
-      <c r="C113" s="41"/>
-      <c r="D113" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E113" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="F113" s="41" t="s">
-        <v>480</v>
-      </c>
-      <c r="G113" s="40" t="s">
-        <v>281</v>
-      </c>
-      <c r="H113" s="41" t="s">
-        <v>408</v>
-      </c>
-      <c r="I113" s="40"/>
-      <c r="J113" s="41"/>
-      <c r="K113" s="40" t="s">
-        <v>491</v>
-      </c>
-      <c r="L113" s="41">
-        <v>1</v>
-      </c>
-      <c r="M113" s="40">
-        <f t="shared" ref="M113" si="103">L113*5</f>
-        <v>5</v>
-      </c>
-      <c r="N113" s="41"/>
-      <c r="O113" s="40"/>
-      <c r="P113" s="54"/>
-      <c r="Q113" s="43">
-        <f t="shared" ref="Q113" si="104">P113*N113</f>
-        <v>0</v>
-      </c>
-      <c r="R113" s="41"/>
-      <c r="S113" s="40"/>
-    </row>
-    <row r="114" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A114" s="1"/>
-      <c r="B114" s="51">
-        <f>ROW(B114) - ROW($B$9)</f>
-        <v>105</v>
-      </c>
-      <c r="C114" s="39"/>
-      <c r="D114" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="E114" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="F114" s="39" t="s">
-        <v>480</v>
-      </c>
-      <c r="G114" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="H114" s="39" t="s">
-        <v>409</v>
-      </c>
-      <c r="I114" s="38"/>
-      <c r="J114" s="39"/>
-      <c r="K114" s="38" t="s">
-        <v>475</v>
-      </c>
-      <c r="L114" s="39">
-        <v>1</v>
-      </c>
-      <c r="M114" s="38">
-        <f>L114*5</f>
-        <v>5</v>
-      </c>
-      <c r="N114" s="39"/>
-      <c r="O114" s="38"/>
-      <c r="P114" s="53"/>
-      <c r="Q114" s="42">
-        <f>P114*N114</f>
-        <v>0</v>
-      </c>
-      <c r="R114" s="39"/>
-      <c r="S114" s="38"/>
-    </row>
-    <row r="115" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A115" s="1"/>
-      <c r="B115" s="52">
-        <f t="shared" si="0"/>
-        <v>106</v>
-      </c>
-      <c r="C115" s="41"/>
-      <c r="D115" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="E115" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="F115" s="41" t="s">
-        <v>480</v>
-      </c>
-      <c r="G115" s="40" t="s">
-        <v>360</v>
-      </c>
-      <c r="H115" s="41" t="s">
-        <v>410</v>
-      </c>
-      <c r="I115" s="40"/>
-      <c r="J115" s="41" t="s">
-        <v>431</v>
-      </c>
-      <c r="K115" s="40" t="s">
-        <v>476</v>
-      </c>
-      <c r="L115" s="41">
-        <v>1</v>
-      </c>
-      <c r="M115" s="40">
-        <f t="shared" ref="M115" si="105">L115*5</f>
-        <v>5</v>
-      </c>
-      <c r="N115" s="41"/>
-      <c r="O115" s="40"/>
-      <c r="P115" s="54"/>
-      <c r="Q115" s="43">
-        <f t="shared" ref="Q115" si="106">P115*N115</f>
-        <v>0</v>
-      </c>
-      <c r="R115" s="41"/>
-      <c r="S115" s="40"/>
-    </row>
-    <row r="116" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="1"/>
-      <c r="B116" s="51">
-        <f>ROW(B116) - ROW($B$9)</f>
-        <v>107</v>
-      </c>
-      <c r="C116" s="39"/>
-      <c r="D116" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="E116" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="F116" s="39" t="s">
-        <v>480</v>
-      </c>
-      <c r="G116" s="73" t="s">
-        <v>283</v>
-      </c>
-      <c r="H116" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="I116" s="38"/>
-      <c r="J116" s="39"/>
-      <c r="K116" s="38" t="s">
-        <v>477</v>
-      </c>
-      <c r="L116" s="39">
-        <v>1</v>
-      </c>
-      <c r="M116" s="38">
-        <f>L116*5</f>
-        <v>5</v>
-      </c>
-      <c r="N116" s="39"/>
-      <c r="O116" s="38"/>
-      <c r="P116" s="53"/>
-      <c r="Q116" s="42">
-        <f>P116*N116</f>
-        <v>0</v>
-      </c>
-      <c r="R116" s="39"/>
-      <c r="S116" s="73"/>
-    </row>
-    <row r="117" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="1"/>
-      <c r="B117" s="45"/>
-      <c r="C117" s="46"/>
-      <c r="D117" s="47"/>
-      <c r="E117" s="48"/>
-      <c r="F117" s="49"/>
-      <c r="G117" s="50"/>
-      <c r="H117" s="49"/>
-      <c r="I117" s="50"/>
-      <c r="J117" s="49"/>
-      <c r="K117" s="50"/>
-      <c r="L117" s="50"/>
-      <c r="M117" s="50"/>
-      <c r="N117" s="69" t="s">
-        <v>5</v>
-      </c>
-      <c r="O117" s="70"/>
-      <c r="P117" s="70"/>
-      <c r="Q117" s="55" t="e">
+      <c r="O107" s="74"/>
+      <c r="P107" s="74"/>
+      <c r="Q107" s="55" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="R117" s="65"/>
-      <c r="S117" s="66"/>
-    </row>
-    <row r="118" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="1"/>
-      <c r="B118" s="25"/>
-      <c r="C118" s="37"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="10"/>
-      <c r="F118" s="10"/>
-      <c r="G118" s="10"/>
-      <c r="H118" s="10"/>
-      <c r="I118" s="10"/>
-      <c r="J118" s="10"/>
-      <c r="K118" s="10"/>
-      <c r="L118" s="10"/>
-      <c r="M118" s="10"/>
-      <c r="N118" s="69" t="s">
+      <c r="R107" s="69"/>
+      <c r="S107" s="70"/>
+    </row>
+    <row r="108" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="37"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="10"/>
+      <c r="F108" s="10"/>
+      <c r="G108" s="10"/>
+      <c r="H108" s="10"/>
+      <c r="I108" s="10"/>
+      <c r="J108" s="10"/>
+      <c r="K108" s="10"/>
+      <c r="L108" s="10"/>
+      <c r="M108" s="10"/>
+      <c r="N108" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="O118" s="70"/>
-      <c r="P118" s="70"/>
-      <c r="Q118" s="56" t="e">
-        <f>Q117/5</f>
+      <c r="O108" s="74"/>
+      <c r="P108" s="74"/>
+      <c r="Q108" s="56" t="e">
+        <f>Q107/5</f>
         <v>#REF!</v>
       </c>
-      <c r="R118" s="67"/>
-      <c r="S118" s="68"/>
+      <c r="R108" s="71"/>
+      <c r="S108" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R117:S118"/>
-    <mergeCell ref="N117:P117"/>
-    <mergeCell ref="N118:P118"/>
+    <mergeCell ref="R107:S108"/>
+    <mergeCell ref="N107:P107"/>
+    <mergeCell ref="N108:P108"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1" xr:uid="{29545A6B-2DC3-435B-BADE-82C52630D80A}"/>
+    <hyperlink ref="O12" r:id="rId2" xr:uid="{BBC75B9C-AC5D-49C9-A4C7-7FA9AFAC7874}"/>
+    <hyperlink ref="O13" r:id="rId3" xr:uid="{FB8725AF-0AB9-4F1B-878B-3AA336F9EE8A}"/>
+    <hyperlink ref="O14" r:id="rId4" xr:uid="{2CA36519-1001-4D49-A579-5B8253BCE21C}"/>
+    <hyperlink ref="O15" r:id="rId5" xr:uid="{1FAA7B4F-D535-448B-8EAD-D7A2AA6D8B34}"/>
+    <hyperlink ref="O16" r:id="rId6" xr:uid="{AD5B6527-FD56-4D41-ACC7-E3121BF43254}"/>
+    <hyperlink ref="O18" r:id="rId7" xr:uid="{19726889-79C0-4DF8-81EE-6D8FEF610496}"/>
+    <hyperlink ref="O17" r:id="rId8" xr:uid="{95F9C39D-35FC-427F-B5E3-7D596DF2C2CB}"/>
+    <hyperlink ref="O19" r:id="rId9" xr:uid="{E4BC9E4C-DB1E-4DEA-90F5-9615226B2AF5}"/>
+    <hyperlink ref="O21" r:id="rId10" xr:uid="{E2E8C389-CB7B-4D67-8706-E4EBB41371FD}"/>
+    <hyperlink ref="O20" r:id="rId11" xr:uid="{BB9D5F01-EBD4-4503-BB49-B48D675332AC}"/>
+    <hyperlink ref="O22" r:id="rId12" xr:uid="{C6818809-9DFA-4DDF-84A1-D61479867C30}"/>
+    <hyperlink ref="O23" r:id="rId13" xr:uid="{6D953B1A-FFDE-495A-88E4-C240D4BF57B4}"/>
+    <hyperlink ref="O24" r:id="rId14" xr:uid="{5011D106-6A0F-4F6E-9267-F288D353B00E}"/>
+    <hyperlink ref="O25" r:id="rId15" xr:uid="{EE2ECDEC-E98A-45B1-B207-3DBAD2323660}"/>
+    <hyperlink ref="O26" r:id="rId16" xr:uid="{4D40891A-B988-44D6-9652-FE93505ACDB0}"/>
+    <hyperlink ref="O27" r:id="rId17" xr:uid="{7101BA46-1526-493C-8856-D44ED4DBFE8C}"/>
+    <hyperlink ref="O30" r:id="rId18" xr:uid="{B14A16AC-46E8-4557-95C5-7C8F1F28DAAC}"/>
+    <hyperlink ref="O29" r:id="rId19" xr:uid="{E8789C28-572E-4265-81C1-5A8B5C768F4E}"/>
+    <hyperlink ref="O33" r:id="rId20" xr:uid="{9F327C80-483D-4ED3-B6C2-E190C5CA625F}"/>
+    <hyperlink ref="O34" r:id="rId21" xr:uid="{57350570-67F1-4AD3-ADA6-073C92CC76DD}"/>
+    <hyperlink ref="O35" r:id="rId22" xr:uid="{87FD1FAE-61BF-4D8F-8390-E05304E09254}"/>
+    <hyperlink ref="O36" r:id="rId23" xr:uid="{2F56312B-0F9F-4659-8FAB-C974882883FA}"/>
+    <hyperlink ref="O37" r:id="rId24" xr:uid="{E56294A2-80BE-437F-BA1B-9D7D79AAA687}"/>
+    <hyperlink ref="O38" r:id="rId25" xr:uid="{C108D980-5003-4FCF-B535-A15F768FA423}"/>
+    <hyperlink ref="O41" r:id="rId26" xr:uid="{61C68625-2DEB-40CC-B0B7-4322723EBCB4}"/>
+    <hyperlink ref="O42" r:id="rId27" xr:uid="{854A4EED-287B-489E-AA0F-CAB0ED5419BB}"/>
+    <hyperlink ref="O43" r:id="rId28" xr:uid="{1E15DE01-165A-4C57-A176-7E783BDBE3BF}"/>
+    <hyperlink ref="O45" r:id="rId29" xr:uid="{171FE4FD-3B7C-4967-AF82-983B6BFE4AFA}"/>
+    <hyperlink ref="O46" r:id="rId30" xr:uid="{10340E91-428B-4115-8CBE-A9E5D59EE90B}"/>
+    <hyperlink ref="O53" r:id="rId31" xr:uid="{0006FFE0-C193-4F0C-85C1-42B9401BAC9B}"/>
+    <hyperlink ref="O40" r:id="rId32" xr:uid="{5D53CE1B-BF6C-4358-81EC-2144E782486A}"/>
+    <hyperlink ref="O49" r:id="rId33" xr:uid="{744404B1-7166-451B-B656-73B6689F805F}"/>
+    <hyperlink ref="O52" r:id="rId34" xr:uid="{E95B2246-35D8-45A7-B13E-9FFBAA5D82F3}"/>
+    <hyperlink ref="O54" r:id="rId35" xr:uid="{A1930886-B67F-4675-8663-FE1B886872F0}"/>
+    <hyperlink ref="O56" r:id="rId36" xr:uid="{4B3E5CD5-63AC-41FF-8F31-4A7E209E5854}"/>
+    <hyperlink ref="O44" r:id="rId37" xr:uid="{10572C88-0415-4A57-9B9D-50943BD946FB}"/>
+    <hyperlink ref="O50" r:id="rId38" xr:uid="{A0CCABC5-D4C5-4595-A3B3-40BBF95EF6D0}"/>
+    <hyperlink ref="O51" r:id="rId39" xr:uid="{7068324F-A2E7-4474-B729-DB1FF6472EA0}"/>
+    <hyperlink ref="O28" r:id="rId40" xr:uid="{CB3D49CF-7E19-4EB8-B41B-5C4EB03CB586}"/>
+    <hyperlink ref="O39" r:id="rId41" xr:uid="{22C2DA5A-BA2A-403C-A5BB-E1E3C904C04D}"/>
+    <hyperlink ref="O48" r:id="rId42" xr:uid="{EDCDD759-3F1D-41F4-8193-D4F65E3B4FC3}"/>
+    <hyperlink ref="O57" r:id="rId43" xr:uid="{456A4A05-84EF-4C2F-9896-3F0C45F994D9}"/>
+    <hyperlink ref="O58" r:id="rId44" xr:uid="{541E11B3-D69F-4EED-928F-AF296FDA000C}"/>
+    <hyperlink ref="O59" r:id="rId45" xr:uid="{6918C750-193B-4AB8-9229-44BC80D9E27C}"/>
+    <hyperlink ref="O60" r:id="rId46" xr:uid="{ADF98DFB-4F1C-460D-A899-62029D6893FA}"/>
+    <hyperlink ref="O61" r:id="rId47" xr:uid="{0AD278DF-C4E6-43AD-8B76-8F0E41A12346}"/>
+    <hyperlink ref="O62" r:id="rId48" xr:uid="{CDB769EF-3F11-4533-9B5D-F493CFBAF9A4}"/>
+    <hyperlink ref="O63" r:id="rId49" xr:uid="{00CCCDA1-0B54-4599-9573-471507073410}"/>
+    <hyperlink ref="O64" r:id="rId50" xr:uid="{C1645A06-B052-488B-A750-C446D699007D}"/>
+    <hyperlink ref="O65" r:id="rId51" xr:uid="{73A9CC2A-BE8E-4844-9585-17C8AE7A1A32}"/>
+    <hyperlink ref="O66" r:id="rId52" xr:uid="{BEAAD7B4-C902-484A-81ED-EA83E13A8C41}"/>
+    <hyperlink ref="O67" r:id="rId53" xr:uid="{8E3AA42A-1B35-46C7-B01A-71EDE622956E}"/>
+    <hyperlink ref="O68" r:id="rId54" xr:uid="{A1935079-A094-413F-B9A7-948CED36635C}"/>
+    <hyperlink ref="O69" r:id="rId55" xr:uid="{3D499A9E-8EE7-4BBB-ACDB-68931E11953D}"/>
+    <hyperlink ref="O71" r:id="rId56" xr:uid="{E07821F2-AD60-4F6B-98CC-E7E698DEAF18}"/>
+    <hyperlink ref="O72" r:id="rId57" xr:uid="{911EBAD4-8428-460D-A4D5-2A0E7245E766}"/>
+    <hyperlink ref="O74" r:id="rId58" xr:uid="{A92CD093-DFA7-4679-A7ED-780AA6E86E78}"/>
+    <hyperlink ref="O77" r:id="rId59" xr:uid="{DC34F4D1-1945-4AD0-85C8-A32483EC1576}"/>
+    <hyperlink ref="O78" r:id="rId60" xr:uid="{AC50B9CD-4B66-49C1-B9A4-755E6A3B7388}"/>
+    <hyperlink ref="O83" r:id="rId61" xr:uid="{9A3E4456-1E48-41E1-A10B-83098555007B}"/>
+    <hyperlink ref="O86" r:id="rId62" xr:uid="{3149E9C4-8DCD-4B7B-AA56-C24793E1FDDD}"/>
+    <hyperlink ref="O87" r:id="rId63" xr:uid="{216F92A5-F104-4692-B17C-6227E8D25A0E}"/>
+    <hyperlink ref="O92" r:id="rId64" xr:uid="{BB0086C3-2D05-4979-8CF3-0132D37DF1DB}"/>
+    <hyperlink ref="O95" r:id="rId65" xr:uid="{571AFD85-72FA-4D23-A240-55270E118838}"/>
+    <hyperlink ref="O96" r:id="rId66" xr:uid="{DB794ED7-FAF2-40D3-BCC4-3D87E9946E04}"/>
+    <hyperlink ref="O100" r:id="rId67" xr:uid="{7F416119-DC76-4A27-8048-AE23EAF496C5}"/>
+    <hyperlink ref="O101" r:id="rId68" xr:uid="{D5517901-37E6-434A-B7DB-9D7ACA270724}"/>
+    <hyperlink ref="O102" r:id="rId69" xr:uid="{1D68F898-6AEA-42FA-94E2-9C9E1498344C}"/>
+    <hyperlink ref="O103" r:id="rId70" xr:uid="{C29175A2-1765-4C45-AC14-06BB76E02B1B}"/>
+    <hyperlink ref="O94" r:id="rId71" xr:uid="{8E588422-7B11-4B05-B296-3911285F17BA}"/>
+    <hyperlink ref="O99" r:id="rId72" xr:uid="{91FF6E37-C9BD-4631-8DF9-4A150C39A80E}"/>
+    <hyperlink ref="O93" r:id="rId73" display="Aliexpress" xr:uid="{101CFFE8-7AA0-460F-85AD-620F85A3941B}"/>
+    <hyperlink ref="O104" r:id="rId74" xr:uid="{C85E336A-E4D8-4F42-95F8-19A806CF9075}"/>
+    <hyperlink ref="O106" r:id="rId75" xr:uid="{61C5202E-87B7-4DFF-BDE8-ADF25A51C4B6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId76"/>
+  <drawing r:id="rId77"/>
 </worksheet>
 </file>
--- a/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
+++ b/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64F0989-431A-48DD-96C9-AA825C29A2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED89801-1873-4E2E-95C8-7518940C31AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="560">
   <si>
     <t>Component list</t>
   </si>
@@ -1418,9 +1418,6 @@
   </si>
   <si>
     <t>R23, R35, R36, R38, R76, R77, R79, R113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                                                                                                          </t>
   </si>
   <si>
     <t>R5, R8, R16, R18, R19, R20, R21, R22, R37, R39, R66, R78, R80, R111, R115</t>
@@ -1604,9 +1601,6 @@
     <t>C99782</t>
   </si>
   <si>
-    <t>C14675</t>
-  </si>
-  <si>
     <t>C2828840</t>
   </si>
   <si>
@@ -1650,6 +1644,63 @@
   </si>
   <si>
     <t>C620155</t>
+  </si>
+  <si>
+    <t>C114612</t>
+  </si>
+  <si>
+    <t>C114623</t>
+  </si>
+  <si>
+    <t>C723637</t>
+  </si>
+  <si>
+    <t>C862245</t>
+  </si>
+  <si>
+    <t>C471801</t>
+  </si>
+  <si>
+    <t>C728597</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>IC</t>
+  </si>
+  <si>
+    <t>Crystal</t>
+  </si>
+  <si>
+    <t>C105574</t>
+  </si>
+  <si>
+    <t>C116674</t>
+  </si>
+  <si>
+    <t>AC0603FR-07100KL</t>
+  </si>
+  <si>
+    <t>RES 1M OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>C105578</t>
+  </si>
+  <si>
+    <t>Winsource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less Stock On LCSC </t>
+  </si>
+  <si>
+    <t>This Part Available On LCSC But Price is Very High</t>
+  </si>
+  <si>
+    <t>C150517</t>
+  </si>
+  <si>
+    <t>20021121-00010C4LF</t>
   </si>
 </sst>
 </file>
@@ -1661,7 +1712,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1823,6 +1874,14 @@
     </font>
     <font>
       <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -2099,7 +2158,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2275,6 +2334,27 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2307,19 +2387,16 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2680,7 +2757,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5703125" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" customWidth="1"/>
     <col min="16" max="16" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -2698,15 +2775,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="73"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2756,7 +2833,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="74"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2781,7 +2858,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="75"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2806,7 +2883,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="75"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2827,7 +2904,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2848,7 +2925,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2869,7 +2946,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2956,7 +3033,7 @@
         <v>448</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K10" s="38" t="s">
         <v>389</v>
@@ -2971,8 +3048,8 @@
       <c r="N10" s="38">
         <v>80</v>
       </c>
-      <c r="O10" s="76" t="s">
-        <v>469</v>
+      <c r="O10" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P10" s="42">
         <v>2.4500000000000001E-2</v>
@@ -3023,7 +3100,7 @@
         <v>5</v>
       </c>
       <c r="N11" s="41"/>
-      <c r="O11" s="77"/>
+      <c r="O11" s="67"/>
       <c r="P11" s="54"/>
       <c r="Q11" s="43">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
@@ -3044,7 +3121,7 @@
       <c r="D12" s="38" t="s">
         <v>458</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="65" t="s">
         <v>108</v>
       </c>
       <c r="F12" s="39" t="s">
@@ -3075,8 +3152,8 @@
       <c r="N12" s="38">
         <v>100</v>
       </c>
-      <c r="O12" s="76" t="s">
-        <v>469</v>
+      <c r="O12" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P12" s="53">
         <v>4.7000000000000002E-3</v>
@@ -3114,7 +3191,7 @@
       </c>
       <c r="I13" s="40"/>
       <c r="J13" s="41" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K13" s="40" t="s">
         <v>392</v>
@@ -3129,8 +3206,8 @@
       <c r="N13" s="41">
         <v>27</v>
       </c>
-      <c r="O13" s="77" t="s">
-        <v>469</v>
+      <c r="O13" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P13" s="54">
         <v>0.28799999999999998</v>
@@ -3154,7 +3231,7 @@
       <c r="D14" s="38" t="s">
         <v>459</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="65" t="s">
         <v>110</v>
       </c>
       <c r="F14" s="39" t="s">
@@ -3170,7 +3247,7 @@
         <v>448</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K14" s="38" t="s">
         <v>390</v>
@@ -3185,8 +3262,8 @@
       <c r="N14" s="38">
         <v>200</v>
       </c>
-      <c r="O14" s="76" t="s">
-        <v>469</v>
+      <c r="O14" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P14" s="53">
         <v>2.7000000000000001E-3</v>
@@ -3226,7 +3303,7 @@
         <v>448</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K15" s="40" t="s">
         <v>393</v>
@@ -3241,8 +3318,8 @@
       <c r="N15" s="41">
         <v>10</v>
       </c>
-      <c r="O15" s="77" t="s">
-        <v>469</v>
+      <c r="O15" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P15" s="54">
         <v>0.13789999999999999</v>
@@ -3266,7 +3343,7 @@
       <c r="D16" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="65" t="s">
         <v>112</v>
       </c>
       <c r="F16" s="39" t="s">
@@ -3282,7 +3359,7 @@
         <v>448</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K16" s="38" t="s">
         <v>394</v>
@@ -3297,8 +3374,8 @@
       <c r="N16" s="38">
         <v>100</v>
       </c>
-      <c r="O16" s="76" t="s">
-        <v>469</v>
+      <c r="O16" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P16" s="53">
         <v>2.5000000000000001E-3</v>
@@ -3338,7 +3415,7 @@
         <v>448</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K17" s="40" t="s">
         <v>391</v>
@@ -3353,8 +3430,8 @@
       <c r="N17" s="41">
         <v>6</v>
       </c>
-      <c r="O17" s="77" t="s">
-        <v>469</v>
+      <c r="O17" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P17" s="54">
         <v>0.19359999999999999</v>
@@ -3378,7 +3455,7 @@
       <c r="D18" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="65" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="39" t="s">
@@ -3394,7 +3471,7 @@
         <v>448</v>
       </c>
       <c r="J18" s="39" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K18" s="38" t="s">
         <v>395</v>
@@ -3409,8 +3486,8 @@
       <c r="N18" s="38">
         <v>100</v>
       </c>
-      <c r="O18" s="76" t="s">
-        <v>469</v>
+      <c r="O18" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P18" s="53">
         <v>2.5999999999999999E-3</v>
@@ -3432,7 +3509,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E19" s="40" t="s">
         <v>115</v>
@@ -3465,8 +3542,8 @@
       <c r="N19" s="41">
         <v>100</v>
       </c>
-      <c r="O19" s="77" t="s">
-        <v>469</v>
+      <c r="O19" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P19" s="54">
         <v>2.8999999999999998E-3</v>
@@ -3490,7 +3567,7 @@
       <c r="D20" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="75" t="s">
+      <c r="E20" s="65" t="s">
         <v>116</v>
       </c>
       <c r="F20" s="39" t="s">
@@ -3521,8 +3598,8 @@
       <c r="N20" s="38">
         <v>20</v>
       </c>
-      <c r="O20" s="76" t="s">
-        <v>469</v>
+      <c r="O20" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P20" s="53">
         <v>3.5200000000000002E-2</v>
@@ -3562,7 +3639,7 @@
         <v>448</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K21" s="40" t="s">
         <v>398</v>
@@ -3577,8 +3654,8 @@
       <c r="N21" s="41">
         <v>20</v>
       </c>
-      <c r="O21" s="77" t="s">
-        <v>469</v>
+      <c r="O21" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P21" s="54">
         <v>3.04E-2</v>
@@ -3602,7 +3679,7 @@
       <c r="D22" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="75" t="s">
+      <c r="E22" s="65" t="s">
         <v>118</v>
       </c>
       <c r="F22" s="39" t="s">
@@ -3618,7 +3695,7 @@
         <v>448</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K22" s="38" t="s">
         <v>399</v>
@@ -3633,8 +3710,8 @@
       <c r="N22" s="38">
         <v>100</v>
       </c>
-      <c r="O22" s="76" t="s">
-        <v>469</v>
+      <c r="O22" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P22" s="53">
         <v>3.3E-3</v>
@@ -3674,7 +3751,7 @@
         <v>448</v>
       </c>
       <c r="J23" s="41" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K23" s="40" t="s">
         <v>400</v>
@@ -3689,8 +3766,8 @@
       <c r="N23" s="41">
         <v>20</v>
       </c>
-      <c r="O23" s="77" t="s">
-        <v>469</v>
+      <c r="O23" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P23" s="54">
         <v>2.9899999999999999E-2</v>
@@ -3714,7 +3791,7 @@
       <c r="D24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="65" t="s">
         <v>120</v>
       </c>
       <c r="F24" s="39" t="s">
@@ -3730,7 +3807,7 @@
         <v>448</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K24" s="38" t="s">
         <v>401</v>
@@ -3745,8 +3822,8 @@
       <c r="N24" s="38">
         <v>100</v>
       </c>
-      <c r="O24" s="76" t="s">
-        <v>469</v>
+      <c r="O24" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P24" s="53">
         <v>3.0999999999999999E-3</v>
@@ -3786,7 +3863,7 @@
         <v>448</v>
       </c>
       <c r="J25" s="41" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K25" s="40" t="s">
         <v>448</v>
@@ -3801,8 +3878,8 @@
       <c r="N25" s="41">
         <v>20</v>
       </c>
-      <c r="O25" s="77" t="s">
-        <v>469</v>
+      <c r="O25" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P25" s="54">
         <v>3.2899999999999999E-2</v>
@@ -3826,7 +3903,7 @@
       <c r="D26" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="75" t="s">
+      <c r="E26" s="65" t="s">
         <v>122</v>
       </c>
       <c r="F26" s="39" t="s">
@@ -3842,7 +3919,7 @@
         <v>448</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K26" s="38" t="s">
         <v>448</v>
@@ -3857,8 +3934,8 @@
       <c r="N26" s="38">
         <v>6</v>
       </c>
-      <c r="O26" s="76" t="s">
-        <v>469</v>
+      <c r="O26" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P26" s="53">
         <v>0.49009999999999998</v>
@@ -3898,7 +3975,7 @@
         <v>448</v>
       </c>
       <c r="J27" s="41" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K27" s="40" t="s">
         <v>448</v>
@@ -3913,8 +3990,8 @@
       <c r="N27" s="41">
         <v>20</v>
       </c>
-      <c r="O27" s="77" t="s">
-        <v>469</v>
+      <c r="O27" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P27" s="54">
         <v>3.1399999999999997E-2</v>
@@ -3938,7 +4015,7 @@
       <c r="D28" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="75" t="s">
+      <c r="E28" s="65" t="s">
         <v>124</v>
       </c>
       <c r="F28" s="39" t="s">
@@ -3969,8 +4046,8 @@
       <c r="N28" s="38">
         <v>40</v>
       </c>
-      <c r="O28" s="76" t="s">
-        <v>469</v>
+      <c r="O28" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P28" s="53">
         <v>2.0400000000000001E-2</v>
@@ -4010,7 +4087,7 @@
         <v>448</v>
       </c>
       <c r="J29" s="41" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K29" s="40" t="s">
         <v>448</v>
@@ -4025,8 +4102,8 @@
       <c r="N29" s="41">
         <v>10</v>
       </c>
-      <c r="O29" s="77" t="s">
-        <v>469</v>
+      <c r="O29" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P29" s="54">
         <v>6.2700000000000006E-2</v>
@@ -4050,7 +4127,7 @@
       <c r="D30" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="75" t="s">
+      <c r="E30" s="65" t="s">
         <v>126</v>
       </c>
       <c r="F30" s="39" t="s">
@@ -4066,7 +4143,7 @@
         <v>448</v>
       </c>
       <c r="J30" s="39" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K30" s="38" t="s">
         <v>448</v>
@@ -4081,8 +4158,8 @@
       <c r="N30" s="38">
         <v>10</v>
       </c>
-      <c r="O30" s="76" t="s">
-        <v>469</v>
+      <c r="O30" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P30" s="53">
         <v>8.7099999999999997E-2</v>
@@ -4135,7 +4212,7 @@
         <v>5</v>
       </c>
       <c r="N31" s="41"/>
-      <c r="O31" s="77"/>
+      <c r="O31" s="67"/>
       <c r="P31" s="54"/>
       <c r="Q31" s="43">
         <f>P31*N31</f>
@@ -4156,23 +4233,23 @@
       <c r="D32" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="75" t="s">
+      <c r="E32" s="65" t="s">
         <v>128</v>
       </c>
       <c r="F32" s="39" t="s">
         <v>437</v>
       </c>
-      <c r="G32" s="38" t="s">
+      <c r="G32" s="69" t="s">
         <v>211</v>
       </c>
       <c r="H32" s="39" t="s">
         <v>336</v>
       </c>
       <c r="I32" s="38" t="s">
-        <v>448</v>
+        <v>559</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>448</v>
+        <v>558</v>
       </c>
       <c r="K32" s="38" t="s">
         <v>448</v>
@@ -4184,12 +4261,18 @@
         <f t="shared" ref="M32" si="23">L32*5</f>
         <v>5</v>
       </c>
-      <c r="N32" s="38"/>
-      <c r="O32" s="76"/>
-      <c r="P32" s="53"/>
+      <c r="N32" s="38">
+        <v>6</v>
+      </c>
+      <c r="O32" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P32" s="53">
+        <v>0.61729999999999996</v>
+      </c>
       <c r="Q32" s="42">
         <f t="shared" ref="Q32" si="24">P32*N32</f>
-        <v>0</v>
+        <v>3.7037999999999998</v>
       </c>
       <c r="R32" s="39"/>
       <c r="S32" s="38"/>
@@ -4212,17 +4295,17 @@
       <c r="F33" s="41" t="s">
         <v>437</v>
       </c>
-      <c r="G33" s="78" t="s">
+      <c r="G33" s="68" t="s">
         <v>212</v>
       </c>
       <c r="H33" s="41" t="s">
         <v>337</v>
       </c>
       <c r="I33" s="40" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J33" s="41" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K33" s="40" t="s">
         <v>448</v>
@@ -4237,8 +4320,8 @@
       <c r="N33" s="41">
         <v>50</v>
       </c>
-      <c r="O33" s="77" t="s">
-        <v>469</v>
+      <c r="O33" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P33" s="54">
         <v>7.1199999999999999E-2</v>
@@ -4262,23 +4345,23 @@
       <c r="D34" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="75" t="s">
+      <c r="E34" s="65" t="s">
         <v>129</v>
       </c>
       <c r="F34" s="39" t="s">
         <v>437</v>
       </c>
-      <c r="G34" s="79" t="s">
+      <c r="G34" s="69" t="s">
         <v>213</v>
       </c>
       <c r="H34" s="39" t="s">
         <v>337</v>
       </c>
       <c r="I34" s="38" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J34" s="39" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K34" s="38" t="s">
         <v>448</v>
@@ -4293,8 +4376,8 @@
       <c r="N34" s="38">
         <v>30</v>
       </c>
-      <c r="O34" s="76" t="s">
-        <v>469</v>
+      <c r="O34" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P34" s="53">
         <v>0.10539999999999999</v>
@@ -4324,17 +4407,17 @@
       <c r="F35" s="41" t="s">
         <v>437</v>
       </c>
-      <c r="G35" s="78" t="s">
+      <c r="G35" s="68" t="s">
         <v>214</v>
       </c>
       <c r="H35" s="41" t="s">
         <v>337</v>
       </c>
       <c r="I35" s="40" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J35" s="41" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K35" s="40" t="s">
         <v>448</v>
@@ -4349,8 +4432,8 @@
       <c r="N35" s="41">
         <v>10</v>
       </c>
-      <c r="O35" s="77" t="s">
-        <v>469</v>
+      <c r="O35" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P35" s="54">
         <v>0.1114</v>
@@ -4374,7 +4457,7 @@
       <c r="D36" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="E36" s="75" t="s">
+      <c r="E36" s="65" t="s">
         <v>130</v>
       </c>
       <c r="F36" s="39" t="s">
@@ -4390,7 +4473,7 @@
         <v>448</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K36" s="38" t="s">
         <v>448</v>
@@ -4405,8 +4488,8 @@
       <c r="N36" s="38">
         <v>6</v>
       </c>
-      <c r="O36" s="76" t="s">
-        <v>469</v>
+      <c r="O36" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P36" s="53">
         <v>0.75180000000000002</v>
@@ -4446,7 +4529,7 @@
         <v>448</v>
       </c>
       <c r="J37" s="41" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K37" s="40" t="s">
         <v>448</v>
@@ -4461,8 +4544,8 @@
       <c r="N37" s="41">
         <v>10</v>
       </c>
-      <c r="O37" s="77" t="s">
-        <v>469</v>
+      <c r="O37" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P37" s="54">
         <v>6.4299999999999996E-2</v>
@@ -4486,7 +4569,7 @@
       <c r="D38" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="75" t="s">
+      <c r="E38" s="65" t="s">
         <v>132</v>
       </c>
       <c r="F38" s="39" t="s">
@@ -4517,8 +4600,8 @@
       <c r="N38" s="38">
         <v>6</v>
       </c>
-      <c r="O38" s="76" t="s">
-        <v>469</v>
+      <c r="O38" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P38" s="53">
         <v>0.22120000000000001</v>
@@ -4573,8 +4656,8 @@
       <c r="N39" s="41">
         <v>27</v>
       </c>
-      <c r="O39" s="77" t="s">
-        <v>469</v>
+      <c r="O39" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P39" s="54">
         <v>1.2012</v>
@@ -4598,7 +4681,7 @@
       <c r="D40" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="75" t="s">
+      <c r="E40" s="65" t="s">
         <v>134</v>
       </c>
       <c r="F40" s="39" t="s">
@@ -4614,7 +4697,7 @@
         <v>448</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K40" s="38" t="s">
         <v>402</v>
@@ -4629,8 +4712,8 @@
       <c r="N40" s="38">
         <v>10</v>
       </c>
-      <c r="O40" s="76" t="s">
-        <v>469</v>
+      <c r="O40" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P40" s="53">
         <v>4.0399999999999998E-2</v>
@@ -4670,7 +4753,7 @@
         <v>448</v>
       </c>
       <c r="J41" s="41" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K41" s="40" t="s">
         <v>403</v>
@@ -4685,8 +4768,8 @@
       <c r="N41" s="41">
         <v>6</v>
       </c>
-      <c r="O41" s="77" t="s">
-        <v>469</v>
+      <c r="O41" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P41" s="54">
         <v>0.47249999999999998</v>
@@ -4710,7 +4793,7 @@
       <c r="D42" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="75" t="s">
+      <c r="E42" s="65" t="s">
         <v>136</v>
       </c>
       <c r="F42" s="39" t="s">
@@ -4726,7 +4809,7 @@
         <v>448</v>
       </c>
       <c r="J42" s="39" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K42" s="38" t="s">
         <v>404</v>
@@ -4741,8 +4824,8 @@
       <c r="N42" s="38">
         <v>10</v>
       </c>
-      <c r="O42" s="76" t="s">
-        <v>469</v>
+      <c r="O42" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P42" s="53">
         <v>7.9100000000000004E-2</v>
@@ -4782,7 +4865,7 @@
         <v>448</v>
       </c>
       <c r="J43" s="41" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K43" s="40" t="s">
         <v>405</v>
@@ -4797,8 +4880,8 @@
       <c r="N43" s="41">
         <v>10</v>
       </c>
-      <c r="O43" s="77" t="s">
-        <v>469</v>
+      <c r="O43" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P43" s="54">
         <v>8.5099999999999995E-2</v>
@@ -4822,23 +4905,23 @@
       <c r="D44" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="E44" s="75" t="s">
+      <c r="E44" s="65" t="s">
         <v>138</v>
       </c>
       <c r="F44" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="G44" s="79" t="s">
+      <c r="G44" s="69" t="s">
         <v>275</v>
       </c>
       <c r="H44" s="39" t="s">
         <v>346</v>
       </c>
       <c r="I44" s="38" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K44" s="38" t="s">
         <v>448</v>
@@ -4853,8 +4936,8 @@
       <c r="N44" s="38">
         <v>40</v>
       </c>
-      <c r="O44" s="76" t="s">
-        <v>469</v>
+      <c r="O44" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P44" s="53">
         <v>3.5400000000000001E-2</v>
@@ -4894,7 +4977,7 @@
         <v>448</v>
       </c>
       <c r="J45" s="41" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K45" s="40" t="s">
         <v>448</v>
@@ -4909,8 +4992,8 @@
       <c r="N45" s="41">
         <v>10</v>
       </c>
-      <c r="O45" s="77" t="s">
-        <v>469</v>
+      <c r="O45" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P45" s="54">
         <v>0.1216</v>
@@ -4934,7 +5017,7 @@
       <c r="D46" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="75" t="s">
+      <c r="E46" s="65" t="s">
         <v>140</v>
       </c>
       <c r="F46" s="39" t="s">
@@ -4950,7 +5033,7 @@
         <v>448</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K46" s="38" t="s">
         <v>448</v>
@@ -4965,8 +5048,8 @@
       <c r="N46" s="38">
         <v>6</v>
       </c>
-      <c r="O46" s="76" t="s">
-        <v>469</v>
+      <c r="O46" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P46" s="53">
         <v>0.34010000000000001</v>
@@ -5017,7 +5100,7 @@
       <c r="N47" s="41" t="s">
         <v>448</v>
       </c>
-      <c r="O47" s="77" t="s">
+      <c r="O47" s="67" t="s">
         <v>448</v>
       </c>
       <c r="P47" s="54" t="s">
@@ -5041,23 +5124,23 @@
       <c r="D48" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E48" s="75" t="s">
+      <c r="E48" s="65" t="s">
         <v>142</v>
       </c>
       <c r="F48" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="G48" s="79">
+      <c r="G48" s="69">
         <v>61300311121</v>
       </c>
       <c r="H48" s="39" t="s">
         <v>349</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K48" s="38" t="s">
         <v>448</v>
@@ -5072,8 +5155,8 @@
       <c r="N48" s="38">
         <v>50</v>
       </c>
-      <c r="O48" s="76" t="s">
-        <v>469</v>
+      <c r="O48" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P48" s="53">
         <v>1.44E-2</v>
@@ -5103,17 +5186,17 @@
       <c r="F49" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="78">
+      <c r="G49" s="68">
         <v>61300611121</v>
       </c>
       <c r="H49" s="41" t="s">
         <v>349</v>
       </c>
       <c r="I49" s="40" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J49" s="41" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K49" s="40" t="s">
         <v>448</v>
@@ -5128,8 +5211,8 @@
       <c r="N49" s="41">
         <v>40</v>
       </c>
-      <c r="O49" s="77" t="s">
-        <v>469</v>
+      <c r="O49" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P49" s="54">
         <v>2.9700000000000001E-2</v>
@@ -5153,23 +5236,23 @@
       <c r="D50" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="E50" s="75" t="s">
+      <c r="E50" s="65" t="s">
         <v>144</v>
       </c>
       <c r="F50" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="G50" s="79" t="s">
+      <c r="G50" s="69" t="s">
         <v>277</v>
       </c>
       <c r="H50" s="39" t="s">
         <v>350</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K50" s="38" t="s">
         <v>448</v>
@@ -5184,8 +5267,8 @@
       <c r="N50" s="38">
         <v>10</v>
       </c>
-      <c r="O50" s="76" t="s">
-        <v>469</v>
+      <c r="O50" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P50" s="53">
         <v>0.11509999999999999</v>
@@ -5215,17 +5298,17 @@
       <c r="F51" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="G51" s="78">
+      <c r="G51" s="68">
         <v>61300211121</v>
       </c>
       <c r="H51" s="41" t="s">
         <v>349</v>
       </c>
       <c r="I51" s="40" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J51" s="41" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K51" s="40" t="s">
         <v>448</v>
@@ -5240,8 +5323,8 @@
       <c r="N51" s="41">
         <v>50</v>
       </c>
-      <c r="O51" s="77" t="s">
-        <v>469</v>
+      <c r="O51" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P51" s="54">
         <v>1.3299999999999999E-2</v>
@@ -5265,23 +5348,23 @@
       <c r="D52" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E52" s="75" t="s">
+      <c r="E52" s="65" t="s">
         <v>146</v>
       </c>
       <c r="F52" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="G52" s="79">
+      <c r="G52" s="69">
         <v>61300411121</v>
       </c>
       <c r="H52" s="39" t="s">
         <v>349</v>
       </c>
       <c r="I52" s="38" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K52" s="38" t="s">
         <v>448</v>
@@ -5296,8 +5379,8 @@
       <c r="N52" s="38">
         <v>20</v>
       </c>
-      <c r="O52" s="76" t="s">
-        <v>469</v>
+      <c r="O52" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P52" s="53">
         <v>2.18E-2</v>
@@ -5337,7 +5420,7 @@
         <v>448</v>
       </c>
       <c r="J53" s="41" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K53" s="40" t="s">
         <v>448</v>
@@ -5352,8 +5435,8 @@
       <c r="N53" s="41">
         <v>47</v>
       </c>
-      <c r="O53" s="77" t="s">
-        <v>469</v>
+      <c r="O53" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P53" s="54">
         <v>0.31269999999999998</v>
@@ -5377,7 +5460,7 @@
       <c r="D54" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="E54" s="75" t="s">
+      <c r="E54" s="65" t="s">
         <v>148</v>
       </c>
       <c r="F54" s="39" t="s">
@@ -5393,7 +5476,7 @@
         <v>448</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K54" s="38" t="s">
         <v>448</v>
@@ -5408,8 +5491,8 @@
       <c r="N54" s="38">
         <v>10</v>
       </c>
-      <c r="O54" s="76" t="s">
-        <v>469</v>
+      <c r="O54" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P54" s="53">
         <v>7.0800000000000002E-2</v>
@@ -5448,7 +5531,9 @@
       <c r="I55" s="40" t="s">
         <v>448</v>
       </c>
-      <c r="J55" s="41"/>
+      <c r="J55" s="41" t="s">
+        <v>448</v>
+      </c>
       <c r="K55" s="40" t="s">
         <v>448</v>
       </c>
@@ -5460,13 +5545,17 @@
         <v>10</v>
       </c>
       <c r="N55" s="41">
-        <v>12</v>
-      </c>
-      <c r="O55" s="77"/>
-      <c r="P55" s="54"/>
+        <v>35</v>
+      </c>
+      <c r="O55" s="67" t="s">
+        <v>555</v>
+      </c>
+      <c r="P55" s="54">
+        <v>1.486</v>
+      </c>
       <c r="Q55" s="43">
         <f>P55*N55</f>
-        <v>0</v>
+        <v>52.01</v>
       </c>
       <c r="R55" s="41"/>
       <c r="S55" s="40"/>
@@ -5483,7 +5572,7 @@
       <c r="D56" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="E56" s="75" t="s">
+      <c r="E56" s="65" t="s">
         <v>150</v>
       </c>
       <c r="F56" s="39" t="s">
@@ -5499,7 +5588,7 @@
         <v>448</v>
       </c>
       <c r="J56" s="39" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K56" s="38" t="s">
         <v>448</v>
@@ -5514,8 +5603,8 @@
       <c r="N56" s="38">
         <v>15</v>
       </c>
-      <c r="O56" s="76" t="s">
-        <v>469</v>
+      <c r="O56" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P56" s="53">
         <v>0.1182</v>
@@ -5570,8 +5659,8 @@
       <c r="N57" s="41">
         <v>20</v>
       </c>
-      <c r="O57" s="77" t="s">
-        <v>469</v>
+      <c r="O57" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P57" s="54">
         <v>3.3500000000000002E-2</v>
@@ -5595,7 +5684,7 @@
       <c r="D58" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="E58" s="75" t="s">
+      <c r="E58" s="65" t="s">
         <v>152</v>
       </c>
       <c r="F58" s="39" t="s">
@@ -5611,7 +5700,7 @@
         <v>448</v>
       </c>
       <c r="J58" s="39" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K58" s="38" t="s">
         <v>448</v>
@@ -5626,8 +5715,8 @@
       <c r="N58" s="38">
         <v>60</v>
       </c>
-      <c r="O58" s="76" t="s">
-        <v>469</v>
+      <c r="O58" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P58" s="53">
         <v>1.9099999999999999E-2</v>
@@ -5667,7 +5756,7 @@
         <v>448</v>
       </c>
       <c r="J59" s="41" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K59" s="40" t="s">
         <v>448</v>
@@ -5682,8 +5771,8 @@
       <c r="N59" s="41">
         <v>20</v>
       </c>
-      <c r="O59" s="77" t="s">
-        <v>469</v>
+      <c r="O59" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P59" s="54">
         <v>2.0299999999999999E-2</v>
@@ -5707,7 +5796,7 @@
       <c r="D60" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E60" s="75" t="s">
+      <c r="E60" s="65" t="s">
         <v>154</v>
       </c>
       <c r="F60" s="39" t="s">
@@ -5723,7 +5812,7 @@
         <v>448</v>
       </c>
       <c r="J60" s="39" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K60" s="38" t="s">
         <v>448</v>
@@ -5738,8 +5827,8 @@
       <c r="N60" s="38">
         <v>20</v>
       </c>
-      <c r="O60" s="76" t="s">
-        <v>469</v>
+      <c r="O60" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P60" s="53">
         <v>2.9899999999999999E-2</v>
@@ -5758,7 +5847,7 @@
         <v>52</v>
       </c>
       <c r="C61" s="62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D61" s="40" t="s">
         <v>66</v>
@@ -5779,7 +5868,7 @@
         <v>448</v>
       </c>
       <c r="J61" s="41" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K61" s="40" t="s">
         <v>448</v>
@@ -5794,8 +5883,8 @@
       <c r="N61" s="41">
         <v>10</v>
       </c>
-      <c r="O61" s="77" t="s">
-        <v>469</v>
+      <c r="O61" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P61" s="54">
         <v>0.3261</v>
@@ -5814,12 +5903,12 @@
         <v>53</v>
       </c>
       <c r="C62" s="61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D62" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="E62" s="75" t="s">
+      <c r="E62" s="65" t="s">
         <v>156</v>
       </c>
       <c r="F62" s="39" t="s">
@@ -5850,8 +5939,8 @@
       <c r="N62" s="38">
         <v>10</v>
       </c>
-      <c r="O62" s="76" t="s">
-        <v>469</v>
+      <c r="O62" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P62" s="53">
         <v>4.3700000000000003E-2</v>
@@ -5891,7 +5980,7 @@
         <v>448</v>
       </c>
       <c r="J63" s="41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K63" s="40" t="s">
         <v>407</v>
@@ -5906,13 +5995,15 @@
       <c r="N63" s="41">
         <v>100</v>
       </c>
-      <c r="O63" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P63" s="54"/>
+      <c r="O63" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P63" s="54">
+        <v>2.0999999999999999E-3</v>
+      </c>
       <c r="Q63" s="43">
         <f>P63*N63</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="R63" s="41"/>
       <c r="S63" s="40"/>
@@ -5929,7 +6020,7 @@
       <c r="D64" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E64" s="75" t="s">
+      <c r="E64" s="65" t="s">
         <v>158</v>
       </c>
       <c r="F64" s="39" t="s">
@@ -5945,7 +6036,7 @@
         <v>448</v>
       </c>
       <c r="J64" s="39" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K64" s="38" t="s">
         <v>408</v>
@@ -5960,13 +6051,15 @@
       <c r="N64" s="38">
         <v>100</v>
       </c>
-      <c r="O64" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P64" s="53"/>
+      <c r="O64" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P64" s="53">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q64" s="42">
         <f t="shared" ref="Q64" si="56">P64*N64</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R64" s="39"/>
       <c r="S64" s="38"/>
@@ -5999,7 +6092,7 @@
         <v>448</v>
       </c>
       <c r="J65" s="41" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K65" s="40" t="s">
         <v>409</v>
@@ -6014,13 +6107,15 @@
       <c r="N65" s="41">
         <v>50</v>
       </c>
-      <c r="O65" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P65" s="54"/>
+      <c r="O65" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P65" s="54">
+        <v>3.8E-3</v>
+      </c>
       <c r="Q65" s="43">
         <f>P65*N65</f>
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="R65" s="41"/>
       <c r="S65" s="40"/>
@@ -6035,9 +6130,9 @@
         <v>16</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="E66" s="75" t="s">
+        <v>466</v>
+      </c>
+      <c r="E66" s="65" t="s">
         <v>160</v>
       </c>
       <c r="F66" s="39" t="s">
@@ -6049,7 +6144,9 @@
       <c r="H66" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I66" s="38"/>
+      <c r="I66" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J66" s="39" t="s">
         <v>386</v>
       </c>
@@ -6066,13 +6163,15 @@
       <c r="N66" s="38">
         <v>100</v>
       </c>
-      <c r="O66" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P66" s="53"/>
+      <c r="O66" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P66" s="53">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q66" s="42">
         <f>P66*N66</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R66" s="39"/>
       <c r="S66" s="38"/>
@@ -6101,9 +6200,11 @@
       <c r="H67" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I67" s="40"/>
+      <c r="I67" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J67" s="41" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K67" s="40" t="s">
         <v>412</v>
@@ -6118,13 +6219,15 @@
       <c r="N67" s="41">
         <v>100</v>
       </c>
-      <c r="O67" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P67" s="54"/>
+      <c r="O67" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P67" s="54">
+        <v>1.5E-3</v>
+      </c>
       <c r="Q67" s="43">
         <f t="shared" ref="Q67" si="58">P67*N67</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="R67" s="41"/>
       <c r="S67" s="40"/>
@@ -6141,7 +6244,7 @@
       <c r="D68" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="E68" s="75" t="s">
+      <c r="E68" s="65" t="s">
         <v>162</v>
       </c>
       <c r="F68" s="39" t="s">
@@ -6153,9 +6256,11 @@
       <c r="H68" s="39" t="s">
         <v>357</v>
       </c>
-      <c r="I68" s="38"/>
+      <c r="I68" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J68" s="39" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K68" s="38" t="s">
         <v>413</v>
@@ -6170,13 +6275,15 @@
       <c r="N68" s="38">
         <v>100</v>
       </c>
-      <c r="O68" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P68" s="53"/>
+      <c r="O68" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P68" s="53">
+        <v>1.6999999999999999E-3</v>
+      </c>
       <c r="Q68" s="42">
         <f>P68*N68</f>
-        <v>0</v>
+        <v>0.16999999999999998</v>
       </c>
       <c r="R68" s="39"/>
       <c r="S68" s="38"/>
@@ -6205,7 +6312,9 @@
       <c r="H69" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I69" s="40"/>
+      <c r="I69" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J69" s="41" t="s">
         <v>381</v>
       </c>
@@ -6222,8 +6331,8 @@
       <c r="N69" s="41">
         <v>200</v>
       </c>
-      <c r="O69" s="77" t="s">
-        <v>469</v>
+      <c r="O69" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P69" s="54">
         <v>1E-3</v>
@@ -6247,7 +6356,7 @@
       <c r="D70" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E70" s="75" t="s">
+      <c r="E70" s="65" t="s">
         <v>164</v>
       </c>
       <c r="F70" s="39" t="s">
@@ -6259,8 +6368,12 @@
       <c r="H70" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I70" s="38"/>
-      <c r="J70" s="39"/>
+      <c r="I70" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J70" s="39" t="s">
+        <v>541</v>
+      </c>
       <c r="K70" s="38" t="s">
         <v>414</v>
       </c>
@@ -6271,12 +6384,18 @@
         <f>L70*5</f>
         <v>5</v>
       </c>
-      <c r="N70" s="38"/>
-      <c r="O70" s="76"/>
-      <c r="P70" s="53"/>
+      <c r="N70" s="38">
+        <v>100</v>
+      </c>
+      <c r="O70" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P70" s="53">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q70" s="42">
         <f>P70*N70</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R70" s="39"/>
       <c r="S70" s="38"/>
@@ -6305,9 +6424,11 @@
       <c r="H71" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I71" s="40"/>
+      <c r="I71" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J71" s="41" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K71" s="40" t="s">
         <v>415</v>
@@ -6322,13 +6443,15 @@
       <c r="N71" s="41">
         <v>100</v>
       </c>
-      <c r="O71" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P71" s="54"/>
+      <c r="O71" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P71" s="54">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q71" s="43">
         <f t="shared" ref="Q71" si="62">P71*N71</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R71" s="41"/>
       <c r="S71" s="40"/>
@@ -6345,7 +6468,7 @@
       <c r="D72" s="38" t="s">
         <v>465</v>
       </c>
-      <c r="E72" s="75" t="s">
+      <c r="E72" s="65" t="s">
         <v>166</v>
       </c>
       <c r="F72" s="39" t="s">
@@ -6357,9 +6480,11 @@
       <c r="H72" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="I72" s="38"/>
+      <c r="I72" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J72" s="39" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K72" s="38" t="s">
         <v>416</v>
@@ -6374,13 +6499,15 @@
       <c r="N72" s="38">
         <v>100</v>
       </c>
-      <c r="O72" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P72" s="53"/>
+      <c r="O72" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P72" s="53">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q72" s="42">
         <f>P72*N72</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R72" s="39"/>
       <c r="S72" s="38"/>
@@ -6409,8 +6536,12 @@
       <c r="H73" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I73" s="40"/>
-      <c r="J73" s="41"/>
+      <c r="I73" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J73" s="41" t="s">
+        <v>542</v>
+      </c>
       <c r="K73" s="40" t="s">
         <v>417</v>
       </c>
@@ -6421,12 +6552,18 @@
         <f t="shared" ref="M73" si="63">L73*5</f>
         <v>10</v>
       </c>
-      <c r="N73" s="41"/>
-      <c r="O73" s="77"/>
-      <c r="P73" s="54"/>
+      <c r="N73" s="41">
+        <v>100</v>
+      </c>
+      <c r="O73" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P73" s="54">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q73" s="43">
         <f t="shared" ref="Q73" si="64">P73*N73</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R73" s="41"/>
       <c r="S73" s="40"/>
@@ -6443,7 +6580,7 @@
       <c r="D74" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="E74" s="75" t="s">
+      <c r="E74" s="65" t="s">
         <v>168</v>
       </c>
       <c r="F74" s="39" t="s">
@@ -6455,9 +6592,11 @@
       <c r="H74" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I74" s="38"/>
+      <c r="I74" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J74" s="39" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K74" s="38" t="s">
         <v>418</v>
@@ -6472,13 +6611,15 @@
       <c r="N74" s="38">
         <v>100</v>
       </c>
-      <c r="O74" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P74" s="53"/>
+      <c r="O74" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P74" s="53">
+        <v>1E-3</v>
+      </c>
       <c r="Q74" s="42">
         <f>P74*N74</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R74" s="39"/>
       <c r="S74" s="38"/>
@@ -6507,8 +6648,12 @@
       <c r="H75" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I75" s="40"/>
-      <c r="J75" s="41"/>
+      <c r="I75" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J75" s="41" t="s">
+        <v>543</v>
+      </c>
       <c r="K75" s="40" t="s">
         <v>420</v>
       </c>
@@ -6519,12 +6664,18 @@
         <f t="shared" ref="M75" si="65">L75*5</f>
         <v>5</v>
       </c>
-      <c r="N75" s="41"/>
-      <c r="O75" s="77"/>
-      <c r="P75" s="54"/>
+      <c r="N75" s="41">
+        <v>20</v>
+      </c>
+      <c r="O75" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P75" s="54">
+        <v>2.92E-2</v>
+      </c>
       <c r="Q75" s="43">
         <f t="shared" ref="Q75" si="66">P75*N75</f>
-        <v>0</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="R75" s="41"/>
       <c r="S75" s="40"/>
@@ -6541,7 +6692,7 @@
       <c r="D76" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="E76" s="75" t="s">
+      <c r="E76" s="65" t="s">
         <v>170</v>
       </c>
       <c r="F76" s="39" t="s">
@@ -6553,8 +6704,12 @@
       <c r="H76" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I76" s="38"/>
-      <c r="J76" s="39"/>
+      <c r="I76" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J76" s="39" t="s">
+        <v>544</v>
+      </c>
       <c r="K76" s="38" t="s">
         <v>421</v>
       </c>
@@ -6565,12 +6720,18 @@
         <f>L76*5</f>
         <v>5</v>
       </c>
-      <c r="N76" s="38"/>
-      <c r="O76" s="76"/>
-      <c r="P76" s="53"/>
+      <c r="N76" s="38">
+        <v>20</v>
+      </c>
+      <c r="O76" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P76" s="53">
+        <v>0.03</v>
+      </c>
       <c r="Q76" s="42">
         <f>P76*N76</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R76" s="39"/>
       <c r="S76" s="38"/>
@@ -6599,9 +6760,11 @@
       <c r="H77" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I77" s="40"/>
+      <c r="I77" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J77" s="41" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K77" s="40" t="s">
         <v>422</v>
@@ -6616,13 +6779,15 @@
       <c r="N77" s="41">
         <v>100</v>
       </c>
-      <c r="O77" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P77" s="54"/>
+      <c r="O77" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P77" s="54">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q77" s="43">
         <f t="shared" ref="Q77" si="68">P77*N77</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R77" s="41"/>
       <c r="S77" s="40"/>
@@ -6639,7 +6804,7 @@
       <c r="D78" s="38" t="s">
         <v>461</v>
       </c>
-      <c r="E78" s="75" t="s">
+      <c r="E78" s="65" t="s">
         <v>172</v>
       </c>
       <c r="F78" s="39" t="s">
@@ -6651,9 +6816,11 @@
       <c r="H78" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I78" s="38"/>
+      <c r="I78" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J78" s="39" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K78" s="38" t="s">
         <v>419</v>
@@ -6668,13 +6835,15 @@
       <c r="N78" s="38">
         <v>200</v>
       </c>
-      <c r="O78" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P78" s="53"/>
+      <c r="O78" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P78" s="53">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q78" s="42">
         <f>P78*N78</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="R78" s="39"/>
       <c r="S78" s="38"/>
@@ -6703,7 +6872,9 @@
       <c r="H79" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I79" s="40"/>
+      <c r="I79" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J79" s="41" t="s">
         <v>382</v>
       </c>
@@ -6717,12 +6888,18 @@
         <f t="shared" ref="M79" si="69">L79*5</f>
         <v>5</v>
       </c>
-      <c r="N79" s="41"/>
-      <c r="O79" s="77"/>
-      <c r="P79" s="54"/>
+      <c r="N79" s="41">
+        <v>100</v>
+      </c>
+      <c r="O79" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P79" s="54">
+        <v>2.2000000000000001E-3</v>
+      </c>
       <c r="Q79" s="43">
         <f t="shared" ref="Q79" si="70">P79*N79</f>
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="R79" s="41"/>
       <c r="S79" s="40"/>
@@ -6739,7 +6916,7 @@
       <c r="D80" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E80" s="75" t="s">
+      <c r="E80" s="65" t="s">
         <v>174</v>
       </c>
       <c r="F80" s="39" t="s">
@@ -6751,7 +6928,9 @@
       <c r="H80" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I80" s="38"/>
+      <c r="I80" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J80" s="39" t="s">
         <v>383</v>
       </c>
@@ -6765,12 +6944,18 @@
         <f>L80*5</f>
         <v>5</v>
       </c>
-      <c r="N80" s="38"/>
-      <c r="O80" s="76"/>
-      <c r="P80" s="53"/>
+      <c r="N80" s="38">
+        <v>50</v>
+      </c>
+      <c r="O80" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P80" s="53">
+        <v>1.6899999999999998E-2</v>
+      </c>
       <c r="Q80" s="42">
         <f>P80*N80</f>
-        <v>0</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="R80" s="39"/>
       <c r="S80" s="38"/>
@@ -6799,7 +6984,9 @@
       <c r="H81" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I81" s="40"/>
+      <c r="I81" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J81" s="41" t="s">
         <v>384</v>
       </c>
@@ -6813,12 +7000,18 @@
         <f t="shared" ref="M81" si="71">L81*5</f>
         <v>5</v>
       </c>
-      <c r="N81" s="41"/>
-      <c r="O81" s="77"/>
-      <c r="P81" s="54"/>
+      <c r="N81" s="41">
+        <v>100</v>
+      </c>
+      <c r="O81" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P81" s="54">
+        <v>1.2999999999999999E-3</v>
+      </c>
       <c r="Q81" s="43">
         <f t="shared" ref="Q81" si="72">P81*N81</f>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="R81" s="41"/>
       <c r="S81" s="40"/>
@@ -6835,7 +7028,7 @@
       <c r="D82" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="E82" s="75" t="s">
+      <c r="E82" s="65" t="s">
         <v>176</v>
       </c>
       <c r="F82" s="39" t="s">
@@ -6847,8 +7040,12 @@
       <c r="H82" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I82" s="38"/>
-      <c r="J82" s="39"/>
+      <c r="I82" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J82" s="39" t="s">
+        <v>550</v>
+      </c>
       <c r="K82" s="38" t="s">
         <v>425</v>
       </c>
@@ -6859,12 +7056,18 @@
         <f>L82*5</f>
         <v>10</v>
       </c>
-      <c r="N82" s="38"/>
-      <c r="O82" s="76"/>
-      <c r="P82" s="53"/>
+      <c r="N82" s="38">
+        <v>100</v>
+      </c>
+      <c r="O82" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P82" s="53">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q82" s="42">
         <f>P82*N82</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R82" s="39"/>
       <c r="S82" s="38"/>
@@ -6887,17 +7090,17 @@
       <c r="F83" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="G83" s="40" t="s">
+      <c r="G83" s="68" t="s">
         <v>306</v>
       </c>
       <c r="H83" s="41" t="s">
         <v>324</v>
       </c>
       <c r="I83" s="40" t="s">
-        <v>448</v>
+        <v>552</v>
       </c>
       <c r="J83" s="41" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="K83" s="40" t="s">
         <v>423</v>
@@ -6912,13 +7115,15 @@
       <c r="N83" s="41">
         <v>100</v>
       </c>
-      <c r="O83" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P83" s="54"/>
+      <c r="O83" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P83" s="54">
+        <v>2E-3</v>
+      </c>
       <c r="Q83" s="43">
         <f t="shared" ref="Q83" si="74">P83*N83</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R83" s="41"/>
       <c r="S83" s="40"/>
@@ -6929,12 +7134,14 @@
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
-      <c r="C84" s="61"/>
+      <c r="C84" s="61" t="s">
+        <v>16</v>
+      </c>
       <c r="D84" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="E84" s="75" t="s">
-        <v>466</v>
+      <c r="E84" s="65" t="s">
+        <v>553</v>
       </c>
       <c r="F84" s="39" t="s">
         <v>234</v>
@@ -6945,8 +7152,12 @@
       <c r="H84" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I84" s="38"/>
-      <c r="J84" s="39"/>
+      <c r="I84" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J84" s="39" t="s">
+        <v>554</v>
+      </c>
       <c r="K84" s="38" t="s">
         <v>426</v>
       </c>
@@ -6957,12 +7168,18 @@
         <f>L84*5</f>
         <v>10</v>
       </c>
-      <c r="N84" s="38"/>
-      <c r="O84" s="76"/>
-      <c r="P84" s="53"/>
+      <c r="N84" s="38">
+        <v>100</v>
+      </c>
+      <c r="O84" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P84" s="53">
+        <v>1.2999999999999999E-3</v>
+      </c>
       <c r="Q84" s="42">
         <f>P84*N84</f>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="R84" s="39"/>
       <c r="S84" s="38"/>
@@ -6973,7 +7190,9 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="62"/>
+      <c r="C85" s="62" t="s">
+        <v>16</v>
+      </c>
       <c r="D85" s="40" t="s">
         <v>83</v>
       </c>
@@ -6989,7 +7208,9 @@
       <c r="H85" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I85" s="40"/>
+      <c r="I85" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J85" s="41" t="s">
         <v>385</v>
       </c>
@@ -7003,12 +7224,18 @@
         <f t="shared" ref="M85" si="75">L85*5</f>
         <v>10</v>
       </c>
-      <c r="N85" s="41"/>
-      <c r="O85" s="77"/>
-      <c r="P85" s="54"/>
+      <c r="N85" s="41">
+        <v>100</v>
+      </c>
+      <c r="O85" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P85" s="54">
+        <v>1.1000000000000001E-3</v>
+      </c>
       <c r="Q85" s="43">
         <f t="shared" ref="Q85" si="76">P85*N85</f>
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="R85" s="41"/>
       <c r="S85" s="40"/>
@@ -7019,18 +7246,20 @@
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="61"/>
+      <c r="C86" s="61" t="s">
+        <v>16</v>
+      </c>
       <c r="D86" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="E86" s="75" t="s">
+      <c r="E86" s="65" t="s">
         <v>179</v>
       </c>
       <c r="F86" s="39" t="s">
         <v>238</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H86" s="39" t="s">
         <v>359</v>
@@ -7039,7 +7268,7 @@
         <v>448</v>
       </c>
       <c r="J86" s="39" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K86" s="38" t="s">
         <v>428</v>
@@ -7054,8 +7283,8 @@
       <c r="N86" s="38">
         <v>50</v>
       </c>
-      <c r="O86" s="76" t="s">
-        <v>469</v>
+      <c r="O86" s="66" t="s">
+        <v>468</v>
       </c>
       <c r="P86" s="53">
         <v>0.01</v>
@@ -7073,12 +7302,14 @@
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="62"/>
+      <c r="C87" s="62" t="s">
+        <v>16</v>
+      </c>
       <c r="D87" s="40" t="s">
         <v>85</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F87" s="41" t="s">
         <v>234</v>
@@ -7093,7 +7324,7 @@
         <v>448</v>
       </c>
       <c r="J87" s="41" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K87" s="40" t="s">
         <v>429</v>
@@ -7108,8 +7339,8 @@
       <c r="N87" s="41">
         <v>100</v>
       </c>
-      <c r="O87" s="77" t="s">
-        <v>469</v>
+      <c r="O87" s="67" t="s">
+        <v>468</v>
       </c>
       <c r="P87" s="54">
         <v>1.1999999999999999E-3</v>
@@ -7127,11 +7358,13 @@
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="61"/>
+      <c r="C88" s="61" t="s">
+        <v>16</v>
+      </c>
       <c r="D88" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E88" s="75" t="s">
+      <c r="E88" s="65" t="s">
         <v>180</v>
       </c>
       <c r="F88" s="39" t="s">
@@ -7143,8 +7376,12 @@
       <c r="H88" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I88" s="38"/>
-      <c r="J88" s="39"/>
+      <c r="I88" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="J88" s="39" t="s">
+        <v>545</v>
+      </c>
       <c r="K88" s="38" t="s">
         <v>430</v>
       </c>
@@ -7155,12 +7392,18 @@
         <f>L88*5</f>
         <v>5</v>
       </c>
-      <c r="N88" s="38"/>
-      <c r="O88" s="76"/>
-      <c r="P88" s="53"/>
+      <c r="N88" s="38">
+        <v>50</v>
+      </c>
+      <c r="O88" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P88" s="53">
+        <v>8.8000000000000005E-3</v>
+      </c>
       <c r="Q88" s="42">
         <f>P88*N88</f>
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="R88" s="39"/>
       <c r="S88" s="38"/>
@@ -7171,7 +7414,9 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C89" s="62"/>
+      <c r="C89" s="62" t="s">
+        <v>16</v>
+      </c>
       <c r="D89" s="40" t="s">
         <v>87</v>
       </c>
@@ -7187,8 +7432,12 @@
       <c r="H89" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="I89" s="40"/>
-      <c r="J89" s="41"/>
+      <c r="I89" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J89" s="41" t="s">
+        <v>546</v>
+      </c>
       <c r="K89" s="40" t="s">
         <v>431</v>
       </c>
@@ -7199,12 +7448,18 @@
         <f t="shared" ref="M89" si="79">L89*5</f>
         <v>5</v>
       </c>
-      <c r="N89" s="41"/>
-      <c r="O89" s="77"/>
-      <c r="P89" s="54"/>
+      <c r="N89" s="41">
+        <v>20</v>
+      </c>
+      <c r="O89" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P89" s="54">
+        <v>2.7900000000000001E-2</v>
+      </c>
       <c r="Q89" s="43">
         <f t="shared" ref="Q89" si="80">P89*N89</f>
-        <v>0</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="R89" s="41"/>
       <c r="S89" s="40"/>
@@ -7215,11 +7470,13 @@
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="C90" s="61"/>
+      <c r="C90" s="61" t="s">
+        <v>16</v>
+      </c>
       <c r="D90" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="E90" s="75" t="s">
+      <c r="E90" s="65" t="s">
         <v>182</v>
       </c>
       <c r="F90" s="39" t="s">
@@ -7231,7 +7488,9 @@
       <c r="H90" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I90" s="38"/>
+      <c r="I90" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J90" s="39" t="s">
         <v>387</v>
       </c>
@@ -7245,12 +7504,18 @@
         <f t="shared" ref="M90" si="81">L90*5</f>
         <v>5</v>
       </c>
-      <c r="N90" s="38"/>
-      <c r="O90" s="76"/>
-      <c r="P90" s="53"/>
+      <c r="N90" s="38">
+        <v>100</v>
+      </c>
+      <c r="O90" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P90" s="53">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q90" s="42">
         <f t="shared" ref="Q90" si="82">P90*N90</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R90" s="39"/>
       <c r="S90" s="38"/>
@@ -7261,7 +7526,9 @@
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C91" s="62"/>
+      <c r="C91" s="62" t="s">
+        <v>239</v>
+      </c>
       <c r="D91" s="40" t="s">
         <v>89</v>
       </c>
@@ -7280,7 +7547,9 @@
       <c r="I91" s="40" t="s">
         <v>448</v>
       </c>
-      <c r="J91" s="41"/>
+      <c r="J91" s="41" t="s">
+        <v>448</v>
+      </c>
       <c r="K91" s="40" t="s">
         <v>448</v>
       </c>
@@ -7291,12 +7560,17 @@
         <f t="shared" ref="M91" si="83">L91*5</f>
         <v>210</v>
       </c>
-      <c r="N91" s="41"/>
-      <c r="O91" s="77"/>
-      <c r="P91" s="54"/>
-      <c r="Q91" s="43">
-        <f t="shared" ref="Q91" si="84">P91*N91</f>
-        <v>0</v>
+      <c r="N91" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="O91" s="67" t="s">
+        <v>448</v>
+      </c>
+      <c r="P91" s="54" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q91" s="43" t="s">
+        <v>448</v>
       </c>
       <c r="R91" s="41"/>
       <c r="S91" s="40"/>
@@ -7307,11 +7581,13 @@
         <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
-      <c r="C92" s="61"/>
+      <c r="C92" s="61" t="s">
+        <v>547</v>
+      </c>
       <c r="D92" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="E92" s="75" t="s">
+      <c r="E92" s="65" t="s">
         <v>184</v>
       </c>
       <c r="F92" s="39" t="s">
@@ -7323,9 +7599,11 @@
       <c r="H92" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="I92" s="38"/>
+      <c r="I92" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J92" s="39" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K92" s="38" t="s">
         <v>448</v>
@@ -7340,24 +7618,28 @@
       <c r="N92" s="38">
         <v>37</v>
       </c>
-      <c r="O92" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P92" s="53"/>
+      <c r="O92" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P92" s="53">
+        <v>0.6905</v>
+      </c>
       <c r="Q92" s="42">
         <f>P92*N92</f>
-        <v>0</v>
+        <v>25.548500000000001</v>
       </c>
       <c r="R92" s="39"/>
       <c r="S92" s="38"/>
     </row>
-    <row r="93" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="52">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="C93" s="62"/>
+      <c r="C93" s="70" t="s">
+        <v>548</v>
+      </c>
       <c r="D93" s="40" t="s">
         <v>91</v>
       </c>
@@ -7384,19 +7666,21 @@
         <v>2</v>
       </c>
       <c r="M93" s="40">
-        <f t="shared" ref="M93" si="85">L93*5</f>
+        <f t="shared" ref="M93" si="84">L93*5</f>
         <v>10</v>
       </c>
       <c r="N93" s="41">
         <v>12</v>
       </c>
-      <c r="O93" s="77" t="s">
-        <v>437</v>
-      </c>
-      <c r="P93" s="54"/>
+      <c r="O93" s="67" t="s">
+        <v>555</v>
+      </c>
+      <c r="P93" s="54">
+        <v>8.8239999999999998</v>
+      </c>
       <c r="Q93" s="43">
-        <f t="shared" ref="Q93" si="86">P93*N93</f>
-        <v>0</v>
+        <f t="shared" ref="Q93" si="85">P93*N93</f>
+        <v>105.88800000000001</v>
       </c>
       <c r="R93" s="41"/>
       <c r="S93" s="40"/>
@@ -7407,11 +7691,13 @@
         <f>ROW(B94) - ROW($B$9)</f>
         <v>85</v>
       </c>
-      <c r="C94" s="61"/>
+      <c r="C94" s="71" t="s">
+        <v>548</v>
+      </c>
       <c r="D94" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="E94" s="75" t="s">
+      <c r="E94" s="65" t="s">
         <v>186</v>
       </c>
       <c r="F94" s="39" t="s">
@@ -7423,9 +7709,11 @@
       <c r="H94" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="I94" s="38"/>
+      <c r="I94" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J94" s="39" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K94" s="38" t="s">
         <v>448</v>
@@ -7440,13 +7728,15 @@
       <c r="N94" s="38">
         <v>6</v>
       </c>
-      <c r="O94" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P94" s="53"/>
+      <c r="O94" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P94" s="53">
+        <v>0.39779999999999999</v>
+      </c>
       <c r="Q94" s="42">
         <f>P94*N94</f>
-        <v>0</v>
+        <v>2.3868</v>
       </c>
       <c r="R94" s="39"/>
       <c r="S94" s="38"/>
@@ -7457,7 +7747,9 @@
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="C95" s="62"/>
+      <c r="C95" s="70" t="s">
+        <v>548</v>
+      </c>
       <c r="D95" s="40" t="s">
         <v>93</v>
       </c>
@@ -7473,9 +7765,11 @@
       <c r="H95" s="41" t="s">
         <v>362</v>
       </c>
-      <c r="I95" s="40"/>
+      <c r="I95" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J95" s="41" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K95" s="40" t="s">
         <v>448</v>
@@ -7484,19 +7778,21 @@
         <v>1</v>
       </c>
       <c r="M95" s="40">
-        <f t="shared" ref="M95" si="87">L95*5</f>
+        <f t="shared" ref="M95" si="86">L95*5</f>
         <v>5</v>
       </c>
       <c r="N95" s="41">
         <v>6</v>
       </c>
-      <c r="O95" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P95" s="54"/>
+      <c r="O95" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P95" s="54">
+        <v>1.0309999999999999</v>
+      </c>
       <c r="Q95" s="43">
-        <f t="shared" ref="Q95" si="88">P95*N95</f>
-        <v>0</v>
+        <f t="shared" ref="Q95" si="87">P95*N95</f>
+        <v>6.1859999999999999</v>
       </c>
       <c r="R95" s="41"/>
       <c r="S95" s="40"/>
@@ -7507,11 +7803,13 @@
         <f>ROW(B96) - ROW($B$9)</f>
         <v>87</v>
       </c>
-      <c r="C96" s="61"/>
+      <c r="C96" s="71" t="s">
+        <v>548</v>
+      </c>
       <c r="D96" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="E96" s="75" t="s">
+      <c r="E96" s="65" t="s">
         <v>188</v>
       </c>
       <c r="F96" s="39" t="s">
@@ -7523,9 +7821,11 @@
       <c r="H96" s="39" t="s">
         <v>363</v>
       </c>
-      <c r="I96" s="38"/>
+      <c r="I96" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J96" s="39" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K96" s="38" t="s">
         <v>448</v>
@@ -7540,24 +7840,28 @@
       <c r="N96" s="38">
         <v>6</v>
       </c>
-      <c r="O96" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P96" s="53"/>
+      <c r="O96" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P96" s="53">
+        <v>7.3596000000000004</v>
+      </c>
       <c r="Q96" s="42">
         <f>P96*N96</f>
-        <v>0</v>
+        <v>44.157600000000002</v>
       </c>
       <c r="R96" s="39"/>
       <c r="S96" s="38"/>
     </row>
-    <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="52">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C97" s="62"/>
+      <c r="C97" s="70" t="s">
+        <v>548</v>
+      </c>
       <c r="D97" s="40" t="s">
         <v>95</v>
       </c>
@@ -7573,7 +7877,9 @@
       <c r="H97" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="I97" s="40"/>
+      <c r="I97" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J97" s="41" t="s">
         <v>448</v>
       </c>
@@ -7584,34 +7890,38 @@
         <v>1</v>
       </c>
       <c r="M97" s="40">
-        <f t="shared" ref="M97" si="89">L97*5</f>
+        <f t="shared" ref="M97" si="88">L97*5</f>
         <v>5</v>
       </c>
       <c r="N97" s="41">
-        <v>6</v>
-      </c>
-      <c r="O97" s="77" t="s">
-        <v>437</v>
-      </c>
-      <c r="P97" s="54"/>
+        <v>8</v>
+      </c>
+      <c r="O97" s="67" t="s">
+        <v>555</v>
+      </c>
+      <c r="P97" s="54">
+        <v>6.944</v>
+      </c>
       <c r="Q97" s="43">
-        <f t="shared" ref="Q97" si="90">P97*N97</f>
-        <v>0</v>
+        <f t="shared" ref="Q97" si="89">P97*N97</f>
+        <v>55.552</v>
       </c>
       <c r="R97" s="41"/>
       <c r="S97" s="40"/>
     </row>
-    <row r="98" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="51">
         <f>ROW(B98) - ROW($B$9)</f>
         <v>89</v>
       </c>
-      <c r="C98" s="61"/>
+      <c r="C98" s="71" t="s">
+        <v>548</v>
+      </c>
       <c r="D98" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="E98" s="75" t="s">
+      <c r="E98" s="65" t="s">
         <v>190</v>
       </c>
       <c r="F98" s="39" t="s">
@@ -7623,7 +7933,9 @@
       <c r="H98" s="39" t="s">
         <v>364</v>
       </c>
-      <c r="I98" s="38"/>
+      <c r="I98" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J98" s="39" t="s">
         <v>448</v>
       </c>
@@ -7638,15 +7950,17 @@
         <v>5</v>
       </c>
       <c r="N98" s="38">
-        <v>6</v>
-      </c>
-      <c r="O98" s="76" t="s">
-        <v>437</v>
-      </c>
-      <c r="P98" s="53"/>
+        <v>7</v>
+      </c>
+      <c r="O98" s="66" t="s">
+        <v>555</v>
+      </c>
+      <c r="P98" s="53">
+        <v>8.2669999999999995</v>
+      </c>
       <c r="Q98" s="42">
         <f>P98*N98</f>
-        <v>0</v>
+        <v>57.869</v>
       </c>
       <c r="R98" s="39"/>
       <c r="S98" s="38"/>
@@ -7657,7 +7971,9 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C99" s="62"/>
+      <c r="C99" s="70" t="s">
+        <v>548</v>
+      </c>
       <c r="D99" s="40" t="s">
         <v>97</v>
       </c>
@@ -7673,9 +7989,11 @@
       <c r="H99" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="I99" s="40"/>
+      <c r="I99" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J99" s="41" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K99" s="40" t="s">
         <v>448</v>
@@ -7684,19 +8002,21 @@
         <v>4</v>
       </c>
       <c r="M99" s="40">
-        <f t="shared" ref="M99" si="91">L99*5</f>
+        <f t="shared" ref="M99" si="90">L99*5</f>
         <v>20</v>
       </c>
       <c r="N99" s="41">
-        <v>22</v>
-      </c>
-      <c r="O99" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P99" s="54"/>
+        <v>25</v>
+      </c>
+      <c r="O99" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P99" s="54">
+        <v>0.41510000000000002</v>
+      </c>
       <c r="Q99" s="43">
-        <f t="shared" ref="Q99" si="92">P99*N99</f>
-        <v>0</v>
+        <f t="shared" ref="Q99" si="91">P99*N99</f>
+        <v>10.377500000000001</v>
       </c>
       <c r="R99" s="41"/>
       <c r="S99" s="40"/>
@@ -7707,11 +8027,13 @@
         <f>ROW(B100) - ROW($B$9)</f>
         <v>91</v>
       </c>
-      <c r="C100" s="61"/>
+      <c r="C100" s="71" t="s">
+        <v>548</v>
+      </c>
       <c r="D100" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="E100" s="75" t="s">
+      <c r="E100" s="65" t="s">
         <v>192</v>
       </c>
       <c r="F100" s="39" t="s">
@@ -7723,9 +8045,11 @@
       <c r="H100" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="I100" s="38"/>
+      <c r="I100" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J100" s="39" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K100" s="38" t="s">
         <v>448</v>
@@ -7738,26 +8062,30 @@
         <v>15</v>
       </c>
       <c r="N100" s="38">
-        <v>17</v>
-      </c>
-      <c r="O100" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P100" s="53"/>
+        <v>20</v>
+      </c>
+      <c r="O100" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P100" s="53">
+        <v>0.24310000000000001</v>
+      </c>
       <c r="Q100" s="42">
         <f>P100*N100</f>
-        <v>0</v>
+        <v>4.8620000000000001</v>
       </c>
       <c r="R100" s="39"/>
       <c r="S100" s="38"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101" s="1"/>
+    <row r="101" spans="1:19" s="83" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A101" s="82"/>
       <c r="B101" s="52">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="C101" s="62"/>
+      <c r="C101" s="70" t="s">
+        <v>548</v>
+      </c>
       <c r="D101" s="40" t="s">
         <v>99</v>
       </c>
@@ -7773,9 +8101,11 @@
       <c r="H101" s="41" t="s">
         <v>362</v>
       </c>
-      <c r="I101" s="40"/>
+      <c r="I101" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J101" s="41" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K101" s="40" t="s">
         <v>448</v>
@@ -7784,21 +8114,25 @@
         <v>1</v>
       </c>
       <c r="M101" s="40">
-        <f t="shared" ref="M101" si="93">L101*5</f>
+        <f t="shared" ref="M101" si="92">L101*5</f>
         <v>5</v>
       </c>
       <c r="N101" s="41">
-        <v>6</v>
-      </c>
-      <c r="O101" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P101" s="54"/>
+        <v>11</v>
+      </c>
+      <c r="O101" s="67" t="s">
+        <v>555</v>
+      </c>
+      <c r="P101" s="54">
+        <v>4.7060000000000004</v>
+      </c>
       <c r="Q101" s="43">
-        <f t="shared" ref="Q101" si="94">P101*N101</f>
-        <v>0</v>
-      </c>
-      <c r="R101" s="41"/>
+        <f t="shared" ref="Q101" si="93">P101*N101</f>
+        <v>51.766000000000005</v>
+      </c>
+      <c r="R101" s="85" t="s">
+        <v>557</v>
+      </c>
       <c r="S101" s="40"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
@@ -7807,11 +8141,13 @@
         <f>ROW(B102) - ROW($B$9)</f>
         <v>93</v>
       </c>
-      <c r="C102" s="61"/>
+      <c r="C102" s="71" t="s">
+        <v>548</v>
+      </c>
       <c r="D102" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="E102" s="75" t="s">
+      <c r="E102" s="65" t="s">
         <v>194</v>
       </c>
       <c r="F102" s="39" t="s">
@@ -7823,9 +8159,11 @@
       <c r="H102" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="I102" s="38"/>
+      <c r="I102" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J102" s="39" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K102" s="38" t="s">
         <v>448</v>
@@ -7840,15 +8178,19 @@
       <c r="N102" s="38">
         <v>6</v>
       </c>
-      <c r="O102" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P102" s="53"/>
+      <c r="O102" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P102" s="53">
+        <v>4.0076000000000001</v>
+      </c>
       <c r="Q102" s="42">
         <f>P102*N102</f>
-        <v>0</v>
-      </c>
-      <c r="R102" s="39"/>
+        <v>24.0456</v>
+      </c>
+      <c r="R102" s="84" t="s">
+        <v>556</v>
+      </c>
       <c r="S102" s="38"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
@@ -7857,7 +8199,9 @@
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="C103" s="62"/>
+      <c r="C103" s="70" t="s">
+        <v>548</v>
+      </c>
       <c r="D103" s="40" t="s">
         <v>101</v>
       </c>
@@ -7873,9 +8217,11 @@
       <c r="H103" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="I103" s="40"/>
+      <c r="I103" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J103" s="41" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K103" s="40" t="s">
         <v>448</v>
@@ -7884,19 +8230,21 @@
         <v>1</v>
       </c>
       <c r="M103" s="40">
-        <f t="shared" ref="M103" si="95">L103*5</f>
+        <f t="shared" ref="M103" si="94">L103*5</f>
         <v>5</v>
       </c>
       <c r="N103" s="41">
         <v>6</v>
       </c>
-      <c r="O103" s="77" t="s">
-        <v>469</v>
-      </c>
-      <c r="P103" s="54"/>
+      <c r="O103" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P103" s="54">
+        <v>0.996</v>
+      </c>
       <c r="Q103" s="43">
-        <f t="shared" ref="Q103" si="96">P103*N103</f>
-        <v>0</v>
+        <f t="shared" ref="Q103" si="95">P103*N103</f>
+        <v>5.976</v>
       </c>
       <c r="R103" s="41"/>
       <c r="S103" s="40"/>
@@ -7907,11 +8255,13 @@
         <f>ROW(B104) - ROW($B$9)</f>
         <v>95</v>
       </c>
-      <c r="C104" s="61"/>
+      <c r="C104" s="71" t="s">
+        <v>549</v>
+      </c>
       <c r="D104" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="E104" s="75" t="s">
+      <c r="E104" s="65" t="s">
         <v>196</v>
       </c>
       <c r="F104" s="39" t="s">
@@ -7923,9 +8273,11 @@
       <c r="H104" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="I104" s="38"/>
+      <c r="I104" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J104" s="39" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K104" s="38" t="s">
         <v>432</v>
@@ -7940,13 +8292,15 @@
       <c r="N104" s="38">
         <v>6</v>
       </c>
-      <c r="O104" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P104" s="53"/>
+      <c r="O104" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P104" s="53">
+        <v>0.19889999999999999</v>
+      </c>
       <c r="Q104" s="42">
         <f>P104*N104</f>
-        <v>0</v>
+        <v>1.1934</v>
       </c>
       <c r="R104" s="39"/>
       <c r="S104" s="38"/>
@@ -7957,7 +8311,9 @@
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="C105" s="62"/>
+      <c r="C105" s="70" t="s">
+        <v>549</v>
+      </c>
       <c r="D105" s="40" t="s">
         <v>103</v>
       </c>
@@ -7973,7 +8329,9 @@
       <c r="H105" s="41" t="s">
         <v>369</v>
       </c>
-      <c r="I105" s="40"/>
+      <c r="I105" s="40" t="s">
+        <v>448</v>
+      </c>
       <c r="J105" s="41" t="s">
         <v>388</v>
       </c>
@@ -7984,15 +8342,21 @@
         <v>1</v>
       </c>
       <c r="M105" s="40">
-        <f t="shared" ref="M105" si="97">L105*5</f>
+        <f t="shared" ref="M105" si="96">L105*5</f>
         <v>5</v>
       </c>
-      <c r="N105" s="41"/>
-      <c r="O105" s="77"/>
-      <c r="P105" s="54"/>
+      <c r="N105" s="41">
+        <v>10</v>
+      </c>
+      <c r="O105" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P105" s="54">
+        <v>9.9900000000000003E-2</v>
+      </c>
       <c r="Q105" s="43">
-        <f t="shared" ref="Q105" si="98">P105*N105</f>
-        <v>0</v>
+        <f t="shared" ref="Q105" si="97">P105*N105</f>
+        <v>0.999</v>
       </c>
       <c r="R105" s="41"/>
       <c r="S105" s="40"/>
@@ -8003,11 +8367,13 @@
         <f>ROW(B106) - ROW($B$9)</f>
         <v>97</v>
       </c>
-      <c r="C106" s="61"/>
+      <c r="C106" s="71" t="s">
+        <v>549</v>
+      </c>
       <c r="D106" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="E106" s="75" t="s">
+      <c r="E106" s="65" t="s">
         <v>198</v>
       </c>
       <c r="F106" s="39" t="s">
@@ -8019,9 +8385,11 @@
       <c r="H106" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="I106" s="38"/>
+      <c r="I106" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="J106" s="39" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K106" s="38" t="s">
         <v>434</v>
@@ -8034,15 +8402,17 @@
         <v>5</v>
       </c>
       <c r="N106" s="38">
-        <v>6</v>
-      </c>
-      <c r="O106" s="76" t="s">
-        <v>469</v>
-      </c>
-      <c r="P106" s="53"/>
+        <v>10</v>
+      </c>
+      <c r="O106" s="66" t="s">
+        <v>468</v>
+      </c>
+      <c r="P106" s="53">
+        <v>0.2218</v>
+      </c>
       <c r="Q106" s="42">
         <f>P106*N106</f>
-        <v>0</v>
+        <v>2.218</v>
       </c>
       <c r="R106" s="39"/>
       <c r="S106" s="38"/>
@@ -8061,17 +8431,17 @@
       <c r="K107" s="50"/>
       <c r="L107" s="50"/>
       <c r="M107" s="50"/>
-      <c r="N107" s="73" t="s">
+      <c r="N107" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="O107" s="74"/>
-      <c r="P107" s="74"/>
-      <c r="Q107" s="55" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R107" s="69"/>
-      <c r="S107" s="70"/>
+      <c r="O107" s="81"/>
+      <c r="P107" s="81"/>
+      <c r="Q107" s="55">
+        <f>SUM(Q10:Q106)</f>
+        <v>568.8522999999999</v>
+      </c>
+      <c r="R107" s="76"/>
+      <c r="S107" s="77"/>
     </row>
     <row r="108" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
@@ -8087,17 +8457,17 @@
       <c r="K108" s="10"/>
       <c r="L108" s="10"/>
       <c r="M108" s="10"/>
-      <c r="N108" s="73" t="s">
+      <c r="N108" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="O108" s="74"/>
-      <c r="P108" s="74"/>
-      <c r="Q108" s="56" t="e">
+      <c r="O108" s="81"/>
+      <c r="P108" s="81"/>
+      <c r="Q108" s="56">
         <f>Q107/5</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R108" s="71"/>
-      <c r="S108" s="72"/>
+        <v>113.77045999999999</v>
+      </c>
+      <c r="R108" s="78"/>
+      <c r="S108" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8168,24 +8538,41 @@
     <hyperlink ref="O74" r:id="rId58" xr:uid="{A92CD093-DFA7-4679-A7ED-780AA6E86E78}"/>
     <hyperlink ref="O77" r:id="rId59" xr:uid="{DC34F4D1-1945-4AD0-85C8-A32483EC1576}"/>
     <hyperlink ref="O78" r:id="rId60" xr:uid="{AC50B9CD-4B66-49C1-B9A4-755E6A3B7388}"/>
-    <hyperlink ref="O83" r:id="rId61" xr:uid="{9A3E4456-1E48-41E1-A10B-83098555007B}"/>
-    <hyperlink ref="O86" r:id="rId62" xr:uid="{3149E9C4-8DCD-4B7B-AA56-C24793E1FDDD}"/>
-    <hyperlink ref="O87" r:id="rId63" xr:uid="{216F92A5-F104-4692-B17C-6227E8D25A0E}"/>
-    <hyperlink ref="O92" r:id="rId64" xr:uid="{BB0086C3-2D05-4979-8CF3-0132D37DF1DB}"/>
-    <hyperlink ref="O95" r:id="rId65" xr:uid="{571AFD85-72FA-4D23-A240-55270E118838}"/>
-    <hyperlink ref="O96" r:id="rId66" xr:uid="{DB794ED7-FAF2-40D3-BCC4-3D87E9946E04}"/>
-    <hyperlink ref="O100" r:id="rId67" xr:uid="{7F416119-DC76-4A27-8048-AE23EAF496C5}"/>
-    <hyperlink ref="O101" r:id="rId68" xr:uid="{D5517901-37E6-434A-B7DB-9D7ACA270724}"/>
-    <hyperlink ref="O102" r:id="rId69" xr:uid="{1D68F898-6AEA-42FA-94E2-9C9E1498344C}"/>
-    <hyperlink ref="O103" r:id="rId70" xr:uid="{C29175A2-1765-4C45-AC14-06BB76E02B1B}"/>
-    <hyperlink ref="O94" r:id="rId71" xr:uid="{8E588422-7B11-4B05-B296-3911285F17BA}"/>
-    <hyperlink ref="O99" r:id="rId72" xr:uid="{91FF6E37-C9BD-4631-8DF9-4A150C39A80E}"/>
-    <hyperlink ref="O93" r:id="rId73" display="Aliexpress" xr:uid="{101CFFE8-7AA0-460F-85AD-620F85A3941B}"/>
-    <hyperlink ref="O104" r:id="rId74" xr:uid="{C85E336A-E4D8-4F42-95F8-19A806CF9075}"/>
-    <hyperlink ref="O106" r:id="rId75" xr:uid="{61C5202E-87B7-4DFF-BDE8-ADF25A51C4B6}"/>
+    <hyperlink ref="O86" r:id="rId61" xr:uid="{3149E9C4-8DCD-4B7B-AA56-C24793E1FDDD}"/>
+    <hyperlink ref="O87" r:id="rId62" xr:uid="{216F92A5-F104-4692-B17C-6227E8D25A0E}"/>
+    <hyperlink ref="O92" r:id="rId63" xr:uid="{BB0086C3-2D05-4979-8CF3-0132D37DF1DB}"/>
+    <hyperlink ref="O95" r:id="rId64" xr:uid="{571AFD85-72FA-4D23-A240-55270E118838}"/>
+    <hyperlink ref="O96" r:id="rId65" xr:uid="{DB794ED7-FAF2-40D3-BCC4-3D87E9946E04}"/>
+    <hyperlink ref="O100" r:id="rId66" xr:uid="{7F416119-DC76-4A27-8048-AE23EAF496C5}"/>
+    <hyperlink ref="O102" r:id="rId67" xr:uid="{1D68F898-6AEA-42FA-94E2-9C9E1498344C}"/>
+    <hyperlink ref="O103" r:id="rId68" xr:uid="{C29175A2-1765-4C45-AC14-06BB76E02B1B}"/>
+    <hyperlink ref="O94" r:id="rId69" xr:uid="{8E588422-7B11-4B05-B296-3911285F17BA}"/>
+    <hyperlink ref="O99" r:id="rId70" xr:uid="{91FF6E37-C9BD-4631-8DF9-4A150C39A80E}"/>
+    <hyperlink ref="O104" r:id="rId71" xr:uid="{C85E336A-E4D8-4F42-95F8-19A806CF9075}"/>
+    <hyperlink ref="O106" r:id="rId72" xr:uid="{61C5202E-87B7-4DFF-BDE8-ADF25A51C4B6}"/>
+    <hyperlink ref="O70" r:id="rId73" xr:uid="{66E54603-F7CF-4DC8-B868-925E9997D858}"/>
+    <hyperlink ref="O73" r:id="rId74" xr:uid="{C69A5D4F-4932-4CB8-8443-136BE55217CE}"/>
+    <hyperlink ref="O75" r:id="rId75" xr:uid="{3F774918-96E7-4172-9CF4-AA3E109A063E}"/>
+    <hyperlink ref="O76" r:id="rId76" xr:uid="{9445D080-5AFC-4BB5-A92D-0655336394FC}"/>
+    <hyperlink ref="O79" r:id="rId77" xr:uid="{A97845DF-9458-4D61-ACC7-3C91301B9221}"/>
+    <hyperlink ref="O80" r:id="rId78" xr:uid="{84808F7E-9EDD-49D9-8971-82350D90541A}"/>
+    <hyperlink ref="O88" r:id="rId79" xr:uid="{6911FE59-7388-45F0-8C34-AEBAC6FD6115}"/>
+    <hyperlink ref="O89" r:id="rId80" xr:uid="{363BECF3-81E8-42F1-B8F0-D447AC307BC4}"/>
+    <hyperlink ref="O90" r:id="rId81" xr:uid="{A9B2E30D-0D28-463F-B5B4-02A931A14865}"/>
+    <hyperlink ref="O81" r:id="rId82" xr:uid="{7E81E536-23B5-4B5B-9C2F-DDA48D563A2C}"/>
+    <hyperlink ref="O82" r:id="rId83" xr:uid="{6D27FA1D-997B-4E9C-BAD8-F397C9652E5D}"/>
+    <hyperlink ref="O83" r:id="rId84" xr:uid="{22FFC267-8FDA-412D-9EBD-8D6DED0D52A7}"/>
+    <hyperlink ref="O84" r:id="rId85" xr:uid="{FE3B66E5-688A-410D-8C9C-4F1003F6068F}"/>
+    <hyperlink ref="O85" r:id="rId86" xr:uid="{996AA183-C9FB-468B-98CB-2A6E462BB81F}"/>
+    <hyperlink ref="O105" r:id="rId87" xr:uid="{D91A7680-9E8E-47E6-B633-5EBFAD828ADB}"/>
+    <hyperlink ref="O93" r:id="rId88" xr:uid="{AF26A144-373A-4F0B-B639-348CFDF1904B}"/>
+    <hyperlink ref="O97" r:id="rId89" xr:uid="{9A5052CF-F17F-468A-BDE6-9E352EC830F2}"/>
+    <hyperlink ref="O98" r:id="rId90" xr:uid="{C233F72D-B204-4E40-AAAD-9034CD27391F}"/>
+    <hyperlink ref="O55" r:id="rId91" xr:uid="{90C35BC1-76DB-4582-A11A-E5E703BB9959}"/>
+    <hyperlink ref="O32" r:id="rId92" xr:uid="{C27551A9-1645-49B0-8FCC-5E4209328A84}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId76"/>
-  <drawing r:id="rId77"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId93"/>
+  <drawing r:id="rId94"/>
 </worksheet>
 </file>
--- a/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
+++ b/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED89801-1873-4E2E-95C8-7518940C31AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFAD8F9-D2F5-4458-8D50-C5567E54A9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="555">
   <si>
     <t>Component list</t>
   </si>
@@ -43,12 +43,6 @@
     <t>Single Board Cost</t>
   </si>
   <si>
-    <t>Bill of Materials for Project [V3_Board.PrjPcb] (No PCB Document Selected)</t>
-  </si>
-  <si>
-    <t>V3_Board.PrjPcb</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
@@ -250,9 +244,6 @@
     <t>R24, R25</t>
   </si>
   <si>
-    <t>R30</t>
-  </si>
-  <si>
     <t>R32</t>
   </si>
   <si>
@@ -286,9 +277,6 @@
     <t>R112</t>
   </si>
   <si>
-    <t>R116</t>
-  </si>
-  <si>
     <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB31, SB32, SB33, SB34, SB35, SB36, SB37, SB38, SB39, SB40, SB41, SB42</t>
   </si>
   <si>
@@ -403,9 +391,6 @@
     <t>SCHOTTKY DIODE SMB 100V 5A</t>
   </si>
   <si>
-    <t>DIODE SCHOTTKY 20V 3A SMC</t>
-  </si>
-  <si>
     <t>CONN HEADER SMD 10POS 1.27MM</t>
   </si>
   <si>
@@ -502,9 +487,6 @@
     <t>±1% 1/10W Thick Film Resistors 75V ±600ppm/℃ -55℃~+155℃ 0.33Ω 0603 Chip Resistor - Surface Mount ROHS</t>
   </si>
   <si>
-    <t>RES 2.2K OHM 1% 1/10W 0603, RES SMD 2.2K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES SMD 470K OHM 5% 1/10W 0603</t>
   </si>
   <si>
@@ -568,9 +550,6 @@
     <t>RES SMD 7.5K OHM 0.1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES 20K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>Solder Bridge ON</t>
   </si>
   <si>
@@ -652,9 +631,6 @@
     <t>SS510B</t>
   </si>
   <si>
-    <t>SMC</t>
-  </si>
-  <si>
     <t>FTSH-105-01-L-DV-K-TR</t>
   </si>
   <si>
@@ -958,9 +934,6 @@
     <t>RT0603BRD077K5L</t>
   </si>
   <si>
-    <t>RC0603FR-0720KL</t>
-  </si>
-  <si>
     <t>ACS723LLCTR-20AU-T</t>
   </si>
   <si>
@@ -1027,9 +1000,6 @@
     <t>MDD</t>
   </si>
   <si>
-    <t>ON Semiconductor / Fairchild</t>
-  </si>
-  <si>
     <t>Samtec</t>
   </si>
   <si>
@@ -1181,9 +1151,6 @@
   </si>
   <si>
     <t>C114662</t>
-  </si>
-  <si>
-    <t>C105575</t>
   </si>
   <si>
     <t>C2681243</t>
@@ -1701,6 +1668,24 @@
   </si>
   <si>
     <t>20021121-00010C4LF</t>
+  </si>
+  <si>
+    <t>RES 2.2K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R30, R116</t>
+  </si>
+  <si>
+    <t>20V 500mV@3A 3A SMA(DO-214AC) Schottky Barrier Diodes (SBD) ROHS</t>
+  </si>
+  <si>
+    <t>C34897</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [V3_Board]</t>
+  </si>
+  <si>
+    <t>V3_Board</t>
   </si>
 </sst>
 </file>
@@ -1712,7 +1697,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1883,6 +1868,24 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2158,7 +2161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2349,10 +2352,16 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2387,16 +2396,37 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2741,7 +2771,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S108"/>
+  <dimension ref="A1:S107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="26" bestFit="1" customWidth="1"/>
@@ -2775,15 +2805,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="73"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="75"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2794,7 +2824,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="57" t="s">
-        <v>7</v>
+        <v>553</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2819,7 +2849,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="58" t="s">
-        <v>8</v>
+        <v>554</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2833,7 +2863,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="74"/>
+      <c r="S3" s="76"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2844,7 +2874,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="59" t="s">
-        <v>8</v>
+        <v>554</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2858,7 +2888,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="75"/>
+      <c r="S4" s="77"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2869,7 +2899,7 @@
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="6"/>
@@ -2883,7 +2913,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="75"/>
+      <c r="S5" s="77"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2904,7 +2934,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="75"/>
+      <c r="S6" s="77"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2925,7 +2955,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="75"/>
+      <c r="S7" s="77"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2946,7 +2976,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="75"/>
+      <c r="S8" s="77"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2954,55 +2984,55 @@
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F9" s="63" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="H9" s="64" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="L9" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>430</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="R9" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>435</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>440</v>
-      </c>
-      <c r="N9" s="31" t="s">
-        <v>441</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="P9" s="31" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="R9" s="31" t="s">
-        <v>445</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -3012,31 +3042,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="L10" s="39">
         <v>13</v>
@@ -3049,7 +3079,7 @@
         <v>80</v>
       </c>
       <c r="O10" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P10" s="42">
         <v>2.4500000000000001E-2</v>
@@ -3064,33 +3094,35 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="52">
-        <f t="shared" ref="B11:B105" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B104" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="H11" s="41" t="s">
-        <v>324</v>
-      </c>
-      <c r="I11" s="40"/>
+        <v>315</v>
+      </c>
+      <c r="I11" s="40" t="s">
+        <v>437</v>
+      </c>
       <c r="J11" s="41" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="K11" s="40" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="L11" s="41">
         <v>1</v>
@@ -3099,12 +3131,18 @@
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>5</v>
       </c>
-      <c r="N11" s="41"/>
-      <c r="O11" s="67"/>
-      <c r="P11" s="54"/>
+      <c r="N11" s="41">
+        <v>50</v>
+      </c>
+      <c r="O11" s="67" t="s">
+        <v>457</v>
+      </c>
+      <c r="P11" s="54">
+        <v>1.18E-2</v>
+      </c>
       <c r="Q11" s="43">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="R11" s="41"/>
       <c r="S11" s="40"/>
@@ -3116,31 +3154,31 @@
         <v>3</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="E12" s="65" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="L12" s="39">
         <v>9</v>
@@ -3153,7 +3191,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P12" s="53">
         <v>4.7000000000000002E-3</v>
@@ -3172,29 +3210,29 @@
         <v>4</v>
       </c>
       <c r="C13" s="62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="I13" s="40"/>
       <c r="J13" s="41" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="K13" s="40" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="L13" s="41">
         <v>5</v>
@@ -3207,7 +3245,7 @@
         <v>27</v>
       </c>
       <c r="O13" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P13" s="54">
         <v>0.28799999999999998</v>
@@ -3226,31 +3264,31 @@
         <v>5</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="E14" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>437</v>
+      </c>
+      <c r="J14" s="39" t="s">
         <v>459</v>
       </c>
-      <c r="E14" s="65" t="s">
-        <v>110</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>201</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>324</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>448</v>
-      </c>
-      <c r="J14" s="39" t="s">
-        <v>470</v>
-      </c>
       <c r="K14" s="38" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="L14" s="39">
         <v>37</v>
@@ -3263,7 +3301,7 @@
         <v>200</v>
       </c>
       <c r="O14" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P14" s="53">
         <v>2.7000000000000001E-3</v>
@@ -3282,31 +3320,31 @@
         <v>6</v>
       </c>
       <c r="C15" s="62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="L15" s="41">
         <v>1</v>
@@ -3319,7 +3357,7 @@
         <v>10</v>
       </c>
       <c r="O15" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P15" s="54">
         <v>0.13789999999999999</v>
@@ -3338,31 +3376,31 @@
         <v>7</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E16" s="65" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I16" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -3375,7 +3413,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P16" s="53">
         <v>2.5000000000000001E-3</v>
@@ -3394,31 +3432,31 @@
         <v>8</v>
       </c>
       <c r="C17" s="62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="H17" s="41" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="K17" s="40" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="L17" s="41">
         <v>1</v>
@@ -3431,7 +3469,7 @@
         <v>6</v>
       </c>
       <c r="O17" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P17" s="54">
         <v>0.19359999999999999</v>
@@ -3450,31 +3488,31 @@
         <v>9</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E18" s="65" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I18" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J18" s="39" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="L18" s="39">
         <v>2</v>
@@ -3487,7 +3525,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P18" s="53">
         <v>2.5999999999999999E-3</v>
@@ -3506,31 +3544,31 @@
         <v>10</v>
       </c>
       <c r="C19" s="62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H19" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I19" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="K19" s="40" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="L19" s="41">
         <v>4</v>
@@ -3543,7 +3581,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P19" s="54">
         <v>2.8999999999999998E-3</v>
@@ -3562,31 +3600,31 @@
         <v>11</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E20" s="65" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="L20" s="39">
         <v>1</v>
@@ -3599,7 +3637,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P20" s="53">
         <v>3.5200000000000002E-2</v>
@@ -3618,31 +3656,31 @@
         <v>12</v>
       </c>
       <c r="C21" s="62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G21" s="40" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="I21" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="K21" s="40" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="L21" s="41">
         <v>1</v>
@@ -3655,7 +3693,7 @@
         <v>20</v>
       </c>
       <c r="O21" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P21" s="54">
         <v>3.04E-2</v>
@@ -3674,31 +3712,31 @@
         <v>13</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E22" s="65" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="L22" s="39">
         <v>1</v>
@@ -3711,7 +3749,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P22" s="53">
         <v>3.3E-3</v>
@@ -3730,31 +3768,31 @@
         <v>14</v>
       </c>
       <c r="C23" s="62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="H23" s="41" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="I23" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J23" s="41" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="L23" s="41">
         <v>1</v>
@@ -3767,7 +3805,7 @@
         <v>20</v>
       </c>
       <c r="O23" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P23" s="54">
         <v>2.9899999999999999E-2</v>
@@ -3786,31 +3824,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E24" s="65" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I24" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="L24" s="39">
         <v>1</v>
@@ -3823,7 +3861,7 @@
         <v>100</v>
       </c>
       <c r="O24" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P24" s="53">
         <v>3.0999999999999999E-3</v>
@@ -3842,31 +3880,31 @@
         <v>16</v>
       </c>
       <c r="C25" s="62" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G25" s="40" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="H25" s="41" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="I25" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J25" s="41" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="K25" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L25" s="41">
         <v>1</v>
@@ -3879,7 +3917,7 @@
         <v>20</v>
       </c>
       <c r="O25" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P25" s="54">
         <v>3.2899999999999999E-2</v>
@@ -3898,31 +3936,31 @@
         <v>17</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E26" s="65" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="I26" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L26" s="39">
         <v>1</v>
@@ -3935,7 +3973,7 @@
         <v>6</v>
       </c>
       <c r="O26" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P26" s="53">
         <v>0.49009999999999998</v>
@@ -3954,31 +3992,31 @@
         <v>18</v>
       </c>
       <c r="C27" s="62" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G27" s="40" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="I27" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J27" s="41" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="K27" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L27" s="41">
         <v>1</v>
@@ -3991,7 +4029,7 @@
         <v>20</v>
       </c>
       <c r="O27" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P27" s="54">
         <v>3.1399999999999997E-2</v>
@@ -4010,31 +4048,31 @@
         <v>19</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E28" s="65" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="H28" s="39" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="I28" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L28" s="39">
         <v>5</v>
@@ -4047,7 +4085,7 @@
         <v>40</v>
       </c>
       <c r="O28" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P28" s="53">
         <v>2.0400000000000001E-2</v>
@@ -4066,31 +4104,31 @@
         <v>20</v>
       </c>
       <c r="C29" s="62" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G29" s="40" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="I29" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J29" s="41" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="K29" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L29" s="41">
         <v>1</v>
@@ -4103,7 +4141,7 @@
         <v>10</v>
       </c>
       <c r="O29" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P29" s="54">
         <v>6.2700000000000006E-2</v>
@@ -4122,31 +4160,31 @@
         <v>21</v>
       </c>
       <c r="C30" s="61" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E30" s="65" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="I30" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J30" s="39" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L30" s="39">
         <v>1</v>
@@ -4159,7 +4197,7 @@
         <v>10</v>
       </c>
       <c r="O30" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P30" s="53">
         <v>8.7099999999999997E-2</v>
@@ -4178,31 +4216,31 @@
         <v>22</v>
       </c>
       <c r="C31" s="62" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="F31" s="41" t="s">
-        <v>210</v>
+        <v>34</v>
+      </c>
+      <c r="E31" s="84" t="s">
+        <v>551</v>
+      </c>
+      <c r="F31" s="84" t="s">
+        <v>198</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="H31" s="41" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I31" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J31" s="41" t="s">
-        <v>448</v>
+        <v>552</v>
       </c>
       <c r="K31" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L31" s="41">
         <v>1</v>
@@ -4211,12 +4249,18 @@
         <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="41"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="54"/>
+      <c r="N31" s="41">
+        <v>20</v>
+      </c>
+      <c r="O31" s="67" t="s">
+        <v>457</v>
+      </c>
+      <c r="P31" s="54">
+        <v>3.6200000000000003E-2</v>
+      </c>
       <c r="Q31" s="43">
         <f>P31*N31</f>
-        <v>0</v>
+        <v>0.72400000000000009</v>
       </c>
       <c r="R31" s="41"/>
       <c r="S31" s="40"/>
@@ -4228,31 +4272,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="61" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E32" s="65" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G32" s="69" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="H32" s="39" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="I32" s="38" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L32" s="39">
         <v>1</v>
@@ -4265,7 +4309,7 @@
         <v>6</v>
       </c>
       <c r="O32" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P32" s="53">
         <v>0.61729999999999996</v>
@@ -4284,31 +4328,31 @@
         <v>24</v>
       </c>
       <c r="C33" s="62" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D33" s="40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G33" s="68" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H33" s="41" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="I33" s="40" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="J33" s="41" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="K33" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L33" s="41">
         <v>9</v>
@@ -4321,7 +4365,7 @@
         <v>50</v>
       </c>
       <c r="O33" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P33" s="54">
         <v>7.1199999999999999E-2</v>
@@ -4340,31 +4384,31 @@
         <v>25</v>
       </c>
       <c r="C34" s="61" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E34" s="65" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F34" s="39" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G34" s="69" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H34" s="39" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="I34" s="38" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="J34" s="39" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L34" s="39">
         <v>5</v>
@@ -4377,7 +4421,7 @@
         <v>30</v>
       </c>
       <c r="O34" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P34" s="53">
         <v>0.10539999999999999</v>
@@ -4396,31 +4440,31 @@
         <v>26</v>
       </c>
       <c r="C35" s="62" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D35" s="40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G35" s="68" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H35" s="41" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="I35" s="40" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="J35" s="41" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="K35" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L35" s="41">
         <v>1</v>
@@ -4433,7 +4477,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P35" s="54">
         <v>0.1114</v>
@@ -4452,31 +4496,31 @@
         <v>27</v>
       </c>
       <c r="C36" s="61" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E36" s="65" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H36" s="39" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="I36" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L36" s="39">
         <v>1</v>
@@ -4489,7 +4533,7 @@
         <v>6</v>
       </c>
       <c r="O36" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P36" s="53">
         <v>0.75180000000000002</v>
@@ -4508,31 +4552,31 @@
         <v>28</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G37" s="40" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="H37" s="41" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="I37" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J37" s="41" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="K37" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L37" s="41">
         <v>1</v>
@@ -4545,7 +4589,7 @@
         <v>10</v>
       </c>
       <c r="O37" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P37" s="54">
         <v>6.4299999999999996E-2</v>
@@ -4564,31 +4608,31 @@
         <v>29</v>
       </c>
       <c r="C38" s="61" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E38" s="65" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="H38" s="39" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="I38" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L38" s="39">
         <v>1</v>
@@ -4601,7 +4645,7 @@
         <v>6</v>
       </c>
       <c r="O38" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P38" s="53">
         <v>0.22120000000000001</v>
@@ -4620,31 +4664,31 @@
         <v>30</v>
       </c>
       <c r="C39" s="62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G39" s="40" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H39" s="41" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="I39" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J39" s="41" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="K39" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L39" s="41">
         <v>5</v>
@@ -4657,7 +4701,7 @@
         <v>27</v>
       </c>
       <c r="O39" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P39" s="54">
         <v>1.2012</v>
@@ -4676,31 +4720,31 @@
         <v>31</v>
       </c>
       <c r="C40" s="61" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E40" s="65" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="I40" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="L40" s="39">
         <v>1</v>
@@ -4713,7 +4757,7 @@
         <v>10</v>
       </c>
       <c r="O40" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P40" s="53">
         <v>4.0399999999999998E-2</v>
@@ -4732,31 +4776,31 @@
         <v>32</v>
       </c>
       <c r="C41" s="62" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G41" s="40" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="H41" s="41" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J41" s="41" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="K41" s="40" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="L41" s="41">
         <v>1</v>
@@ -4769,7 +4813,7 @@
         <v>6</v>
       </c>
       <c r="O41" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P41" s="54">
         <v>0.47249999999999998</v>
@@ -4788,31 +4832,31 @@
         <v>33</v>
       </c>
       <c r="C42" s="61" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E42" s="65" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="H42" s="39" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="I42" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J42" s="39" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="L42" s="39">
         <v>1</v>
@@ -4825,7 +4869,7 @@
         <v>10</v>
       </c>
       <c r="O42" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P42" s="53">
         <v>7.9100000000000004E-2</v>
@@ -4844,31 +4888,31 @@
         <v>34</v>
       </c>
       <c r="C43" s="62" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F43" s="41" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="G43" s="40" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="H43" s="41" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="I43" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J43" s="41" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="K43" s="40" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="L43" s="41">
         <v>1</v>
@@ -4881,7 +4925,7 @@
         <v>10</v>
       </c>
       <c r="O43" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P43" s="54">
         <v>8.5099999999999995E-2</v>
@@ -4900,31 +4944,31 @@
         <v>35</v>
       </c>
       <c r="C44" s="61" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E44" s="65" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G44" s="69" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="I44" s="38" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L44" s="39">
         <v>7</v>
@@ -4937,7 +4981,7 @@
         <v>40</v>
       </c>
       <c r="O44" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P44" s="53">
         <v>3.5400000000000001E-2</v>
@@ -4956,31 +5000,31 @@
         <v>36</v>
       </c>
       <c r="C45" s="62" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G45" s="40" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H45" s="41" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="I45" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J45" s="41" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="K45" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L45" s="41">
         <v>1</v>
@@ -4993,7 +5037,7 @@
         <v>10</v>
       </c>
       <c r="O45" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P45" s="54">
         <v>0.1216</v>
@@ -5012,31 +5056,31 @@
         <v>37</v>
       </c>
       <c r="C46" s="61" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E46" s="65" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="H46" s="39" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I46" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L46" s="39">
         <v>1</v>
@@ -5049,7 +5093,7 @@
         <v>6</v>
       </c>
       <c r="O46" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P46" s="53">
         <v>0.34010000000000001</v>
@@ -5067,50 +5111,54 @@
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="62" t="s">
-        <v>406</v>
-      </c>
-      <c r="D47" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="E47" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="F47" s="41" t="s">
-        <v>437</v>
-      </c>
-      <c r="G47" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="H47" s="41"/>
-      <c r="I47" s="40" t="s">
-        <v>448</v>
-      </c>
-      <c r="J47" s="41"/>
-      <c r="K47" s="40" t="s">
-        <v>448</v>
-      </c>
-      <c r="L47" s="41">
+      <c r="C47" s="90" t="s">
+        <v>395</v>
+      </c>
+      <c r="D47" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="F47" s="91" t="s">
+        <v>426</v>
+      </c>
+      <c r="G47" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="H47" s="91" t="s">
+        <v>437</v>
+      </c>
+      <c r="I47" s="68" t="s">
+        <v>437</v>
+      </c>
+      <c r="J47" s="91" t="s">
+        <v>437</v>
+      </c>
+      <c r="K47" s="68" t="s">
+        <v>437</v>
+      </c>
+      <c r="L47" s="91">
         <v>2</v>
       </c>
-      <c r="M47" s="40">
+      <c r="M47" s="68">
         <f>L47*5</f>
         <v>10</v>
       </c>
-      <c r="N47" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="O47" s="67" t="s">
-        <v>448</v>
-      </c>
-      <c r="P47" s="54" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q47" s="43" t="s">
-        <v>448</v>
-      </c>
-      <c r="R47" s="41"/>
-      <c r="S47" s="40"/>
+      <c r="N47" s="91" t="s">
+        <v>437</v>
+      </c>
+      <c r="O47" s="92" t="s">
+        <v>437</v>
+      </c>
+      <c r="P47" s="93" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q47" s="94" t="s">
+        <v>437</v>
+      </c>
+      <c r="R47" s="91"/>
+      <c r="S47" s="68"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
@@ -5119,31 +5167,31 @@
         <v>39</v>
       </c>
       <c r="C48" s="61" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E48" s="65" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G48" s="69">
         <v>61300311121</v>
       </c>
       <c r="H48" s="39" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L48" s="39">
         <v>2</v>
@@ -5156,7 +5204,7 @@
         <v>50</v>
       </c>
       <c r="O48" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P48" s="53">
         <v>1.44E-2</v>
@@ -5175,31 +5223,31 @@
         <v>40</v>
       </c>
       <c r="C49" s="62" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F49" s="41" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G49" s="68">
         <v>61300611121</v>
       </c>
       <c r="H49" s="41" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I49" s="40" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="J49" s="41" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="K49" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L49" s="41">
         <v>4</v>
@@ -5212,7 +5260,7 @@
         <v>40</v>
       </c>
       <c r="O49" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P49" s="54">
         <v>2.9700000000000001E-2</v>
@@ -5231,31 +5279,31 @@
         <v>41</v>
       </c>
       <c r="C50" s="61" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E50" s="65" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G50" s="69" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="H50" s="39" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L50" s="39">
         <v>1</v>
@@ -5268,7 +5316,7 @@
         <v>10</v>
       </c>
       <c r="O50" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P50" s="53">
         <v>0.11509999999999999</v>
@@ -5287,31 +5335,31 @@
         <v>42</v>
       </c>
       <c r="C51" s="62" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F51" s="41" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G51" s="68">
         <v>61300211121</v>
       </c>
       <c r="H51" s="41" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I51" s="40" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="J51" s="41" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="K51" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L51" s="41">
         <v>3</v>
@@ -5324,7 +5372,7 @@
         <v>50</v>
       </c>
       <c r="O51" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P51" s="54">
         <v>1.3299999999999999E-2</v>
@@ -5343,31 +5391,31 @@
         <v>43</v>
       </c>
       <c r="C52" s="61" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E52" s="65" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G52" s="69">
         <v>61300411121</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I52" s="38" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L52" s="39">
         <v>1</v>
@@ -5380,7 +5428,7 @@
         <v>20</v>
       </c>
       <c r="O52" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P52" s="53">
         <v>2.18E-2</v>
@@ -5399,31 +5447,31 @@
         <v>44</v>
       </c>
       <c r="C53" s="62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F53" s="41" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="H53" s="41" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="I53" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J53" s="41" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="K53" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L53" s="41">
         <v>9</v>
@@ -5436,7 +5484,7 @@
         <v>47</v>
       </c>
       <c r="O53" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P53" s="54">
         <v>0.31269999999999998</v>
@@ -5455,31 +5503,31 @@
         <v>45</v>
       </c>
       <c r="C54" s="61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E54" s="65" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G54" s="38" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="H54" s="39" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="I54" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L54" s="39">
         <v>1</v>
@@ -5492,7 +5540,7 @@
         <v>10</v>
       </c>
       <c r="O54" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P54" s="53">
         <v>7.0800000000000002E-2</v>
@@ -5511,31 +5559,31 @@
         <v>46</v>
       </c>
       <c r="C55" s="62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F55" s="41" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G55" s="40" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="H55" s="41" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="I55" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J55" s="41" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="K55" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L55" s="41">
         <v>2</v>
@@ -5548,7 +5596,7 @@
         <v>35</v>
       </c>
       <c r="O55" s="67" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="P55" s="54">
         <v>1.486</v>
@@ -5567,31 +5615,31 @@
         <v>47</v>
       </c>
       <c r="C56" s="61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E56" s="65" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G56" s="38" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="H56" s="39" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="I56" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J56" s="39" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L56" s="39">
         <v>2</v>
@@ -5604,7 +5652,7 @@
         <v>15</v>
       </c>
       <c r="O56" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P56" s="53">
         <v>0.1182</v>
@@ -5623,31 +5671,31 @@
         <v>48</v>
       </c>
       <c r="C57" s="62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F57" s="41" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="H57" s="41" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="I57" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J57" s="41" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="K57" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L57" s="41">
         <v>6</v>
@@ -5660,7 +5708,7 @@
         <v>20</v>
       </c>
       <c r="O57" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P57" s="54">
         <v>3.3500000000000002E-2</v>
@@ -5679,31 +5727,31 @@
         <v>49</v>
       </c>
       <c r="C58" s="61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E58" s="65" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G58" s="38" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="H58" s="39" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="I58" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J58" s="39" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L58" s="39">
         <v>10</v>
@@ -5716,7 +5764,7 @@
         <v>60</v>
       </c>
       <c r="O58" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P58" s="53">
         <v>1.9099999999999999E-2</v>
@@ -5735,31 +5783,31 @@
         <v>50</v>
       </c>
       <c r="C59" s="62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F59" s="41" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="H59" s="41" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="I59" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J59" s="41" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="K59" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L59" s="41">
         <v>2</v>
@@ -5772,7 +5820,7 @@
         <v>20</v>
       </c>
       <c r="O59" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P59" s="54">
         <v>2.0299999999999999E-2</v>
@@ -5791,31 +5839,31 @@
         <v>51</v>
       </c>
       <c r="C60" s="61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E60" s="65" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F60" s="39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="H60" s="39" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="I60" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J60" s="39" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L60" s="39">
         <v>3</v>
@@ -5828,7 +5876,7 @@
         <v>20</v>
       </c>
       <c r="O60" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P60" s="53">
         <v>2.9899999999999999E-2</v>
@@ -5847,31 +5895,31 @@
         <v>52</v>
       </c>
       <c r="C61" s="62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F61" s="41" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="G61" s="40" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H61" s="41" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="I61" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J61" s="41" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="K61" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L61" s="41">
         <v>1</v>
@@ -5884,7 +5932,7 @@
         <v>10</v>
       </c>
       <c r="O61" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P61" s="54">
         <v>0.3261</v>
@@ -5903,31 +5951,31 @@
         <v>53</v>
       </c>
       <c r="C62" s="61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E62" s="65" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F62" s="39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G62" s="38" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="H62" s="39" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="I62" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J62" s="39" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L62" s="39">
         <v>1</v>
@@ -5940,7 +5988,7 @@
         <v>10</v>
       </c>
       <c r="O62" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P62" s="53">
         <v>4.3700000000000003E-2</v>
@@ -5959,31 +6007,31 @@
         <v>54</v>
       </c>
       <c r="C63" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D63" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F63" s="41" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G63" s="40" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="H63" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I63" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J63" s="41" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="K63" s="40" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="L63" s="41">
         <v>1</v>
@@ -5996,7 +6044,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P63" s="54">
         <v>2.0999999999999999E-3</v>
@@ -6015,31 +6063,31 @@
         <v>55</v>
       </c>
       <c r="C64" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E64" s="65" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F64" s="39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G64" s="38" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="H64" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I64" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J64" s="39" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="L64" s="39">
         <v>1</v>
@@ -6052,7 +6100,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P64" s="53">
         <v>1.1999999999999999E-3</v>
@@ -6071,31 +6119,31 @@
         <v>56</v>
       </c>
       <c r="C65" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F65" s="41" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G65" s="40" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="H65" s="41" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I65" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J65" s="41" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="K65" s="40" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="L65" s="41">
         <v>1</v>
@@ -6108,7 +6156,7 @@
         <v>50</v>
       </c>
       <c r="O65" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P65" s="54">
         <v>3.8E-3</v>
@@ -6127,31 +6175,31 @@
         <v>57</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="E66" s="65" t="s">
-        <v>160</v>
+        <v>549</v>
       </c>
       <c r="F66" s="39" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="H66" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I66" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J66" s="39" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="L66" s="39">
         <v>15</v>
@@ -6164,7 +6212,7 @@
         <v>100</v>
       </c>
       <c r="O66" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P66" s="53">
         <v>1.1999999999999999E-3</v>
@@ -6183,31 +6231,31 @@
         <v>58</v>
       </c>
       <c r="C67" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F67" s="41" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G67" s="40" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="H67" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I67" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J67" s="41" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="K67" s="40" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="L67" s="41">
         <v>2</v>
@@ -6220,7 +6268,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P67" s="54">
         <v>1.5E-3</v>
@@ -6239,31 +6287,31 @@
         <v>59</v>
       </c>
       <c r="C68" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E68" s="65" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F68" s="39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="H68" s="39" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I68" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J68" s="39" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="L68" s="39">
         <v>1</v>
@@ -6276,7 +6324,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P68" s="53">
         <v>1.6999999999999999E-3</v>
@@ -6295,31 +6343,31 @@
         <v>60</v>
       </c>
       <c r="C69" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D69" s="40" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F69" s="41" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G69" s="40" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H69" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I69" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J69" s="41" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="L69" s="41">
         <v>20</v>
@@ -6332,7 +6380,7 @@
         <v>200</v>
       </c>
       <c r="O69" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P69" s="54">
         <v>1E-3</v>
@@ -6351,31 +6399,31 @@
         <v>61</v>
       </c>
       <c r="C70" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E70" s="65" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F70" s="39" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H70" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I70" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J70" s="39" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="L70" s="39">
         <v>1</v>
@@ -6388,7 +6436,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P70" s="53">
         <v>1.1999999999999999E-3</v>
@@ -6407,31 +6455,31 @@
         <v>62</v>
       </c>
       <c r="C71" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F71" s="41" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G71" s="40" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="H71" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I71" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J71" s="41" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="K71" s="40" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="L71" s="41">
         <v>3</v>
@@ -6444,7 +6492,7 @@
         <v>100</v>
       </c>
       <c r="O71" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P71" s="54">
         <v>1.1999999999999999E-3</v>
@@ -6463,31 +6511,31 @@
         <v>63</v>
       </c>
       <c r="C72" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E72" s="65" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F72" s="39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H72" s="39" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="I72" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J72" s="39" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="L72" s="39">
         <v>8</v>
@@ -6500,7 +6548,7 @@
         <v>100</v>
       </c>
       <c r="O72" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P72" s="53">
         <v>1.1999999999999999E-3</v>
@@ -6519,31 +6567,31 @@
         <v>64</v>
       </c>
       <c r="C73" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F73" s="41" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H73" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I73" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J73" s="41" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="K73" s="40" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="L73" s="41">
         <v>2</v>
@@ -6556,7 +6604,7 @@
         <v>100</v>
       </c>
       <c r="O73" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P73" s="54">
         <v>1.1999999999999999E-3</v>
@@ -6575,31 +6623,31 @@
         <v>65</v>
       </c>
       <c r="C74" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="E74" s="65" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F74" s="39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="H74" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I74" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J74" s="39" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="L74" s="39">
         <v>13</v>
@@ -6612,7 +6660,7 @@
         <v>100</v>
       </c>
       <c r="O74" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P74" s="53">
         <v>1E-3</v>
@@ -6631,44 +6679,44 @@
         <v>66</v>
       </c>
       <c r="C75" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>76</v>
+        <v>550</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F75" s="41" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="H75" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I75" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J75" s="41" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="K75" s="40" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="L75" s="41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="40">
         <f t="shared" ref="M75" si="65">L75*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N75" s="41">
         <v>20</v>
       </c>
       <c r="O75" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P75" s="54">
         <v>2.92E-2</v>
@@ -6687,31 +6735,31 @@
         <v>67</v>
       </c>
       <c r="C76" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E76" s="65" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F76" s="39" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="H76" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I76" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J76" s="39" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="L76" s="39">
         <v>1</v>
@@ -6724,7 +6772,7 @@
         <v>20</v>
       </c>
       <c r="O76" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P76" s="53">
         <v>0.03</v>
@@ -6743,31 +6791,31 @@
         <v>68</v>
       </c>
       <c r="C77" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F77" s="41" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H77" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I77" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J77" s="41" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="K77" s="40" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="L77" s="41">
         <v>3</v>
@@ -6780,7 +6828,7 @@
         <v>100</v>
       </c>
       <c r="O77" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P77" s="54">
         <v>1.1999999999999999E-3</v>
@@ -6799,31 +6847,31 @@
         <v>69</v>
       </c>
       <c r="C78" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="E78" s="65" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F78" s="39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G78" s="38" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I78" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J78" s="39" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="L78" s="39">
         <v>24</v>
@@ -6836,7 +6884,7 @@
         <v>200</v>
       </c>
       <c r="O78" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P78" s="53">
         <v>1.1999999999999999E-3</v>
@@ -6855,31 +6903,31 @@
         <v>70</v>
       </c>
       <c r="C79" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F79" s="41" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G79" s="40" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="H79" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I79" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J79" s="41" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="K79" s="40" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="L79" s="41">
         <v>1</v>
@@ -6892,7 +6940,7 @@
         <v>100</v>
       </c>
       <c r="O79" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P79" s="54">
         <v>2.2000000000000001E-3</v>
@@ -6911,31 +6959,31 @@
         <v>71</v>
       </c>
       <c r="C80" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E80" s="65" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F80" s="39" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G80" s="38" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="H80" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I80" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J80" s="39" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="K80" s="38" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="L80" s="39">
         <v>1</v>
@@ -6948,7 +6996,7 @@
         <v>50</v>
       </c>
       <c r="O80" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P80" s="53">
         <v>1.6899999999999998E-2</v>
@@ -6967,31 +7015,31 @@
         <v>72</v>
       </c>
       <c r="C81" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F81" s="41" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G81" s="40" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H81" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I81" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J81" s="41" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="L81" s="41">
         <v>1</v>
@@ -7004,7 +7052,7 @@
         <v>100</v>
       </c>
       <c r="O81" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P81" s="54">
         <v>1.2999999999999999E-3</v>
@@ -7023,31 +7071,31 @@
         <v>73</v>
       </c>
       <c r="C82" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E82" s="65" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F82" s="39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G82" s="38" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="H82" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I82" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J82" s="39" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="K82" s="38" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="L82" s="39">
         <v>2</v>
@@ -7060,7 +7108,7 @@
         <v>100</v>
       </c>
       <c r="O82" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P82" s="53">
         <v>1.1999999999999999E-3</v>
@@ -7079,31 +7127,31 @@
         <v>74</v>
       </c>
       <c r="C83" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F83" s="41" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G83" s="68" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="H83" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I83" s="40" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="J83" s="41" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="K83" s="40" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="L83" s="41">
         <v>5</v>
@@ -7116,7 +7164,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P83" s="54">
         <v>2E-3</v>
@@ -7135,31 +7183,31 @@
         <v>75</v>
       </c>
       <c r="C84" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E84" s="65" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="F84" s="39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G84" s="38" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="H84" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I84" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J84" s="39" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="K84" s="38" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="L84" s="39">
         <v>2</v>
@@ -7172,7 +7220,7 @@
         <v>100</v>
       </c>
       <c r="O84" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P84" s="53">
         <v>1.2999999999999999E-3</v>
@@ -7191,31 +7239,31 @@
         <v>76</v>
       </c>
       <c r="C85" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F85" s="41" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G85" s="40" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="H85" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I85" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J85" s="41" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="K85" s="40" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="L85" s="41">
         <v>2</v>
@@ -7228,7 +7276,7 @@
         <v>100</v>
       </c>
       <c r="O85" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P85" s="54">
         <v>1.1000000000000001E-3</v>
@@ -7247,31 +7295,31 @@
         <v>77</v>
       </c>
       <c r="C86" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E86" s="65" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F86" s="39" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="H86" s="39" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="I86" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J86" s="39" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="K86" s="38" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="L86" s="39">
         <v>2</v>
@@ -7284,7 +7332,7 @@
         <v>50</v>
       </c>
       <c r="O86" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P86" s="53">
         <v>0.01</v>
@@ -7303,31 +7351,31 @@
         <v>78</v>
       </c>
       <c r="C87" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="F87" s="41" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="H87" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I87" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J87" s="41" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="L87" s="41">
         <v>2</v>
@@ -7340,7 +7388,7 @@
         <v>100</v>
       </c>
       <c r="O87" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P87" s="54">
         <v>1.1999999999999999E-3</v>
@@ -7359,31 +7407,31 @@
         <v>79</v>
       </c>
       <c r="C88" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E88" s="65" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F88" s="39" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G88" s="38" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="H88" s="39" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I88" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J88" s="39" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="K88" s="38" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="L88" s="39">
         <v>1</v>
@@ -7396,7 +7444,7 @@
         <v>50</v>
       </c>
       <c r="O88" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P88" s="53">
         <v>8.8000000000000005E-3</v>
@@ -7415,31 +7463,31 @@
         <v>80</v>
       </c>
       <c r="C89" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F89" s="41" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G89" s="40" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="H89" s="41" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I89" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J89" s="41" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="K89" s="40" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="L89" s="41">
         <v>1</v>
@@ -7452,7 +7500,7 @@
         <v>20</v>
       </c>
       <c r="O89" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P89" s="54">
         <v>2.7900000000000001E-2</v>
@@ -7464,1018 +7512,962 @@
       <c r="R89" s="41"/>
       <c r="S89" s="40"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" ht="84" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="52">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="C90" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="D90" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="E90" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="F90" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="G90" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="H90" s="39" t="s">
-        <v>324</v>
-      </c>
-      <c r="I90" s="38" t="s">
-        <v>448</v>
-      </c>
-      <c r="J90" s="39" t="s">
-        <v>387</v>
-      </c>
-      <c r="K90" s="38" t="s">
-        <v>420</v>
-      </c>
-      <c r="L90" s="39">
-        <v>1</v>
-      </c>
-      <c r="M90" s="38">
+      <c r="C90" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="D90" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="E90" s="69" t="s">
+        <v>176</v>
+      </c>
+      <c r="F90" s="86" t="s">
+        <v>426</v>
+      </c>
+      <c r="G90" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="H90" s="86" t="s">
+        <v>437</v>
+      </c>
+      <c r="I90" s="69" t="s">
+        <v>437</v>
+      </c>
+      <c r="J90" s="86" t="s">
+        <v>437</v>
+      </c>
+      <c r="K90" s="69" t="s">
+        <v>437</v>
+      </c>
+      <c r="L90" s="86">
+        <v>42</v>
+      </c>
+      <c r="M90" s="69">
         <f t="shared" ref="M90" si="81">L90*5</f>
-        <v>5</v>
-      </c>
-      <c r="N90" s="38">
-        <v>100</v>
-      </c>
-      <c r="O90" s="66" t="s">
-        <v>468</v>
-      </c>
-      <c r="P90" s="53">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q90" s="42">
-        <f t="shared" ref="Q90" si="82">P90*N90</f>
-        <v>0.12</v>
-      </c>
-      <c r="R90" s="39"/>
-      <c r="S90" s="38"/>
-    </row>
-    <row r="91" spans="1:19" ht="84" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="N90" s="69" t="s">
+        <v>437</v>
+      </c>
+      <c r="O90" s="87" t="s">
+        <v>437</v>
+      </c>
+      <c r="P90" s="88" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q90" s="89" t="s">
+        <v>437</v>
+      </c>
+      <c r="R90" s="86"/>
+      <c r="S90" s="69"/>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
-      <c r="B91" s="52">
-        <f t="shared" si="0"/>
+      <c r="B91" s="51">
+        <f>ROW(B91) - ROW($B$9)</f>
         <v>82</v>
       </c>
       <c r="C91" s="62" t="s">
-        <v>239</v>
+        <v>536</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F91" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G91" s="40" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="H91" s="41" t="s">
-        <v>448</v>
+        <v>350</v>
       </c>
       <c r="I91" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J91" s="41" t="s">
-        <v>448</v>
+        <v>519</v>
       </c>
       <c r="K91" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L91" s="41">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="M91" s="40">
-        <f t="shared" ref="M91" si="83">L91*5</f>
-        <v>210</v>
-      </c>
-      <c r="N91" s="41" t="s">
-        <v>448</v>
+        <f>L91*5</f>
+        <v>35</v>
+      </c>
+      <c r="N91" s="41">
+        <v>37</v>
       </c>
       <c r="O91" s="67" t="s">
-        <v>448</v>
-      </c>
-      <c r="P91" s="54" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q91" s="43" t="s">
-        <v>448</v>
+        <v>457</v>
+      </c>
+      <c r="P91" s="54">
+        <v>0.6905</v>
+      </c>
+      <c r="Q91" s="43">
+        <f>P91*N91</f>
+        <v>25.548500000000001</v>
       </c>
       <c r="R91" s="41"/>
       <c r="S91" s="40"/>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
-      <c r="B92" s="51">
-        <f>ROW(B92) - ROW($B$9)</f>
+      <c r="B92" s="52">
+        <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="C92" s="61" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="D92" s="38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E92" s="65" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F92" s="39" t="s">
-        <v>437</v>
+        <v>233</v>
       </c>
       <c r="G92" s="38" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="H92" s="39" t="s">
-        <v>360</v>
-      </c>
-      <c r="I92" s="38" t="s">
-        <v>448</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="I92" s="38"/>
       <c r="J92" s="39" t="s">
-        <v>530</v>
+        <v>437</v>
       </c>
       <c r="K92" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L92" s="39">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M92" s="38">
-        <f>L92*5</f>
-        <v>35</v>
+        <f t="shared" ref="M92" si="82">L92*5</f>
+        <v>10</v>
       </c>
       <c r="N92" s="38">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="O92" s="66" t="s">
-        <v>468</v>
+        <v>544</v>
       </c>
       <c r="P92" s="53">
-        <v>0.6905</v>
+        <v>8.8239999999999998</v>
       </c>
       <c r="Q92" s="42">
-        <f>P92*N92</f>
-        <v>25.548500000000001</v>
+        <f t="shared" ref="Q92" si="83">P92*N92</f>
+        <v>105.88800000000001</v>
       </c>
       <c r="R92" s="39"/>
       <c r="S92" s="38"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="B93" s="52">
-        <f t="shared" si="0"/>
+      <c r="B93" s="51">
+        <f>ROW(B93) - ROW($B$9)</f>
         <v>84</v>
       </c>
-      <c r="C93" s="70" t="s">
-        <v>548</v>
+      <c r="C93" s="62" t="s">
+        <v>537</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F93" s="41" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="G93" s="40" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="H93" s="41" t="s">
-        <v>361</v>
-      </c>
-      <c r="I93" s="40"/>
+        <v>352</v>
+      </c>
+      <c r="I93" s="40" t="s">
+        <v>437</v>
+      </c>
       <c r="J93" s="41" t="s">
-        <v>448</v>
+        <v>520</v>
       </c>
       <c r="K93" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L93" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M93" s="40">
-        <f t="shared" ref="M93" si="84">L93*5</f>
-        <v>10</v>
+        <f>L93*5</f>
+        <v>5</v>
       </c>
       <c r="N93" s="41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O93" s="67" t="s">
-        <v>555</v>
+        <v>457</v>
       </c>
       <c r="P93" s="54">
-        <v>8.8239999999999998</v>
+        <v>0.39779999999999999</v>
       </c>
       <c r="Q93" s="43">
-        <f t="shared" ref="Q93" si="85">P93*N93</f>
-        <v>105.88800000000001</v>
+        <f>P93*N93</f>
+        <v>2.3868</v>
       </c>
       <c r="R93" s="41"/>
       <c r="S93" s="40"/>
     </row>
-    <row r="94" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
-      <c r="B94" s="51">
-        <f>ROW(B94) - ROW($B$9)</f>
+      <c r="B94" s="52">
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="C94" s="71" t="s">
-        <v>548</v>
+      <c r="C94" s="61" t="s">
+        <v>537</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E94" s="65" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F94" s="39" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="G94" s="38" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="H94" s="39" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I94" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J94" s="39" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="K94" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L94" s="39">
         <v>1</v>
       </c>
       <c r="M94" s="38">
-        <f>L94*5</f>
+        <f t="shared" ref="M94" si="84">L94*5</f>
         <v>5</v>
       </c>
       <c r="N94" s="38">
         <v>6</v>
       </c>
       <c r="O94" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P94" s="53">
-        <v>0.39779999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="Q94" s="42">
-        <f>P94*N94</f>
-        <v>2.3868</v>
+        <f t="shared" ref="Q94" si="85">P94*N94</f>
+        <v>6.1859999999999999</v>
       </c>
       <c r="R94" s="39"/>
       <c r="S94" s="38"/>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
-      <c r="B95" s="52">
-        <f t="shared" si="0"/>
+      <c r="B95" s="51">
+        <f>ROW(B95) - ROW($B$9)</f>
         <v>86</v>
       </c>
-      <c r="C95" s="70" t="s">
-        <v>548</v>
+      <c r="C95" s="62" t="s">
+        <v>537</v>
       </c>
       <c r="D95" s="40" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F95" s="41" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G95" s="40" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="H95" s="41" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="I95" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J95" s="41" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="K95" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L95" s="41">
         <v>1</v>
       </c>
       <c r="M95" s="40">
-        <f t="shared" ref="M95" si="86">L95*5</f>
+        <f>L95*5</f>
         <v>5</v>
       </c>
       <c r="N95" s="41">
         <v>6</v>
       </c>
       <c r="O95" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P95" s="54">
-        <v>1.0309999999999999</v>
+        <v>7.3596000000000004</v>
       </c>
       <c r="Q95" s="43">
-        <f t="shared" ref="Q95" si="87">P95*N95</f>
-        <v>6.1859999999999999</v>
+        <f>P95*N95</f>
+        <v>44.157600000000002</v>
       </c>
       <c r="R95" s="41"/>
       <c r="S95" s="40"/>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="B96" s="51">
-        <f>ROW(B96) - ROW($B$9)</f>
+      <c r="B96" s="52">
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="C96" s="71" t="s">
-        <v>548</v>
+      <c r="C96" s="61" t="s">
+        <v>537</v>
       </c>
       <c r="D96" s="38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E96" s="65" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F96" s="39" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="G96" s="38" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="H96" s="39" t="s">
-        <v>363</v>
+        <v>321</v>
       </c>
       <c r="I96" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J96" s="39" t="s">
-        <v>533</v>
+        <v>437</v>
       </c>
       <c r="K96" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L96" s="39">
         <v>1</v>
       </c>
       <c r="M96" s="38">
-        <f>L96*5</f>
+        <f t="shared" ref="M96" si="86">L96*5</f>
         <v>5</v>
       </c>
       <c r="N96" s="38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O96" s="66" t="s">
-        <v>468</v>
+        <v>544</v>
       </c>
       <c r="P96" s="53">
-        <v>7.3596000000000004</v>
+        <v>6.944</v>
       </c>
       <c r="Q96" s="42">
-        <f>P96*N96</f>
-        <v>44.157600000000002</v>
+        <f t="shared" ref="Q96" si="87">P96*N96</f>
+        <v>55.552</v>
       </c>
       <c r="R96" s="39"/>
       <c r="S96" s="38"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
-      <c r="B97" s="52">
-        <f t="shared" si="0"/>
+      <c r="B97" s="51">
+        <f>ROW(B97) - ROW($B$9)</f>
         <v>88</v>
       </c>
-      <c r="C97" s="70" t="s">
-        <v>548</v>
+      <c r="C97" s="62" t="s">
+        <v>537</v>
       </c>
       <c r="D97" s="40" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E97" s="40" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F97" s="41" t="s">
-        <v>241</v>
+        <v>440</v>
       </c>
       <c r="G97" s="40" t="s">
-        <v>317</v>
+        <v>236</v>
       </c>
       <c r="H97" s="41" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="I97" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J97" s="41" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="K97" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L97" s="41">
         <v>1</v>
       </c>
       <c r="M97" s="40">
-        <f t="shared" ref="M97" si="88">L97*5</f>
+        <f>L97*5</f>
         <v>5</v>
       </c>
       <c r="N97" s="41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O97" s="67" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="P97" s="54">
-        <v>6.944</v>
+        <v>8.2669999999999995</v>
       </c>
       <c r="Q97" s="43">
-        <f t="shared" ref="Q97" si="89">P97*N97</f>
-        <v>55.552</v>
+        <f>P97*N97</f>
+        <v>57.869</v>
       </c>
       <c r="R97" s="41"/>
       <c r="S97" s="40"/>
     </row>
     <row r="98" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
-      <c r="B98" s="51">
-        <f>ROW(B98) - ROW($B$9)</f>
+      <c r="B98" s="52">
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="C98" s="71" t="s">
-        <v>548</v>
+      <c r="C98" s="61" t="s">
+        <v>537</v>
       </c>
       <c r="D98" s="38" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E98" s="65" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F98" s="39" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="G98" s="38" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H98" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="I98" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J98" s="39" t="s">
-        <v>448</v>
+        <v>523</v>
       </c>
       <c r="K98" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L98" s="39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M98" s="38">
-        <f>L98*5</f>
-        <v>5</v>
+        <f t="shared" ref="M98" si="88">L98*5</f>
+        <v>20</v>
       </c>
       <c r="N98" s="38">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="O98" s="66" t="s">
-        <v>555</v>
+        <v>457</v>
       </c>
       <c r="P98" s="53">
-        <v>8.2669999999999995</v>
+        <v>0.41510000000000002</v>
       </c>
       <c r="Q98" s="42">
-        <f>P98*N98</f>
-        <v>57.869</v>
+        <f t="shared" ref="Q98" si="89">P98*N98</f>
+        <v>10.377500000000001</v>
       </c>
       <c r="R98" s="39"/>
       <c r="S98" s="38"/>
     </row>
-    <row r="99" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
-      <c r="B99" s="52">
-        <f t="shared" si="0"/>
+      <c r="B99" s="51">
+        <f>ROW(B99) - ROW($B$9)</f>
         <v>90</v>
       </c>
-      <c r="C99" s="70" t="s">
-        <v>548</v>
+      <c r="C99" s="62" t="s">
+        <v>537</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F99" s="41" t="s">
-        <v>449</v>
+        <v>238</v>
       </c>
       <c r="G99" s="40" t="s">
-        <v>245</v>
+        <v>309</v>
       </c>
       <c r="H99" s="41" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="I99" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J99" s="41" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="K99" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L99" s="41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M99" s="40">
-        <f t="shared" ref="M99" si="90">L99*5</f>
+        <f>L99*5</f>
+        <v>15</v>
+      </c>
+      <c r="N99" s="41">
         <v>20</v>
       </c>
-      <c r="N99" s="41">
-        <v>25</v>
-      </c>
       <c r="O99" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P99" s="54">
-        <v>0.41510000000000002</v>
+        <v>0.24310000000000001</v>
       </c>
       <c r="Q99" s="43">
-        <f t="shared" ref="Q99" si="91">P99*N99</f>
-        <v>10.377500000000001</v>
+        <f>P99*N99</f>
+        <v>4.8620000000000001</v>
       </c>
       <c r="R99" s="41"/>
       <c r="S99" s="40"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-      <c r="B100" s="51">
-        <f>ROW(B100) - ROW($B$9)</f>
+    <row r="100" spans="1:19" s="71" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A100" s="70"/>
+      <c r="B100" s="52">
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="C100" s="71" t="s">
-        <v>548</v>
+      <c r="C100" s="61" t="s">
+        <v>537</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E100" s="65" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F100" s="39" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G100" s="38" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="H100" s="39" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I100" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J100" s="39" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="K100" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L100" s="39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M100" s="38">
-        <f>L100*5</f>
-        <v>15</v>
+        <f t="shared" ref="M100" si="90">L100*5</f>
+        <v>5</v>
       </c>
       <c r="N100" s="38">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="O100" s="66" t="s">
-        <v>468</v>
+        <v>544</v>
       </c>
       <c r="P100" s="53">
-        <v>0.24310000000000001</v>
+        <v>4.7060000000000004</v>
       </c>
       <c r="Q100" s="42">
-        <f>P100*N100</f>
-        <v>4.8620000000000001</v>
-      </c>
-      <c r="R100" s="39"/>
+        <f t="shared" ref="Q100" si="91">P100*N100</f>
+        <v>51.766000000000005</v>
+      </c>
+      <c r="R100" s="72" t="s">
+        <v>546</v>
+      </c>
       <c r="S100" s="38"/>
     </row>
-    <row r="101" spans="1:19" s="83" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A101" s="82"/>
-      <c r="B101" s="52">
-        <f t="shared" si="0"/>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+      <c r="B101" s="51">
+        <f>ROW(B101) - ROW($B$9)</f>
         <v>92</v>
       </c>
-      <c r="C101" s="70" t="s">
-        <v>548</v>
+      <c r="C101" s="62" t="s">
+        <v>537</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F101" s="41" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="G101" s="40" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="H101" s="41" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="I101" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J101" s="41" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="K101" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L101" s="41">
         <v>1</v>
       </c>
       <c r="M101" s="40">
-        <f t="shared" ref="M101" si="92">L101*5</f>
+        <f>L101*5</f>
         <v>5</v>
       </c>
       <c r="N101" s="41">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O101" s="67" t="s">
-        <v>555</v>
+        <v>457</v>
       </c>
       <c r="P101" s="54">
-        <v>4.7060000000000004</v>
+        <v>4.0076000000000001</v>
       </c>
       <c r="Q101" s="43">
-        <f t="shared" ref="Q101" si="93">P101*N101</f>
-        <v>51.766000000000005</v>
-      </c>
-      <c r="R101" s="85" t="s">
-        <v>557</v>
+        <f>P101*N101</f>
+        <v>24.0456</v>
+      </c>
+      <c r="R101" s="73" t="s">
+        <v>545</v>
       </c>
       <c r="S101" s="40"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
-      <c r="B102" s="51">
-        <f>ROW(B102) - ROW($B$9)</f>
+      <c r="B102" s="52">
+        <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="C102" s="71" t="s">
-        <v>548</v>
+      <c r="C102" s="61" t="s">
+        <v>537</v>
       </c>
       <c r="D102" s="38" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E102" s="65" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>248</v>
+        <v>426</v>
       </c>
       <c r="G102" s="38" t="s">
-        <v>320</v>
+        <v>241</v>
       </c>
       <c r="H102" s="39" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="I102" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J102" s="39" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="K102" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L102" s="39">
         <v>1</v>
       </c>
       <c r="M102" s="38">
-        <f>L102*5</f>
+        <f t="shared" ref="M102" si="92">L102*5</f>
         <v>5</v>
       </c>
       <c r="N102" s="38">
         <v>6</v>
       </c>
       <c r="O102" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P102" s="53">
-        <v>4.0076000000000001</v>
+        <v>0.996</v>
       </c>
       <c r="Q102" s="42">
-        <f>P102*N102</f>
-        <v>24.0456</v>
-      </c>
-      <c r="R102" s="84" t="s">
-        <v>556</v>
-      </c>
+        <f t="shared" ref="Q102" si="93">P102*N102</f>
+        <v>5.976</v>
+      </c>
+      <c r="R102" s="39"/>
       <c r="S102" s="38"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
-      <c r="B103" s="52">
-        <f t="shared" si="0"/>
+      <c r="B103" s="51">
+        <f>ROW(B103) - ROW($B$9)</f>
         <v>94</v>
       </c>
-      <c r="C103" s="70" t="s">
-        <v>548</v>
+      <c r="C103" s="62" t="s">
+        <v>538</v>
       </c>
       <c r="D103" s="40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F103" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G103" s="40" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="H103" s="41" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="I103" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J103" s="41" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="K103" s="40" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="L103" s="41">
         <v>1</v>
       </c>
       <c r="M103" s="40">
-        <f t="shared" ref="M103" si="94">L103*5</f>
+        <f>L103*5</f>
         <v>5</v>
       </c>
       <c r="N103" s="41">
         <v>6</v>
       </c>
       <c r="O103" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P103" s="54">
-        <v>0.996</v>
+        <v>0.19889999999999999</v>
       </c>
       <c r="Q103" s="43">
-        <f t="shared" ref="Q103" si="95">P103*N103</f>
-        <v>5.976</v>
+        <f>P103*N103</f>
+        <v>1.1934</v>
       </c>
       <c r="R103" s="41"/>
       <c r="S103" s="40"/>
     </row>
     <row r="104" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
-      <c r="B104" s="51">
-        <f>ROW(B104) - ROW($B$9)</f>
+      <c r="B104" s="52">
+        <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="C104" s="71" t="s">
-        <v>549</v>
+      <c r="C104" s="61" t="s">
+        <v>538</v>
       </c>
       <c r="D104" s="38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E104" s="65" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F104" s="39" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G104" s="38" t="s">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="H104" s="39" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="I104" s="38" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J104" s="39" t="s">
-        <v>539</v>
+        <v>377</v>
       </c>
       <c r="K104" s="38" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="L104" s="39">
         <v>1</v>
       </c>
       <c r="M104" s="38">
-        <f>L104*5</f>
+        <f t="shared" ref="M104" si="94">L104*5</f>
         <v>5</v>
       </c>
       <c r="N104" s="38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O104" s="66" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P104" s="53">
-        <v>0.19889999999999999</v>
+        <v>9.9900000000000003E-2</v>
       </c>
       <c r="Q104" s="42">
-        <f>P104*N104</f>
-        <v>1.1934</v>
+        <f t="shared" ref="Q104" si="95">P104*N104</f>
+        <v>0.999</v>
       </c>
       <c r="R104" s="39"/>
       <c r="S104" s="38"/>
     </row>
-    <row r="105" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
-      <c r="B105" s="52">
-        <f t="shared" si="0"/>
+      <c r="B105" s="51">
+        <f>ROW(B105) - ROW($B$9)</f>
         <v>96</v>
       </c>
-      <c r="C105" s="70" t="s">
-        <v>549</v>
+      <c r="C105" s="62" t="s">
+        <v>538</v>
       </c>
       <c r="D105" s="40" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E105" s="40" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F105" s="41" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G105" s="40" t="s">
-        <v>321</v>
+        <v>243</v>
       </c>
       <c r="H105" s="41" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="I105" s="40" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J105" s="41" t="s">
-        <v>388</v>
+        <v>529</v>
       </c>
       <c r="K105" s="40" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="L105" s="41">
         <v>1</v>
       </c>
       <c r="M105" s="40">
-        <f t="shared" ref="M105" si="96">L105*5</f>
+        <f>L105*5</f>
         <v>5</v>
       </c>
       <c r="N105" s="41">
         <v>10</v>
       </c>
       <c r="O105" s="67" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P105" s="54">
-        <v>9.9900000000000003E-2</v>
+        <v>0.2218</v>
       </c>
       <c r="Q105" s="43">
-        <f t="shared" ref="Q105" si="97">P105*N105</f>
-        <v>0.999</v>
+        <f>P105*N105</f>
+        <v>2.218</v>
       </c>
       <c r="R105" s="41"/>
       <c r="S105" s="40"/>
     </row>
-    <row r="106" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
-      <c r="B106" s="51">
-        <f>ROW(B106) - ROW($B$9)</f>
-        <v>97</v>
-      </c>
-      <c r="C106" s="71" t="s">
-        <v>549</v>
-      </c>
-      <c r="D106" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="E106" s="65" t="s">
-        <v>198</v>
-      </c>
-      <c r="F106" s="39" t="s">
-        <v>437</v>
-      </c>
-      <c r="G106" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="H106" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="I106" s="38" t="s">
-        <v>448</v>
-      </c>
-      <c r="J106" s="39" t="s">
-        <v>540</v>
-      </c>
-      <c r="K106" s="38" t="s">
-        <v>434</v>
-      </c>
-      <c r="L106" s="39">
-        <v>1</v>
-      </c>
-      <c r="M106" s="38">
-        <f>L106*5</f>
+      <c r="B106" s="45"/>
+      <c r="C106" s="46"/>
+      <c r="D106" s="47"/>
+      <c r="E106" s="48"/>
+      <c r="F106" s="49"/>
+      <c r="G106" s="50"/>
+      <c r="H106" s="49"/>
+      <c r="I106" s="50"/>
+      <c r="J106" s="49"/>
+      <c r="K106" s="50"/>
+      <c r="L106" s="50"/>
+      <c r="M106" s="50"/>
+      <c r="N106" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="N106" s="38">
-        <v>10</v>
-      </c>
-      <c r="O106" s="66" t="s">
-        <v>468</v>
-      </c>
-      <c r="P106" s="53">
-        <v>0.2218</v>
-      </c>
-      <c r="Q106" s="42">
-        <f>P106*N106</f>
-        <v>2.218</v>
-      </c>
-      <c r="R106" s="39"/>
-      <c r="S106" s="38"/>
+      <c r="O106" s="83"/>
+      <c r="P106" s="83"/>
+      <c r="Q106" s="55">
+        <f>SUM(Q10:Q105)</f>
+        <v>570.04629999999997</v>
+      </c>
+      <c r="R106" s="78"/>
+      <c r="S106" s="79"/>
     </row>
     <row r="107" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
-      <c r="B107" s="45"/>
-      <c r="C107" s="46"/>
-      <c r="D107" s="47"/>
-      <c r="E107" s="48"/>
-      <c r="F107" s="49"/>
-      <c r="G107" s="50"/>
-      <c r="H107" s="49"/>
-      <c r="I107" s="50"/>
-      <c r="J107" s="49"/>
-      <c r="K107" s="50"/>
-      <c r="L107" s="50"/>
-      <c r="M107" s="50"/>
-      <c r="N107" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="O107" s="81"/>
-      <c r="P107" s="81"/>
-      <c r="Q107" s="55">
-        <f>SUM(Q10:Q106)</f>
-        <v>568.8522999999999</v>
-      </c>
-      <c r="R107" s="76"/>
-      <c r="S107" s="77"/>
-    </row>
-    <row r="108" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="1"/>
-      <c r="B108" s="25"/>
-      <c r="C108" s="37"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
-      <c r="I108" s="10"/>
-      <c r="J108" s="10"/>
-      <c r="K108" s="10"/>
-      <c r="L108" s="10"/>
-      <c r="M108" s="10"/>
-      <c r="N108" s="80" t="s">
+      <c r="B107" s="25"/>
+      <c r="C107" s="37"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="10"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="10"/>
+      <c r="H107" s="10"/>
+      <c r="I107" s="10"/>
+      <c r="J107" s="10"/>
+      <c r="K107" s="10"/>
+      <c r="L107" s="10"/>
+      <c r="M107" s="10"/>
+      <c r="N107" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="O108" s="81"/>
-      <c r="P108" s="81"/>
-      <c r="Q108" s="56">
-        <f>Q107/5</f>
-        <v>113.77045999999999</v>
-      </c>
-      <c r="R108" s="78"/>
-      <c r="S108" s="79"/>
+      <c r="O107" s="83"/>
+      <c r="P107" s="83"/>
+      <c r="Q107" s="56">
+        <f>Q106/5</f>
+        <v>114.00926</v>
+      </c>
+      <c r="R107" s="80"/>
+      <c r="S107" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R107:S108"/>
+    <mergeCell ref="R106:S107"/>
+    <mergeCell ref="N106:P106"/>
     <mergeCell ref="N107:P107"/>
-    <mergeCell ref="N108:P108"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1" xr:uid="{29545A6B-2DC3-435B-BADE-82C52630D80A}"/>
@@ -8540,16 +8532,16 @@
     <hyperlink ref="O78" r:id="rId60" xr:uid="{AC50B9CD-4B66-49C1-B9A4-755E6A3B7388}"/>
     <hyperlink ref="O86" r:id="rId61" xr:uid="{3149E9C4-8DCD-4B7B-AA56-C24793E1FDDD}"/>
     <hyperlink ref="O87" r:id="rId62" xr:uid="{216F92A5-F104-4692-B17C-6227E8D25A0E}"/>
-    <hyperlink ref="O92" r:id="rId63" xr:uid="{BB0086C3-2D05-4979-8CF3-0132D37DF1DB}"/>
-    <hyperlink ref="O95" r:id="rId64" xr:uid="{571AFD85-72FA-4D23-A240-55270E118838}"/>
-    <hyperlink ref="O96" r:id="rId65" xr:uid="{DB794ED7-FAF2-40D3-BCC4-3D87E9946E04}"/>
-    <hyperlink ref="O100" r:id="rId66" xr:uid="{7F416119-DC76-4A27-8048-AE23EAF496C5}"/>
-    <hyperlink ref="O102" r:id="rId67" xr:uid="{1D68F898-6AEA-42FA-94E2-9C9E1498344C}"/>
-    <hyperlink ref="O103" r:id="rId68" xr:uid="{C29175A2-1765-4C45-AC14-06BB76E02B1B}"/>
-    <hyperlink ref="O94" r:id="rId69" xr:uid="{8E588422-7B11-4B05-B296-3911285F17BA}"/>
-    <hyperlink ref="O99" r:id="rId70" xr:uid="{91FF6E37-C9BD-4631-8DF9-4A150C39A80E}"/>
-    <hyperlink ref="O104" r:id="rId71" xr:uid="{C85E336A-E4D8-4F42-95F8-19A806CF9075}"/>
-    <hyperlink ref="O106" r:id="rId72" xr:uid="{61C5202E-87B7-4DFF-BDE8-ADF25A51C4B6}"/>
+    <hyperlink ref="O91" r:id="rId63" xr:uid="{BB0086C3-2D05-4979-8CF3-0132D37DF1DB}"/>
+    <hyperlink ref="O94" r:id="rId64" xr:uid="{571AFD85-72FA-4D23-A240-55270E118838}"/>
+    <hyperlink ref="O95" r:id="rId65" xr:uid="{DB794ED7-FAF2-40D3-BCC4-3D87E9946E04}"/>
+    <hyperlink ref="O99" r:id="rId66" xr:uid="{7F416119-DC76-4A27-8048-AE23EAF496C5}"/>
+    <hyperlink ref="O101" r:id="rId67" xr:uid="{1D68F898-6AEA-42FA-94E2-9C9E1498344C}"/>
+    <hyperlink ref="O102" r:id="rId68" xr:uid="{C29175A2-1765-4C45-AC14-06BB76E02B1B}"/>
+    <hyperlink ref="O93" r:id="rId69" xr:uid="{8E588422-7B11-4B05-B296-3911285F17BA}"/>
+    <hyperlink ref="O98" r:id="rId70" xr:uid="{91FF6E37-C9BD-4631-8DF9-4A150C39A80E}"/>
+    <hyperlink ref="O103" r:id="rId71" xr:uid="{C85E336A-E4D8-4F42-95F8-19A806CF9075}"/>
+    <hyperlink ref="O105" r:id="rId72" xr:uid="{61C5202E-87B7-4DFF-BDE8-ADF25A51C4B6}"/>
     <hyperlink ref="O70" r:id="rId73" xr:uid="{66E54603-F7CF-4DC8-B868-925E9997D858}"/>
     <hyperlink ref="O73" r:id="rId74" xr:uid="{C69A5D4F-4932-4CB8-8443-136BE55217CE}"/>
     <hyperlink ref="O75" r:id="rId75" xr:uid="{3F774918-96E7-4172-9CF4-AA3E109A063E}"/>
@@ -8558,21 +8550,22 @@
     <hyperlink ref="O80" r:id="rId78" xr:uid="{84808F7E-9EDD-49D9-8971-82350D90541A}"/>
     <hyperlink ref="O88" r:id="rId79" xr:uid="{6911FE59-7388-45F0-8C34-AEBAC6FD6115}"/>
     <hyperlink ref="O89" r:id="rId80" xr:uid="{363BECF3-81E8-42F1-B8F0-D447AC307BC4}"/>
-    <hyperlink ref="O90" r:id="rId81" xr:uid="{A9B2E30D-0D28-463F-B5B4-02A931A14865}"/>
-    <hyperlink ref="O81" r:id="rId82" xr:uid="{7E81E536-23B5-4B5B-9C2F-DDA48D563A2C}"/>
-    <hyperlink ref="O82" r:id="rId83" xr:uid="{6D27FA1D-997B-4E9C-BAD8-F397C9652E5D}"/>
-    <hyperlink ref="O83" r:id="rId84" xr:uid="{22FFC267-8FDA-412D-9EBD-8D6DED0D52A7}"/>
-    <hyperlink ref="O84" r:id="rId85" xr:uid="{FE3B66E5-688A-410D-8C9C-4F1003F6068F}"/>
-    <hyperlink ref="O85" r:id="rId86" xr:uid="{996AA183-C9FB-468B-98CB-2A6E462BB81F}"/>
-    <hyperlink ref="O105" r:id="rId87" xr:uid="{D91A7680-9E8E-47E6-B633-5EBFAD828ADB}"/>
-    <hyperlink ref="O93" r:id="rId88" xr:uid="{AF26A144-373A-4F0B-B639-348CFDF1904B}"/>
-    <hyperlink ref="O97" r:id="rId89" xr:uid="{9A5052CF-F17F-468A-BDE6-9E352EC830F2}"/>
-    <hyperlink ref="O98" r:id="rId90" xr:uid="{C233F72D-B204-4E40-AAAD-9034CD27391F}"/>
-    <hyperlink ref="O55" r:id="rId91" xr:uid="{90C35BC1-76DB-4582-A11A-E5E703BB9959}"/>
-    <hyperlink ref="O32" r:id="rId92" xr:uid="{C27551A9-1645-49B0-8FCC-5E4209328A84}"/>
+    <hyperlink ref="O81" r:id="rId81" xr:uid="{7E81E536-23B5-4B5B-9C2F-DDA48D563A2C}"/>
+    <hyperlink ref="O82" r:id="rId82" xr:uid="{6D27FA1D-997B-4E9C-BAD8-F397C9652E5D}"/>
+    <hyperlink ref="O83" r:id="rId83" xr:uid="{22FFC267-8FDA-412D-9EBD-8D6DED0D52A7}"/>
+    <hyperlink ref="O84" r:id="rId84" xr:uid="{FE3B66E5-688A-410D-8C9C-4F1003F6068F}"/>
+    <hyperlink ref="O85" r:id="rId85" xr:uid="{996AA183-C9FB-468B-98CB-2A6E462BB81F}"/>
+    <hyperlink ref="O104" r:id="rId86" xr:uid="{D91A7680-9E8E-47E6-B633-5EBFAD828ADB}"/>
+    <hyperlink ref="O92" r:id="rId87" xr:uid="{AF26A144-373A-4F0B-B639-348CFDF1904B}"/>
+    <hyperlink ref="O96" r:id="rId88" xr:uid="{9A5052CF-F17F-468A-BDE6-9E352EC830F2}"/>
+    <hyperlink ref="O97" r:id="rId89" xr:uid="{C233F72D-B204-4E40-AAAD-9034CD27391F}"/>
+    <hyperlink ref="O55" r:id="rId90" xr:uid="{90C35BC1-76DB-4582-A11A-E5E703BB9959}"/>
+    <hyperlink ref="O32" r:id="rId91" xr:uid="{C27551A9-1645-49B0-8FCC-5E4209328A84}"/>
+    <hyperlink ref="O11" r:id="rId92" xr:uid="{CB26DDE1-0C10-4D39-AA3E-73DFC8C2B5F0}"/>
+    <hyperlink ref="O31" r:id="rId93" xr:uid="{BCB68738-F2BF-4F5A-83C2-B998009E23BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId93"/>
-  <drawing r:id="rId94"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId94"/>
+  <drawing r:id="rId95"/>
 </worksheet>
 </file>
--- a/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
+++ b/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFAD8F9-D2F5-4458-8D50-C5567E54A9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -1691,7 +1690,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -2364,38 +2363,6 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2428,6 +2395,38 @@
     </xf>
     <xf numFmtId="165" fontId="23" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2473,7 +2472,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2769,7 +2768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2805,15 +2804,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="75"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="86"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2863,7 +2862,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="76"/>
+      <c r="S3" s="87"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2888,7 +2887,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="77"/>
+      <c r="S4" s="88"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2913,7 +2912,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="77"/>
+      <c r="S5" s="88"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2934,7 +2933,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="77"/>
+      <c r="S6" s="88"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2955,7 +2954,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="77"/>
+      <c r="S7" s="88"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2976,7 +2975,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="77"/>
+      <c r="S8" s="88"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4221,10 +4220,10 @@
       <c r="D31" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="84" t="s">
+      <c r="E31" s="74" t="s">
         <v>551</v>
       </c>
-      <c r="F31" s="84" t="s">
+      <c r="F31" s="74" t="s">
         <v>198</v>
       </c>
       <c r="G31" s="40" t="s">
@@ -5111,7 +5110,7 @@
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="90" t="s">
+      <c r="C47" s="80" t="s">
         <v>395</v>
       </c>
       <c r="D47" s="68" t="s">
@@ -5120,44 +5119,44 @@
       <c r="E47" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="F47" s="91" t="s">
+      <c r="F47" s="81" t="s">
         <v>426</v>
       </c>
       <c r="G47" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="H47" s="91" t="s">
+      <c r="H47" s="81" t="s">
         <v>437</v>
       </c>
       <c r="I47" s="68" t="s">
         <v>437</v>
       </c>
-      <c r="J47" s="91" t="s">
+      <c r="J47" s="81" t="s">
         <v>437</v>
       </c>
       <c r="K47" s="68" t="s">
         <v>437</v>
       </c>
-      <c r="L47" s="91">
+      <c r="L47" s="81">
         <v>2</v>
       </c>
       <c r="M47" s="68">
         <f>L47*5</f>
         <v>10</v>
       </c>
-      <c r="N47" s="91" t="s">
-        <v>437</v>
-      </c>
-      <c r="O47" s="92" t="s">
-        <v>437</v>
-      </c>
-      <c r="P47" s="93" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q47" s="94" t="s">
-        <v>437</v>
-      </c>
-      <c r="R47" s="91"/>
+      <c r="N47" s="81" t="s">
+        <v>437</v>
+      </c>
+      <c r="O47" s="82" t="s">
+        <v>437</v>
+      </c>
+      <c r="P47" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q47" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="R47" s="81"/>
       <c r="S47" s="68"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -5593,17 +5592,17 @@
         <v>10</v>
       </c>
       <c r="N55" s="41">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O55" s="67" t="s">
-        <v>544</v>
+        <v>457</v>
       </c>
       <c r="P55" s="54">
-        <v>1.486</v>
+        <v>0.72070000000000001</v>
       </c>
       <c r="Q55" s="43">
         <f>P55*N55</f>
-        <v>52.01</v>
+        <v>28.827999999999999</v>
       </c>
       <c r="R55" s="41"/>
       <c r="S55" s="40"/>
@@ -7518,7 +7517,7 @@
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="C90" s="85" t="s">
+      <c r="C90" s="75" t="s">
         <v>231</v>
       </c>
       <c r="D90" s="69" t="s">
@@ -7527,25 +7526,25 @@
       <c r="E90" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="F90" s="86" t="s">
+      <c r="F90" s="76" t="s">
         <v>426</v>
       </c>
       <c r="G90" s="69" t="s">
         <v>231</v>
       </c>
-      <c r="H90" s="86" t="s">
+      <c r="H90" s="76" t="s">
         <v>437</v>
       </c>
       <c r="I90" s="69" t="s">
         <v>437</v>
       </c>
-      <c r="J90" s="86" t="s">
+      <c r="J90" s="76" t="s">
         <v>437</v>
       </c>
       <c r="K90" s="69" t="s">
         <v>437</v>
       </c>
-      <c r="L90" s="86">
+      <c r="L90" s="76">
         <v>42</v>
       </c>
       <c r="M90" s="69">
@@ -7555,16 +7554,16 @@
       <c r="N90" s="69" t="s">
         <v>437</v>
       </c>
-      <c r="O90" s="87" t="s">
-        <v>437</v>
-      </c>
-      <c r="P90" s="88" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q90" s="89" t="s">
-        <v>437</v>
-      </c>
-      <c r="R90" s="86"/>
+      <c r="O90" s="77" t="s">
+        <v>437</v>
+      </c>
+      <c r="P90" s="78" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q90" s="79" t="s">
+        <v>437</v>
+      </c>
+      <c r="R90" s="76"/>
       <c r="S90" s="69"/>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
@@ -8423,17 +8422,17 @@
       <c r="K106" s="50"/>
       <c r="L106" s="50"/>
       <c r="M106" s="50"/>
-      <c r="N106" s="82" t="s">
+      <c r="N106" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="O106" s="83"/>
-      <c r="P106" s="83"/>
+      <c r="O106" s="94"/>
+      <c r="P106" s="94"/>
       <c r="Q106" s="55">
         <f>SUM(Q10:Q105)</f>
-        <v>570.04629999999997</v>
-      </c>
-      <c r="R106" s="78"/>
-      <c r="S106" s="79"/>
+        <v>546.86429999999996</v>
+      </c>
+      <c r="R106" s="89"/>
+      <c r="S106" s="90"/>
     </row>
     <row r="107" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
@@ -8449,17 +8448,17 @@
       <c r="K107" s="10"/>
       <c r="L107" s="10"/>
       <c r="M107" s="10"/>
-      <c r="N107" s="82" t="s">
+      <c r="N107" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="O107" s="83"/>
-      <c r="P107" s="83"/>
+      <c r="O107" s="94"/>
+      <c r="P107" s="94"/>
       <c r="Q107" s="56">
         <f>Q106/5</f>
-        <v>114.00926</v>
-      </c>
-      <c r="R107" s="80"/>
-      <c r="S107" s="81"/>
+        <v>109.37285999999999</v>
+      </c>
+      <c r="R107" s="91"/>
+      <c r="S107" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8470,99 +8469,99 @@
     <mergeCell ref="N107:P107"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{29545A6B-2DC3-435B-BADE-82C52630D80A}"/>
-    <hyperlink ref="O12" r:id="rId2" xr:uid="{BBC75B9C-AC5D-49C9-A4C7-7FA9AFAC7874}"/>
-    <hyperlink ref="O13" r:id="rId3" xr:uid="{FB8725AF-0AB9-4F1B-878B-3AA336F9EE8A}"/>
-    <hyperlink ref="O14" r:id="rId4" xr:uid="{2CA36519-1001-4D49-A579-5B8253BCE21C}"/>
-    <hyperlink ref="O15" r:id="rId5" xr:uid="{1FAA7B4F-D535-448B-8EAD-D7A2AA6D8B34}"/>
-    <hyperlink ref="O16" r:id="rId6" xr:uid="{AD5B6527-FD56-4D41-ACC7-E3121BF43254}"/>
-    <hyperlink ref="O18" r:id="rId7" xr:uid="{19726889-79C0-4DF8-81EE-6D8FEF610496}"/>
-    <hyperlink ref="O17" r:id="rId8" xr:uid="{95F9C39D-35FC-427F-B5E3-7D596DF2C2CB}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{E4BC9E4C-DB1E-4DEA-90F5-9615226B2AF5}"/>
-    <hyperlink ref="O21" r:id="rId10" xr:uid="{E2E8C389-CB7B-4D67-8706-E4EBB41371FD}"/>
-    <hyperlink ref="O20" r:id="rId11" xr:uid="{BB9D5F01-EBD4-4503-BB49-B48D675332AC}"/>
-    <hyperlink ref="O22" r:id="rId12" xr:uid="{C6818809-9DFA-4DDF-84A1-D61479867C30}"/>
-    <hyperlink ref="O23" r:id="rId13" xr:uid="{6D953B1A-FFDE-495A-88E4-C240D4BF57B4}"/>
-    <hyperlink ref="O24" r:id="rId14" xr:uid="{5011D106-6A0F-4F6E-9267-F288D353B00E}"/>
-    <hyperlink ref="O25" r:id="rId15" xr:uid="{EE2ECDEC-E98A-45B1-B207-3DBAD2323660}"/>
-    <hyperlink ref="O26" r:id="rId16" xr:uid="{4D40891A-B988-44D6-9652-FE93505ACDB0}"/>
-    <hyperlink ref="O27" r:id="rId17" xr:uid="{7101BA46-1526-493C-8856-D44ED4DBFE8C}"/>
-    <hyperlink ref="O30" r:id="rId18" xr:uid="{B14A16AC-46E8-4557-95C5-7C8F1F28DAAC}"/>
-    <hyperlink ref="O29" r:id="rId19" xr:uid="{E8789C28-572E-4265-81C1-5A8B5C768F4E}"/>
-    <hyperlink ref="O33" r:id="rId20" xr:uid="{9F327C80-483D-4ED3-B6C2-E190C5CA625F}"/>
-    <hyperlink ref="O34" r:id="rId21" xr:uid="{57350570-67F1-4AD3-ADA6-073C92CC76DD}"/>
-    <hyperlink ref="O35" r:id="rId22" xr:uid="{87FD1FAE-61BF-4D8F-8390-E05304E09254}"/>
-    <hyperlink ref="O36" r:id="rId23" xr:uid="{2F56312B-0F9F-4659-8FAB-C974882883FA}"/>
-    <hyperlink ref="O37" r:id="rId24" xr:uid="{E56294A2-80BE-437F-BA1B-9D7D79AAA687}"/>
-    <hyperlink ref="O38" r:id="rId25" xr:uid="{C108D980-5003-4FCF-B535-A15F768FA423}"/>
-    <hyperlink ref="O41" r:id="rId26" xr:uid="{61C68625-2DEB-40CC-B0B7-4322723EBCB4}"/>
-    <hyperlink ref="O42" r:id="rId27" xr:uid="{854A4EED-287B-489E-AA0F-CAB0ED5419BB}"/>
-    <hyperlink ref="O43" r:id="rId28" xr:uid="{1E15DE01-165A-4C57-A176-7E783BDBE3BF}"/>
-    <hyperlink ref="O45" r:id="rId29" xr:uid="{171FE4FD-3B7C-4967-AF82-983B6BFE4AFA}"/>
-    <hyperlink ref="O46" r:id="rId30" xr:uid="{10340E91-428B-4115-8CBE-A9E5D59EE90B}"/>
-    <hyperlink ref="O53" r:id="rId31" xr:uid="{0006FFE0-C193-4F0C-85C1-42B9401BAC9B}"/>
-    <hyperlink ref="O40" r:id="rId32" xr:uid="{5D53CE1B-BF6C-4358-81EC-2144E782486A}"/>
-    <hyperlink ref="O49" r:id="rId33" xr:uid="{744404B1-7166-451B-B656-73B6689F805F}"/>
-    <hyperlink ref="O52" r:id="rId34" xr:uid="{E95B2246-35D8-45A7-B13E-9FFBAA5D82F3}"/>
-    <hyperlink ref="O54" r:id="rId35" xr:uid="{A1930886-B67F-4675-8663-FE1B886872F0}"/>
-    <hyperlink ref="O56" r:id="rId36" xr:uid="{4B3E5CD5-63AC-41FF-8F31-4A7E209E5854}"/>
-    <hyperlink ref="O44" r:id="rId37" xr:uid="{10572C88-0415-4A57-9B9D-50943BD946FB}"/>
-    <hyperlink ref="O50" r:id="rId38" xr:uid="{A0CCABC5-D4C5-4595-A3B3-40BBF95EF6D0}"/>
-    <hyperlink ref="O51" r:id="rId39" xr:uid="{7068324F-A2E7-4474-B729-DB1FF6472EA0}"/>
-    <hyperlink ref="O28" r:id="rId40" xr:uid="{CB3D49CF-7E19-4EB8-B41B-5C4EB03CB586}"/>
-    <hyperlink ref="O39" r:id="rId41" xr:uid="{22C2DA5A-BA2A-403C-A5BB-E1E3C904C04D}"/>
-    <hyperlink ref="O48" r:id="rId42" xr:uid="{EDCDD759-3F1D-41F4-8193-D4F65E3B4FC3}"/>
-    <hyperlink ref="O57" r:id="rId43" xr:uid="{456A4A05-84EF-4C2F-9896-3F0C45F994D9}"/>
-    <hyperlink ref="O58" r:id="rId44" xr:uid="{541E11B3-D69F-4EED-928F-AF296FDA000C}"/>
-    <hyperlink ref="O59" r:id="rId45" xr:uid="{6918C750-193B-4AB8-9229-44BC80D9E27C}"/>
-    <hyperlink ref="O60" r:id="rId46" xr:uid="{ADF98DFB-4F1C-460D-A899-62029D6893FA}"/>
-    <hyperlink ref="O61" r:id="rId47" xr:uid="{0AD278DF-C4E6-43AD-8B76-8F0E41A12346}"/>
-    <hyperlink ref="O62" r:id="rId48" xr:uid="{CDB769EF-3F11-4533-9B5D-F493CFBAF9A4}"/>
-    <hyperlink ref="O63" r:id="rId49" xr:uid="{00CCCDA1-0B54-4599-9573-471507073410}"/>
-    <hyperlink ref="O64" r:id="rId50" xr:uid="{C1645A06-B052-488B-A750-C446D699007D}"/>
-    <hyperlink ref="O65" r:id="rId51" xr:uid="{73A9CC2A-BE8E-4844-9585-17C8AE7A1A32}"/>
-    <hyperlink ref="O66" r:id="rId52" xr:uid="{BEAAD7B4-C902-484A-81ED-EA83E13A8C41}"/>
-    <hyperlink ref="O67" r:id="rId53" xr:uid="{8E3AA42A-1B35-46C7-B01A-71EDE622956E}"/>
-    <hyperlink ref="O68" r:id="rId54" xr:uid="{A1935079-A094-413F-B9A7-948CED36635C}"/>
-    <hyperlink ref="O69" r:id="rId55" xr:uid="{3D499A9E-8EE7-4BBB-ACDB-68931E11953D}"/>
-    <hyperlink ref="O71" r:id="rId56" xr:uid="{E07821F2-AD60-4F6B-98CC-E7E698DEAF18}"/>
-    <hyperlink ref="O72" r:id="rId57" xr:uid="{911EBAD4-8428-460D-A4D5-2A0E7245E766}"/>
-    <hyperlink ref="O74" r:id="rId58" xr:uid="{A92CD093-DFA7-4679-A7ED-780AA6E86E78}"/>
-    <hyperlink ref="O77" r:id="rId59" xr:uid="{DC34F4D1-1945-4AD0-85C8-A32483EC1576}"/>
-    <hyperlink ref="O78" r:id="rId60" xr:uid="{AC50B9CD-4B66-49C1-B9A4-755E6A3B7388}"/>
-    <hyperlink ref="O86" r:id="rId61" xr:uid="{3149E9C4-8DCD-4B7B-AA56-C24793E1FDDD}"/>
-    <hyperlink ref="O87" r:id="rId62" xr:uid="{216F92A5-F104-4692-B17C-6227E8D25A0E}"/>
-    <hyperlink ref="O91" r:id="rId63" xr:uid="{BB0086C3-2D05-4979-8CF3-0132D37DF1DB}"/>
-    <hyperlink ref="O94" r:id="rId64" xr:uid="{571AFD85-72FA-4D23-A240-55270E118838}"/>
-    <hyperlink ref="O95" r:id="rId65" xr:uid="{DB794ED7-FAF2-40D3-BCC4-3D87E9946E04}"/>
-    <hyperlink ref="O99" r:id="rId66" xr:uid="{7F416119-DC76-4A27-8048-AE23EAF496C5}"/>
-    <hyperlink ref="O101" r:id="rId67" xr:uid="{1D68F898-6AEA-42FA-94E2-9C9E1498344C}"/>
-    <hyperlink ref="O102" r:id="rId68" xr:uid="{C29175A2-1765-4C45-AC14-06BB76E02B1B}"/>
-    <hyperlink ref="O93" r:id="rId69" xr:uid="{8E588422-7B11-4B05-B296-3911285F17BA}"/>
-    <hyperlink ref="O98" r:id="rId70" xr:uid="{91FF6E37-C9BD-4631-8DF9-4A150C39A80E}"/>
-    <hyperlink ref="O103" r:id="rId71" xr:uid="{C85E336A-E4D8-4F42-95F8-19A806CF9075}"/>
-    <hyperlink ref="O105" r:id="rId72" xr:uid="{61C5202E-87B7-4DFF-BDE8-ADF25A51C4B6}"/>
-    <hyperlink ref="O70" r:id="rId73" xr:uid="{66E54603-F7CF-4DC8-B868-925E9997D858}"/>
-    <hyperlink ref="O73" r:id="rId74" xr:uid="{C69A5D4F-4932-4CB8-8443-136BE55217CE}"/>
-    <hyperlink ref="O75" r:id="rId75" xr:uid="{3F774918-96E7-4172-9CF4-AA3E109A063E}"/>
-    <hyperlink ref="O76" r:id="rId76" xr:uid="{9445D080-5AFC-4BB5-A92D-0655336394FC}"/>
-    <hyperlink ref="O79" r:id="rId77" xr:uid="{A97845DF-9458-4D61-ACC7-3C91301B9221}"/>
-    <hyperlink ref="O80" r:id="rId78" xr:uid="{84808F7E-9EDD-49D9-8971-82350D90541A}"/>
-    <hyperlink ref="O88" r:id="rId79" xr:uid="{6911FE59-7388-45F0-8C34-AEBAC6FD6115}"/>
-    <hyperlink ref="O89" r:id="rId80" xr:uid="{363BECF3-81E8-42F1-B8F0-D447AC307BC4}"/>
-    <hyperlink ref="O81" r:id="rId81" xr:uid="{7E81E536-23B5-4B5B-9C2F-DDA48D563A2C}"/>
-    <hyperlink ref="O82" r:id="rId82" xr:uid="{6D27FA1D-997B-4E9C-BAD8-F397C9652E5D}"/>
-    <hyperlink ref="O83" r:id="rId83" xr:uid="{22FFC267-8FDA-412D-9EBD-8D6DED0D52A7}"/>
-    <hyperlink ref="O84" r:id="rId84" xr:uid="{FE3B66E5-688A-410D-8C9C-4F1003F6068F}"/>
-    <hyperlink ref="O85" r:id="rId85" xr:uid="{996AA183-C9FB-468B-98CB-2A6E462BB81F}"/>
-    <hyperlink ref="O104" r:id="rId86" xr:uid="{D91A7680-9E8E-47E6-B633-5EBFAD828ADB}"/>
-    <hyperlink ref="O92" r:id="rId87" xr:uid="{AF26A144-373A-4F0B-B639-348CFDF1904B}"/>
-    <hyperlink ref="O96" r:id="rId88" xr:uid="{9A5052CF-F17F-468A-BDE6-9E352EC830F2}"/>
-    <hyperlink ref="O97" r:id="rId89" xr:uid="{C233F72D-B204-4E40-AAAD-9034CD27391F}"/>
-    <hyperlink ref="O55" r:id="rId90" xr:uid="{90C35BC1-76DB-4582-A11A-E5E703BB9959}"/>
-    <hyperlink ref="O32" r:id="rId91" xr:uid="{C27551A9-1645-49B0-8FCC-5E4209328A84}"/>
-    <hyperlink ref="O11" r:id="rId92" xr:uid="{CB26DDE1-0C10-4D39-AA3E-73DFC8C2B5F0}"/>
-    <hyperlink ref="O31" r:id="rId93" xr:uid="{BCB68738-F2BF-4F5A-83C2-B998009E23BA}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O17" r:id="rId8"/>
+    <hyperlink ref="O19" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O20" r:id="rId11"/>
+    <hyperlink ref="O22" r:id="rId12"/>
+    <hyperlink ref="O23" r:id="rId13"/>
+    <hyperlink ref="O24" r:id="rId14"/>
+    <hyperlink ref="O25" r:id="rId15"/>
+    <hyperlink ref="O26" r:id="rId16"/>
+    <hyperlink ref="O27" r:id="rId17"/>
+    <hyperlink ref="O30" r:id="rId18"/>
+    <hyperlink ref="O29" r:id="rId19"/>
+    <hyperlink ref="O33" r:id="rId20"/>
+    <hyperlink ref="O34" r:id="rId21"/>
+    <hyperlink ref="O35" r:id="rId22"/>
+    <hyperlink ref="O36" r:id="rId23"/>
+    <hyperlink ref="O37" r:id="rId24"/>
+    <hyperlink ref="O38" r:id="rId25"/>
+    <hyperlink ref="O41" r:id="rId26"/>
+    <hyperlink ref="O42" r:id="rId27"/>
+    <hyperlink ref="O43" r:id="rId28"/>
+    <hyperlink ref="O45" r:id="rId29"/>
+    <hyperlink ref="O46" r:id="rId30"/>
+    <hyperlink ref="O53" r:id="rId31"/>
+    <hyperlink ref="O40" r:id="rId32"/>
+    <hyperlink ref="O49" r:id="rId33"/>
+    <hyperlink ref="O52" r:id="rId34"/>
+    <hyperlink ref="O54" r:id="rId35"/>
+    <hyperlink ref="O56" r:id="rId36"/>
+    <hyperlink ref="O44" r:id="rId37"/>
+    <hyperlink ref="O50" r:id="rId38"/>
+    <hyperlink ref="O51" r:id="rId39"/>
+    <hyperlink ref="O28" r:id="rId40"/>
+    <hyperlink ref="O39" r:id="rId41"/>
+    <hyperlink ref="O48" r:id="rId42"/>
+    <hyperlink ref="O57" r:id="rId43"/>
+    <hyperlink ref="O58" r:id="rId44"/>
+    <hyperlink ref="O59" r:id="rId45"/>
+    <hyperlink ref="O60" r:id="rId46"/>
+    <hyperlink ref="O61" r:id="rId47"/>
+    <hyperlink ref="O62" r:id="rId48"/>
+    <hyperlink ref="O63" r:id="rId49"/>
+    <hyperlink ref="O64" r:id="rId50"/>
+    <hyperlink ref="O65" r:id="rId51"/>
+    <hyperlink ref="O66" r:id="rId52"/>
+    <hyperlink ref="O67" r:id="rId53"/>
+    <hyperlink ref="O68" r:id="rId54"/>
+    <hyperlink ref="O69" r:id="rId55"/>
+    <hyperlink ref="O71" r:id="rId56"/>
+    <hyperlink ref="O72" r:id="rId57"/>
+    <hyperlink ref="O74" r:id="rId58"/>
+    <hyperlink ref="O77" r:id="rId59"/>
+    <hyperlink ref="O78" r:id="rId60"/>
+    <hyperlink ref="O86" r:id="rId61"/>
+    <hyperlink ref="O87" r:id="rId62"/>
+    <hyperlink ref="O91" r:id="rId63"/>
+    <hyperlink ref="O94" r:id="rId64"/>
+    <hyperlink ref="O95" r:id="rId65"/>
+    <hyperlink ref="O99" r:id="rId66"/>
+    <hyperlink ref="O101" r:id="rId67"/>
+    <hyperlink ref="O102" r:id="rId68"/>
+    <hyperlink ref="O93" r:id="rId69"/>
+    <hyperlink ref="O98" r:id="rId70"/>
+    <hyperlink ref="O103" r:id="rId71"/>
+    <hyperlink ref="O105" r:id="rId72"/>
+    <hyperlink ref="O70" r:id="rId73"/>
+    <hyperlink ref="O73" r:id="rId74"/>
+    <hyperlink ref="O75" r:id="rId75"/>
+    <hyperlink ref="O76" r:id="rId76"/>
+    <hyperlink ref="O79" r:id="rId77"/>
+    <hyperlink ref="O80" r:id="rId78"/>
+    <hyperlink ref="O88" r:id="rId79"/>
+    <hyperlink ref="O89" r:id="rId80"/>
+    <hyperlink ref="O81" r:id="rId81"/>
+    <hyperlink ref="O82" r:id="rId82"/>
+    <hyperlink ref="O83" r:id="rId83"/>
+    <hyperlink ref="O84" r:id="rId84"/>
+    <hyperlink ref="O85" r:id="rId85"/>
+    <hyperlink ref="O104" r:id="rId86"/>
+    <hyperlink ref="O92" r:id="rId87"/>
+    <hyperlink ref="O96" r:id="rId88"/>
+    <hyperlink ref="O97" r:id="rId89"/>
+    <hyperlink ref="O55" r:id="rId90"/>
+    <hyperlink ref="O32" r:id="rId91"/>
+    <hyperlink ref="O11" r:id="rId92"/>
+    <hyperlink ref="O31" r:id="rId93"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId94"/>

--- a/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
+++ b/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="570">
   <si>
     <t>Component list</t>
   </si>
@@ -1008,9 +1008,6 @@
     <t>HJ Tech</t>
   </si>
   <si>
-    <t>DEALON</t>
-  </si>
-  <si>
     <t>Amphenol FCI</t>
   </si>
   <si>
@@ -1462,9 +1459,6 @@
   </si>
   <si>
     <t>C1509209</t>
-  </si>
-  <si>
-    <t>C2935994</t>
   </si>
   <si>
     <t>C281113</t>
@@ -1685,12 +1679,64 @@
   </si>
   <si>
     <t>V3_Board</t>
+  </si>
+  <si>
+    <t>320V 15A 2 2.5 1 12~24 5.08mm Green Plug P=5.08mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>KF2EDGK-5.08-2P-AA</t>
+  </si>
+  <si>
+    <t>Cixi Kefa Elec</t>
+  </si>
+  <si>
+    <t>C440880</t>
+  </si>
+  <si>
+    <t>C440881</t>
+  </si>
+  <si>
+    <t>320V 15A 3 2.5 1 12~24 5.08mm Green Plug P=5.08mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KF2EDGK-5.08-3P-AA
+</t>
+  </si>
+  <si>
+    <t>Mating Terminal</t>
+  </si>
+  <si>
+    <t>320V 15A 4 2.5 1 12~24 5.08mm Green Plug P=5.08mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>C440882</t>
+  </si>
+  <si>
+    <t>KF2EDGK-5.08-4P-AA</t>
+  </si>
+  <si>
+    <t>C2718488</t>
+  </si>
+  <si>
+    <t>BOOMELE</t>
+  </si>
+  <si>
+    <t>J18 Right Angle Header ha Ise vertical Header se Replace kia ha for Testing Purpose</t>
+  </si>
+  <si>
+    <t>Female Jumper</t>
+  </si>
+  <si>
+    <t>Daraz</t>
+  </si>
+  <si>
+    <t>Jumper Wires Male to Female 30cm 1 x 40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1891,7 +1937,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1907,12 +1953,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF03A4CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2228,10 +2268,10 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2259,20 +2299,8 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2294,16 +2322,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2327,25 +2352,16 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2358,12 +2374,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2379,21 +2389,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2427,6 +2422,51 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2472,7 +2512,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2770,7 +2810,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S107"/>
+  <dimension ref="A1:S111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="26" bestFit="1" customWidth="1"/>
@@ -2804,15 +2844,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="86"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2822,8 +2862,8 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="57" t="s">
-        <v>553</v>
+      <c r="F2" s="52" t="s">
+        <v>551</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2847,8 +2887,8 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="58" t="s">
-        <v>554</v>
+      <c r="F3" s="53" t="s">
+        <v>552</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2862,7 +2902,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="87"/>
+      <c r="S3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2872,8 +2912,8 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="59" t="s">
-        <v>554</v>
+      <c r="F4" s="54" t="s">
+        <v>552</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2887,7 +2927,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="88"/>
+      <c r="S4" s="73"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2897,7 +2937,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="60" t="s">
+      <c r="F5" s="55" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="15"/>
@@ -2912,7 +2952,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="88"/>
+      <c r="S5" s="73"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2933,7 +2973,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="88"/>
+      <c r="S6" s="73"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2954,7 +2994,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="88"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2975,7 +3015,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="88"/>
+      <c r="S8" s="73"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2991,56 +3031,56 @@
       <c r="E9" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="57" t="s">
         <v>192</v>
       </c>
       <c r="G9" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="58" t="s">
         <v>313</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="K9" s="30" t="s">
         <v>427</v>
       </c>
-      <c r="J9" s="31" t="s">
-        <v>361</v>
-      </c>
-      <c r="K9" s="30" t="s">
+      <c r="L9" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>428</v>
       </c>
-      <c r="L9" s="31" t="s">
-        <v>424</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="31" t="s">
         <v>429</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="O9" s="30" t="s">
         <v>430</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="31" t="s">
         <v>431</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="Q9" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="31" t="s">
         <v>433</v>
       </c>
-      <c r="R9" s="31" t="s">
+      <c r="S9" s="30" t="s">
         <v>434</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="51">
+      <c r="B10" s="47">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="56" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="38" t="s">
@@ -3050,22 +3090,22 @@
         <v>102</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H10" s="39" t="s">
         <v>314</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L10" s="39">
         <v>13</v>
@@ -3077,88 +3117,88 @@
       <c r="N10" s="38">
         <v>80</v>
       </c>
-      <c r="O10" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P10" s="42">
+      <c r="O10" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P10" s="40">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="Q10" s="42">
+      <c r="Q10" s="40">
         <f>P10*N10</f>
         <v>1.96</v>
       </c>
       <c r="R10" s="39"/>
-      <c r="S10" s="44"/>
+      <c r="S10" s="80"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="52">
+      <c r="B11" s="48">
         <f t="shared" ref="B11:B104" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="83" t="s">
         <v>193</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I11" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J11" s="41" t="s">
-        <v>362</v>
-      </c>
-      <c r="K11" s="40" t="s">
-        <v>379</v>
-      </c>
-      <c r="L11" s="41">
+      <c r="I11" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J11" s="83" t="s">
+        <v>361</v>
+      </c>
+      <c r="K11" s="82" t="s">
+        <v>378</v>
+      </c>
+      <c r="L11" s="83">
         <v>1</v>
       </c>
-      <c r="M11" s="40">
+      <c r="M11" s="82">
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>5</v>
       </c>
-      <c r="N11" s="41">
+      <c r="N11" s="83">
         <v>50</v>
       </c>
-      <c r="O11" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P11" s="54">
+      <c r="O11" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P11" s="85">
         <v>1.18E-2</v>
       </c>
-      <c r="Q11" s="43">
+      <c r="Q11" s="86">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
         <v>0.59</v>
       </c>
-      <c r="R11" s="41"/>
-      <c r="S11" s="40"/>
+      <c r="R11" s="83"/>
+      <c r="S11" s="82"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="51">
+      <c r="B12" s="47">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="56" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>447</v>
-      </c>
-      <c r="E12" s="65" t="s">
+        <v>446</v>
+      </c>
+      <c r="E12" s="59" t="s">
         <v>104</v>
       </c>
       <c r="F12" s="39" t="s">
@@ -3171,13 +3211,13 @@
         <v>315</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L12" s="39">
         <v>9</v>
@@ -3189,13 +3229,13 @@
       <c r="N12" s="38">
         <v>100</v>
       </c>
-      <c r="O12" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P12" s="53">
+      <c r="O12" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P12" s="49">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="Q12" s="42">
+      <c r="Q12" s="40">
         <f>P12*N12</f>
         <v>0.47000000000000003</v>
       </c>
@@ -3204,71 +3244,71 @@
     </row>
     <row r="13" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="52">
+      <c r="B13" s="48">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="F13" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G13" s="40" t="s">
+      <c r="F13" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G13" s="82" t="s">
         <v>195</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="83" t="s">
         <v>316</v>
       </c>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41" t="s">
-        <v>458</v>
-      </c>
-      <c r="K13" s="40" t="s">
-        <v>381</v>
-      </c>
-      <c r="L13" s="41">
+      <c r="I13" s="82"/>
+      <c r="J13" s="83" t="s">
+        <v>457</v>
+      </c>
+      <c r="K13" s="82" t="s">
+        <v>380</v>
+      </c>
+      <c r="L13" s="83">
         <v>5</v>
       </c>
-      <c r="M13" s="40">
+      <c r="M13" s="82">
         <f t="shared" ref="M13" si="3">L13*5</f>
         <v>25</v>
       </c>
-      <c r="N13" s="41">
+      <c r="N13" s="83">
         <v>27</v>
       </c>
-      <c r="O13" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P13" s="54">
+      <c r="O13" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P13" s="85">
         <v>0.28799999999999998</v>
       </c>
-      <c r="Q13" s="43">
+      <c r="Q13" s="86">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
         <v>7.7759999999999998</v>
       </c>
-      <c r="R13" s="41"/>
-      <c r="S13" s="40"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="82"/>
     </row>
     <row r="14" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="51">
+      <c r="B14" s="47">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="56" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>448</v>
-      </c>
-      <c r="E14" s="65" t="s">
+        <v>447</v>
+      </c>
+      <c r="E14" s="59" t="s">
         <v>106</v>
       </c>
       <c r="F14" s="39" t="s">
@@ -3281,13 +3321,13 @@
         <v>315</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L14" s="39">
         <v>37</v>
@@ -3299,13 +3339,13 @@
       <c r="N14" s="38">
         <v>200</v>
       </c>
-      <c r="O14" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P14" s="53">
+      <c r="O14" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P14" s="49">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="Q14" s="42">
+      <c r="Q14" s="40">
         <f>P14*N14</f>
         <v>0.54</v>
       </c>
@@ -3314,73 +3354,73 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="52">
+      <c r="B15" s="48">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G15" s="40" t="s">
+      <c r="F15" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G15" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="H15" s="83" t="s">
         <v>317</v>
       </c>
-      <c r="I15" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J15" s="41" t="s">
-        <v>460</v>
-      </c>
-      <c r="K15" s="40" t="s">
-        <v>382</v>
-      </c>
-      <c r="L15" s="41">
+      <c r="I15" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J15" s="83" t="s">
+        <v>459</v>
+      </c>
+      <c r="K15" s="82" t="s">
+        <v>381</v>
+      </c>
+      <c r="L15" s="83">
         <v>1</v>
       </c>
-      <c r="M15" s="40">
+      <c r="M15" s="82">
         <f t="shared" ref="M15" si="5">L15*5</f>
         <v>5</v>
       </c>
-      <c r="N15" s="41">
+      <c r="N15" s="83">
         <v>10</v>
       </c>
-      <c r="O15" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P15" s="54">
+      <c r="O15" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P15" s="85">
         <v>0.13789999999999999</v>
       </c>
-      <c r="Q15" s="43">
+      <c r="Q15" s="86">
         <f t="shared" ref="Q15" si="6">P15*N15</f>
         <v>1.379</v>
       </c>
-      <c r="R15" s="41"/>
-      <c r="S15" s="40"/>
+      <c r="R15" s="83"/>
+      <c r="S15" s="82"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="51">
+      <c r="B16" s="47">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="56" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>108</v>
       </c>
       <c r="F16" s="39" t="s">
@@ -3393,13 +3433,13 @@
         <v>315</v>
       </c>
       <c r="I16" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -3411,13 +3451,13 @@
       <c r="N16" s="38">
         <v>100</v>
       </c>
-      <c r="O16" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P16" s="53">
+      <c r="O16" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P16" s="49">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="Q16" s="42">
+      <c r="Q16" s="40">
         <f>P16*N16</f>
         <v>0.25</v>
       </c>
@@ -3426,73 +3466,73 @@
     </row>
     <row r="17" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="52">
+      <c r="B17" s="48">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="83" t="s">
         <v>197</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="82" t="s">
         <v>249</v>
       </c>
-      <c r="H17" s="41" t="s">
+      <c r="H17" s="83" t="s">
         <v>318</v>
       </c>
-      <c r="I17" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J17" s="41" t="s">
-        <v>462</v>
-      </c>
-      <c r="K17" s="40" t="s">
-        <v>380</v>
-      </c>
-      <c r="L17" s="41">
+      <c r="I17" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J17" s="83" t="s">
+        <v>461</v>
+      </c>
+      <c r="K17" s="82" t="s">
+        <v>379</v>
+      </c>
+      <c r="L17" s="83">
         <v>1</v>
       </c>
-      <c r="M17" s="40">
+      <c r="M17" s="82">
         <f t="shared" ref="M17" si="7">L17*5</f>
         <v>5</v>
       </c>
-      <c r="N17" s="41">
+      <c r="N17" s="83">
         <v>6</v>
       </c>
-      <c r="O17" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P17" s="54">
+      <c r="O17" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P17" s="85">
         <v>0.19359999999999999</v>
       </c>
-      <c r="Q17" s="43">
+      <c r="Q17" s="86">
         <f t="shared" ref="Q17" si="8">P17*N17</f>
         <v>1.1616</v>
       </c>
-      <c r="R17" s="41"/>
-      <c r="S17" s="40"/>
+      <c r="R17" s="83"/>
+      <c r="S17" s="82"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="51">
+      <c r="B18" s="47">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="56" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="59" t="s">
         <v>110</v>
       </c>
       <c r="F18" s="39" t="s">
@@ -3505,13 +3545,13 @@
         <v>315</v>
       </c>
       <c r="I18" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J18" s="39" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L18" s="39">
         <v>2</v>
@@ -3523,13 +3563,13 @@
       <c r="N18" s="38">
         <v>100</v>
       </c>
-      <c r="O18" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P18" s="53">
+      <c r="O18" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P18" s="49">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="Q18" s="42">
+      <c r="Q18" s="40">
         <f>P18*N18</f>
         <v>0.26</v>
       </c>
@@ -3538,73 +3578,73 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="52">
+      <c r="B19" s="48">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>465</v>
-      </c>
-      <c r="E19" s="40" t="s">
+      <c r="D19" s="82" t="s">
+        <v>464</v>
+      </c>
+      <c r="E19" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="83" t="s">
         <v>194</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="82" t="s">
         <v>251</v>
       </c>
-      <c r="H19" s="41" t="s">
+      <c r="H19" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I19" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J19" s="41" t="s">
-        <v>365</v>
-      </c>
-      <c r="K19" s="40" t="s">
-        <v>385</v>
-      </c>
-      <c r="L19" s="41">
+      <c r="I19" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J19" s="83" t="s">
+        <v>364</v>
+      </c>
+      <c r="K19" s="82" t="s">
+        <v>384</v>
+      </c>
+      <c r="L19" s="83">
         <v>4</v>
       </c>
-      <c r="M19" s="40">
+      <c r="M19" s="82">
         <f t="shared" ref="M19" si="9">L19*5</f>
         <v>20</v>
       </c>
-      <c r="N19" s="41">
+      <c r="N19" s="83">
         <v>100</v>
       </c>
-      <c r="O19" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P19" s="54">
+      <c r="O19" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P19" s="85">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="Q19" s="43">
+      <c r="Q19" s="86">
         <f t="shared" ref="Q19" si="10">P19*N19</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="R19" s="41"/>
-      <c r="S19" s="40"/>
+      <c r="R19" s="83"/>
+      <c r="S19" s="82"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="51">
+      <c r="B20" s="47">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="56" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="59" t="s">
         <v>112</v>
       </c>
       <c r="F20" s="39" t="s">
@@ -3617,13 +3657,13 @@
         <v>315</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L20" s="39">
         <v>1</v>
@@ -3635,13 +3675,13 @@
       <c r="N20" s="38">
         <v>20</v>
       </c>
-      <c r="O20" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P20" s="53">
+      <c r="O20" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P20" s="49">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="Q20" s="42">
+      <c r="Q20" s="40">
         <f>P20*N20</f>
         <v>0.70400000000000007</v>
       </c>
@@ -3650,73 +3690,73 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="52">
+      <c r="B21" s="48">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="F21" s="83" t="s">
         <v>194</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="82" t="s">
         <v>253</v>
       </c>
-      <c r="H21" s="41" t="s">
+      <c r="H21" s="83" t="s">
         <v>319</v>
       </c>
-      <c r="I21" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J21" s="41" t="s">
-        <v>464</v>
-      </c>
-      <c r="K21" s="40" t="s">
-        <v>387</v>
-      </c>
-      <c r="L21" s="41">
+      <c r="I21" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J21" s="83" t="s">
+        <v>463</v>
+      </c>
+      <c r="K21" s="82" t="s">
+        <v>386</v>
+      </c>
+      <c r="L21" s="83">
         <v>1</v>
       </c>
-      <c r="M21" s="40">
+      <c r="M21" s="82">
         <f t="shared" ref="M21" si="11">L21*5</f>
         <v>5</v>
       </c>
-      <c r="N21" s="41">
+      <c r="N21" s="83">
         <v>20</v>
       </c>
-      <c r="O21" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P21" s="54">
+      <c r="O21" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P21" s="85">
         <v>3.04E-2</v>
       </c>
-      <c r="Q21" s="43">
+      <c r="Q21" s="86">
         <f t="shared" ref="Q21" si="12">P21*N21</f>
         <v>0.60799999999999998</v>
       </c>
-      <c r="R21" s="41"/>
-      <c r="S21" s="40"/>
+      <c r="R21" s="83"/>
+      <c r="S21" s="82"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="52">
+      <c r="B22" s="48">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="56" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="65" t="s">
+      <c r="E22" s="59" t="s">
         <v>114</v>
       </c>
       <c r="F22" s="39" t="s">
@@ -3729,13 +3769,13 @@
         <v>315</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L22" s="39">
         <v>1</v>
@@ -3747,13 +3787,13 @@
       <c r="N22" s="38">
         <v>100</v>
       </c>
-      <c r="O22" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P22" s="53">
+      <c r="O22" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P22" s="49">
         <v>3.3E-3</v>
       </c>
-      <c r="Q22" s="42">
+      <c r="Q22" s="40">
         <f t="shared" ref="Q22" si="14">P22*N22</f>
         <v>0.33</v>
       </c>
@@ -3762,73 +3802,73 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="51">
+      <c r="B23" s="47">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="82" t="s">
         <v>115</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="83" t="s">
         <v>194</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="82" t="s">
         <v>255</v>
       </c>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="83" t="s">
         <v>319</v>
       </c>
-      <c r="I23" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J23" s="41" t="s">
-        <v>467</v>
-      </c>
-      <c r="K23" s="40" t="s">
-        <v>389</v>
-      </c>
-      <c r="L23" s="41">
+      <c r="I23" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J23" s="83" t="s">
+        <v>466</v>
+      </c>
+      <c r="K23" s="82" t="s">
+        <v>388</v>
+      </c>
+      <c r="L23" s="83">
         <v>1</v>
       </c>
-      <c r="M23" s="40">
+      <c r="M23" s="82">
         <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="41">
+      <c r="N23" s="83">
         <v>20</v>
       </c>
-      <c r="O23" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P23" s="54">
+      <c r="O23" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P23" s="85">
         <v>2.9899999999999999E-2</v>
       </c>
-      <c r="Q23" s="43">
+      <c r="Q23" s="86">
         <f>P23*N23</f>
         <v>0.59799999999999998</v>
       </c>
-      <c r="R23" s="41"/>
-      <c r="S23" s="40"/>
+      <c r="R23" s="83"/>
+      <c r="S23" s="82"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="52">
+      <c r="B24" s="48">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="56" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="59" t="s">
         <v>116</v>
       </c>
       <c r="F24" s="39" t="s">
@@ -3841,13 +3881,13 @@
         <v>315</v>
       </c>
       <c r="I24" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L24" s="39">
         <v>1</v>
@@ -3859,13 +3899,13 @@
       <c r="N24" s="38">
         <v>100</v>
       </c>
-      <c r="O24" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P24" s="53">
+      <c r="O24" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P24" s="49">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="Q24" s="42">
+      <c r="Q24" s="40">
         <f t="shared" ref="Q24" si="16">P24*N24</f>
         <v>0.31</v>
       </c>
@@ -3874,73 +3914,73 @@
     </row>
     <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="51">
+      <c r="B25" s="47">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="40" t="s">
+      <c r="E25" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="F25" s="41" t="s">
+      <c r="F25" s="83" t="s">
         <v>198</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="82" t="s">
         <v>257</v>
       </c>
-      <c r="H25" s="41" t="s">
+      <c r="H25" s="83" t="s">
         <v>320</v>
       </c>
-      <c r="I25" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J25" s="41" t="s">
-        <v>469</v>
-      </c>
-      <c r="K25" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L25" s="41">
+      <c r="I25" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J25" s="83" t="s">
+        <v>468</v>
+      </c>
+      <c r="K25" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L25" s="83">
         <v>1</v>
       </c>
-      <c r="M25" s="40">
+      <c r="M25" s="82">
         <f>L25*5</f>
         <v>5</v>
       </c>
-      <c r="N25" s="41">
+      <c r="N25" s="83">
         <v>20</v>
       </c>
-      <c r="O25" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P25" s="54">
+      <c r="O25" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P25" s="85">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="Q25" s="43">
+      <c r="Q25" s="86">
         <f>P25*N25</f>
         <v>0.65799999999999992</v>
       </c>
-      <c r="R25" s="41"/>
-      <c r="S25" s="40"/>
+      <c r="R25" s="83"/>
+      <c r="S25" s="82"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="52">
+      <c r="B26" s="48">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="56" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="65" t="s">
+      <c r="E26" s="59" t="s">
         <v>118</v>
       </c>
       <c r="F26" s="39" t="s">
@@ -3953,13 +3993,13 @@
         <v>321</v>
       </c>
       <c r="I26" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L26" s="39">
         <v>1</v>
@@ -3971,13 +4011,13 @@
       <c r="N26" s="38">
         <v>6</v>
       </c>
-      <c r="O26" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P26" s="53">
+      <c r="O26" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P26" s="49">
         <v>0.49009999999999998</v>
       </c>
-      <c r="Q26" s="42">
+      <c r="Q26" s="40">
         <f t="shared" ref="Q26" si="18">P26*N26</f>
         <v>2.9405999999999999</v>
       </c>
@@ -3986,73 +4026,73 @@
     </row>
     <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="51">
+      <c r="B27" s="47">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="40" t="s">
+      <c r="D27" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="40" t="s">
+      <c r="E27" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="F27" s="41" t="s">
+      <c r="F27" s="83" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="82" t="s">
         <v>199</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="H27" s="83" t="s">
         <v>322</v>
       </c>
-      <c r="I27" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J27" s="41" t="s">
-        <v>471</v>
-      </c>
-      <c r="K27" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L27" s="41">
+      <c r="I27" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J27" s="83" t="s">
+        <v>470</v>
+      </c>
+      <c r="K27" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L27" s="83">
         <v>1</v>
       </c>
-      <c r="M27" s="40">
+      <c r="M27" s="82">
         <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N27" s="41">
+      <c r="N27" s="83">
         <v>20</v>
       </c>
-      <c r="O27" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P27" s="54">
+      <c r="O27" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P27" s="85">
         <v>3.1399999999999997E-2</v>
       </c>
-      <c r="Q27" s="43">
+      <c r="Q27" s="86">
         <f>P27*N27</f>
         <v>0.62799999999999989</v>
       </c>
-      <c r="R27" s="41"/>
-      <c r="S27" s="40"/>
+      <c r="R27" s="83"/>
+      <c r="S27" s="82"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="52">
+      <c r="B28" s="48">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="56" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="59" t="s">
         <v>120</v>
       </c>
       <c r="F28" s="39" t="s">
@@ -4065,13 +4105,13 @@
         <v>323</v>
       </c>
       <c r="I28" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L28" s="39">
         <v>5</v>
@@ -4083,13 +4123,13 @@
       <c r="N28" s="38">
         <v>40</v>
       </c>
-      <c r="O28" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P28" s="53">
+      <c r="O28" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P28" s="49">
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="Q28" s="42">
+      <c r="Q28" s="40">
         <f t="shared" ref="Q28" si="20">P28*N28</f>
         <v>0.81600000000000006</v>
       </c>
@@ -4098,73 +4138,73 @@
     </row>
     <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="51">
+      <c r="B29" s="47">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="62" t="s">
+      <c r="C29" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="40" t="s">
+      <c r="E29" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="F29" s="83" t="s">
         <v>201</v>
       </c>
-      <c r="G29" s="40" t="s">
+      <c r="G29" s="82" t="s">
         <v>260</v>
       </c>
-      <c r="H29" s="41" t="s">
+      <c r="H29" s="83" t="s">
         <v>324</v>
       </c>
-      <c r="I29" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J29" s="41" t="s">
-        <v>472</v>
-      </c>
-      <c r="K29" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L29" s="41">
+      <c r="I29" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J29" s="83" t="s">
+        <v>471</v>
+      </c>
+      <c r="K29" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L29" s="83">
         <v>1</v>
       </c>
-      <c r="M29" s="40">
+      <c r="M29" s="82">
         <f>L29*5</f>
         <v>5</v>
       </c>
-      <c r="N29" s="41">
+      <c r="N29" s="83">
         <v>10</v>
       </c>
-      <c r="O29" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P29" s="54">
+      <c r="O29" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P29" s="85">
         <v>6.2700000000000006E-2</v>
       </c>
-      <c r="Q29" s="43">
+      <c r="Q29" s="86">
         <f>P29*N29</f>
         <v>0.627</v>
       </c>
-      <c r="R29" s="41"/>
-      <c r="S29" s="40"/>
+      <c r="R29" s="83"/>
+      <c r="S29" s="82"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="52">
+      <c r="B30" s="48">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="56" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>122</v>
       </c>
       <c r="F30" s="39" t="s">
@@ -4177,13 +4217,13 @@
         <v>325</v>
       </c>
       <c r="I30" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J30" s="39" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L30" s="39">
         <v>1</v>
@@ -4195,13 +4235,13 @@
       <c r="N30" s="38">
         <v>10</v>
       </c>
-      <c r="O30" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P30" s="53">
+      <c r="O30" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P30" s="49">
         <v>8.7099999999999997E-2</v>
       </c>
-      <c r="Q30" s="42">
+      <c r="Q30" s="40">
         <f t="shared" ref="Q30" si="22">P30*N30</f>
         <v>0.871</v>
       </c>
@@ -4210,92 +4250,92 @@
     </row>
     <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="51">
+      <c r="B31" s="47">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="62" t="s">
+      <c r="C31" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="74" t="s">
-        <v>551</v>
-      </c>
-      <c r="F31" s="74" t="s">
+      <c r="E31" s="38" t="s">
+        <v>549</v>
+      </c>
+      <c r="F31" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="40" t="s">
+      <c r="G31" s="82" t="s">
         <v>261</v>
       </c>
-      <c r="H31" s="41" t="s">
+      <c r="H31" s="83" t="s">
         <v>325</v>
       </c>
-      <c r="I31" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J31" s="41" t="s">
-        <v>552</v>
-      </c>
-      <c r="K31" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L31" s="41">
+      <c r="I31" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J31" s="83" t="s">
+        <v>550</v>
+      </c>
+      <c r="K31" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L31" s="83">
         <v>1</v>
       </c>
-      <c r="M31" s="40">
+      <c r="M31" s="82">
         <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="41">
+      <c r="N31" s="83">
         <v>20</v>
       </c>
-      <c r="O31" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P31" s="54">
+      <c r="O31" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P31" s="85">
         <v>3.6200000000000003E-2</v>
       </c>
-      <c r="Q31" s="43">
+      <c r="Q31" s="86">
         <f>P31*N31</f>
         <v>0.72400000000000009</v>
       </c>
-      <c r="R31" s="41"/>
-      <c r="S31" s="40"/>
+      <c r="R31" s="83"/>
+      <c r="S31" s="82"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="52">
+      <c r="B32" s="48">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="61" t="s">
-        <v>439</v>
+      <c r="C32" s="56" t="s">
+        <v>438</v>
       </c>
       <c r="D32" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="65" t="s">
+      <c r="E32" s="59" t="s">
         <v>123</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>426</v>
-      </c>
-      <c r="G32" s="69" t="s">
+        <v>425</v>
+      </c>
+      <c r="G32" s="61" t="s">
         <v>203</v>
       </c>
       <c r="H32" s="39" t="s">
         <v>326</v>
       </c>
       <c r="I32" s="38" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L32" s="39">
         <v>1</v>
@@ -4307,13 +4347,13 @@
       <c r="N32" s="38">
         <v>6</v>
       </c>
-      <c r="O32" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P32" s="53">
+      <c r="O32" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P32" s="49">
         <v>0.61729999999999996</v>
       </c>
-      <c r="Q32" s="42">
+      <c r="Q32" s="40">
         <f t="shared" ref="Q32" si="24">P32*N32</f>
         <v>3.7037999999999998</v>
       </c>
@@ -4322,92 +4362,92 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="51">
+      <c r="B33" s="47">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="62" t="s">
-        <v>442</v>
-      </c>
-      <c r="D33" s="40" t="s">
+      <c r="C33" s="81" t="s">
+        <v>441</v>
+      </c>
+      <c r="D33" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="40" t="s">
+      <c r="E33" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G33" s="68" t="s">
+      <c r="F33" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G33" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="H33" s="41" t="s">
+      <c r="H33" s="83" t="s">
         <v>327</v>
       </c>
-      <c r="I33" s="40" t="s">
-        <v>474</v>
-      </c>
-      <c r="J33" s="41" t="s">
-        <v>477</v>
-      </c>
-      <c r="K33" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L33" s="41">
+      <c r="I33" s="82" t="s">
+        <v>473</v>
+      </c>
+      <c r="J33" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="K33" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L33" s="83">
         <v>9</v>
       </c>
-      <c r="M33" s="40">
+      <c r="M33" s="82">
         <f>L33*5</f>
         <v>45</v>
       </c>
-      <c r="N33" s="41">
+      <c r="N33" s="83">
         <v>50</v>
       </c>
-      <c r="O33" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P33" s="54">
+      <c r="O33" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P33" s="85">
         <v>7.1199999999999999E-2</v>
       </c>
-      <c r="Q33" s="43">
+      <c r="Q33" s="86">
         <f>P33*N33</f>
         <v>3.56</v>
       </c>
-      <c r="R33" s="41"/>
-      <c r="S33" s="40"/>
+      <c r="R33" s="83"/>
+      <c r="S33" s="82"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="52">
+      <c r="B34" s="48">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="61" t="s">
-        <v>442</v>
+      <c r="C34" s="56" t="s">
+        <v>441</v>
       </c>
       <c r="D34" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="E34" s="65" t="s">
+      <c r="E34" s="59" t="s">
         <v>124</v>
       </c>
       <c r="F34" s="39" t="s">
-        <v>426</v>
-      </c>
-      <c r="G34" s="69" t="s">
+        <v>425</v>
+      </c>
+      <c r="G34" s="61" t="s">
         <v>205</v>
       </c>
       <c r="H34" s="39" t="s">
         <v>327</v>
       </c>
       <c r="I34" s="38" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J34" s="39" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L34" s="39">
         <v>5</v>
@@ -4419,13 +4459,13 @@
       <c r="N34" s="38">
         <v>30</v>
       </c>
-      <c r="O34" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P34" s="53">
+      <c r="O34" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P34" s="49">
         <v>0.10539999999999999</v>
       </c>
-      <c r="Q34" s="42">
+      <c r="Q34" s="40">
         <f t="shared" ref="Q34" si="26">P34*N34</f>
         <v>3.1619999999999999</v>
       </c>
@@ -4434,77 +4474,77 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="51">
+      <c r="B35" s="47">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="62" t="s">
-        <v>442</v>
-      </c>
-      <c r="D35" s="40" t="s">
+      <c r="C35" s="81" t="s">
+        <v>441</v>
+      </c>
+      <c r="D35" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="E35" s="40" t="s">
+      <c r="E35" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="F35" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G35" s="68" t="s">
+      <c r="F35" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G35" s="87" t="s">
         <v>206</v>
       </c>
-      <c r="H35" s="41" t="s">
+      <c r="H35" s="83" t="s">
         <v>327</v>
       </c>
-      <c r="I35" s="40" t="s">
-        <v>476</v>
-      </c>
-      <c r="J35" s="41" t="s">
-        <v>479</v>
-      </c>
-      <c r="K35" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L35" s="41">
+      <c r="I35" s="82" t="s">
+        <v>475</v>
+      </c>
+      <c r="J35" s="83" t="s">
+        <v>478</v>
+      </c>
+      <c r="K35" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L35" s="83">
         <v>1</v>
       </c>
-      <c r="M35" s="40">
+      <c r="M35" s="82">
         <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="41">
+      <c r="N35" s="83">
         <v>10</v>
       </c>
-      <c r="O35" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P35" s="54">
+      <c r="O35" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P35" s="85">
         <v>0.1114</v>
       </c>
-      <c r="Q35" s="43">
+      <c r="Q35" s="86">
         <f>P35*N35</f>
         <v>1.1139999999999999</v>
       </c>
-      <c r="R35" s="41"/>
-      <c r="S35" s="40"/>
+      <c r="R35" s="83"/>
+      <c r="S35" s="82"/>
     </row>
     <row r="36" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="52">
+      <c r="B36" s="48">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="61" t="s">
-        <v>443</v>
+      <c r="C36" s="56" t="s">
+        <v>442</v>
       </c>
       <c r="D36" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="59" t="s">
         <v>125</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G36" s="38" t="s">
         <v>207</v>
@@ -4513,13 +4553,13 @@
         <v>328</v>
       </c>
       <c r="I36" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L36" s="39">
         <v>1</v>
@@ -4531,107 +4571,109 @@
       <c r="N36" s="38">
         <v>6</v>
       </c>
-      <c r="O36" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P36" s="53">
+      <c r="O36" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P36" s="49">
         <v>0.75180000000000002</v>
       </c>
-      <c r="Q36" s="42">
+      <c r="Q36" s="40">
         <f t="shared" ref="Q36" si="28">P36*N36</f>
         <v>4.5107999999999997</v>
       </c>
       <c r="R36" s="39"/>
       <c r="S36" s="38"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="51">
+      <c r="B37" s="47">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="62" t="s">
-        <v>439</v>
-      </c>
-      <c r="D37" s="40" t="s">
+      <c r="C37" s="81" t="s">
+        <v>438</v>
+      </c>
+      <c r="D37" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="E37" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="F37" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G37" s="40" t="s">
+      <c r="F37" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G37" s="87" t="s">
         <v>208</v>
       </c>
-      <c r="H37" s="41" t="s">
-        <v>329</v>
-      </c>
-      <c r="I37" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J37" s="41" t="s">
-        <v>481</v>
-      </c>
-      <c r="K37" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L37" s="41">
+      <c r="H37" s="83" t="s">
+        <v>565</v>
+      </c>
+      <c r="I37" s="82" t="s">
+        <v>564</v>
+      </c>
+      <c r="J37" s="83" t="s">
+        <v>564</v>
+      </c>
+      <c r="K37" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L37" s="83">
         <v>1</v>
       </c>
-      <c r="M37" s="40">
+      <c r="M37" s="82">
         <f>L37*5</f>
         <v>5</v>
       </c>
-      <c r="N37" s="41">
+      <c r="N37" s="83">
         <v>10</v>
       </c>
-      <c r="O37" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P37" s="54">
-        <v>6.4299999999999996E-2</v>
-      </c>
-      <c r="Q37" s="43">
+      <c r="O37" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P37" s="85">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="Q37" s="86">
         <f>P37*N37</f>
-        <v>0.64300000000000002</v>
-      </c>
-      <c r="R37" s="41"/>
-      <c r="S37" s="40"/>
+        <v>0.43200000000000005</v>
+      </c>
+      <c r="R37" s="93" t="s">
+        <v>566</v>
+      </c>
+      <c r="S37" s="82"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="52">
+      <c r="B38" s="48">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="56" t="s">
         <v>11</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="E38" s="65" t="s">
+      <c r="E38" s="59" t="s">
         <v>127</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G38" s="38" t="s">
         <v>262</v>
       </c>
       <c r="H38" s="39" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I38" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L38" s="39">
         <v>1</v>
@@ -4643,13 +4685,13 @@
       <c r="N38" s="38">
         <v>6</v>
       </c>
-      <c r="O38" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P38" s="53">
+      <c r="O38" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P38" s="49">
         <v>0.22120000000000001</v>
       </c>
-      <c r="Q38" s="42">
+      <c r="Q38" s="40">
         <f t="shared" ref="Q38" si="30">P38*N38</f>
         <v>1.3271999999999999</v>
       </c>
@@ -4658,73 +4700,73 @@
     </row>
     <row r="39" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="51">
+      <c r="B39" s="47">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="40" t="s">
+      <c r="D39" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="E39" s="40" t="s">
+      <c r="E39" s="82" t="s">
         <v>128</v>
       </c>
-      <c r="F39" s="41" t="s">
+      <c r="F39" s="83" t="s">
         <v>209</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="82" t="s">
         <v>263</v>
       </c>
-      <c r="H39" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="I39" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J39" s="41" t="s">
-        <v>368</v>
-      </c>
-      <c r="K39" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L39" s="41">
+      <c r="H39" s="83" t="s">
+        <v>330</v>
+      </c>
+      <c r="I39" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J39" s="83" t="s">
+        <v>367</v>
+      </c>
+      <c r="K39" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L39" s="83">
         <v>5</v>
       </c>
-      <c r="M39" s="40">
+      <c r="M39" s="82">
         <f>L39*5</f>
         <v>25</v>
       </c>
-      <c r="N39" s="41">
+      <c r="N39" s="83">
         <v>27</v>
       </c>
-      <c r="O39" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P39" s="54">
+      <c r="O39" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P39" s="85">
         <v>1.2012</v>
       </c>
-      <c r="Q39" s="43">
+      <c r="Q39" s="86">
         <f>P39*N39</f>
         <v>32.432400000000001</v>
       </c>
-      <c r="R39" s="41"/>
-      <c r="S39" s="40"/>
+      <c r="R39" s="83"/>
+      <c r="S39" s="82"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="52">
+      <c r="B40" s="48">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="61" t="s">
-        <v>444</v>
+      <c r="C40" s="56" t="s">
+        <v>443</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E40" s="65" t="s">
+      <c r="E40" s="59" t="s">
         <v>129</v>
       </c>
       <c r="F40" s="39" t="s">
@@ -4734,16 +4776,16 @@
         <v>264</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I40" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L40" s="39">
         <v>1</v>
@@ -4755,13 +4797,13 @@
       <c r="N40" s="38">
         <v>10</v>
       </c>
-      <c r="O40" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P40" s="53">
+      <c r="O40" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P40" s="49">
         <v>4.0399999999999998E-2</v>
       </c>
-      <c r="Q40" s="42">
+      <c r="Q40" s="40">
         <f t="shared" ref="Q40" si="32">P40*N40</f>
         <v>0.40399999999999997</v>
       </c>
@@ -4770,73 +4812,73 @@
     </row>
     <row r="41" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="51">
+      <c r="B41" s="47">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="62" t="s">
-        <v>444</v>
-      </c>
-      <c r="D41" s="40" t="s">
+      <c r="C41" s="81" t="s">
+        <v>443</v>
+      </c>
+      <c r="D41" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="E41" s="40" t="s">
+      <c r="E41" s="82" t="s">
         <v>130</v>
       </c>
-      <c r="F41" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G41" s="40" t="s">
+      <c r="F41" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G41" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="H41" s="41" t="s">
-        <v>333</v>
-      </c>
-      <c r="I41" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J41" s="41" t="s">
-        <v>483</v>
-      </c>
-      <c r="K41" s="40" t="s">
-        <v>392</v>
-      </c>
-      <c r="L41" s="41">
+      <c r="H41" s="83" t="s">
+        <v>332</v>
+      </c>
+      <c r="I41" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J41" s="83" t="s">
+        <v>481</v>
+      </c>
+      <c r="K41" s="82" t="s">
+        <v>391</v>
+      </c>
+      <c r="L41" s="83">
         <v>1</v>
       </c>
-      <c r="M41" s="40">
+      <c r="M41" s="82">
         <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="41">
+      <c r="N41" s="83">
         <v>6</v>
       </c>
-      <c r="O41" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P41" s="54">
+      <c r="O41" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P41" s="85">
         <v>0.47249999999999998</v>
       </c>
-      <c r="Q41" s="43">
+      <c r="Q41" s="86">
         <f>P41*N41</f>
         <v>2.835</v>
       </c>
-      <c r="R41" s="41"/>
-      <c r="S41" s="40"/>
+      <c r="R41" s="83"/>
+      <c r="S41" s="82"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="52">
+      <c r="B42" s="48">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="61" t="s">
-        <v>444</v>
+      <c r="C42" s="56" t="s">
+        <v>443</v>
       </c>
       <c r="D42" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E42" s="59" t="s">
         <v>131</v>
       </c>
       <c r="F42" s="39" t="s">
@@ -4846,16 +4888,16 @@
         <v>265</v>
       </c>
       <c r="H42" s="39" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I42" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J42" s="39" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L42" s="39">
         <v>1</v>
@@ -4867,13 +4909,13 @@
       <c r="N42" s="38">
         <v>10</v>
       </c>
-      <c r="O42" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P42" s="53">
+      <c r="O42" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P42" s="49">
         <v>7.9100000000000004E-2</v>
       </c>
-      <c r="Q42" s="42">
+      <c r="Q42" s="40">
         <f t="shared" ref="Q42" si="34">P42*N42</f>
         <v>0.79100000000000004</v>
       </c>
@@ -4882,92 +4924,92 @@
     </row>
     <row r="43" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="51">
+      <c r="B43" s="47">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="62" t="s">
-        <v>444</v>
-      </c>
-      <c r="D43" s="40" t="s">
+      <c r="C43" s="81" t="s">
+        <v>443</v>
+      </c>
+      <c r="D43" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="40" t="s">
+      <c r="E43" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="F43" s="41" t="s">
+      <c r="F43" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="G43" s="40" t="s">
+      <c r="G43" s="82" t="s">
         <v>266</v>
       </c>
-      <c r="H43" s="41" t="s">
-        <v>335</v>
-      </c>
-      <c r="I43" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J43" s="41" t="s">
-        <v>485</v>
-      </c>
-      <c r="K43" s="40" t="s">
-        <v>394</v>
-      </c>
-      <c r="L43" s="41">
+      <c r="H43" s="83" t="s">
+        <v>334</v>
+      </c>
+      <c r="I43" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J43" s="83" t="s">
+        <v>483</v>
+      </c>
+      <c r="K43" s="82" t="s">
+        <v>393</v>
+      </c>
+      <c r="L43" s="83">
         <v>1</v>
       </c>
-      <c r="M43" s="40">
+      <c r="M43" s="82">
         <f>L43*5</f>
         <v>5</v>
       </c>
-      <c r="N43" s="41">
+      <c r="N43" s="83">
         <v>10</v>
       </c>
-      <c r="O43" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P43" s="54">
+      <c r="O43" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P43" s="85">
         <v>8.5099999999999995E-2</v>
       </c>
-      <c r="Q43" s="43">
+      <c r="Q43" s="86">
         <f>P43*N43</f>
         <v>0.85099999999999998</v>
       </c>
-      <c r="R43" s="41"/>
-      <c r="S43" s="40"/>
+      <c r="R43" s="83"/>
+      <c r="S43" s="82"/>
     </row>
     <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="52">
+      <c r="B44" s="48">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="61" t="s">
-        <v>445</v>
+      <c r="C44" s="56" t="s">
+        <v>444</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>133</v>
       </c>
       <c r="F44" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="G44" s="69" t="s">
+      <c r="G44" s="61" t="s">
         <v>267</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I44" s="38" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L44" s="39">
         <v>7</v>
@@ -4979,13 +5021,13 @@
       <c r="N44" s="38">
         <v>40</v>
       </c>
-      <c r="O44" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P44" s="53">
+      <c r="O44" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P44" s="49">
         <v>3.5400000000000001E-2</v>
       </c>
-      <c r="Q44" s="42">
+      <c r="Q44" s="40">
         <f t="shared" ref="Q44" si="36">P44*N44</f>
         <v>1.4159999999999999</v>
       </c>
@@ -4994,92 +5036,92 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="51">
+      <c r="B45" s="47">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="62" t="s">
-        <v>445</v>
-      </c>
-      <c r="D45" s="40" t="s">
+      <c r="C45" s="81" t="s">
+        <v>444</v>
+      </c>
+      <c r="D45" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="40" t="s">
+      <c r="E45" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="F45" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G45" s="40" t="s">
+      <c r="F45" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G45" s="82" t="s">
         <v>268</v>
       </c>
-      <c r="H45" s="41" t="s">
-        <v>337</v>
-      </c>
-      <c r="I45" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J45" s="41" t="s">
-        <v>487</v>
-      </c>
-      <c r="K45" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L45" s="41">
+      <c r="H45" s="83" t="s">
+        <v>336</v>
+      </c>
+      <c r="I45" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J45" s="83" t="s">
+        <v>485</v>
+      </c>
+      <c r="K45" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L45" s="83">
         <v>1</v>
       </c>
-      <c r="M45" s="40">
+      <c r="M45" s="82">
         <f>L45*5</f>
         <v>5</v>
       </c>
-      <c r="N45" s="41">
+      <c r="N45" s="83">
         <v>10</v>
       </c>
-      <c r="O45" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P45" s="54">
+      <c r="O45" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P45" s="85">
         <v>0.1216</v>
       </c>
-      <c r="Q45" s="43">
+      <c r="Q45" s="86">
         <f>P45*N45</f>
         <v>1.216</v>
       </c>
-      <c r="R45" s="41"/>
-      <c r="S45" s="40"/>
+      <c r="R45" s="83"/>
+      <c r="S45" s="82"/>
     </row>
     <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="52">
+      <c r="B46" s="48">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="61" t="s">
-        <v>446</v>
+      <c r="C46" s="56" t="s">
+        <v>445</v>
       </c>
       <c r="D46" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E46" s="59" t="s">
         <v>135</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G46" s="38" t="s">
         <v>215</v>
       </c>
       <c r="H46" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I46" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L46" s="39">
         <v>1</v>
@@ -5091,13 +5133,13 @@
       <c r="N46" s="38">
         <v>6</v>
       </c>
-      <c r="O46" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P46" s="53">
+      <c r="O46" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P46" s="49">
         <v>0.34010000000000001</v>
       </c>
-      <c r="Q46" s="42">
+      <c r="Q46" s="40">
         <f t="shared" ref="Q46" si="38">P46*N46</f>
         <v>2.0406</v>
       </c>
@@ -5106,91 +5148,91 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="51">
+      <c r="B47" s="47">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="80" t="s">
-        <v>395</v>
-      </c>
-      <c r="D47" s="68" t="s">
+      <c r="C47" s="88" t="s">
+        <v>394</v>
+      </c>
+      <c r="D47" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="E47" s="68" t="s">
+      <c r="E47" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="F47" s="81" t="s">
-        <v>426</v>
-      </c>
-      <c r="G47" s="68" t="s">
+      <c r="F47" s="89" t="s">
+        <v>425</v>
+      </c>
+      <c r="G47" s="87" t="s">
         <v>216</v>
       </c>
-      <c r="H47" s="81" t="s">
-        <v>437</v>
-      </c>
-      <c r="I47" s="68" t="s">
-        <v>437</v>
-      </c>
-      <c r="J47" s="81" t="s">
-        <v>437</v>
-      </c>
-      <c r="K47" s="68" t="s">
-        <v>437</v>
-      </c>
-      <c r="L47" s="81">
+      <c r="H47" s="89" t="s">
+        <v>436</v>
+      </c>
+      <c r="I47" s="87" t="s">
+        <v>436</v>
+      </c>
+      <c r="J47" s="89" t="s">
+        <v>436</v>
+      </c>
+      <c r="K47" s="87" t="s">
+        <v>436</v>
+      </c>
+      <c r="L47" s="89">
         <v>2</v>
       </c>
-      <c r="M47" s="68">
+      <c r="M47" s="87">
         <f>L47*5</f>
         <v>10</v>
       </c>
-      <c r="N47" s="81" t="s">
-        <v>437</v>
-      </c>
-      <c r="O47" s="82" t="s">
-        <v>437</v>
-      </c>
-      <c r="P47" s="83" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q47" s="84" t="s">
-        <v>437</v>
-      </c>
-      <c r="R47" s="81"/>
-      <c r="S47" s="68"/>
+      <c r="N47" s="89" t="s">
+        <v>436</v>
+      </c>
+      <c r="O47" s="90" t="s">
+        <v>436</v>
+      </c>
+      <c r="P47" s="91" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q47" s="92" t="s">
+        <v>436</v>
+      </c>
+      <c r="R47" s="89"/>
+      <c r="S47" s="87"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="52">
+      <c r="B48" s="48">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="61" t="s">
-        <v>439</v>
+      <c r="C48" s="56" t="s">
+        <v>438</v>
       </c>
       <c r="D48" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="65" t="s">
+      <c r="E48" s="59" t="s">
         <v>137</v>
       </c>
       <c r="F48" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="G48" s="69">
+      <c r="G48" s="61">
         <v>61300311121</v>
       </c>
       <c r="H48" s="39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L48" s="39">
         <v>2</v>
@@ -5202,13 +5244,13 @@
       <c r="N48" s="38">
         <v>50</v>
       </c>
-      <c r="O48" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P48" s="53">
+      <c r="O48" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P48" s="49">
         <v>1.44E-2</v>
       </c>
-      <c r="Q48" s="42">
+      <c r="Q48" s="40">
         <f t="shared" ref="Q48" si="40">P48*N48</f>
         <v>0.72</v>
       </c>
@@ -5217,92 +5259,92 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="51">
+      <c r="B49" s="47">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="62" t="s">
-        <v>439</v>
-      </c>
-      <c r="D49" s="40" t="s">
+      <c r="C49" s="81" t="s">
+        <v>438</v>
+      </c>
+      <c r="D49" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="E49" s="40" t="s">
+      <c r="E49" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="F49" s="41" t="s">
+      <c r="F49" s="83" t="s">
         <v>218</v>
       </c>
-      <c r="G49" s="68">
+      <c r="G49" s="87">
         <v>61300611121</v>
       </c>
-      <c r="H49" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="I49" s="40" t="s">
-        <v>497</v>
-      </c>
-      <c r="J49" s="41" t="s">
-        <v>489</v>
-      </c>
-      <c r="K49" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L49" s="41">
+      <c r="H49" s="83" t="s">
+        <v>338</v>
+      </c>
+      <c r="I49" s="82" t="s">
+        <v>495</v>
+      </c>
+      <c r="J49" s="83" t="s">
+        <v>487</v>
+      </c>
+      <c r="K49" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L49" s="83">
         <v>4</v>
       </c>
-      <c r="M49" s="40">
+      <c r="M49" s="82">
         <f>L49*5</f>
         <v>20</v>
       </c>
-      <c r="N49" s="41">
+      <c r="N49" s="83">
         <v>40</v>
       </c>
-      <c r="O49" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P49" s="54">
+      <c r="O49" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P49" s="85">
         <v>2.9700000000000001E-2</v>
       </c>
-      <c r="Q49" s="43">
+      <c r="Q49" s="86">
         <f>P49*N49</f>
         <v>1.1879999999999999</v>
       </c>
-      <c r="R49" s="41"/>
-      <c r="S49" s="40"/>
+      <c r="R49" s="83"/>
+      <c r="S49" s="82"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="52">
+      <c r="B50" s="48">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="61" t="s">
-        <v>439</v>
+      <c r="C50" s="56" t="s">
+        <v>438</v>
       </c>
       <c r="D50" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E50" s="59" t="s">
         <v>139</v>
       </c>
       <c r="F50" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="G50" s="69" t="s">
+      <c r="G50" s="61" t="s">
         <v>269</v>
       </c>
       <c r="H50" s="39" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L50" s="39">
         <v>1</v>
@@ -5314,13 +5356,13 @@
       <c r="N50" s="38">
         <v>10</v>
       </c>
-      <c r="O50" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P50" s="53">
+      <c r="O50" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P50" s="49">
         <v>0.11509999999999999</v>
       </c>
-      <c r="Q50" s="42">
+      <c r="Q50" s="40">
         <f t="shared" ref="Q50" si="42">P50*N50</f>
         <v>1.151</v>
       </c>
@@ -5329,92 +5371,92 @@
     </row>
     <row r="51" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="51">
+      <c r="B51" s="47">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="62" t="s">
-        <v>439</v>
-      </c>
-      <c r="D51" s="40" t="s">
+      <c r="C51" s="81" t="s">
+        <v>438</v>
+      </c>
+      <c r="D51" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="E51" s="40" t="s">
+      <c r="E51" s="82" t="s">
         <v>140</v>
       </c>
-      <c r="F51" s="41" t="s">
+      <c r="F51" s="83" t="s">
         <v>220</v>
       </c>
-      <c r="G51" s="68">
+      <c r="G51" s="87">
         <v>61300211121</v>
       </c>
-      <c r="H51" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="I51" s="40" t="s">
-        <v>498</v>
-      </c>
-      <c r="J51" s="41" t="s">
-        <v>491</v>
-      </c>
-      <c r="K51" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L51" s="41">
+      <c r="H51" s="83" t="s">
+        <v>338</v>
+      </c>
+      <c r="I51" s="82" t="s">
+        <v>496</v>
+      </c>
+      <c r="J51" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="K51" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L51" s="83">
         <v>3</v>
       </c>
-      <c r="M51" s="40">
+      <c r="M51" s="82">
         <f>L51*5</f>
         <v>15</v>
       </c>
-      <c r="N51" s="41">
+      <c r="N51" s="83">
         <v>50</v>
       </c>
-      <c r="O51" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P51" s="54">
+      <c r="O51" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P51" s="85">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="Q51" s="43">
+      <c r="Q51" s="86">
         <f>P51*N51</f>
         <v>0.66499999999999992</v>
       </c>
-      <c r="R51" s="41"/>
-      <c r="S51" s="40"/>
+      <c r="R51" s="83"/>
+      <c r="S51" s="82"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="52">
+      <c r="B52" s="48">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="61" t="s">
-        <v>439</v>
+      <c r="C52" s="56" t="s">
+        <v>438</v>
       </c>
       <c r="D52" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="E52" s="65" t="s">
+      <c r="E52" s="59" t="s">
         <v>141</v>
       </c>
       <c r="F52" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="G52" s="69">
+      <c r="G52" s="61">
         <v>61300411121</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I52" s="38" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L52" s="39">
         <v>1</v>
@@ -5426,13 +5468,13 @@
       <c r="N52" s="38">
         <v>20</v>
       </c>
-      <c r="O52" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P52" s="53">
+      <c r="O52" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P52" s="49">
         <v>2.18E-2</v>
       </c>
-      <c r="Q52" s="42">
+      <c r="Q52" s="40">
         <f t="shared" ref="Q52" si="44">P52*N52</f>
         <v>0.436</v>
       </c>
@@ -5441,73 +5483,73 @@
     </row>
     <row r="53" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="51">
+      <c r="B53" s="47">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="62" t="s">
+      <c r="C53" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="40" t="s">
+      <c r="D53" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="E53" s="40" t="s">
+      <c r="E53" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="F53" s="41" t="s">
+      <c r="F53" s="83" t="s">
         <v>222</v>
       </c>
-      <c r="G53" s="40" t="s">
+      <c r="G53" s="82" t="s">
         <v>270</v>
       </c>
-      <c r="H53" s="41" t="s">
+      <c r="H53" s="83" t="s">
         <v>323</v>
       </c>
-      <c r="I53" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J53" s="41" t="s">
-        <v>493</v>
-      </c>
-      <c r="K53" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L53" s="41">
+      <c r="I53" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J53" s="83" t="s">
+        <v>491</v>
+      </c>
+      <c r="K53" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L53" s="83">
         <v>9</v>
       </c>
-      <c r="M53" s="40">
+      <c r="M53" s="82">
         <f>L53*5</f>
         <v>45</v>
       </c>
-      <c r="N53" s="41">
+      <c r="N53" s="83">
         <v>47</v>
       </c>
-      <c r="O53" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P53" s="54">
+      <c r="O53" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P53" s="85">
         <v>0.31269999999999998</v>
       </c>
-      <c r="Q53" s="43">
+      <c r="Q53" s="86">
         <f>P53*N53</f>
         <v>14.696899999999999</v>
       </c>
-      <c r="R53" s="41"/>
-      <c r="S53" s="40"/>
+      <c r="R53" s="83"/>
+      <c r="S53" s="82"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="52">
+      <c r="B54" s="48">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="61" t="s">
+      <c r="C54" s="56" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E54" s="65" t="s">
+      <c r="E54" s="59" t="s">
         <v>143</v>
       </c>
       <c r="F54" s="39" t="s">
@@ -5517,16 +5559,16 @@
         <v>271</v>
       </c>
       <c r="H54" s="39" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I54" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L54" s="39">
         <v>1</v>
@@ -5538,13 +5580,13 @@
       <c r="N54" s="38">
         <v>10</v>
       </c>
-      <c r="O54" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P54" s="53">
+      <c r="O54" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P54" s="49">
         <v>7.0800000000000002E-2</v>
       </c>
-      <c r="Q54" s="42">
+      <c r="Q54" s="40">
         <f t="shared" ref="Q54" si="46">P54*N54</f>
         <v>0.70799999999999996</v>
       </c>
@@ -5553,73 +5595,73 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="51">
+      <c r="B55" s="47">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="62" t="s">
+      <c r="C55" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="40" t="s">
+      <c r="D55" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="E55" s="40" t="s">
+      <c r="E55" s="82" t="s">
         <v>144</v>
       </c>
-      <c r="F55" s="41" t="s">
+      <c r="F55" s="83" t="s">
         <v>224</v>
       </c>
-      <c r="G55" s="40" t="s">
+      <c r="G55" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="H55" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="I55" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J55" s="41" t="s">
-        <v>437</v>
-      </c>
-      <c r="K55" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L55" s="41">
+      <c r="H55" s="83" t="s">
+        <v>341</v>
+      </c>
+      <c r="I55" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J55" s="83" t="s">
+        <v>436</v>
+      </c>
+      <c r="K55" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L55" s="83">
         <v>2</v>
       </c>
-      <c r="M55" s="40">
+      <c r="M55" s="82">
         <f>L55*5</f>
         <v>10</v>
       </c>
-      <c r="N55" s="41">
+      <c r="N55" s="83">
         <v>40</v>
       </c>
-      <c r="O55" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P55" s="54">
+      <c r="O55" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P55" s="85">
         <v>0.72070000000000001</v>
       </c>
-      <c r="Q55" s="43">
+      <c r="Q55" s="86">
         <f>P55*N55</f>
         <v>28.827999999999999</v>
       </c>
-      <c r="R55" s="41"/>
-      <c r="S55" s="40"/>
+      <c r="R55" s="83"/>
+      <c r="S55" s="82"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="52">
+      <c r="B56" s="48">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="61" t="s">
+      <c r="C56" s="56" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="E56" s="65" t="s">
+      <c r="E56" s="59" t="s">
         <v>145</v>
       </c>
       <c r="F56" s="39" t="s">
@@ -5629,16 +5671,16 @@
         <v>273</v>
       </c>
       <c r="H56" s="39" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I56" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J56" s="39" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L56" s="39">
         <v>2</v>
@@ -5650,13 +5692,13 @@
       <c r="N56" s="38">
         <v>15</v>
       </c>
-      <c r="O56" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P56" s="53">
+      <c r="O56" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P56" s="49">
         <v>0.1182</v>
       </c>
-      <c r="Q56" s="42">
+      <c r="Q56" s="40">
         <f t="shared" ref="Q56" si="48">P56*N56</f>
         <v>1.7729999999999999</v>
       </c>
@@ -5665,73 +5707,73 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="51">
+      <c r="B57" s="47">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="62" t="s">
+      <c r="C57" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="D57" s="40" t="s">
+      <c r="D57" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="E57" s="40" t="s">
+      <c r="E57" s="82" t="s">
         <v>146</v>
       </c>
-      <c r="F57" s="41" t="s">
+      <c r="F57" s="83" t="s">
         <v>223</v>
       </c>
-      <c r="G57" s="40" t="s">
+      <c r="G57" s="82" t="s">
         <v>274</v>
       </c>
-      <c r="H57" s="41" t="s">
+      <c r="H57" s="83" t="s">
         <v>323</v>
       </c>
-      <c r="I57" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J57" s="41" t="s">
-        <v>369</v>
-      </c>
-      <c r="K57" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L57" s="41">
+      <c r="I57" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J57" s="83" t="s">
+        <v>368</v>
+      </c>
+      <c r="K57" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L57" s="83">
         <v>6</v>
       </c>
-      <c r="M57" s="40">
+      <c r="M57" s="82">
         <f>L57*5</f>
         <v>30</v>
       </c>
-      <c r="N57" s="41">
+      <c r="N57" s="83">
         <v>20</v>
       </c>
-      <c r="O57" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P57" s="54">
+      <c r="O57" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P57" s="85">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="Q57" s="43">
+      <c r="Q57" s="86">
         <f>P57*N57</f>
         <v>0.67</v>
       </c>
-      <c r="R57" s="41"/>
-      <c r="S57" s="40"/>
+      <c r="R57" s="83"/>
+      <c r="S57" s="82"/>
     </row>
     <row r="58" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="52">
+      <c r="B58" s="48">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="61" t="s">
+      <c r="C58" s="56" t="s">
         <v>13</v>
       </c>
       <c r="D58" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>147</v>
       </c>
       <c r="F58" s="39" t="s">
@@ -5741,16 +5783,16 @@
         <v>275</v>
       </c>
       <c r="H58" s="39" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I58" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J58" s="39" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L58" s="39">
         <v>10</v>
@@ -5762,13 +5804,13 @@
       <c r="N58" s="38">
         <v>60</v>
       </c>
-      <c r="O58" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P58" s="53">
+      <c r="O58" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P58" s="49">
         <v>1.9099999999999999E-2</v>
       </c>
-      <c r="Q58" s="42">
+      <c r="Q58" s="40">
         <f t="shared" ref="Q58" si="50">P58*N58</f>
         <v>1.1459999999999999</v>
       </c>
@@ -5777,73 +5819,73 @@
     </row>
     <row r="59" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="51">
+      <c r="B59" s="47">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="62" t="s">
+      <c r="C59" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="40" t="s">
+      <c r="D59" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="E59" s="40" t="s">
+      <c r="E59" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="F59" s="41" t="s">
+      <c r="F59" s="83" t="s">
         <v>223</v>
       </c>
-      <c r="G59" s="40" t="s">
+      <c r="G59" s="82" t="s">
         <v>276</v>
       </c>
-      <c r="H59" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="I59" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J59" s="41" t="s">
-        <v>502</v>
-      </c>
-      <c r="K59" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L59" s="41">
+      <c r="H59" s="83" t="s">
+        <v>342</v>
+      </c>
+      <c r="I59" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J59" s="83" t="s">
+        <v>500</v>
+      </c>
+      <c r="K59" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L59" s="83">
         <v>2</v>
       </c>
-      <c r="M59" s="40">
+      <c r="M59" s="82">
         <f>L59*5</f>
         <v>10</v>
       </c>
-      <c r="N59" s="41">
+      <c r="N59" s="83">
         <v>20</v>
       </c>
-      <c r="O59" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P59" s="54">
+      <c r="O59" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P59" s="85">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="Q59" s="43">
+      <c r="Q59" s="86">
         <f>P59*N59</f>
         <v>0.40599999999999997</v>
       </c>
-      <c r="R59" s="41"/>
-      <c r="S59" s="40"/>
+      <c r="R59" s="83"/>
+      <c r="S59" s="82"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="52">
+      <c r="B60" s="48">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="61" t="s">
+      <c r="C60" s="56" t="s">
         <v>13</v>
       </c>
       <c r="D60" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="E60" s="65" t="s">
+      <c r="E60" s="59" t="s">
         <v>149</v>
       </c>
       <c r="F60" s="39" t="s">
@@ -5856,13 +5898,13 @@
         <v>321</v>
       </c>
       <c r="I60" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J60" s="39" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L60" s="39">
         <v>3</v>
@@ -5874,13 +5916,13 @@
       <c r="N60" s="38">
         <v>20</v>
       </c>
-      <c r="O60" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P60" s="53">
+      <c r="O60" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P60" s="49">
         <v>2.9899999999999999E-2</v>
       </c>
-      <c r="Q60" s="42">
+      <c r="Q60" s="40">
         <f t="shared" ref="Q60" si="52">P60*N60</f>
         <v>0.59799999999999998</v>
       </c>
@@ -5889,73 +5931,73 @@
     </row>
     <row r="61" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="51">
+      <c r="B61" s="47">
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="62" t="s">
+      <c r="C61" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="40" t="s">
+      <c r="D61" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="E61" s="40" t="s">
+      <c r="E61" s="82" t="s">
         <v>150</v>
       </c>
-      <c r="F61" s="41" t="s">
-        <v>441</v>
-      </c>
-      <c r="G61" s="40" t="s">
+      <c r="F61" s="83" t="s">
+        <v>440</v>
+      </c>
+      <c r="G61" s="82" t="s">
         <v>225</v>
       </c>
-      <c r="H61" s="41" t="s">
-        <v>344</v>
-      </c>
-      <c r="I61" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J61" s="41" t="s">
-        <v>504</v>
-      </c>
-      <c r="K61" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L61" s="41">
+      <c r="H61" s="83" t="s">
+        <v>343</v>
+      </c>
+      <c r="I61" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J61" s="83" t="s">
+        <v>502</v>
+      </c>
+      <c r="K61" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L61" s="83">
         <v>1</v>
       </c>
-      <c r="M61" s="40">
+      <c r="M61" s="82">
         <f>L61*5</f>
         <v>5</v>
       </c>
-      <c r="N61" s="41">
+      <c r="N61" s="83">
         <v>10</v>
       </c>
-      <c r="O61" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P61" s="54">
+      <c r="O61" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P61" s="85">
         <v>0.3261</v>
       </c>
-      <c r="Q61" s="43">
+      <c r="Q61" s="86">
         <f>P61*N61</f>
         <v>3.2610000000000001</v>
       </c>
-      <c r="R61" s="41"/>
-      <c r="S61" s="40"/>
+      <c r="R61" s="83"/>
+      <c r="S61" s="82"/>
     </row>
     <row r="62" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="52">
+      <c r="B62" s="48">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="61" t="s">
+      <c r="C62" s="56" t="s">
         <v>13</v>
       </c>
       <c r="D62" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E62" s="65" t="s">
+      <c r="E62" s="59" t="s">
         <v>151</v>
       </c>
       <c r="F62" s="39" t="s">
@@ -5965,16 +6007,16 @@
         <v>278</v>
       </c>
       <c r="H62" s="39" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I62" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J62" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L62" s="39">
         <v>1</v>
@@ -5986,13 +6028,13 @@
       <c r="N62" s="38">
         <v>10</v>
       </c>
-      <c r="O62" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P62" s="53">
+      <c r="O62" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P62" s="49">
         <v>4.3700000000000003E-2</v>
       </c>
-      <c r="Q62" s="42">
+      <c r="Q62" s="40">
         <f t="shared" ref="Q62" si="54">P62*N62</f>
         <v>0.43700000000000006</v>
       </c>
@@ -6001,73 +6043,73 @@
     </row>
     <row r="63" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="51">
+      <c r="B63" s="47">
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="62" t="s">
+      <c r="C63" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D63" s="40" t="s">
+      <c r="D63" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="E63" s="40" t="s">
+      <c r="E63" s="82" t="s">
         <v>152</v>
       </c>
-      <c r="F63" s="41" t="s">
+      <c r="F63" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="G63" s="40" t="s">
+      <c r="G63" s="82" t="s">
         <v>279</v>
       </c>
-      <c r="H63" s="41" t="s">
+      <c r="H63" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I63" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J63" s="41" t="s">
-        <v>505</v>
-      </c>
-      <c r="K63" s="40" t="s">
-        <v>396</v>
-      </c>
-      <c r="L63" s="41">
+      <c r="I63" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J63" s="83" t="s">
+        <v>503</v>
+      </c>
+      <c r="K63" s="82" t="s">
+        <v>395</v>
+      </c>
+      <c r="L63" s="83">
         <v>1</v>
       </c>
-      <c r="M63" s="40">
+      <c r="M63" s="82">
         <f>L63*5</f>
         <v>5</v>
       </c>
-      <c r="N63" s="41">
+      <c r="N63" s="83">
         <v>100</v>
       </c>
-      <c r="O63" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P63" s="54">
+      <c r="O63" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P63" s="85">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="Q63" s="43">
+      <c r="Q63" s="86">
         <f>P63*N63</f>
         <v>0.21</v>
       </c>
-      <c r="R63" s="41"/>
-      <c r="S63" s="40"/>
+      <c r="R63" s="83"/>
+      <c r="S63" s="82"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="52">
+      <c r="B64" s="48">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="61" t="s">
+      <c r="C64" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D64" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="E64" s="65" t="s">
+      <c r="E64" s="59" t="s">
         <v>153</v>
       </c>
       <c r="F64" s="39" t="s">
@@ -6080,13 +6122,13 @@
         <v>315</v>
       </c>
       <c r="I64" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J64" s="39" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L64" s="39">
         <v>1</v>
@@ -6098,13 +6140,13 @@
       <c r="N64" s="38">
         <v>100</v>
       </c>
-      <c r="O64" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P64" s="53">
+      <c r="O64" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P64" s="49">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q64" s="42">
+      <c r="Q64" s="40">
         <f t="shared" ref="Q64" si="56">P64*N64</f>
         <v>0.12</v>
       </c>
@@ -6113,74 +6155,74 @@
     </row>
     <row r="65" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="51">
+      <c r="B65" s="47">
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="62" t="s">
+      <c r="C65" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="40" t="s">
+      <c r="D65" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="E65" s="40" t="s">
+      <c r="E65" s="82" t="s">
         <v>154</v>
       </c>
-      <c r="F65" s="41" t="s">
+      <c r="F65" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="G65" s="40" t="s">
-        <v>436</v>
-      </c>
-      <c r="H65" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="I65" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J65" s="41" t="s">
-        <v>507</v>
-      </c>
-      <c r="K65" s="40" t="s">
-        <v>398</v>
-      </c>
-      <c r="L65" s="41">
+      <c r="G65" s="82" t="s">
+        <v>435</v>
+      </c>
+      <c r="H65" s="83" t="s">
+        <v>345</v>
+      </c>
+      <c r="I65" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J65" s="83" t="s">
+        <v>505</v>
+      </c>
+      <c r="K65" s="82" t="s">
+        <v>397</v>
+      </c>
+      <c r="L65" s="83">
         <v>1</v>
       </c>
-      <c r="M65" s="40">
+      <c r="M65" s="82">
         <f>L65*5</f>
         <v>5</v>
       </c>
-      <c r="N65" s="41">
+      <c r="N65" s="83">
         <v>50</v>
       </c>
-      <c r="O65" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P65" s="54">
+      <c r="O65" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P65" s="85">
         <v>3.8E-3</v>
       </c>
-      <c r="Q65" s="43">
+      <c r="Q65" s="86">
         <f>P65*N65</f>
         <v>0.19</v>
       </c>
-      <c r="R65" s="41"/>
-      <c r="S65" s="40"/>
+      <c r="R65" s="83"/>
+      <c r="S65" s="82"/>
     </row>
     <row r="66" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="51">
+      <c r="B66" s="47">
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="61" t="s">
+      <c r="C66" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>455</v>
-      </c>
-      <c r="E66" s="65" t="s">
-        <v>549</v>
+        <v>454</v>
+      </c>
+      <c r="E66" s="59" t="s">
+        <v>547</v>
       </c>
       <c r="F66" s="39" t="s">
         <v>227</v>
@@ -6192,13 +6234,13 @@
         <v>315</v>
       </c>
       <c r="I66" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J66" s="39" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L66" s="39">
         <v>15</v>
@@ -6210,13 +6252,13 @@
       <c r="N66" s="38">
         <v>100</v>
       </c>
-      <c r="O66" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P66" s="53">
+      <c r="O66" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P66" s="49">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q66" s="42">
+      <c r="Q66" s="40">
         <f>P66*N66</f>
         <v>0.12</v>
       </c>
@@ -6225,73 +6267,73 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="52">
+      <c r="B67" s="48">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="62" t="s">
+      <c r="C67" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D67" s="40" t="s">
+      <c r="D67" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="E67" s="40" t="s">
+      <c r="E67" s="82" t="s">
         <v>155</v>
       </c>
-      <c r="F67" s="41" t="s">
+      <c r="F67" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="G67" s="40" t="s">
+      <c r="G67" s="82" t="s">
         <v>282</v>
       </c>
-      <c r="H67" s="41" t="s">
+      <c r="H67" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I67" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J67" s="41" t="s">
-        <v>508</v>
-      </c>
-      <c r="K67" s="40" t="s">
-        <v>401</v>
-      </c>
-      <c r="L67" s="41">
+      <c r="I67" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J67" s="83" t="s">
+        <v>506</v>
+      </c>
+      <c r="K67" s="82" t="s">
+        <v>400</v>
+      </c>
+      <c r="L67" s="83">
         <v>2</v>
       </c>
-      <c r="M67" s="40">
+      <c r="M67" s="82">
         <f t="shared" ref="M67" si="57">L67*5</f>
         <v>10</v>
       </c>
-      <c r="N67" s="41">
+      <c r="N67" s="83">
         <v>100</v>
       </c>
-      <c r="O67" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P67" s="54">
+      <c r="O67" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P67" s="85">
         <v>1.5E-3</v>
       </c>
-      <c r="Q67" s="43">
+      <c r="Q67" s="86">
         <f t="shared" ref="Q67" si="58">P67*N67</f>
         <v>0.15</v>
       </c>
-      <c r="R67" s="41"/>
-      <c r="S67" s="40"/>
+      <c r="R67" s="83"/>
+      <c r="S67" s="82"/>
     </row>
     <row r="68" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="51">
+      <c r="B68" s="47">
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="61" t="s">
+      <c r="C68" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D68" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="E68" s="65" t="s">
+      <c r="E68" s="59" t="s">
         <v>156</v>
       </c>
       <c r="F68" s="39" t="s">
@@ -6301,16 +6343,16 @@
         <v>283</v>
       </c>
       <c r="H68" s="39" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I68" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J68" s="39" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L68" s="39">
         <v>1</v>
@@ -6322,13 +6364,13 @@
       <c r="N68" s="38">
         <v>100</v>
       </c>
-      <c r="O68" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P68" s="53">
+      <c r="O68" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P68" s="49">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="Q68" s="42">
+      <c r="Q68" s="40">
         <f>P68*N68</f>
         <v>0.16999999999999998</v>
       </c>
@@ -6337,73 +6379,73 @@
     </row>
     <row r="69" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="52">
+      <c r="B69" s="48">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="62" t="s">
+      <c r="C69" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D69" s="40" t="s">
-        <v>449</v>
-      </c>
-      <c r="E69" s="40" t="s">
+      <c r="D69" s="82" t="s">
+        <v>448</v>
+      </c>
+      <c r="E69" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="F69" s="41" t="s">
+      <c r="F69" s="83" t="s">
         <v>227</v>
       </c>
-      <c r="G69" s="40" t="s">
+      <c r="G69" s="82" t="s">
         <v>284</v>
       </c>
-      <c r="H69" s="41" t="s">
+      <c r="H69" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I69" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J69" s="41" t="s">
-        <v>371</v>
-      </c>
-      <c r="K69" s="40" t="s">
-        <v>399</v>
-      </c>
-      <c r="L69" s="41">
+      <c r="I69" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J69" s="83" t="s">
+        <v>370</v>
+      </c>
+      <c r="K69" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="L69" s="83">
         <v>20</v>
       </c>
-      <c r="M69" s="40">
+      <c r="M69" s="82">
         <f t="shared" ref="M69" si="59">L69*5</f>
         <v>100</v>
       </c>
-      <c r="N69" s="41">
+      <c r="N69" s="83">
         <v>200</v>
       </c>
-      <c r="O69" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P69" s="54">
+      <c r="O69" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P69" s="85">
         <v>1E-3</v>
       </c>
-      <c r="Q69" s="43">
+      <c r="Q69" s="86">
         <f t="shared" ref="Q69" si="60">P69*N69</f>
         <v>0.2</v>
       </c>
-      <c r="R69" s="41"/>
-      <c r="S69" s="40"/>
+      <c r="R69" s="83"/>
+      <c r="S69" s="82"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="51">
+      <c r="B70" s="47">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="61" t="s">
+      <c r="C70" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D70" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="E70" s="65" t="s">
+      <c r="E70" s="59" t="s">
         <v>158</v>
       </c>
       <c r="F70" s="39" t="s">
@@ -6416,13 +6458,13 @@
         <v>315</v>
       </c>
       <c r="I70" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J70" s="39" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L70" s="39">
         <v>1</v>
@@ -6434,13 +6476,13 @@
       <c r="N70" s="38">
         <v>100</v>
       </c>
-      <c r="O70" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P70" s="53">
+      <c r="O70" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P70" s="49">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q70" s="42">
+      <c r="Q70" s="40">
         <f>P70*N70</f>
         <v>0.12</v>
       </c>
@@ -6449,73 +6491,73 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="52">
+      <c r="B71" s="48">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="62" t="s">
+      <c r="C71" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="40" t="s">
+      <c r="D71" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="E71" s="40" t="s">
+      <c r="E71" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="F71" s="41" t="s">
+      <c r="F71" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="G71" s="40" t="s">
+      <c r="G71" s="82" t="s">
         <v>286</v>
       </c>
-      <c r="H71" s="41" t="s">
+      <c r="H71" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I71" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J71" s="41" t="s">
-        <v>510</v>
-      </c>
-      <c r="K71" s="40" t="s">
-        <v>404</v>
-      </c>
-      <c r="L71" s="41">
+      <c r="I71" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J71" s="83" t="s">
+        <v>508</v>
+      </c>
+      <c r="K71" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="L71" s="83">
         <v>3</v>
       </c>
-      <c r="M71" s="40">
+      <c r="M71" s="82">
         <f t="shared" ref="M71" si="61">L71*5</f>
         <v>15</v>
       </c>
-      <c r="N71" s="41">
+      <c r="N71" s="83">
         <v>100</v>
       </c>
-      <c r="O71" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P71" s="54">
+      <c r="O71" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P71" s="85">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q71" s="43">
+      <c r="Q71" s="86">
         <f t="shared" ref="Q71" si="62">P71*N71</f>
         <v>0.12</v>
       </c>
-      <c r="R71" s="41"/>
-      <c r="S71" s="40"/>
+      <c r="R71" s="83"/>
+      <c r="S71" s="82"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="51">
+      <c r="B72" s="47">
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="61" t="s">
+      <c r="C72" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>454</v>
-      </c>
-      <c r="E72" s="65" t="s">
+        <v>453</v>
+      </c>
+      <c r="E72" s="59" t="s">
         <v>160</v>
       </c>
       <c r="F72" s="39" t="s">
@@ -6525,16 +6567,16 @@
         <v>287</v>
       </c>
       <c r="H72" s="39" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I72" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J72" s="39" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L72" s="39">
         <v>8</v>
@@ -6546,13 +6588,13 @@
       <c r="N72" s="38">
         <v>100</v>
       </c>
-      <c r="O72" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P72" s="53">
+      <c r="O72" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P72" s="49">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q72" s="42">
+      <c r="Q72" s="40">
         <f>P72*N72</f>
         <v>0.12</v>
       </c>
@@ -6561,73 +6603,73 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="B73" s="52">
+      <c r="B73" s="48">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="62" t="s">
+      <c r="C73" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="40" t="s">
+      <c r="D73" s="82" t="s">
         <v>73</v>
       </c>
-      <c r="E73" s="40" t="s">
+      <c r="E73" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="F73" s="41" t="s">
+      <c r="F73" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="G73" s="40" t="s">
+      <c r="G73" s="82" t="s">
         <v>288</v>
       </c>
-      <c r="H73" s="41" t="s">
+      <c r="H73" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I73" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J73" s="41" t="s">
-        <v>531</v>
-      </c>
-      <c r="K73" s="40" t="s">
-        <v>406</v>
-      </c>
-      <c r="L73" s="41">
+      <c r="I73" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J73" s="83" t="s">
+        <v>529</v>
+      </c>
+      <c r="K73" s="82" t="s">
+        <v>405</v>
+      </c>
+      <c r="L73" s="83">
         <v>2</v>
       </c>
-      <c r="M73" s="40">
+      <c r="M73" s="82">
         <f t="shared" ref="M73" si="63">L73*5</f>
         <v>10</v>
       </c>
-      <c r="N73" s="41">
+      <c r="N73" s="83">
         <v>100</v>
       </c>
-      <c r="O73" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P73" s="54">
+      <c r="O73" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P73" s="85">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q73" s="43">
+      <c r="Q73" s="86">
         <f t="shared" ref="Q73" si="64">P73*N73</f>
         <v>0.12</v>
       </c>
-      <c r="R73" s="41"/>
-      <c r="S73" s="40"/>
+      <c r="R73" s="83"/>
+      <c r="S73" s="82"/>
     </row>
     <row r="74" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="51">
+      <c r="B74" s="47">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="61" t="s">
+      <c r="C74" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="E74" s="65" t="s">
+        <v>450</v>
+      </c>
+      <c r="E74" s="59" t="s">
         <v>162</v>
       </c>
       <c r="F74" s="39" t="s">
@@ -6640,13 +6682,13 @@
         <v>315</v>
       </c>
       <c r="I74" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J74" s="39" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L74" s="39">
         <v>13</v>
@@ -6658,13 +6700,13 @@
       <c r="N74" s="38">
         <v>100</v>
       </c>
-      <c r="O74" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P74" s="53">
+      <c r="O74" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P74" s="49">
         <v>1E-3</v>
       </c>
-      <c r="Q74" s="42">
+      <c r="Q74" s="40">
         <f>P74*N74</f>
         <v>0.1</v>
       </c>
@@ -6673,73 +6715,73 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="52">
+      <c r="B75" s="48">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="62" t="s">
+      <c r="C75" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="40" t="s">
-        <v>550</v>
-      </c>
-      <c r="E75" s="40" t="s">
+      <c r="D75" s="82" t="s">
+        <v>548</v>
+      </c>
+      <c r="E75" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="F75" s="41" t="s">
+      <c r="F75" s="83" t="s">
         <v>227</v>
       </c>
-      <c r="G75" s="40" t="s">
+      <c r="G75" s="82" t="s">
         <v>290</v>
       </c>
-      <c r="H75" s="41" t="s">
+      <c r="H75" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I75" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J75" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="K75" s="40" t="s">
-        <v>409</v>
-      </c>
-      <c r="L75" s="41">
+      <c r="I75" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J75" s="83" t="s">
+        <v>530</v>
+      </c>
+      <c r="K75" s="82" t="s">
+        <v>408</v>
+      </c>
+      <c r="L75" s="83">
         <v>2</v>
       </c>
-      <c r="M75" s="40">
+      <c r="M75" s="82">
         <f t="shared" ref="M75" si="65">L75*5</f>
         <v>10</v>
       </c>
-      <c r="N75" s="41">
+      <c r="N75" s="83">
         <v>20</v>
       </c>
-      <c r="O75" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P75" s="54">
+      <c r="O75" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P75" s="85">
         <v>2.92E-2</v>
       </c>
-      <c r="Q75" s="43">
+      <c r="Q75" s="86">
         <f t="shared" ref="Q75" si="66">P75*N75</f>
         <v>0.58399999999999996</v>
       </c>
-      <c r="R75" s="41"/>
-      <c r="S75" s="40"/>
+      <c r="R75" s="83"/>
+      <c r="S75" s="82"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="51">
+      <c r="B76" s="47">
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="61" t="s">
+      <c r="C76" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D76" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="E76" s="65" t="s">
+      <c r="E76" s="59" t="s">
         <v>164</v>
       </c>
       <c r="F76" s="39" t="s">
@@ -6752,13 +6794,13 @@
         <v>315</v>
       </c>
       <c r="I76" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J76" s="39" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L76" s="39">
         <v>1</v>
@@ -6770,13 +6812,13 @@
       <c r="N76" s="38">
         <v>20</v>
       </c>
-      <c r="O76" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P76" s="53">
+      <c r="O76" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P76" s="49">
         <v>0.03</v>
       </c>
-      <c r="Q76" s="42">
+      <c r="Q76" s="40">
         <f>P76*N76</f>
         <v>0.6</v>
       </c>
@@ -6785,73 +6827,73 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="52">
+      <c r="B77" s="48">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="62" t="s">
+      <c r="C77" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D77" s="40" t="s">
-        <v>452</v>
-      </c>
-      <c r="E77" s="40" t="s">
+      <c r="D77" s="82" t="s">
+        <v>451</v>
+      </c>
+      <c r="E77" s="82" t="s">
         <v>165</v>
       </c>
-      <c r="F77" s="41" t="s">
+      <c r="F77" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="G77" s="40" t="s">
+      <c r="G77" s="82" t="s">
         <v>292</v>
       </c>
-      <c r="H77" s="41" t="s">
+      <c r="H77" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I77" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J77" s="41" t="s">
-        <v>513</v>
-      </c>
-      <c r="K77" s="40" t="s">
-        <v>411</v>
-      </c>
-      <c r="L77" s="41">
+      <c r="I77" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J77" s="83" t="s">
+        <v>511</v>
+      </c>
+      <c r="K77" s="82" t="s">
+        <v>410</v>
+      </c>
+      <c r="L77" s="83">
         <v>3</v>
       </c>
-      <c r="M77" s="40">
+      <c r="M77" s="82">
         <f t="shared" ref="M77" si="67">L77*5</f>
         <v>15</v>
       </c>
-      <c r="N77" s="41">
+      <c r="N77" s="83">
         <v>100</v>
       </c>
-      <c r="O77" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P77" s="54">
+      <c r="O77" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P77" s="85">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q77" s="43">
+      <c r="Q77" s="86">
         <f t="shared" ref="Q77" si="68">P77*N77</f>
         <v>0.12</v>
       </c>
-      <c r="R77" s="41"/>
-      <c r="S77" s="40"/>
+      <c r="R77" s="83"/>
+      <c r="S77" s="82"/>
     </row>
     <row r="78" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="51">
+      <c r="B78" s="47">
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
-      <c r="C78" s="61" t="s">
+      <c r="C78" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="E78" s="65" t="s">
+        <v>449</v>
+      </c>
+      <c r="E78" s="59" t="s">
         <v>166</v>
       </c>
       <c r="F78" s="39" t="s">
@@ -6864,13 +6906,13 @@
         <v>315</v>
       </c>
       <c r="I78" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J78" s="39" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L78" s="39">
         <v>24</v>
@@ -6882,13 +6924,13 @@
       <c r="N78" s="38">
         <v>200</v>
       </c>
-      <c r="O78" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P78" s="53">
+      <c r="O78" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P78" s="49">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q78" s="42">
+      <c r="Q78" s="40">
         <f>P78*N78</f>
         <v>0.24</v>
       </c>
@@ -6897,73 +6939,73 @@
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="52">
+      <c r="B79" s="48">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="62" t="s">
+      <c r="C79" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="40" t="s">
+      <c r="D79" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="E79" s="40" t="s">
+      <c r="E79" s="82" t="s">
         <v>167</v>
       </c>
-      <c r="F79" s="41" t="s">
+      <c r="F79" s="83" t="s">
         <v>228</v>
       </c>
-      <c r="G79" s="40" t="s">
+      <c r="G79" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="H79" s="41" t="s">
+      <c r="H79" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I79" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J79" s="41" t="s">
-        <v>372</v>
-      </c>
-      <c r="K79" s="40" t="s">
-        <v>412</v>
-      </c>
-      <c r="L79" s="41">
+      <c r="I79" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J79" s="83" t="s">
+        <v>371</v>
+      </c>
+      <c r="K79" s="82" t="s">
+        <v>411</v>
+      </c>
+      <c r="L79" s="83">
         <v>1</v>
       </c>
-      <c r="M79" s="40">
+      <c r="M79" s="82">
         <f t="shared" ref="M79" si="69">L79*5</f>
         <v>5</v>
       </c>
-      <c r="N79" s="41">
+      <c r="N79" s="83">
         <v>100</v>
       </c>
-      <c r="O79" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P79" s="54">
+      <c r="O79" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P79" s="85">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="Q79" s="43">
+      <c r="Q79" s="86">
         <f t="shared" ref="Q79" si="70">P79*N79</f>
         <v>0.22</v>
       </c>
-      <c r="R79" s="41"/>
-      <c r="S79" s="40"/>
+      <c r="R79" s="83"/>
+      <c r="S79" s="82"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="B80" s="51">
+      <c r="B80" s="47">
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
-      <c r="C80" s="61" t="s">
+      <c r="C80" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D80" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="E80" s="65" t="s">
+      <c r="E80" s="59" t="s">
         <v>168</v>
       </c>
       <c r="F80" s="39" t="s">
@@ -6976,13 +7018,13 @@
         <v>315</v>
       </c>
       <c r="I80" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J80" s="39" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K80" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L80" s="39">
         <v>1</v>
@@ -6994,13 +7036,13 @@
       <c r="N80" s="38">
         <v>50</v>
       </c>
-      <c r="O80" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P80" s="53">
+      <c r="O80" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P80" s="49">
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="Q80" s="42">
+      <c r="Q80" s="40">
         <f>P80*N80</f>
         <v>0.84499999999999997</v>
       </c>
@@ -7009,73 +7051,73 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="52">
+      <c r="B81" s="48">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="62" t="s">
+      <c r="C81" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D81" s="40" t="s">
+      <c r="D81" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="E81" s="40" t="s">
+      <c r="E81" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="F81" s="41" t="s">
+      <c r="F81" s="83" t="s">
         <v>227</v>
       </c>
-      <c r="G81" s="40" t="s">
+      <c r="G81" s="82" t="s">
         <v>296</v>
       </c>
-      <c r="H81" s="41" t="s">
+      <c r="H81" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I81" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J81" s="41" t="s">
-        <v>374</v>
-      </c>
-      <c r="K81" s="40" t="s">
-        <v>413</v>
-      </c>
-      <c r="L81" s="41">
+      <c r="I81" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J81" s="83" t="s">
+        <v>373</v>
+      </c>
+      <c r="K81" s="82" t="s">
+        <v>412</v>
+      </c>
+      <c r="L81" s="83">
         <v>1</v>
       </c>
-      <c r="M81" s="40">
+      <c r="M81" s="82">
         <f t="shared" ref="M81" si="71">L81*5</f>
         <v>5</v>
       </c>
-      <c r="N81" s="41">
+      <c r="N81" s="83">
         <v>100</v>
       </c>
-      <c r="O81" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P81" s="54">
+      <c r="O81" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P81" s="85">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q81" s="43">
+      <c r="Q81" s="86">
         <f t="shared" ref="Q81" si="72">P81*N81</f>
         <v>0.13</v>
       </c>
-      <c r="R81" s="41"/>
-      <c r="S81" s="40"/>
+      <c r="R81" s="83"/>
+      <c r="S81" s="82"/>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
-      <c r="B82" s="51">
+      <c r="B82" s="47">
         <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
-      <c r="C82" s="61" t="s">
+      <c r="C82" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D82" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="E82" s="65" t="s">
+      <c r="E82" s="59" t="s">
         <v>170</v>
       </c>
       <c r="F82" s="39" t="s">
@@ -7088,13 +7130,13 @@
         <v>315</v>
       </c>
       <c r="I82" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J82" s="39" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K82" s="38" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L82" s="39">
         <v>2</v>
@@ -7106,13 +7148,13 @@
       <c r="N82" s="38">
         <v>100</v>
       </c>
-      <c r="O82" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P82" s="53">
+      <c r="O82" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P82" s="49">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q82" s="42">
+      <c r="Q82" s="40">
         <f>P82*N82</f>
         <v>0.12</v>
       </c>
@@ -7121,74 +7163,74 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="B83" s="52">
+      <c r="B83" s="48">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C83" s="62" t="s">
+      <c r="C83" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D83" s="40" t="s">
-        <v>453</v>
-      </c>
-      <c r="E83" s="40" t="s">
+      <c r="D83" s="82" t="s">
+        <v>452</v>
+      </c>
+      <c r="E83" s="82" t="s">
         <v>171</v>
       </c>
-      <c r="F83" s="41" t="s">
+      <c r="F83" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="G83" s="68" t="s">
+      <c r="G83" s="87" t="s">
         <v>298</v>
       </c>
-      <c r="H83" s="41" t="s">
+      <c r="H83" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I83" s="40" t="s">
-        <v>541</v>
-      </c>
-      <c r="J83" s="41" t="s">
-        <v>540</v>
-      </c>
-      <c r="K83" s="40" t="s">
-        <v>412</v>
-      </c>
-      <c r="L83" s="41">
+      <c r="I83" s="82" t="s">
+        <v>539</v>
+      </c>
+      <c r="J83" s="83" t="s">
+        <v>538</v>
+      </c>
+      <c r="K83" s="82" t="s">
+        <v>411</v>
+      </c>
+      <c r="L83" s="83">
         <v>5</v>
       </c>
-      <c r="M83" s="40">
+      <c r="M83" s="82">
         <f t="shared" ref="M83" si="73">L83*5</f>
         <v>25</v>
       </c>
-      <c r="N83" s="41">
+      <c r="N83" s="83">
         <v>100</v>
       </c>
-      <c r="O83" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P83" s="54">
+      <c r="O83" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P83" s="85">
         <v>2E-3</v>
       </c>
-      <c r="Q83" s="43">
+      <c r="Q83" s="86">
         <f t="shared" ref="Q83" si="74">P83*N83</f>
         <v>0.2</v>
       </c>
-      <c r="R83" s="41"/>
-      <c r="S83" s="40"/>
+      <c r="R83" s="83"/>
+      <c r="S83" s="82"/>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="B84" s="51">
+      <c r="B84" s="47">
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
-      <c r="C84" s="61" t="s">
+      <c r="C84" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D84" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E84" s="65" t="s">
-        <v>542</v>
+      <c r="E84" s="59" t="s">
+        <v>540</v>
       </c>
       <c r="F84" s="39" t="s">
         <v>226</v>
@@ -7200,13 +7242,13 @@
         <v>315</v>
       </c>
       <c r="I84" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J84" s="39" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K84" s="38" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L84" s="39">
         <v>2</v>
@@ -7218,13 +7260,13 @@
       <c r="N84" s="38">
         <v>100</v>
       </c>
-      <c r="O84" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P84" s="53">
+      <c r="O84" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P84" s="49">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q84" s="42">
+      <c r="Q84" s="40">
         <f>P84*N84</f>
         <v>0.13</v>
       </c>
@@ -7233,92 +7275,92 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
-      <c r="B85" s="52">
+      <c r="B85" s="48">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="62" t="s">
+      <c r="C85" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D85" s="40" t="s">
+      <c r="D85" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="E85" s="40" t="s">
+      <c r="E85" s="82" t="s">
         <v>172</v>
       </c>
-      <c r="F85" s="41" t="s">
+      <c r="F85" s="83" t="s">
         <v>227</v>
       </c>
-      <c r="G85" s="40" t="s">
+      <c r="G85" s="82" t="s">
         <v>300</v>
       </c>
-      <c r="H85" s="41" t="s">
+      <c r="H85" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I85" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J85" s="41" t="s">
-        <v>375</v>
-      </c>
-      <c r="K85" s="40" t="s">
-        <v>416</v>
-      </c>
-      <c r="L85" s="41">
+      <c r="I85" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J85" s="83" t="s">
+        <v>374</v>
+      </c>
+      <c r="K85" s="82" t="s">
+        <v>415</v>
+      </c>
+      <c r="L85" s="83">
         <v>2</v>
       </c>
-      <c r="M85" s="40">
+      <c r="M85" s="82">
         <f t="shared" ref="M85" si="75">L85*5</f>
         <v>10</v>
       </c>
-      <c r="N85" s="41">
+      <c r="N85" s="83">
         <v>100</v>
       </c>
-      <c r="O85" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P85" s="54">
+      <c r="O85" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P85" s="85">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q85" s="43">
+      <c r="Q85" s="86">
         <f t="shared" ref="Q85" si="76">P85*N85</f>
         <v>0.11</v>
       </c>
-      <c r="R85" s="41"/>
-      <c r="S85" s="40"/>
+      <c r="R85" s="83"/>
+      <c r="S85" s="82"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
-      <c r="B86" s="51">
+      <c r="B86" s="47">
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="61" t="s">
+      <c r="C86" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D86" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="E86" s="65" t="s">
+      <c r="E86" s="59" t="s">
         <v>173</v>
       </c>
       <c r="F86" s="39" t="s">
         <v>230</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H86" s="39" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I86" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J86" s="39" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K86" s="38" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L86" s="39">
         <v>2</v>
@@ -7330,13 +7372,13 @@
       <c r="N86" s="38">
         <v>50</v>
       </c>
-      <c r="O86" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P86" s="53">
+      <c r="O86" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P86" s="49">
         <v>0.01</v>
       </c>
-      <c r="Q86" s="42">
+      <c r="Q86" s="40">
         <f>P86*N86</f>
         <v>0.5</v>
       </c>
@@ -7345,73 +7387,73 @@
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
-      <c r="B87" s="52">
+      <c r="B87" s="48">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="62" t="s">
+      <c r="C87" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="40" t="s">
+      <c r="D87" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="E87" s="40" t="s">
-        <v>518</v>
-      </c>
-      <c r="F87" s="41" t="s">
+      <c r="E87" s="82" t="s">
+        <v>516</v>
+      </c>
+      <c r="F87" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="G87" s="40" t="s">
+      <c r="G87" s="82" t="s">
         <v>301</v>
       </c>
-      <c r="H87" s="41" t="s">
+      <c r="H87" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I87" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J87" s="41" t="s">
-        <v>517</v>
-      </c>
-      <c r="K87" s="40" t="s">
-        <v>418</v>
-      </c>
-      <c r="L87" s="41">
+      <c r="I87" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J87" s="83" t="s">
+        <v>515</v>
+      </c>
+      <c r="K87" s="82" t="s">
+        <v>417</v>
+      </c>
+      <c r="L87" s="83">
         <v>2</v>
       </c>
-      <c r="M87" s="40">
+      <c r="M87" s="82">
         <f t="shared" ref="M87" si="77">L87*5</f>
         <v>10</v>
       </c>
-      <c r="N87" s="41">
+      <c r="N87" s="83">
         <v>100</v>
       </c>
-      <c r="O87" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P87" s="54">
+      <c r="O87" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P87" s="85">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q87" s="43">
+      <c r="Q87" s="86">
         <f t="shared" ref="Q87" si="78">P87*N87</f>
         <v>0.12</v>
       </c>
-      <c r="R87" s="41"/>
-      <c r="S87" s="40"/>
+      <c r="R87" s="83"/>
+      <c r="S87" s="82"/>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
-      <c r="B88" s="51">
+      <c r="B88" s="47">
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="61" t="s">
+      <c r="C88" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D88" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="E88" s="65" t="s">
+      <c r="E88" s="59" t="s">
         <v>174</v>
       </c>
       <c r="F88" s="39" t="s">
@@ -7424,13 +7466,13 @@
         <v>315</v>
       </c>
       <c r="I88" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J88" s="39" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K88" s="38" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L88" s="39">
         <v>1</v>
@@ -7442,13 +7484,13 @@
       <c r="N88" s="38">
         <v>50</v>
       </c>
-      <c r="O88" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P88" s="53">
+      <c r="O88" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P88" s="49">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="Q88" s="42">
+      <c r="Q88" s="40">
         <f>P88*N88</f>
         <v>0.44</v>
       </c>
@@ -7457,184 +7499,184 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
-      <c r="B89" s="52">
+      <c r="B89" s="48">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C89" s="62" t="s">
+      <c r="C89" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="D89" s="40" t="s">
+      <c r="D89" s="82" t="s">
         <v>84</v>
       </c>
-      <c r="E89" s="40" t="s">
+      <c r="E89" s="82" t="s">
         <v>175</v>
       </c>
-      <c r="F89" s="41" t="s">
+      <c r="F89" s="83" t="s">
         <v>227</v>
       </c>
-      <c r="G89" s="40" t="s">
+      <c r="G89" s="82" t="s">
         <v>303</v>
       </c>
-      <c r="H89" s="41" t="s">
+      <c r="H89" s="83" t="s">
         <v>315</v>
       </c>
-      <c r="I89" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J89" s="41" t="s">
-        <v>535</v>
-      </c>
-      <c r="K89" s="40" t="s">
-        <v>420</v>
-      </c>
-      <c r="L89" s="41">
+      <c r="I89" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J89" s="83" t="s">
+        <v>533</v>
+      </c>
+      <c r="K89" s="82" t="s">
+        <v>419</v>
+      </c>
+      <c r="L89" s="83">
         <v>1</v>
       </c>
-      <c r="M89" s="40">
+      <c r="M89" s="82">
         <f t="shared" ref="M89" si="79">L89*5</f>
         <v>5</v>
       </c>
-      <c r="N89" s="41">
+      <c r="N89" s="83">
         <v>20</v>
       </c>
-      <c r="O89" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P89" s="54">
+      <c r="O89" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P89" s="85">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="Q89" s="43">
+      <c r="Q89" s="86">
         <f t="shared" ref="Q89" si="80">P89*N89</f>
         <v>0.55800000000000005</v>
       </c>
-      <c r="R89" s="41"/>
-      <c r="S89" s="40"/>
+      <c r="R89" s="83"/>
+      <c r="S89" s="82"/>
     </row>
     <row r="90" spans="1:19" ht="84" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
-      <c r="B90" s="52">
+      <c r="B90" s="48">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="C90" s="75" t="s">
+      <c r="C90" s="65" t="s">
         <v>231</v>
       </c>
-      <c r="D90" s="69" t="s">
+      <c r="D90" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="E90" s="69" t="s">
+      <c r="E90" s="61" t="s">
         <v>176</v>
       </c>
-      <c r="F90" s="76" t="s">
-        <v>426</v>
-      </c>
-      <c r="G90" s="69" t="s">
+      <c r="F90" s="66" t="s">
+        <v>425</v>
+      </c>
+      <c r="G90" s="61" t="s">
         <v>231</v>
       </c>
-      <c r="H90" s="76" t="s">
-        <v>437</v>
-      </c>
-      <c r="I90" s="69" t="s">
-        <v>437</v>
-      </c>
-      <c r="J90" s="76" t="s">
-        <v>437</v>
-      </c>
-      <c r="K90" s="69" t="s">
-        <v>437</v>
-      </c>
-      <c r="L90" s="76">
+      <c r="H90" s="66" t="s">
+        <v>436</v>
+      </c>
+      <c r="I90" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="J90" s="66" t="s">
+        <v>436</v>
+      </c>
+      <c r="K90" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="L90" s="66">
         <v>42</v>
       </c>
-      <c r="M90" s="69">
+      <c r="M90" s="61">
         <f t="shared" ref="M90" si="81">L90*5</f>
         <v>210</v>
       </c>
-      <c r="N90" s="69" t="s">
-        <v>437</v>
-      </c>
-      <c r="O90" s="77" t="s">
-        <v>437</v>
-      </c>
-      <c r="P90" s="78" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q90" s="79" t="s">
-        <v>437</v>
-      </c>
-      <c r="R90" s="76"/>
-      <c r="S90" s="69"/>
+      <c r="N90" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="O90" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="P90" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q90" s="69" t="s">
+        <v>436</v>
+      </c>
+      <c r="R90" s="66"/>
+      <c r="S90" s="61"/>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
-      <c r="B91" s="51">
+      <c r="B91" s="47">
         <f>ROW(B91) - ROW($B$9)</f>
         <v>82</v>
       </c>
-      <c r="C91" s="62" t="s">
-        <v>536</v>
-      </c>
-      <c r="D91" s="40" t="s">
+      <c r="C91" s="81" t="s">
+        <v>534</v>
+      </c>
+      <c r="D91" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="E91" s="40" t="s">
+      <c r="E91" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G91" s="40" t="s">
+      <c r="F91" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G91" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="H91" s="41" t="s">
-        <v>350</v>
-      </c>
-      <c r="I91" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J91" s="41" t="s">
-        <v>519</v>
-      </c>
-      <c r="K91" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L91" s="41">
+      <c r="H91" s="83" t="s">
+        <v>349</v>
+      </c>
+      <c r="I91" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J91" s="83" t="s">
+        <v>517</v>
+      </c>
+      <c r="K91" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L91" s="83">
         <v>7</v>
       </c>
-      <c r="M91" s="40">
+      <c r="M91" s="82">
         <f>L91*5</f>
         <v>35</v>
       </c>
-      <c r="N91" s="41">
+      <c r="N91" s="83">
         <v>37</v>
       </c>
-      <c r="O91" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P91" s="54">
+      <c r="O91" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P91" s="85">
         <v>0.6905</v>
       </c>
-      <c r="Q91" s="43">
+      <c r="Q91" s="86">
         <f>P91*N91</f>
         <v>25.548500000000001</v>
       </c>
-      <c r="R91" s="41"/>
-      <c r="S91" s="40"/>
+      <c r="R91" s="83"/>
+      <c r="S91" s="82"/>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
-      <c r="B92" s="52">
+      <c r="B92" s="48">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="C92" s="61" t="s">
-        <v>537</v>
+      <c r="C92" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="D92" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="E92" s="65" t="s">
+      <c r="E92" s="59" t="s">
         <v>178</v>
       </c>
       <c r="F92" s="39" t="s">
@@ -7644,14 +7686,14 @@
         <v>304</v>
       </c>
       <c r="H92" s="39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I92" s="38"/>
       <c r="J92" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K92" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L92" s="39">
         <v>2</v>
@@ -7663,13 +7705,13 @@
       <c r="N92" s="38">
         <v>12</v>
       </c>
-      <c r="O92" s="66" t="s">
-        <v>544</v>
-      </c>
-      <c r="P92" s="53">
+      <c r="O92" s="60" t="s">
+        <v>542</v>
+      </c>
+      <c r="P92" s="49">
         <v>8.8239999999999998</v>
       </c>
-      <c r="Q92" s="42">
+      <c r="Q92" s="40">
         <f t="shared" ref="Q92" si="83">P92*N92</f>
         <v>105.88800000000001</v>
       </c>
@@ -7678,73 +7720,73 @@
     </row>
     <row r="93" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="B93" s="51">
+      <c r="B93" s="47">
         <f>ROW(B93) - ROW($B$9)</f>
         <v>84</v>
       </c>
-      <c r="C93" s="62" t="s">
-        <v>537</v>
-      </c>
-      <c r="D93" s="40" t="s">
+      <c r="C93" s="81" t="s">
+        <v>535</v>
+      </c>
+      <c r="D93" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="E93" s="40" t="s">
+      <c r="E93" s="82" t="s">
         <v>179</v>
       </c>
-      <c r="F93" s="41" t="s">
+      <c r="F93" s="83" t="s">
         <v>233</v>
       </c>
-      <c r="G93" s="40" t="s">
+      <c r="G93" s="82" t="s">
         <v>305</v>
       </c>
-      <c r="H93" s="41" t="s">
-        <v>352</v>
-      </c>
-      <c r="I93" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J93" s="41" t="s">
-        <v>520</v>
-      </c>
-      <c r="K93" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L93" s="41">
+      <c r="H93" s="83" t="s">
+        <v>351</v>
+      </c>
+      <c r="I93" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J93" s="83" t="s">
+        <v>518</v>
+      </c>
+      <c r="K93" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L93" s="83">
         <v>1</v>
       </c>
-      <c r="M93" s="40">
+      <c r="M93" s="82">
         <f>L93*5</f>
         <v>5</v>
       </c>
-      <c r="N93" s="41">
+      <c r="N93" s="83">
         <v>6</v>
       </c>
-      <c r="O93" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P93" s="54">
+      <c r="O93" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P93" s="85">
         <v>0.39779999999999999</v>
       </c>
-      <c r="Q93" s="43">
+      <c r="Q93" s="86">
         <f>P93*N93</f>
         <v>2.3868</v>
       </c>
-      <c r="R93" s="41"/>
-      <c r="S93" s="40"/>
+      <c r="R93" s="83"/>
+      <c r="S93" s="82"/>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
-      <c r="B94" s="52">
+      <c r="B94" s="48">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="C94" s="61" t="s">
-        <v>537</v>
+      <c r="C94" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="D94" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="E94" s="65" t="s">
+      <c r="E94" s="59" t="s">
         <v>180</v>
       </c>
       <c r="F94" s="39" t="s">
@@ -7754,16 +7796,16 @@
         <v>306</v>
       </c>
       <c r="H94" s="39" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I94" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J94" s="39" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K94" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L94" s="39">
         <v>1</v>
@@ -7775,13 +7817,13 @@
       <c r="N94" s="38">
         <v>6</v>
       </c>
-      <c r="O94" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P94" s="53">
+      <c r="O94" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P94" s="49">
         <v>1.0309999999999999</v>
       </c>
-      <c r="Q94" s="42">
+      <c r="Q94" s="40">
         <f t="shared" ref="Q94" si="85">P94*N94</f>
         <v>6.1859999999999999</v>
       </c>
@@ -7790,73 +7832,73 @@
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
-      <c r="B95" s="51">
+      <c r="B95" s="47">
         <f>ROW(B95) - ROW($B$9)</f>
         <v>86</v>
       </c>
-      <c r="C95" s="62" t="s">
-        <v>537</v>
-      </c>
-      <c r="D95" s="40" t="s">
+      <c r="C95" s="81" t="s">
+        <v>535</v>
+      </c>
+      <c r="D95" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="E95" s="40" t="s">
+      <c r="E95" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="F95" s="41" t="s">
+      <c r="F95" s="83" t="s">
         <v>235</v>
       </c>
-      <c r="G95" s="40" t="s">
+      <c r="G95" s="82" t="s">
         <v>307</v>
       </c>
-      <c r="H95" s="41" t="s">
-        <v>353</v>
-      </c>
-      <c r="I95" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J95" s="41" t="s">
-        <v>522</v>
-      </c>
-      <c r="K95" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L95" s="41">
+      <c r="H95" s="83" t="s">
+        <v>352</v>
+      </c>
+      <c r="I95" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J95" s="83" t="s">
+        <v>520</v>
+      </c>
+      <c r="K95" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L95" s="83">
         <v>1</v>
       </c>
-      <c r="M95" s="40">
+      <c r="M95" s="82">
         <f>L95*5</f>
         <v>5</v>
       </c>
-      <c r="N95" s="41">
+      <c r="N95" s="83">
         <v>6</v>
       </c>
-      <c r="O95" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P95" s="54">
+      <c r="O95" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P95" s="85">
         <v>7.3596000000000004</v>
       </c>
-      <c r="Q95" s="43">
+      <c r="Q95" s="86">
         <f>P95*N95</f>
         <v>44.157600000000002</v>
       </c>
-      <c r="R95" s="41"/>
-      <c r="S95" s="40"/>
+      <c r="R95" s="83"/>
+      <c r="S95" s="82"/>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="B96" s="52">
+      <c r="B96" s="48">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="C96" s="61" t="s">
-        <v>537</v>
+      <c r="C96" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="D96" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="E96" s="65" t="s">
+      <c r="E96" s="59" t="s">
         <v>182</v>
       </c>
       <c r="F96" s="39" t="s">
@@ -7869,13 +7911,13 @@
         <v>321</v>
       </c>
       <c r="I96" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J96" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K96" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L96" s="39">
         <v>1</v>
@@ -7887,13 +7929,13 @@
       <c r="N96" s="38">
         <v>8</v>
       </c>
-      <c r="O96" s="66" t="s">
-        <v>544</v>
-      </c>
-      <c r="P96" s="53">
+      <c r="O96" s="60" t="s">
+        <v>542</v>
+      </c>
+      <c r="P96" s="49">
         <v>6.944</v>
       </c>
-      <c r="Q96" s="42">
+      <c r="Q96" s="40">
         <f t="shared" ref="Q96" si="87">P96*N96</f>
         <v>55.552</v>
       </c>
@@ -7902,92 +7944,92 @@
     </row>
     <row r="97" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
-      <c r="B97" s="51">
+      <c r="B97" s="47">
         <f>ROW(B97) - ROW($B$9)</f>
         <v>88</v>
       </c>
-      <c r="C97" s="62" t="s">
-        <v>537</v>
-      </c>
-      <c r="D97" s="40" t="s">
+      <c r="C97" s="81" t="s">
+        <v>535</v>
+      </c>
+      <c r="D97" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="E97" s="40" t="s">
+      <c r="E97" s="82" t="s">
         <v>183</v>
       </c>
-      <c r="F97" s="41" t="s">
-        <v>440</v>
-      </c>
-      <c r="G97" s="40" t="s">
+      <c r="F97" s="83" t="s">
+        <v>439</v>
+      </c>
+      <c r="G97" s="82" t="s">
         <v>236</v>
       </c>
-      <c r="H97" s="41" t="s">
-        <v>354</v>
-      </c>
-      <c r="I97" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J97" s="41" t="s">
-        <v>437</v>
-      </c>
-      <c r="K97" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L97" s="41">
+      <c r="H97" s="83" t="s">
+        <v>353</v>
+      </c>
+      <c r="I97" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J97" s="83" t="s">
+        <v>436</v>
+      </c>
+      <c r="K97" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L97" s="83">
         <v>1</v>
       </c>
-      <c r="M97" s="40">
+      <c r="M97" s="82">
         <f>L97*5</f>
         <v>5</v>
       </c>
-      <c r="N97" s="41">
+      <c r="N97" s="83">
         <v>7</v>
       </c>
-      <c r="O97" s="67" t="s">
-        <v>544</v>
-      </c>
-      <c r="P97" s="54">
+      <c r="O97" s="84" t="s">
+        <v>542</v>
+      </c>
+      <c r="P97" s="85">
         <v>8.2669999999999995</v>
       </c>
-      <c r="Q97" s="43">
+      <c r="Q97" s="86">
         <f>P97*N97</f>
         <v>57.869</v>
       </c>
-      <c r="R97" s="41"/>
-      <c r="S97" s="40"/>
+      <c r="R97" s="83"/>
+      <c r="S97" s="82"/>
     </row>
     <row r="98" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
-      <c r="B98" s="52">
+      <c r="B98" s="48">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="C98" s="61" t="s">
-        <v>537</v>
+      <c r="C98" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="D98" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="E98" s="65" t="s">
+      <c r="E98" s="59" t="s">
         <v>184</v>
       </c>
       <c r="F98" s="39" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G98" s="38" t="s">
         <v>237</v>
       </c>
       <c r="H98" s="39" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I98" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J98" s="39" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K98" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L98" s="39">
         <v>4</v>
@@ -7999,13 +8041,13 @@
       <c r="N98" s="38">
         <v>25</v>
       </c>
-      <c r="O98" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P98" s="53">
+      <c r="O98" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P98" s="49">
         <v>0.41510000000000002</v>
       </c>
-      <c r="Q98" s="42">
+      <c r="Q98" s="40">
         <f t="shared" ref="Q98" si="89">P98*N98</f>
         <v>10.377500000000001</v>
       </c>
@@ -8014,73 +8056,73 @@
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
-      <c r="B99" s="51">
+      <c r="B99" s="47">
         <f>ROW(B99) - ROW($B$9)</f>
         <v>90</v>
       </c>
-      <c r="C99" s="62" t="s">
-        <v>537</v>
-      </c>
-      <c r="D99" s="40" t="s">
+      <c r="C99" s="81" t="s">
+        <v>535</v>
+      </c>
+      <c r="D99" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="E99" s="40" t="s">
+      <c r="E99" s="82" t="s">
         <v>185</v>
       </c>
-      <c r="F99" s="41" t="s">
+      <c r="F99" s="83" t="s">
         <v>238</v>
       </c>
-      <c r="G99" s="40" t="s">
+      <c r="G99" s="82" t="s">
         <v>309</v>
       </c>
-      <c r="H99" s="41" t="s">
-        <v>352</v>
-      </c>
-      <c r="I99" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J99" s="41" t="s">
-        <v>524</v>
-      </c>
-      <c r="K99" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L99" s="41">
+      <c r="H99" s="83" t="s">
+        <v>351</v>
+      </c>
+      <c r="I99" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J99" s="83" t="s">
+        <v>522</v>
+      </c>
+      <c r="K99" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L99" s="83">
         <v>3</v>
       </c>
-      <c r="M99" s="40">
+      <c r="M99" s="82">
         <f>L99*5</f>
         <v>15</v>
       </c>
-      <c r="N99" s="41">
+      <c r="N99" s="83">
         <v>20</v>
       </c>
-      <c r="O99" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P99" s="54">
+      <c r="O99" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P99" s="85">
         <v>0.24310000000000001</v>
       </c>
-      <c r="Q99" s="43">
+      <c r="Q99" s="86">
         <f>P99*N99</f>
         <v>4.8620000000000001</v>
       </c>
-      <c r="R99" s="41"/>
-      <c r="S99" s="40"/>
-    </row>
-    <row r="100" spans="1:19" s="71" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A100" s="70"/>
-      <c r="B100" s="52">
+      <c r="R99" s="83"/>
+      <c r="S99" s="82"/>
+    </row>
+    <row r="100" spans="1:19" s="63" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A100" s="62"/>
+      <c r="B100" s="48">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="C100" s="61" t="s">
-        <v>537</v>
+      <c r="C100" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="D100" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="E100" s="65" t="s">
+      <c r="E100" s="59" t="s">
         <v>186</v>
       </c>
       <c r="F100" s="39" t="s">
@@ -8090,16 +8132,16 @@
         <v>310</v>
       </c>
       <c r="H100" s="39" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I100" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J100" s="39" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="K100" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L100" s="39">
         <v>1</v>
@@ -8111,111 +8153,111 @@
       <c r="N100" s="38">
         <v>11</v>
       </c>
-      <c r="O100" s="66" t="s">
-        <v>544</v>
-      </c>
-      <c r="P100" s="53">
+      <c r="O100" s="60" t="s">
+        <v>542</v>
+      </c>
+      <c r="P100" s="49">
         <v>4.7060000000000004</v>
       </c>
-      <c r="Q100" s="42">
+      <c r="Q100" s="40">
         <f t="shared" ref="Q100" si="91">P100*N100</f>
         <v>51.766000000000005</v>
       </c>
-      <c r="R100" s="72" t="s">
-        <v>546</v>
+      <c r="R100" s="64" t="s">
+        <v>544</v>
       </c>
       <c r="S100" s="38"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
-      <c r="B101" s="51">
+      <c r="B101" s="47">
         <f>ROW(B101) - ROW($B$9)</f>
         <v>92</v>
       </c>
-      <c r="C101" s="62" t="s">
-        <v>537</v>
-      </c>
-      <c r="D101" s="40" t="s">
+      <c r="C101" s="81" t="s">
+        <v>535</v>
+      </c>
+      <c r="D101" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="E101" s="40" t="s">
+      <c r="E101" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="F101" s="41" t="s">
+      <c r="F101" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="G101" s="40" t="s">
+      <c r="G101" s="82" t="s">
         <v>311</v>
       </c>
-      <c r="H101" s="41" t="s">
-        <v>356</v>
-      </c>
-      <c r="I101" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J101" s="41" t="s">
-        <v>526</v>
-      </c>
-      <c r="K101" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="L101" s="41">
+      <c r="H101" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="I101" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J101" s="83" t="s">
+        <v>524</v>
+      </c>
+      <c r="K101" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L101" s="83">
         <v>1</v>
       </c>
-      <c r="M101" s="40">
+      <c r="M101" s="82">
         <f>L101*5</f>
         <v>5</v>
       </c>
-      <c r="N101" s="41">
+      <c r="N101" s="83">
         <v>6</v>
       </c>
-      <c r="O101" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P101" s="54">
+      <c r="O101" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P101" s="85">
         <v>4.0076000000000001</v>
       </c>
-      <c r="Q101" s="43">
+      <c r="Q101" s="86">
         <f>P101*N101</f>
         <v>24.0456</v>
       </c>
-      <c r="R101" s="73" t="s">
-        <v>545</v>
-      </c>
-      <c r="S101" s="40"/>
+      <c r="R101" s="93" t="s">
+        <v>543</v>
+      </c>
+      <c r="S101" s="82"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
-      <c r="B102" s="52">
+      <c r="B102" s="48">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="C102" s="61" t="s">
-        <v>537</v>
+      <c r="C102" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="D102" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="E102" s="65" t="s">
+      <c r="E102" s="59" t="s">
         <v>188</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G102" s="38" t="s">
         <v>241</v>
       </c>
       <c r="H102" s="39" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I102" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J102" s="39" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K102" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L102" s="39">
         <v>1</v>
@@ -8227,13 +8269,13 @@
       <c r="N102" s="38">
         <v>6</v>
       </c>
-      <c r="O102" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P102" s="53">
+      <c r="O102" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P102" s="49">
         <v>0.996</v>
       </c>
-      <c r="Q102" s="42">
+      <c r="Q102" s="40">
         <f t="shared" ref="Q102" si="93">P102*N102</f>
         <v>5.976</v>
       </c>
@@ -8242,92 +8284,92 @@
     </row>
     <row r="103" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
-      <c r="B103" s="51">
+      <c r="B103" s="47">
         <f>ROW(B103) - ROW($B$9)</f>
         <v>94</v>
       </c>
-      <c r="C103" s="62" t="s">
-        <v>538</v>
-      </c>
-      <c r="D103" s="40" t="s">
+      <c r="C103" s="81" t="s">
+        <v>536</v>
+      </c>
+      <c r="D103" s="82" t="s">
         <v>98</v>
       </c>
-      <c r="E103" s="40" t="s">
+      <c r="E103" s="82" t="s">
         <v>189</v>
       </c>
-      <c r="F103" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G103" s="40" t="s">
+      <c r="F103" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G103" s="82" t="s">
         <v>242</v>
       </c>
-      <c r="H103" s="41" t="s">
-        <v>358</v>
-      </c>
-      <c r="I103" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J103" s="41" t="s">
-        <v>528</v>
-      </c>
-      <c r="K103" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="L103" s="41">
+      <c r="H103" s="83" t="s">
+        <v>357</v>
+      </c>
+      <c r="I103" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J103" s="83" t="s">
+        <v>526</v>
+      </c>
+      <c r="K103" s="82" t="s">
+        <v>420</v>
+      </c>
+      <c r="L103" s="83">
         <v>1</v>
       </c>
-      <c r="M103" s="40">
+      <c r="M103" s="82">
         <f>L103*5</f>
         <v>5</v>
       </c>
-      <c r="N103" s="41">
+      <c r="N103" s="83">
         <v>6</v>
       </c>
-      <c r="O103" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P103" s="54">
+      <c r="O103" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P103" s="85">
         <v>0.19889999999999999</v>
       </c>
-      <c r="Q103" s="43">
+      <c r="Q103" s="86">
         <f>P103*N103</f>
         <v>1.1934</v>
       </c>
-      <c r="R103" s="41"/>
-      <c r="S103" s="40"/>
+      <c r="R103" s="83"/>
+      <c r="S103" s="82"/>
     </row>
     <row r="104" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
-      <c r="B104" s="52">
+      <c r="B104" s="48">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="C104" s="61" t="s">
-        <v>538</v>
+      <c r="C104" s="56" t="s">
+        <v>536</v>
       </c>
       <c r="D104" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="E104" s="65" t="s">
+      <c r="E104" s="59" t="s">
         <v>190</v>
       </c>
       <c r="F104" s="39" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G104" s="38" t="s">
         <v>312</v>
       </c>
       <c r="H104" s="39" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I104" s="38" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J104" s="39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K104" s="38" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L104" s="39">
         <v>1</v>
@@ -8339,134 +8381,357 @@
       <c r="N104" s="38">
         <v>10</v>
       </c>
-      <c r="O104" s="66" t="s">
-        <v>457</v>
-      </c>
-      <c r="P104" s="53">
+      <c r="O104" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="P104" s="49">
         <v>9.9900000000000003E-2</v>
       </c>
-      <c r="Q104" s="42">
+      <c r="Q104" s="40">
         <f t="shared" ref="Q104" si="95">P104*N104</f>
         <v>0.999</v>
       </c>
       <c r="R104" s="39"/>
       <c r="S104" s="38"/>
     </row>
-    <row r="105" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
-      <c r="B105" s="51">
+      <c r="B105" s="47">
         <f>ROW(B105) - ROW($B$9)</f>
         <v>96</v>
       </c>
-      <c r="C105" s="62" t="s">
-        <v>538</v>
-      </c>
-      <c r="D105" s="40" t="s">
+      <c r="C105" s="81" t="s">
+        <v>536</v>
+      </c>
+      <c r="D105" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="E105" s="40" t="s">
+      <c r="E105" s="82" t="s">
         <v>191</v>
       </c>
-      <c r="F105" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="G105" s="40" t="s">
+      <c r="F105" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G105" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="H105" s="41" t="s">
-        <v>360</v>
-      </c>
-      <c r="I105" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="J105" s="41" t="s">
-        <v>529</v>
-      </c>
-      <c r="K105" s="40" t="s">
-        <v>423</v>
-      </c>
-      <c r="L105" s="41">
+      <c r="H105" s="83" t="s">
+        <v>359</v>
+      </c>
+      <c r="I105" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J105" s="83" t="s">
+        <v>527</v>
+      </c>
+      <c r="K105" s="82" t="s">
+        <v>422</v>
+      </c>
+      <c r="L105" s="83">
         <v>1</v>
       </c>
-      <c r="M105" s="40">
+      <c r="M105" s="82">
         <f>L105*5</f>
         <v>5</v>
       </c>
-      <c r="N105" s="41">
+      <c r="N105" s="83">
         <v>10</v>
       </c>
-      <c r="O105" s="67" t="s">
-        <v>457</v>
-      </c>
-      <c r="P105" s="54">
+      <c r="O105" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P105" s="85">
         <v>0.2218</v>
       </c>
-      <c r="Q105" s="43">
+      <c r="Q105" s="86">
         <f>P105*N105</f>
         <v>2.218</v>
       </c>
-      <c r="R105" s="41"/>
-      <c r="S105" s="40"/>
-    </row>
-    <row r="106" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R105" s="83"/>
+      <c r="S105" s="82"/>
+    </row>
+    <row r="106" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
-      <c r="B106" s="45"/>
-      <c r="C106" s="46"/>
-      <c r="D106" s="47"/>
-      <c r="E106" s="48"/>
-      <c r="F106" s="49"/>
-      <c r="G106" s="50"/>
-      <c r="H106" s="49"/>
-      <c r="I106" s="50"/>
-      <c r="J106" s="49"/>
-      <c r="K106" s="50"/>
-      <c r="L106" s="50"/>
-      <c r="M106" s="50"/>
-      <c r="N106" s="93" t="s">
+      <c r="B106" s="47">
+        <f t="shared" ref="B106:B109" si="96">ROW(B106) - ROW($B$9)</f>
+        <v>97</v>
+      </c>
+      <c r="C106" s="81" t="s">
+        <v>560</v>
+      </c>
+      <c r="D106" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="E106" s="82" t="s">
+        <v>553</v>
+      </c>
+      <c r="F106" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G106" s="82" t="s">
+        <v>554</v>
+      </c>
+      <c r="H106" s="83" t="s">
+        <v>555</v>
+      </c>
+      <c r="I106" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J106" s="83" t="s">
+        <v>556</v>
+      </c>
+      <c r="K106" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L106" s="83">
+        <v>9</v>
+      </c>
+      <c r="M106" s="82">
+        <f>L106*5</f>
+        <v>45</v>
+      </c>
+      <c r="N106" s="83">
+        <v>50</v>
+      </c>
+      <c r="O106" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P106" s="85">
+        <v>0.1595</v>
+      </c>
+      <c r="Q106" s="86">
+        <f t="shared" ref="Q106:Q109" si="97">P106*N106</f>
+        <v>7.9750000000000005</v>
+      </c>
+      <c r="R106" s="83"/>
+      <c r="S106" s="82"/>
+    </row>
+    <row r="107" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A107" s="1"/>
+      <c r="B107" s="47">
+        <f t="shared" si="96"/>
+        <v>98</v>
+      </c>
+      <c r="C107" s="81" t="s">
+        <v>560</v>
+      </c>
+      <c r="D107" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="E107" s="82" t="s">
+        <v>558</v>
+      </c>
+      <c r="F107" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G107" s="82" t="s">
+        <v>559</v>
+      </c>
+      <c r="H107" s="83" t="s">
+        <v>555</v>
+      </c>
+      <c r="I107" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J107" s="83" t="s">
+        <v>557</v>
+      </c>
+      <c r="K107" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L107" s="83">
         <v>5</v>
       </c>
-      <c r="O106" s="94"/>
-      <c r="P106" s="94"/>
-      <c r="Q106" s="55">
+      <c r="M107" s="82">
+        <f>L107*5</f>
+        <v>25</v>
+      </c>
+      <c r="N107" s="83">
+        <v>30</v>
+      </c>
+      <c r="O107" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P107" s="85">
+        <v>0.29559999999999997</v>
+      </c>
+      <c r="Q107" s="86">
+        <f t="shared" si="97"/>
+        <v>8.8679999999999986</v>
+      </c>
+      <c r="R107" s="83"/>
+      <c r="S107" s="82"/>
+    </row>
+    <row r="108" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A108" s="1"/>
+      <c r="B108" s="47">
+        <f t="shared" si="96"/>
+        <v>99</v>
+      </c>
+      <c r="C108" s="81" t="s">
+        <v>560</v>
+      </c>
+      <c r="D108" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="E108" s="82" t="s">
+        <v>561</v>
+      </c>
+      <c r="F108" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G108" s="82" t="s">
+        <v>563</v>
+      </c>
+      <c r="H108" s="83" t="s">
+        <v>555</v>
+      </c>
+      <c r="I108" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J108" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="K108" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L108" s="83">
+        <v>1</v>
+      </c>
+      <c r="M108" s="82">
+        <f>L108*5</f>
+        <v>5</v>
+      </c>
+      <c r="N108" s="83">
+        <v>10</v>
+      </c>
+      <c r="O108" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="P108" s="85">
+        <v>0.34520000000000001</v>
+      </c>
+      <c r="Q108" s="86">
+        <f t="shared" si="97"/>
+        <v>3.452</v>
+      </c>
+      <c r="R108" s="83"/>
+      <c r="S108" s="82"/>
+    </row>
+    <row r="109" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1"/>
+      <c r="B109" s="47">
+        <f t="shared" si="96"/>
+        <v>100</v>
+      </c>
+      <c r="C109" s="94" t="s">
+        <v>567</v>
+      </c>
+      <c r="D109" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="E109" s="82" t="s">
+        <v>569</v>
+      </c>
+      <c r="F109" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G109" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="H109" s="83" t="s">
+        <v>436</v>
+      </c>
+      <c r="I109" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J109" s="83" t="s">
+        <v>436</v>
+      </c>
+      <c r="K109" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L109" s="83" t="s">
+        <v>436</v>
+      </c>
+      <c r="M109" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="N109" s="83">
+        <v>3</v>
+      </c>
+      <c r="O109" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="P109" s="85">
+        <v>1.33</v>
+      </c>
+      <c r="Q109" s="86">
+        <f t="shared" si="97"/>
+        <v>3.99</v>
+      </c>
+      <c r="R109" s="83"/>
+      <c r="S109" s="82"/>
+    </row>
+    <row r="110" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1"/>
+      <c r="B110" s="41"/>
+      <c r="C110" s="42"/>
+      <c r="D110" s="43"/>
+      <c r="E110" s="44"/>
+      <c r="F110" s="45"/>
+      <c r="G110" s="46"/>
+      <c r="H110" s="45"/>
+      <c r="I110" s="46"/>
+      <c r="J110" s="45"/>
+      <c r="K110" s="46"/>
+      <c r="L110" s="46"/>
+      <c r="M110" s="46"/>
+      <c r="N110" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="O110" s="79"/>
+      <c r="P110" s="79"/>
+      <c r="Q110" s="50">
         <f>SUM(Q10:Q105)</f>
-        <v>546.86429999999996</v>
-      </c>
-      <c r="R106" s="89"/>
-      <c r="S106" s="90"/>
-    </row>
-    <row r="107" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="1"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="37"/>
-      <c r="D107" s="9"/>
-      <c r="E107" s="10"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="10"/>
-      <c r="H107" s="10"/>
-      <c r="I107" s="10"/>
-      <c r="J107" s="10"/>
-      <c r="K107" s="10"/>
-      <c r="L107" s="10"/>
-      <c r="M107" s="10"/>
-      <c r="N107" s="93" t="s">
+        <v>546.65329999999994</v>
+      </c>
+      <c r="R110" s="74"/>
+      <c r="S110" s="75"/>
+    </row>
+    <row r="111" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="1"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="37"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="10"/>
+      <c r="F111" s="10"/>
+      <c r="G111" s="10"/>
+      <c r="H111" s="10"/>
+      <c r="I111" s="10"/>
+      <c r="J111" s="10"/>
+      <c r="K111" s="10"/>
+      <c r="L111" s="10"/>
+      <c r="M111" s="10"/>
+      <c r="N111" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="O107" s="94"/>
-      <c r="P107" s="94"/>
-      <c r="Q107" s="56">
-        <f>Q106/5</f>
-        <v>109.37285999999999</v>
-      </c>
-      <c r="R107" s="91"/>
-      <c r="S107" s="92"/>
+      <c r="O111" s="79"/>
+      <c r="P111" s="79"/>
+      <c r="Q111" s="51">
+        <f>Q110/5</f>
+        <v>109.33065999999999</v>
+      </c>
+      <c r="R111" s="76"/>
+      <c r="S111" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R106:S107"/>
-    <mergeCell ref="N106:P106"/>
-    <mergeCell ref="N107:P107"/>
+    <mergeCell ref="R110:S111"/>
+    <mergeCell ref="N110:P110"/>
+    <mergeCell ref="N111:P111"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -8492,79 +8757,83 @@
     <hyperlink ref="O34" r:id="rId21"/>
     <hyperlink ref="O35" r:id="rId22"/>
     <hyperlink ref="O36" r:id="rId23"/>
-    <hyperlink ref="O37" r:id="rId24"/>
-    <hyperlink ref="O38" r:id="rId25"/>
-    <hyperlink ref="O41" r:id="rId26"/>
-    <hyperlink ref="O42" r:id="rId27"/>
-    <hyperlink ref="O43" r:id="rId28"/>
-    <hyperlink ref="O45" r:id="rId29"/>
-    <hyperlink ref="O46" r:id="rId30"/>
-    <hyperlink ref="O53" r:id="rId31"/>
-    <hyperlink ref="O40" r:id="rId32"/>
-    <hyperlink ref="O49" r:id="rId33"/>
-    <hyperlink ref="O52" r:id="rId34"/>
-    <hyperlink ref="O54" r:id="rId35"/>
-    <hyperlink ref="O56" r:id="rId36"/>
-    <hyperlink ref="O44" r:id="rId37"/>
-    <hyperlink ref="O50" r:id="rId38"/>
-    <hyperlink ref="O51" r:id="rId39"/>
-    <hyperlink ref="O28" r:id="rId40"/>
-    <hyperlink ref="O39" r:id="rId41"/>
-    <hyperlink ref="O48" r:id="rId42"/>
-    <hyperlink ref="O57" r:id="rId43"/>
-    <hyperlink ref="O58" r:id="rId44"/>
-    <hyperlink ref="O59" r:id="rId45"/>
-    <hyperlink ref="O60" r:id="rId46"/>
-    <hyperlink ref="O61" r:id="rId47"/>
-    <hyperlink ref="O62" r:id="rId48"/>
-    <hyperlink ref="O63" r:id="rId49"/>
-    <hyperlink ref="O64" r:id="rId50"/>
-    <hyperlink ref="O65" r:id="rId51"/>
-    <hyperlink ref="O66" r:id="rId52"/>
-    <hyperlink ref="O67" r:id="rId53"/>
-    <hyperlink ref="O68" r:id="rId54"/>
-    <hyperlink ref="O69" r:id="rId55"/>
-    <hyperlink ref="O71" r:id="rId56"/>
-    <hyperlink ref="O72" r:id="rId57"/>
-    <hyperlink ref="O74" r:id="rId58"/>
-    <hyperlink ref="O77" r:id="rId59"/>
-    <hyperlink ref="O78" r:id="rId60"/>
-    <hyperlink ref="O86" r:id="rId61"/>
-    <hyperlink ref="O87" r:id="rId62"/>
-    <hyperlink ref="O91" r:id="rId63"/>
-    <hyperlink ref="O94" r:id="rId64"/>
-    <hyperlink ref="O95" r:id="rId65"/>
-    <hyperlink ref="O99" r:id="rId66"/>
-    <hyperlink ref="O101" r:id="rId67"/>
-    <hyperlink ref="O102" r:id="rId68"/>
-    <hyperlink ref="O93" r:id="rId69"/>
-    <hyperlink ref="O98" r:id="rId70"/>
-    <hyperlink ref="O103" r:id="rId71"/>
-    <hyperlink ref="O105" r:id="rId72"/>
-    <hyperlink ref="O70" r:id="rId73"/>
-    <hyperlink ref="O73" r:id="rId74"/>
-    <hyperlink ref="O75" r:id="rId75"/>
-    <hyperlink ref="O76" r:id="rId76"/>
-    <hyperlink ref="O79" r:id="rId77"/>
-    <hyperlink ref="O80" r:id="rId78"/>
-    <hyperlink ref="O88" r:id="rId79"/>
-    <hyperlink ref="O89" r:id="rId80"/>
-    <hyperlink ref="O81" r:id="rId81"/>
-    <hyperlink ref="O82" r:id="rId82"/>
-    <hyperlink ref="O83" r:id="rId83"/>
-    <hyperlink ref="O84" r:id="rId84"/>
-    <hyperlink ref="O85" r:id="rId85"/>
-    <hyperlink ref="O104" r:id="rId86"/>
-    <hyperlink ref="O92" r:id="rId87"/>
-    <hyperlink ref="O96" r:id="rId88"/>
-    <hyperlink ref="O97" r:id="rId89"/>
-    <hyperlink ref="O55" r:id="rId90"/>
-    <hyperlink ref="O32" r:id="rId91"/>
-    <hyperlink ref="O11" r:id="rId92"/>
-    <hyperlink ref="O31" r:id="rId93"/>
+    <hyperlink ref="O38" r:id="rId24"/>
+    <hyperlink ref="O41" r:id="rId25"/>
+    <hyperlink ref="O42" r:id="rId26"/>
+    <hyperlink ref="O43" r:id="rId27"/>
+    <hyperlink ref="O45" r:id="rId28"/>
+    <hyperlink ref="O46" r:id="rId29"/>
+    <hyperlink ref="O53" r:id="rId30"/>
+    <hyperlink ref="O40" r:id="rId31"/>
+    <hyperlink ref="O49" r:id="rId32"/>
+    <hyperlink ref="O52" r:id="rId33"/>
+    <hyperlink ref="O54" r:id="rId34"/>
+    <hyperlink ref="O56" r:id="rId35"/>
+    <hyperlink ref="O44" r:id="rId36"/>
+    <hyperlink ref="O50" r:id="rId37"/>
+    <hyperlink ref="O51" r:id="rId38"/>
+    <hyperlink ref="O28" r:id="rId39"/>
+    <hyperlink ref="O39" r:id="rId40"/>
+    <hyperlink ref="O48" r:id="rId41"/>
+    <hyperlink ref="O57" r:id="rId42"/>
+    <hyperlink ref="O58" r:id="rId43"/>
+    <hyperlink ref="O59" r:id="rId44"/>
+    <hyperlink ref="O60" r:id="rId45"/>
+    <hyperlink ref="O61" r:id="rId46"/>
+    <hyperlink ref="O62" r:id="rId47"/>
+    <hyperlink ref="O63" r:id="rId48"/>
+    <hyperlink ref="O64" r:id="rId49"/>
+    <hyperlink ref="O65" r:id="rId50"/>
+    <hyperlink ref="O66" r:id="rId51"/>
+    <hyperlink ref="O67" r:id="rId52"/>
+    <hyperlink ref="O68" r:id="rId53"/>
+    <hyperlink ref="O69" r:id="rId54"/>
+    <hyperlink ref="O71" r:id="rId55"/>
+    <hyperlink ref="O72" r:id="rId56"/>
+    <hyperlink ref="O74" r:id="rId57"/>
+    <hyperlink ref="O77" r:id="rId58"/>
+    <hyperlink ref="O78" r:id="rId59"/>
+    <hyperlink ref="O86" r:id="rId60"/>
+    <hyperlink ref="O87" r:id="rId61"/>
+    <hyperlink ref="O91" r:id="rId62"/>
+    <hyperlink ref="O94" r:id="rId63"/>
+    <hyperlink ref="O95" r:id="rId64"/>
+    <hyperlink ref="O99" r:id="rId65"/>
+    <hyperlink ref="O101" r:id="rId66"/>
+    <hyperlink ref="O102" r:id="rId67"/>
+    <hyperlink ref="O93" r:id="rId68"/>
+    <hyperlink ref="O98" r:id="rId69"/>
+    <hyperlink ref="O103" r:id="rId70"/>
+    <hyperlink ref="O105" r:id="rId71"/>
+    <hyperlink ref="O70" r:id="rId72"/>
+    <hyperlink ref="O73" r:id="rId73"/>
+    <hyperlink ref="O75" r:id="rId74"/>
+    <hyperlink ref="O76" r:id="rId75"/>
+    <hyperlink ref="O79" r:id="rId76"/>
+    <hyperlink ref="O80" r:id="rId77"/>
+    <hyperlink ref="O88" r:id="rId78"/>
+    <hyperlink ref="O89" r:id="rId79"/>
+    <hyperlink ref="O81" r:id="rId80"/>
+    <hyperlink ref="O82" r:id="rId81"/>
+    <hyperlink ref="O83" r:id="rId82"/>
+    <hyperlink ref="O84" r:id="rId83"/>
+    <hyperlink ref="O85" r:id="rId84"/>
+    <hyperlink ref="O104" r:id="rId85"/>
+    <hyperlink ref="O92" r:id="rId86"/>
+    <hyperlink ref="O96" r:id="rId87"/>
+    <hyperlink ref="O97" r:id="rId88"/>
+    <hyperlink ref="O55" r:id="rId89"/>
+    <hyperlink ref="O32" r:id="rId90"/>
+    <hyperlink ref="O11" r:id="rId91"/>
+    <hyperlink ref="O31" r:id="rId92"/>
+    <hyperlink ref="O106" r:id="rId93"/>
+    <hyperlink ref="O107" r:id="rId94"/>
+    <hyperlink ref="O108" r:id="rId95"/>
+    <hyperlink ref="O37" r:id="rId96"/>
+    <hyperlink ref="O109" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId94"/>
-  <drawing r:id="rId95"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId98"/>
+  <drawing r:id="rId99"/>
 </worksheet>
 </file>
--- a/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
+++ b/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="585">
   <si>
     <t>Component list</t>
   </si>
@@ -1509,10 +1509,6 @@
     <t>PZ254V-11-06P</t>
   </si>
   <si>
-    <t xml:space="preserve">PZ254V-11-02P
-</t>
-  </si>
-  <si>
     <t>DZ254R-11-04-63</t>
   </si>
   <si>
@@ -1573,9 +1569,6 @@
     <t>RES 150K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>C273516</t>
-  </si>
-  <si>
     <t>C100023</t>
   </si>
   <si>
@@ -1648,19 +1641,7 @@
     <t>C105578</t>
   </si>
   <si>
-    <t>Winsource</t>
-  </si>
-  <si>
     <t xml:space="preserve">Less Stock On LCSC </t>
-  </si>
-  <si>
-    <t>This Part Available On LCSC But Price is Very High</t>
-  </si>
-  <si>
-    <t>C150517</t>
-  </si>
-  <si>
-    <t>20021121-00010C4LF</t>
   </si>
   <si>
     <t>RES 2.2K OHM 1% 1/10W 0603</t>
@@ -1731,6 +1712,69 @@
   </si>
   <si>
     <t>Jumper Wires Male to Female 30cm 1 x 40</t>
+  </si>
+  <si>
+    <t>PZ127VS-12-10-H10-A38</t>
+  </si>
+  <si>
+    <t>C2935458</t>
+  </si>
+  <si>
+    <t>PZ254V-11-02P</t>
+  </si>
+  <si>
+    <t>LULU</t>
+  </si>
+  <si>
+    <t>C231723</t>
+  </si>
+  <si>
+    <t>KAN1241-1201C-L</t>
+  </si>
+  <si>
+    <t>LULU Quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less Stock On LCSC And JLCPCB Also </t>
+  </si>
+  <si>
+    <t>LCD</t>
+  </si>
+  <si>
+    <t>1.8 SPLC780 - LCD Displays Modules ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS </t>
+  </si>
+  <si>
+    <t>C2939933</t>
+  </si>
+  <si>
+    <t>DL-RXB3BV-433M</t>
+  </si>
+  <si>
+    <t>C381158</t>
+  </si>
+  <si>
+    <t>Receiver Module</t>
+  </si>
+  <si>
+    <t>Receiver Antenna</t>
+  </si>
+  <si>
+    <t>2 弹簧天线 2.5dBi Vertical 433MHz 50Ω - Antennas ROHS</t>
+  </si>
+  <si>
+    <t>VG433SNX39-6W3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vollgo </t>
+  </si>
+  <si>
+    <t>C718844</t>
+  </si>
+  <si>
+    <t>Do NOT MOUNT</t>
   </si>
 </sst>
 </file>
@@ -1742,7 +1786,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1936,6 +1980,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1963,7 +2016,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -2195,12 +2248,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2322,12 +2423,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2348,9 +2443,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2376,9 +2468,6 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2389,6 +2478,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2423,49 +2584,7 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2810,7 +2929,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S111"/>
+  <dimension ref="A1:S114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="26" bestFit="1" customWidth="1"/>
@@ -2844,15 +2963,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="71"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="91"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2862,8 +2981,8 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="52" t="s">
-        <v>551</v>
+      <c r="F2" s="50" t="s">
+        <v>545</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2887,8 +3006,8 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="53" t="s">
-        <v>552</v>
+      <c r="F3" s="51" t="s">
+        <v>546</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2902,7 +3021,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="72"/>
+      <c r="S3" s="92"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2912,8 +3031,8 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="54" t="s">
-        <v>552</v>
+      <c r="F4" s="52" t="s">
+        <v>546</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2927,7 +3046,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="73"/>
+      <c r="S4" s="93"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2937,7 +3056,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="15"/>
@@ -2952,7 +3071,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="73"/>
+      <c r="S5" s="93"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2973,7 +3092,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="73"/>
+      <c r="S6" s="93"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2994,7 +3113,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="73"/>
+      <c r="S7" s="93"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3015,29 +3134,29 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="73"/>
+      <c r="S8" s="93"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="54" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="55" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="54" t="s">
         <v>192</v>
       </c>
       <c r="G9" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="H9" s="55" t="s">
         <v>313</v>
       </c>
       <c r="I9" s="30" t="s">
@@ -3076,14 +3195,14 @@
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="47">
+      <c r="B10" s="78">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="82" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="38" t="s">
@@ -3117,7 +3236,7 @@
       <c r="N10" s="38">
         <v>80</v>
       </c>
-      <c r="O10" s="60" t="s">
+      <c r="O10" s="57" t="s">
         <v>456</v>
       </c>
       <c r="P10" s="40">
@@ -3128,77 +3247,77 @@
         <v>1.96</v>
       </c>
       <c r="R10" s="39"/>
-      <c r="S10" s="80"/>
+      <c r="S10" s="66"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="48">
+      <c r="B11" s="81">
         <f t="shared" ref="B11:B104" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="81" t="s">
+      <c r="C11" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="82" t="s">
+      <c r="D11" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="82" t="s">
+      <c r="E11" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="83" t="s">
+      <c r="F11" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="G11" s="82" t="s">
+      <c r="G11" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="H11" s="83" t="s">
+      <c r="H11" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I11" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J11" s="83" t="s">
+      <c r="I11" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J11" s="68" t="s">
         <v>361</v>
       </c>
-      <c r="K11" s="82" t="s">
+      <c r="K11" s="67" t="s">
         <v>378</v>
       </c>
-      <c r="L11" s="83">
+      <c r="L11" s="68">
         <v>1</v>
       </c>
-      <c r="M11" s="82">
+      <c r="M11" s="67">
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>5</v>
       </c>
-      <c r="N11" s="83">
+      <c r="N11" s="68">
         <v>50</v>
       </c>
-      <c r="O11" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P11" s="85">
+      <c r="O11" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P11" s="70">
         <v>1.18E-2</v>
       </c>
-      <c r="Q11" s="86">
+      <c r="Q11" s="71">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
         <v>0.59</v>
       </c>
-      <c r="R11" s="83"/>
-      <c r="S11" s="82"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="67"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="47">
+      <c r="B12" s="78">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="82" t="s">
         <v>446</v>
       </c>
-      <c r="E12" s="59" t="s">
+      <c r="E12" s="56" t="s">
         <v>104</v>
       </c>
       <c r="F12" s="39" t="s">
@@ -3229,10 +3348,10 @@
       <c r="N12" s="38">
         <v>100</v>
       </c>
-      <c r="O12" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P12" s="49">
+      <c r="O12" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P12" s="47">
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="Q12" s="40">
@@ -3244,71 +3363,71 @@
     </row>
     <row r="13" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="48">
+      <c r="B13" s="81">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="82" t="s">
+      <c r="E13" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="F13" s="83" t="s">
+      <c r="F13" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="H13" s="83" t="s">
+      <c r="H13" s="68" t="s">
         <v>316</v>
       </c>
-      <c r="I13" s="82"/>
-      <c r="J13" s="83" t="s">
+      <c r="I13" s="67"/>
+      <c r="J13" s="68" t="s">
         <v>457</v>
       </c>
-      <c r="K13" s="82" t="s">
+      <c r="K13" s="67" t="s">
         <v>380</v>
       </c>
-      <c r="L13" s="83">
+      <c r="L13" s="68">
         <v>5</v>
       </c>
-      <c r="M13" s="82">
+      <c r="M13" s="67">
         <f t="shared" ref="M13" si="3">L13*5</f>
         <v>25</v>
       </c>
-      <c r="N13" s="83">
+      <c r="N13" s="68">
         <v>27</v>
       </c>
-      <c r="O13" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P13" s="85">
+      <c r="O13" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P13" s="70">
         <v>0.28799999999999998</v>
       </c>
-      <c r="Q13" s="86">
+      <c r="Q13" s="71">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
         <v>7.7759999999999998</v>
       </c>
-      <c r="R13" s="83"/>
-      <c r="S13" s="82"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="67"/>
     </row>
     <row r="14" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="47">
+      <c r="B14" s="78">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="82" t="s">
         <v>447</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="E14" s="56" t="s">
         <v>106</v>
       </c>
       <c r="F14" s="39" t="s">
@@ -3339,10 +3458,10 @@
       <c r="N14" s="38">
         <v>200</v>
       </c>
-      <c r="O14" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P14" s="49">
+      <c r="O14" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P14" s="47">
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="Q14" s="40">
@@ -3354,73 +3473,73 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="48">
+      <c r="B15" s="81">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="82" t="s">
+      <c r="D15" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="82" t="s">
+      <c r="E15" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="83" t="s">
+      <c r="F15" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G15" s="82" t="s">
+      <c r="G15" s="67" t="s">
         <v>196</v>
       </c>
-      <c r="H15" s="83" t="s">
+      <c r="H15" s="68" t="s">
         <v>317</v>
       </c>
-      <c r="I15" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J15" s="83" t="s">
+      <c r="I15" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J15" s="68" t="s">
         <v>459</v>
       </c>
-      <c r="K15" s="82" t="s">
+      <c r="K15" s="67" t="s">
         <v>381</v>
       </c>
-      <c r="L15" s="83">
+      <c r="L15" s="68">
         <v>1</v>
       </c>
-      <c r="M15" s="82">
+      <c r="M15" s="67">
         <f t="shared" ref="M15" si="5">L15*5</f>
         <v>5</v>
       </c>
-      <c r="N15" s="83">
+      <c r="N15" s="68">
         <v>10</v>
       </c>
-      <c r="O15" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P15" s="85">
+      <c r="O15" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P15" s="70">
         <v>0.13789999999999999</v>
       </c>
-      <c r="Q15" s="86">
+      <c r="Q15" s="71">
         <f t="shared" ref="Q15" si="6">P15*N15</f>
         <v>1.379</v>
       </c>
-      <c r="R15" s="83"/>
-      <c r="S15" s="82"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="67"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="47">
+      <c r="B16" s="78">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="56" t="s">
         <v>108</v>
       </c>
       <c r="F16" s="39" t="s">
@@ -3451,10 +3570,10 @@
       <c r="N16" s="38">
         <v>100</v>
       </c>
-      <c r="O16" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P16" s="49">
+      <c r="O16" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P16" s="47">
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="Q16" s="40">
@@ -3466,73 +3585,73 @@
     </row>
     <row r="17" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="48">
+      <c r="B17" s="81">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="82" t="s">
+      <c r="D17" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="82" t="s">
+      <c r="E17" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="83" t="s">
+      <c r="F17" s="68" t="s">
         <v>197</v>
       </c>
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="67" t="s">
         <v>249</v>
       </c>
-      <c r="H17" s="83" t="s">
+      <c r="H17" s="68" t="s">
         <v>318</v>
       </c>
-      <c r="I17" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J17" s="83" t="s">
+      <c r="I17" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J17" s="68" t="s">
         <v>461</v>
       </c>
-      <c r="K17" s="82" t="s">
+      <c r="K17" s="67" t="s">
         <v>379</v>
       </c>
-      <c r="L17" s="83">
+      <c r="L17" s="68">
         <v>1</v>
       </c>
-      <c r="M17" s="82">
+      <c r="M17" s="67">
         <f t="shared" ref="M17" si="7">L17*5</f>
         <v>5</v>
       </c>
-      <c r="N17" s="83">
+      <c r="N17" s="68">
         <v>6</v>
       </c>
-      <c r="O17" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P17" s="85">
+      <c r="O17" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P17" s="70">
         <v>0.19359999999999999</v>
       </c>
-      <c r="Q17" s="86">
+      <c r="Q17" s="71">
         <f t="shared" ref="Q17" si="8">P17*N17</f>
         <v>1.1616</v>
       </c>
-      <c r="R17" s="83"/>
-      <c r="S17" s="82"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="67"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="47">
+      <c r="B18" s="78">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="56" t="s">
         <v>110</v>
       </c>
       <c r="F18" s="39" t="s">
@@ -3563,10 +3682,10 @@
       <c r="N18" s="38">
         <v>100</v>
       </c>
-      <c r="O18" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P18" s="49">
+      <c r="O18" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P18" s="47">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="Q18" s="40">
@@ -3578,73 +3697,73 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="48">
+      <c r="B19" s="81">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="81" t="s">
+      <c r="C19" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="79" t="s">
         <v>464</v>
       </c>
-      <c r="E19" s="82" t="s">
+      <c r="E19" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="83" t="s">
+      <c r="F19" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="G19" s="82" t="s">
+      <c r="G19" s="67" t="s">
         <v>251</v>
       </c>
-      <c r="H19" s="83" t="s">
+      <c r="H19" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I19" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J19" s="83" t="s">
+      <c r="I19" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J19" s="68" t="s">
         <v>364</v>
       </c>
-      <c r="K19" s="82" t="s">
+      <c r="K19" s="67" t="s">
         <v>384</v>
       </c>
-      <c r="L19" s="83">
+      <c r="L19" s="68">
         <v>4</v>
       </c>
-      <c r="M19" s="82">
+      <c r="M19" s="67">
         <f t="shared" ref="M19" si="9">L19*5</f>
         <v>20</v>
       </c>
-      <c r="N19" s="83">
+      <c r="N19" s="68">
         <v>100</v>
       </c>
-      <c r="O19" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P19" s="85">
+      <c r="O19" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P19" s="70">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="Q19" s="86">
+      <c r="Q19" s="71">
         <f t="shared" ref="Q19" si="10">P19*N19</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="R19" s="83"/>
-      <c r="S19" s="82"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="67"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="47">
+      <c r="B20" s="78">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="56" t="s">
         <v>112</v>
       </c>
       <c r="F20" s="39" t="s">
@@ -3675,10 +3794,10 @@
       <c r="N20" s="38">
         <v>20</v>
       </c>
-      <c r="O20" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P20" s="49">
+      <c r="O20" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P20" s="47">
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="Q20" s="40">
@@ -3690,73 +3809,73 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="48">
+      <c r="B21" s="81">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="81" t="s">
+      <c r="C21" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="82" t="s">
+      <c r="D21" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="82" t="s">
+      <c r="E21" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="F21" s="83" t="s">
+      <c r="F21" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="G21" s="82" t="s">
+      <c r="G21" s="67" t="s">
         <v>253</v>
       </c>
-      <c r="H21" s="83" t="s">
+      <c r="H21" s="68" t="s">
         <v>319</v>
       </c>
-      <c r="I21" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J21" s="83" t="s">
+      <c r="I21" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J21" s="68" t="s">
         <v>463</v>
       </c>
-      <c r="K21" s="82" t="s">
+      <c r="K21" s="67" t="s">
         <v>386</v>
       </c>
-      <c r="L21" s="83">
+      <c r="L21" s="68">
         <v>1</v>
       </c>
-      <c r="M21" s="82">
+      <c r="M21" s="67">
         <f t="shared" ref="M21" si="11">L21*5</f>
         <v>5</v>
       </c>
-      <c r="N21" s="83">
+      <c r="N21" s="68">
         <v>20</v>
       </c>
-      <c r="O21" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P21" s="85">
+      <c r="O21" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P21" s="70">
         <v>3.04E-2</v>
       </c>
-      <c r="Q21" s="86">
+      <c r="Q21" s="71">
         <f t="shared" ref="Q21" si="12">P21*N21</f>
         <v>0.60799999999999998</v>
       </c>
-      <c r="R21" s="83"/>
-      <c r="S21" s="82"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="67"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="48">
+      <c r="B22" s="81">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="56" t="s">
         <v>114</v>
       </c>
       <c r="F22" s="39" t="s">
@@ -3787,10 +3906,10 @@
       <c r="N22" s="38">
         <v>100</v>
       </c>
-      <c r="O22" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P22" s="49">
+      <c r="O22" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P22" s="47">
         <v>3.3E-3</v>
       </c>
       <c r="Q22" s="40">
@@ -3802,73 +3921,73 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="47">
+      <c r="B23" s="78">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="81" t="s">
+      <c r="C23" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="82" t="s">
+      <c r="D23" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="82" t="s">
+      <c r="E23" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="F23" s="83" t="s">
+      <c r="F23" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="G23" s="82" t="s">
+      <c r="G23" s="67" t="s">
         <v>255</v>
       </c>
-      <c r="H23" s="83" t="s">
+      <c r="H23" s="68" t="s">
         <v>319</v>
       </c>
-      <c r="I23" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J23" s="83" t="s">
+      <c r="I23" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J23" s="68" t="s">
         <v>466</v>
       </c>
-      <c r="K23" s="82" t="s">
+      <c r="K23" s="67" t="s">
         <v>388</v>
       </c>
-      <c r="L23" s="83">
+      <c r="L23" s="68">
         <v>1</v>
       </c>
-      <c r="M23" s="82">
+      <c r="M23" s="67">
         <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="83">
+      <c r="N23" s="68">
         <v>20</v>
       </c>
-      <c r="O23" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P23" s="85">
+      <c r="O23" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P23" s="70">
         <v>2.9899999999999999E-2</v>
       </c>
-      <c r="Q23" s="86">
+      <c r="Q23" s="71">
         <f>P23*N23</f>
         <v>0.59799999999999998</v>
       </c>
-      <c r="R23" s="83"/>
-      <c r="S23" s="82"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="67"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="48">
+      <c r="B24" s="81">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="59" t="s">
+      <c r="E24" s="56" t="s">
         <v>116</v>
       </c>
       <c r="F24" s="39" t="s">
@@ -3899,10 +4018,10 @@
       <c r="N24" s="38">
         <v>100</v>
       </c>
-      <c r="O24" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P24" s="49">
+      <c r="O24" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P24" s="47">
         <v>3.0999999999999999E-3</v>
       </c>
       <c r="Q24" s="40">
@@ -3914,73 +4033,73 @@
     </row>
     <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="47">
+      <c r="B25" s="78">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="82" t="s">
+      <c r="D25" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="82" t="s">
+      <c r="E25" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="F25" s="83" t="s">
+      <c r="F25" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="G25" s="82" t="s">
+      <c r="G25" s="67" t="s">
         <v>257</v>
       </c>
-      <c r="H25" s="83" t="s">
+      <c r="H25" s="68" t="s">
         <v>320</v>
       </c>
-      <c r="I25" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J25" s="83" t="s">
+      <c r="I25" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J25" s="68" t="s">
         <v>468</v>
       </c>
-      <c r="K25" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L25" s="83">
+      <c r="K25" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L25" s="68">
         <v>1</v>
       </c>
-      <c r="M25" s="82">
+      <c r="M25" s="67">
         <f>L25*5</f>
         <v>5</v>
       </c>
-      <c r="N25" s="83">
+      <c r="N25" s="68">
         <v>20</v>
       </c>
-      <c r="O25" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P25" s="85">
+      <c r="O25" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P25" s="70">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="Q25" s="86">
+      <c r="Q25" s="71">
         <f>P25*N25</f>
         <v>0.65799999999999992</v>
       </c>
-      <c r="R25" s="83"/>
-      <c r="S25" s="82"/>
+      <c r="R25" s="68"/>
+      <c r="S25" s="67"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="48">
+      <c r="B26" s="81">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="56" t="s">
+      <c r="C26" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="59" t="s">
+      <c r="E26" s="56" t="s">
         <v>118</v>
       </c>
       <c r="F26" s="39" t="s">
@@ -4011,10 +4130,10 @@
       <c r="N26" s="38">
         <v>6</v>
       </c>
-      <c r="O26" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P26" s="49">
+      <c r="O26" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P26" s="47">
         <v>0.49009999999999998</v>
       </c>
       <c r="Q26" s="40">
@@ -4026,73 +4145,73 @@
     </row>
     <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="47">
+      <c r="B27" s="78">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="82" t="s">
+      <c r="D27" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="82" t="s">
+      <c r="E27" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="F27" s="83" t="s">
+      <c r="F27" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="82" t="s">
+      <c r="G27" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="H27" s="83" t="s">
+      <c r="H27" s="68" t="s">
         <v>322</v>
       </c>
-      <c r="I27" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J27" s="83" t="s">
+      <c r="I27" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J27" s="68" t="s">
         <v>470</v>
       </c>
-      <c r="K27" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L27" s="83">
+      <c r="K27" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L27" s="68">
         <v>1</v>
       </c>
-      <c r="M27" s="82">
+      <c r="M27" s="67">
         <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N27" s="83">
+      <c r="N27" s="68">
         <v>20</v>
       </c>
-      <c r="O27" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P27" s="85">
+      <c r="O27" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P27" s="70">
         <v>3.1399999999999997E-2</v>
       </c>
-      <c r="Q27" s="86">
+      <c r="Q27" s="71">
         <f>P27*N27</f>
         <v>0.62799999999999989</v>
       </c>
-      <c r="R27" s="83"/>
-      <c r="S27" s="82"/>
+      <c r="R27" s="68"/>
+      <c r="S27" s="67"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="48">
+      <c r="B28" s="81">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="59" t="s">
+      <c r="E28" s="56" t="s">
         <v>120</v>
       </c>
       <c r="F28" s="39" t="s">
@@ -4123,10 +4242,10 @@
       <c r="N28" s="38">
         <v>40</v>
       </c>
-      <c r="O28" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P28" s="49">
+      <c r="O28" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P28" s="47">
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="Q28" s="40">
@@ -4138,73 +4257,73 @@
     </row>
     <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="47">
+      <c r="B29" s="78">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="82" t="s">
+      <c r="D29" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="82" t="s">
+      <c r="E29" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="F29" s="83" t="s">
+      <c r="F29" s="68" t="s">
         <v>201</v>
       </c>
-      <c r="G29" s="82" t="s">
+      <c r="G29" s="67" t="s">
         <v>260</v>
       </c>
-      <c r="H29" s="83" t="s">
+      <c r="H29" s="68" t="s">
         <v>324</v>
       </c>
-      <c r="I29" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J29" s="83" t="s">
+      <c r="I29" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J29" s="68" t="s">
         <v>471</v>
       </c>
-      <c r="K29" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L29" s="83">
+      <c r="K29" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L29" s="68">
         <v>1</v>
       </c>
-      <c r="M29" s="82">
+      <c r="M29" s="67">
         <f>L29*5</f>
         <v>5</v>
       </c>
-      <c r="N29" s="83">
+      <c r="N29" s="68">
         <v>10</v>
       </c>
-      <c r="O29" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P29" s="85">
+      <c r="O29" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P29" s="70">
         <v>6.2700000000000006E-2</v>
       </c>
-      <c r="Q29" s="86">
+      <c r="Q29" s="71">
         <f>P29*N29</f>
         <v>0.627</v>
       </c>
-      <c r="R29" s="83"/>
-      <c r="S29" s="82"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="67"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="48">
+      <c r="B30" s="81">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="C30" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="56" t="s">
         <v>122</v>
       </c>
       <c r="F30" s="39" t="s">
@@ -4235,10 +4354,10 @@
       <c r="N30" s="38">
         <v>10</v>
       </c>
-      <c r="O30" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P30" s="49">
+      <c r="O30" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P30" s="47">
         <v>8.7099999999999997E-2</v>
       </c>
       <c r="Q30" s="40">
@@ -4250,89 +4369,89 @@
     </row>
     <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="47">
+      <c r="B31" s="78">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="81" t="s">
+      <c r="C31" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="82" t="s">
+      <c r="D31" s="79" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="82" t="s">
+      <c r="G31" s="67" t="s">
         <v>261</v>
       </c>
-      <c r="H31" s="83" t="s">
+      <c r="H31" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="I31" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J31" s="83" t="s">
-        <v>550</v>
-      </c>
-      <c r="K31" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L31" s="83">
+      <c r="I31" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J31" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="K31" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L31" s="68">
         <v>1</v>
       </c>
-      <c r="M31" s="82">
+      <c r="M31" s="67">
         <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="83">
+      <c r="N31" s="68">
         <v>20</v>
       </c>
-      <c r="O31" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P31" s="85">
+      <c r="O31" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P31" s="70">
         <v>3.6200000000000003E-2</v>
       </c>
-      <c r="Q31" s="86">
+      <c r="Q31" s="71">
         <f>P31*N31</f>
         <v>0.72400000000000009</v>
       </c>
-      <c r="R31" s="83"/>
-      <c r="S31" s="82"/>
+      <c r="R31" s="68"/>
+      <c r="S31" s="67"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="48">
+      <c r="B32" s="81">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="85" t="s">
         <v>438</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="56" t="s">
         <v>123</v>
       </c>
       <c r="F32" s="39" t="s">
         <v>425</v>
       </c>
-      <c r="G32" s="61" t="s">
+      <c r="G32" s="58" t="s">
         <v>203</v>
       </c>
       <c r="H32" s="39" t="s">
         <v>326</v>
       </c>
       <c r="I32" s="38" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="K32" s="38" t="s">
         <v>436</v>
@@ -4345,96 +4464,96 @@
         <v>5</v>
       </c>
       <c r="N32" s="38">
-        <v>6</v>
-      </c>
-      <c r="O32" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P32" s="49">
-        <v>0.61729999999999996</v>
+        <v>10</v>
+      </c>
+      <c r="O32" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P32" s="47">
+        <v>0.15229999999999999</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" ref="Q32" si="24">P32*N32</f>
-        <v>3.7037999999999998</v>
+        <v>1.5229999999999999</v>
       </c>
       <c r="R32" s="39"/>
       <c r="S32" s="38"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="47">
+      <c r="B33" s="78">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="86" t="s">
         <v>441</v>
       </c>
-      <c r="D33" s="82" t="s">
+      <c r="D33" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="82" t="s">
+      <c r="E33" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="83" t="s">
+      <c r="F33" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G33" s="87" t="s">
+      <c r="G33" s="72" t="s">
         <v>204</v>
       </c>
-      <c r="H33" s="83" t="s">
+      <c r="H33" s="68" t="s">
         <v>327</v>
       </c>
-      <c r="I33" s="82" t="s">
+      <c r="I33" s="67" t="s">
         <v>473</v>
       </c>
-      <c r="J33" s="83" t="s">
+      <c r="J33" s="68" t="s">
         <v>476</v>
       </c>
-      <c r="K33" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L33" s="83">
+      <c r="K33" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L33" s="68">
         <v>9</v>
       </c>
-      <c r="M33" s="82">
+      <c r="M33" s="67">
         <f>L33*5</f>
         <v>45</v>
       </c>
-      <c r="N33" s="83">
+      <c r="N33" s="68">
         <v>50</v>
       </c>
-      <c r="O33" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P33" s="85">
+      <c r="O33" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P33" s="70">
         <v>7.1199999999999999E-2</v>
       </c>
-      <c r="Q33" s="86">
+      <c r="Q33" s="71">
         <f>P33*N33</f>
         <v>3.56</v>
       </c>
-      <c r="R33" s="83"/>
-      <c r="S33" s="82"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="67"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="48">
+      <c r="B34" s="81">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="56" t="s">
+      <c r="C34" s="85" t="s">
         <v>441</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="E34" s="59" t="s">
+      <c r="E34" s="56" t="s">
         <v>124</v>
       </c>
       <c r="F34" s="39" t="s">
         <v>425</v>
       </c>
-      <c r="G34" s="61" t="s">
+      <c r="G34" s="58" t="s">
         <v>205</v>
       </c>
       <c r="H34" s="39" t="s">
@@ -4459,10 +4578,10 @@
       <c r="N34" s="38">
         <v>30</v>
       </c>
-      <c r="O34" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P34" s="49">
+      <c r="O34" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P34" s="47">
         <v>0.10539999999999999</v>
       </c>
       <c r="Q34" s="40">
@@ -4474,187 +4593,188 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="47">
+      <c r="B35" s="78">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="86" t="s">
         <v>441</v>
       </c>
-      <c r="D35" s="82" t="s">
+      <c r="D35" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="E35" s="82" t="s">
+      <c r="E35" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="F35" s="83" t="s">
+      <c r="F35" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G35" s="87" t="s">
+      <c r="G35" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="H35" s="83" t="s">
+      <c r="H35" s="68" t="s">
         <v>327</v>
       </c>
-      <c r="I35" s="82" t="s">
+      <c r="I35" s="67" t="s">
         <v>475</v>
       </c>
-      <c r="J35" s="83" t="s">
+      <c r="J35" s="68" t="s">
         <v>478</v>
       </c>
-      <c r="K35" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L35" s="83">
+      <c r="K35" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L35" s="68">
         <v>1</v>
       </c>
-      <c r="M35" s="82">
+      <c r="M35" s="67">
         <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="83">
+      <c r="N35" s="68">
         <v>10</v>
       </c>
-      <c r="O35" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P35" s="85">
+      <c r="O35" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P35" s="70">
         <v>0.1114</v>
       </c>
-      <c r="Q35" s="86">
+      <c r="Q35" s="71">
         <f>P35*N35</f>
         <v>1.1139999999999999</v>
       </c>
-      <c r="R35" s="83"/>
-      <c r="S35" s="82"/>
+      <c r="R35" s="68"/>
+      <c r="S35" s="67"/>
     </row>
     <row r="36" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="48">
+      <c r="B36" s="81">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="56" t="s">
+      <c r="C36" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="59" t="s">
+      <c r="E36" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="F36" s="39" t="s">
+      <c r="F36" s="62" t="s">
         <v>425</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G36" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="H36" s="39" t="s">
+      <c r="H36" s="62" t="s">
         <v>328</v>
       </c>
-      <c r="I36" s="38" t="s">
-        <v>436</v>
-      </c>
-      <c r="J36" s="39" t="s">
+      <c r="I36" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="J36" s="62" t="s">
         <v>479</v>
       </c>
-      <c r="K36" s="38" t="s">
-        <v>436</v>
-      </c>
-      <c r="L36" s="39">
+      <c r="K36" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="L36" s="62">
         <v>1</v>
       </c>
-      <c r="M36" s="38">
+      <c r="M36" s="58">
         <f t="shared" ref="M36" si="27">L36*5</f>
         <v>5</v>
       </c>
-      <c r="N36" s="38">
+      <c r="N36" s="58">
         <v>6</v>
       </c>
-      <c r="O36" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P36" s="49">
-        <v>0.75180000000000002</v>
-      </c>
-      <c r="Q36" s="40">
-        <f t="shared" ref="Q36" si="28">P36*N36</f>
-        <v>4.5107999999999997</v>
-      </c>
-      <c r="R36" s="39"/>
+      <c r="O36" s="63" t="s">
+        <v>456</v>
+      </c>
+      <c r="P36" s="64" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q36" s="65" t="s">
+        <v>436</v>
+      </c>
+      <c r="R36" s="100" t="s">
+        <v>584</v>
+      </c>
       <c r="S36" s="38"/>
     </row>
     <row r="37" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="47">
+      <c r="B37" s="78">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="81" t="s">
+      <c r="C37" s="86" t="s">
         <v>438</v>
       </c>
-      <c r="D37" s="82" t="s">
+      <c r="D37" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="E37" s="82" t="s">
+      <c r="E37" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="F37" s="83" t="s">
+      <c r="F37" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G37" s="87" t="s">
+      <c r="G37" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="H37" s="83" t="s">
-        <v>565</v>
-      </c>
-      <c r="I37" s="82" t="s">
-        <v>564</v>
-      </c>
-      <c r="J37" s="83" t="s">
-        <v>564</v>
-      </c>
-      <c r="K37" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L37" s="83">
+      <c r="H37" s="68" t="s">
+        <v>559</v>
+      </c>
+      <c r="I37" s="67" t="s">
+        <v>558</v>
+      </c>
+      <c r="J37" s="68" t="s">
+        <v>558</v>
+      </c>
+      <c r="K37" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L37" s="68">
         <v>1</v>
       </c>
-      <c r="M37" s="82">
+      <c r="M37" s="67">
         <f>L37*5</f>
         <v>5</v>
       </c>
-      <c r="N37" s="83">
+      <c r="N37" s="68">
         <v>10</v>
       </c>
-      <c r="O37" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P37" s="85">
+      <c r="O37" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P37" s="70">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="Q37" s="86">
+      <c r="Q37" s="71">
         <f>P37*N37</f>
         <v>0.43200000000000005</v>
       </c>
-      <c r="R37" s="93" t="s">
-        <v>566</v>
-      </c>
-      <c r="S37" s="82"/>
+      <c r="R37" s="77" t="s">
+        <v>560</v>
+      </c>
+      <c r="S37" s="67"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="48">
+      <c r="B38" s="81">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="E38" s="59" t="s">
+      <c r="E38" s="56" t="s">
         <v>127</v>
       </c>
       <c r="F38" s="39" t="s">
@@ -4679,20 +4799,20 @@
         <v>1</v>
       </c>
       <c r="M38" s="38">
-        <f t="shared" ref="M38" si="29">L38*5</f>
+        <f t="shared" ref="M38" si="28">L38*5</f>
         <v>5</v>
       </c>
       <c r="N38" s="38">
         <v>6</v>
       </c>
-      <c r="O38" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P38" s="49">
+      <c r="O38" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P38" s="47">
         <v>0.22120000000000001</v>
       </c>
       <c r="Q38" s="40">
-        <f t="shared" ref="Q38" si="30">P38*N38</f>
+        <f t="shared" ref="Q38" si="29">P38*N38</f>
         <v>1.3271999999999999</v>
       </c>
       <c r="R38" s="39"/>
@@ -4700,73 +4820,73 @@
     </row>
     <row r="39" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="47">
+      <c r="B39" s="78">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="81" t="s">
+      <c r="C39" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="82" t="s">
+      <c r="D39" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="E39" s="82" t="s">
+      <c r="E39" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="F39" s="83" t="s">
+      <c r="F39" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="G39" s="82" t="s">
+      <c r="G39" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="H39" s="83" t="s">
+      <c r="H39" s="68" t="s">
         <v>330</v>
       </c>
-      <c r="I39" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J39" s="83" t="s">
+      <c r="I39" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J39" s="68" t="s">
         <v>367</v>
       </c>
-      <c r="K39" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L39" s="83">
+      <c r="K39" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L39" s="68">
         <v>5</v>
       </c>
-      <c r="M39" s="82">
+      <c r="M39" s="67">
         <f>L39*5</f>
         <v>25</v>
       </c>
-      <c r="N39" s="83">
+      <c r="N39" s="68">
         <v>27</v>
       </c>
-      <c r="O39" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P39" s="85">
-        <v>1.2012</v>
-      </c>
-      <c r="Q39" s="86">
+      <c r="O39" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P39" s="70">
+        <v>1.0485</v>
+      </c>
+      <c r="Q39" s="71">
         <f>P39*N39</f>
-        <v>32.432400000000001</v>
-      </c>
-      <c r="R39" s="83"/>
-      <c r="S39" s="82"/>
+        <v>28.3095</v>
+      </c>
+      <c r="R39" s="68"/>
+      <c r="S39" s="67"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="48">
+      <c r="B40" s="81">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="56" t="s">
+      <c r="C40" s="85" t="s">
         <v>443</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="56" t="s">
         <v>129</v>
       </c>
       <c r="F40" s="39" t="s">
@@ -4791,20 +4911,20 @@
         <v>1</v>
       </c>
       <c r="M40" s="38">
-        <f t="shared" ref="M40" si="31">L40*5</f>
+        <f t="shared" ref="M40" si="30">L40*5</f>
         <v>5</v>
       </c>
       <c r="N40" s="38">
         <v>10</v>
       </c>
-      <c r="O40" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P40" s="49">
+      <c r="O40" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P40" s="47">
         <v>4.0399999999999998E-2</v>
       </c>
       <c r="Q40" s="40">
-        <f t="shared" ref="Q40" si="32">P40*N40</f>
+        <f t="shared" ref="Q40" si="31">P40*N40</f>
         <v>0.40399999999999997</v>
       </c>
       <c r="R40" s="39"/>
@@ -4812,73 +4932,73 @@
     </row>
     <row r="41" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="47">
+      <c r="B41" s="78">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="81" t="s">
+      <c r="C41" s="86" t="s">
         <v>443</v>
       </c>
-      <c r="D41" s="82" t="s">
+      <c r="D41" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="E41" s="82" t="s">
+      <c r="E41" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="F41" s="83" t="s">
+      <c r="F41" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G41" s="82" t="s">
+      <c r="G41" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="H41" s="83" t="s">
+      <c r="H41" s="68" t="s">
         <v>332</v>
       </c>
-      <c r="I41" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J41" s="83" t="s">
+      <c r="I41" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J41" s="68" t="s">
         <v>481</v>
       </c>
-      <c r="K41" s="82" t="s">
+      <c r="K41" s="67" t="s">
         <v>391</v>
       </c>
-      <c r="L41" s="83">
+      <c r="L41" s="68">
         <v>1</v>
       </c>
-      <c r="M41" s="82">
+      <c r="M41" s="67">
         <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="83">
+      <c r="N41" s="68">
         <v>6</v>
       </c>
-      <c r="O41" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P41" s="85">
-        <v>0.47249999999999998</v>
-      </c>
-      <c r="Q41" s="86">
+      <c r="O41" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P41" s="70">
+        <v>0.5091</v>
+      </c>
+      <c r="Q41" s="71">
         <f>P41*N41</f>
-        <v>2.835</v>
-      </c>
-      <c r="R41" s="83"/>
-      <c r="S41" s="82"/>
+        <v>3.0545999999999998</v>
+      </c>
+      <c r="R41" s="68"/>
+      <c r="S41" s="67"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="48">
+      <c r="B42" s="81">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="56" t="s">
+      <c r="C42" s="85" t="s">
         <v>443</v>
       </c>
-      <c r="D42" s="38" t="s">
+      <c r="D42" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="E42" s="59" t="s">
+      <c r="E42" s="56" t="s">
         <v>131</v>
       </c>
       <c r="F42" s="39" t="s">
@@ -4903,20 +5023,20 @@
         <v>1</v>
       </c>
       <c r="M42" s="38">
-        <f t="shared" ref="M42" si="33">L42*5</f>
+        <f t="shared" ref="M42" si="32">L42*5</f>
         <v>5</v>
       </c>
       <c r="N42" s="38">
         <v>10</v>
       </c>
-      <c r="O42" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P42" s="49">
+      <c r="O42" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P42" s="47">
         <v>7.9100000000000004E-2</v>
       </c>
       <c r="Q42" s="40">
-        <f t="shared" ref="Q42" si="34">P42*N42</f>
+        <f t="shared" ref="Q42" si="33">P42*N42</f>
         <v>0.79100000000000004</v>
       </c>
       <c r="R42" s="39"/>
@@ -4924,79 +5044,79 @@
     </row>
     <row r="43" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="47">
+      <c r="B43" s="78">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="81" t="s">
+      <c r="C43" s="86" t="s">
         <v>443</v>
       </c>
-      <c r="D43" s="82" t="s">
+      <c r="D43" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="82" t="s">
+      <c r="E43" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="F43" s="83" t="s">
+      <c r="F43" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="G43" s="82" t="s">
+      <c r="G43" s="67" t="s">
         <v>266</v>
       </c>
-      <c r="H43" s="83" t="s">
+      <c r="H43" s="68" t="s">
         <v>334</v>
       </c>
-      <c r="I43" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J43" s="83" t="s">
+      <c r="I43" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J43" s="68" t="s">
         <v>483</v>
       </c>
-      <c r="K43" s="82" t="s">
+      <c r="K43" s="67" t="s">
         <v>393</v>
       </c>
-      <c r="L43" s="83">
+      <c r="L43" s="68">
         <v>1</v>
       </c>
-      <c r="M43" s="82">
+      <c r="M43" s="67">
         <f>L43*5</f>
         <v>5</v>
       </c>
-      <c r="N43" s="83">
+      <c r="N43" s="68">
         <v>10</v>
       </c>
-      <c r="O43" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P43" s="85">
-        <v>8.5099999999999995E-2</v>
-      </c>
-      <c r="Q43" s="86">
+      <c r="O43" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P43" s="70">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="Q43" s="71">
         <f>P43*N43</f>
-        <v>0.85099999999999998</v>
-      </c>
-      <c r="R43" s="83"/>
-      <c r="S43" s="82"/>
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="R43" s="68"/>
+      <c r="S43" s="67"/>
     </row>
     <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="48">
+      <c r="B44" s="81">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="56" t="s">
+      <c r="C44" s="85" t="s">
         <v>444</v>
       </c>
-      <c r="D44" s="38" t="s">
+      <c r="D44" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="56" t="s">
         <v>133</v>
       </c>
       <c r="F44" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="58" t="s">
         <v>267</v>
       </c>
       <c r="H44" s="39" t="s">
@@ -5015,94 +5135,94 @@
         <v>7</v>
       </c>
       <c r="M44" s="38">
-        <f t="shared" ref="M44" si="35">L44*5</f>
+        <f t="shared" ref="M44" si="34">L44*5</f>
         <v>35</v>
       </c>
       <c r="N44" s="38">
         <v>40</v>
       </c>
-      <c r="O44" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P44" s="49">
-        <v>3.5400000000000001E-2</v>
+      <c r="O44" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P44" s="47">
+        <v>3.6700000000000003E-2</v>
       </c>
       <c r="Q44" s="40">
-        <f t="shared" ref="Q44" si="36">P44*N44</f>
-        <v>1.4159999999999999</v>
+        <f t="shared" ref="Q44" si="35">P44*N44</f>
+        <v>1.4680000000000002</v>
       </c>
       <c r="R44" s="39"/>
       <c r="S44" s="38"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="47">
+      <c r="B45" s="78">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="81" t="s">
+      <c r="C45" s="86" t="s">
         <v>444</v>
       </c>
-      <c r="D45" s="82" t="s">
+      <c r="D45" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="82" t="s">
+      <c r="E45" s="67" t="s">
         <v>134</v>
       </c>
-      <c r="F45" s="83" t="s">
+      <c r="F45" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G45" s="82" t="s">
+      <c r="G45" s="67" t="s">
         <v>268</v>
       </c>
-      <c r="H45" s="83" t="s">
+      <c r="H45" s="68" t="s">
         <v>336</v>
       </c>
-      <c r="I45" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J45" s="83" t="s">
+      <c r="I45" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J45" s="68" t="s">
         <v>485</v>
       </c>
-      <c r="K45" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L45" s="83">
+      <c r="K45" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L45" s="68">
         <v>1</v>
       </c>
-      <c r="M45" s="82">
+      <c r="M45" s="67">
         <f>L45*5</f>
         <v>5</v>
       </c>
-      <c r="N45" s="83">
+      <c r="N45" s="68">
         <v>10</v>
       </c>
-      <c r="O45" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P45" s="85">
+      <c r="O45" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P45" s="70">
         <v>0.1216</v>
       </c>
-      <c r="Q45" s="86">
+      <c r="Q45" s="71">
         <f>P45*N45</f>
         <v>1.216</v>
       </c>
-      <c r="R45" s="83"/>
-      <c r="S45" s="82"/>
+      <c r="R45" s="68"/>
+      <c r="S45" s="67"/>
     </row>
     <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="48">
+      <c r="B46" s="81">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="85" t="s">
         <v>445</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="E46" s="59" t="s">
+      <c r="E46" s="56" t="s">
         <v>135</v>
       </c>
       <c r="F46" s="39" t="s">
@@ -5127,109 +5247,109 @@
         <v>1</v>
       </c>
       <c r="M46" s="38">
-        <f t="shared" ref="M46" si="37">L46*5</f>
+        <f t="shared" ref="M46" si="36">L46*5</f>
         <v>5</v>
       </c>
       <c r="N46" s="38">
-        <v>6</v>
-      </c>
-      <c r="O46" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P46" s="49">
-        <v>0.34010000000000001</v>
+        <v>10</v>
+      </c>
+      <c r="O46" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P46" s="47">
+        <v>0.3352</v>
       </c>
       <c r="Q46" s="40">
-        <f t="shared" ref="Q46" si="38">P46*N46</f>
-        <v>2.0406</v>
+        <f t="shared" ref="Q46" si="37">P46*N46</f>
+        <v>3.3519999999999999</v>
       </c>
       <c r="R46" s="39"/>
       <c r="S46" s="38"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="47">
+      <c r="B47" s="78">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="88" t="s">
+      <c r="C47" s="87" t="s">
         <v>394</v>
       </c>
-      <c r="D47" s="87" t="s">
+      <c r="D47" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="E47" s="87" t="s">
+      <c r="E47" s="72" t="s">
         <v>136</v>
       </c>
-      <c r="F47" s="89" t="s">
+      <c r="F47" s="73" t="s">
         <v>425</v>
       </c>
-      <c r="G47" s="87" t="s">
+      <c r="G47" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="H47" s="89" t="s">
-        <v>436</v>
-      </c>
-      <c r="I47" s="87" t="s">
-        <v>436</v>
-      </c>
-      <c r="J47" s="89" t="s">
-        <v>436</v>
-      </c>
-      <c r="K47" s="87" t="s">
-        <v>436</v>
-      </c>
-      <c r="L47" s="89">
+      <c r="H47" s="73" t="s">
+        <v>436</v>
+      </c>
+      <c r="I47" s="72" t="s">
+        <v>436</v>
+      </c>
+      <c r="J47" s="73" t="s">
+        <v>436</v>
+      </c>
+      <c r="K47" s="72" t="s">
+        <v>436</v>
+      </c>
+      <c r="L47" s="73">
         <v>2</v>
       </c>
-      <c r="M47" s="87">
+      <c r="M47" s="72">
         <f>L47*5</f>
         <v>10</v>
       </c>
-      <c r="N47" s="89" t="s">
-        <v>436</v>
-      </c>
-      <c r="O47" s="90" t="s">
-        <v>436</v>
-      </c>
-      <c r="P47" s="91" t="s">
-        <v>436</v>
-      </c>
-      <c r="Q47" s="92" t="s">
-        <v>436</v>
-      </c>
-      <c r="R47" s="89"/>
-      <c r="S47" s="87"/>
+      <c r="N47" s="73" t="s">
+        <v>436</v>
+      </c>
+      <c r="O47" s="74" t="s">
+        <v>436</v>
+      </c>
+      <c r="P47" s="75" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q47" s="76" t="s">
+        <v>436</v>
+      </c>
+      <c r="R47" s="73"/>
+      <c r="S47" s="72"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="48">
+      <c r="B48" s="81">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="56" t="s">
+      <c r="C48" s="85" t="s">
         <v>438</v>
       </c>
-      <c r="D48" s="38" t="s">
+      <c r="D48" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="59" t="s">
+      <c r="E48" s="56" t="s">
         <v>137</v>
       </c>
       <c r="F48" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="G48" s="61">
+      <c r="G48" s="58">
         <v>61300311121</v>
       </c>
       <c r="H48" s="39" t="s">
         <v>338</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K48" s="38" t="s">
         <v>436</v>
@@ -5238,20 +5358,20 @@
         <v>2</v>
       </c>
       <c r="M48" s="38">
-        <f t="shared" ref="M48" si="39">L48*5</f>
+        <f t="shared" ref="M48" si="38">L48*5</f>
         <v>10</v>
       </c>
       <c r="N48" s="38">
         <v>50</v>
       </c>
-      <c r="O48" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P48" s="49">
+      <c r="O48" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P48" s="47">
         <v>1.44E-2</v>
       </c>
       <c r="Q48" s="40">
-        <f t="shared" ref="Q48" si="40">P48*N48</f>
+        <f t="shared" ref="Q48" si="39">P48*N48</f>
         <v>0.72</v>
       </c>
       <c r="R48" s="39"/>
@@ -5259,79 +5379,79 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="47">
+      <c r="B49" s="78">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="81" t="s">
+      <c r="C49" s="86" t="s">
         <v>438</v>
       </c>
-      <c r="D49" s="82" t="s">
+      <c r="D49" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="E49" s="82" t="s">
+      <c r="E49" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="F49" s="83" t="s">
+      <c r="F49" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="G49" s="87">
+      <c r="G49" s="72">
         <v>61300611121</v>
       </c>
-      <c r="H49" s="83" t="s">
+      <c r="H49" s="68" t="s">
         <v>338</v>
       </c>
-      <c r="I49" s="82" t="s">
+      <c r="I49" s="67" t="s">
         <v>495</v>
       </c>
-      <c r="J49" s="83" t="s">
+      <c r="J49" s="68" t="s">
         <v>487</v>
       </c>
-      <c r="K49" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L49" s="83">
+      <c r="K49" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L49" s="68">
         <v>4</v>
       </c>
-      <c r="M49" s="82">
+      <c r="M49" s="67">
         <f>L49*5</f>
         <v>20</v>
       </c>
-      <c r="N49" s="83">
+      <c r="N49" s="68">
         <v>40</v>
       </c>
-      <c r="O49" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P49" s="85">
-        <v>2.9700000000000001E-2</v>
-      </c>
-      <c r="Q49" s="86">
+      <c r="O49" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P49" s="70">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="Q49" s="71">
         <f>P49*N49</f>
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="R49" s="83"/>
-      <c r="S49" s="82"/>
+        <v>1.232</v>
+      </c>
+      <c r="R49" s="68"/>
+      <c r="S49" s="67"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="48">
+      <c r="B50" s="81">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="56" t="s">
+      <c r="C50" s="85" t="s">
         <v>438</v>
       </c>
-      <c r="D50" s="38" t="s">
+      <c r="D50" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="59" t="s">
+      <c r="E50" s="56" t="s">
         <v>139</v>
       </c>
       <c r="F50" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="G50" s="61" t="s">
+      <c r="G50" s="58" t="s">
         <v>269</v>
       </c>
       <c r="H50" s="39" t="s">
@@ -5350,107 +5470,107 @@
         <v>1</v>
       </c>
       <c r="M50" s="38">
-        <f t="shared" ref="M50" si="41">L50*5</f>
+        <f t="shared" ref="M50" si="40">L50*5</f>
         <v>5</v>
       </c>
       <c r="N50" s="38">
         <v>10</v>
       </c>
-      <c r="O50" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P50" s="49">
+      <c r="O50" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P50" s="47">
         <v>0.11509999999999999</v>
       </c>
       <c r="Q50" s="40">
-        <f t="shared" ref="Q50" si="42">P50*N50</f>
+        <f t="shared" ref="Q50" si="41">P50*N50</f>
         <v>1.151</v>
       </c>
       <c r="R50" s="39"/>
       <c r="S50" s="38"/>
     </row>
-    <row r="51" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="47">
+      <c r="B51" s="78">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="81" t="s">
+      <c r="C51" s="86" t="s">
         <v>438</v>
       </c>
-      <c r="D51" s="82" t="s">
+      <c r="D51" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="E51" s="82" t="s">
+      <c r="E51" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="F51" s="83" t="s">
+      <c r="F51" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="G51" s="87">
+      <c r="G51" s="72">
         <v>61300211121</v>
       </c>
-      <c r="H51" s="83" t="s">
+      <c r="H51" s="68" t="s">
         <v>338</v>
       </c>
-      <c r="I51" s="82" t="s">
-        <v>496</v>
-      </c>
-      <c r="J51" s="83" t="s">
+      <c r="I51" s="67" t="s">
+        <v>566</v>
+      </c>
+      <c r="J51" s="68" t="s">
         <v>489</v>
       </c>
-      <c r="K51" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L51" s="83">
+      <c r="K51" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L51" s="68">
         <v>3</v>
       </c>
-      <c r="M51" s="82">
+      <c r="M51" s="67">
         <f>L51*5</f>
         <v>15</v>
       </c>
-      <c r="N51" s="83">
+      <c r="N51" s="68">
         <v>50</v>
       </c>
-      <c r="O51" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P51" s="85">
-        <v>1.3299999999999999E-2</v>
-      </c>
-      <c r="Q51" s="86">
+      <c r="O51" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P51" s="70">
+        <v>1.37E-2</v>
+      </c>
+      <c r="Q51" s="71">
         <f>P51*N51</f>
-        <v>0.66499999999999992</v>
-      </c>
-      <c r="R51" s="83"/>
-      <c r="S51" s="82"/>
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="R51" s="68"/>
+      <c r="S51" s="67"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="48">
+      <c r="B52" s="81">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="56" t="s">
+      <c r="C52" s="85" t="s">
         <v>438</v>
       </c>
-      <c r="D52" s="38" t="s">
+      <c r="D52" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="E52" s="59" t="s">
+      <c r="E52" s="56" t="s">
         <v>141</v>
       </c>
       <c r="F52" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="G52" s="61">
+      <c r="G52" s="58">
         <v>61300411121</v>
       </c>
       <c r="H52" s="39" t="s">
         <v>338</v>
       </c>
       <c r="I52" s="38" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J52" s="39" t="s">
         <v>490</v>
@@ -5462,94 +5582,94 @@
         <v>1</v>
       </c>
       <c r="M52" s="38">
-        <f t="shared" ref="M52" si="43">L52*5</f>
+        <f t="shared" ref="M52" si="42">L52*5</f>
         <v>5</v>
       </c>
       <c r="N52" s="38">
         <v>20</v>
       </c>
-      <c r="O52" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P52" s="49">
-        <v>2.18E-2</v>
+      <c r="O52" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P52" s="47">
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="Q52" s="40">
-        <f t="shared" ref="Q52" si="44">P52*N52</f>
-        <v>0.436</v>
+        <f t="shared" ref="Q52" si="43">P52*N52</f>
+        <v>0.44200000000000006</v>
       </c>
       <c r="R52" s="39"/>
       <c r="S52" s="38"/>
     </row>
     <row r="53" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="47">
+      <c r="B53" s="78">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="82" t="s">
+      <c r="D53" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E53" s="82" t="s">
+      <c r="E53" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="F53" s="83" t="s">
+      <c r="F53" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="G53" s="82" t="s">
+      <c r="G53" s="67" t="s">
         <v>270</v>
       </c>
-      <c r="H53" s="83" t="s">
+      <c r="H53" s="68" t="s">
         <v>323</v>
       </c>
-      <c r="I53" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J53" s="83" t="s">
+      <c r="I53" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J53" s="68" t="s">
         <v>491</v>
       </c>
-      <c r="K53" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L53" s="83">
+      <c r="K53" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L53" s="68">
         <v>9</v>
       </c>
-      <c r="M53" s="82">
+      <c r="M53" s="67">
         <f>L53*5</f>
         <v>45</v>
       </c>
-      <c r="N53" s="83">
+      <c r="N53" s="68">
         <v>47</v>
       </c>
-      <c r="O53" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P53" s="85">
+      <c r="O53" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P53" s="70">
         <v>0.31269999999999998</v>
       </c>
-      <c r="Q53" s="86">
+      <c r="Q53" s="71">
         <f>P53*N53</f>
         <v>14.696899999999999</v>
       </c>
-      <c r="R53" s="83"/>
-      <c r="S53" s="82"/>
+      <c r="R53" s="68"/>
+      <c r="S53" s="67"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="48">
+      <c r="B54" s="81">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="56" t="s">
+      <c r="C54" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="38" t="s">
+      <c r="D54" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="E54" s="59" t="s">
+      <c r="E54" s="56" t="s">
         <v>143</v>
       </c>
       <c r="F54" s="39" t="s">
@@ -5574,94 +5694,94 @@
         <v>1</v>
       </c>
       <c r="M54" s="38">
-        <f t="shared" ref="M54" si="45">L54*5</f>
+        <f t="shared" ref="M54" si="44">L54*5</f>
         <v>5</v>
       </c>
       <c r="N54" s="38">
         <v>10</v>
       </c>
-      <c r="O54" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P54" s="49">
-        <v>7.0800000000000002E-2</v>
+      <c r="O54" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P54" s="47">
+        <v>7.3599999999999999E-2</v>
       </c>
       <c r="Q54" s="40">
-        <f t="shared" ref="Q54" si="46">P54*N54</f>
-        <v>0.70799999999999996</v>
+        <f t="shared" ref="Q54" si="45">P54*N54</f>
+        <v>0.73599999999999999</v>
       </c>
       <c r="R54" s="39"/>
       <c r="S54" s="38"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="47">
+      <c r="B55" s="78">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="81" t="s">
+      <c r="C55" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="82" t="s">
+      <c r="D55" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="E55" s="82" t="s">
+      <c r="E55" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="F55" s="83" t="s">
+      <c r="F55" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="G55" s="82" t="s">
+      <c r="G55" s="67" t="s">
         <v>272</v>
       </c>
-      <c r="H55" s="83" t="s">
+      <c r="H55" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="I55" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J55" s="83" t="s">
-        <v>436</v>
-      </c>
-      <c r="K55" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L55" s="83">
+      <c r="I55" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J55" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="K55" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L55" s="68">
         <v>2</v>
       </c>
-      <c r="M55" s="82">
+      <c r="M55" s="67">
         <f>L55*5</f>
         <v>10</v>
       </c>
-      <c r="N55" s="83">
-        <v>40</v>
-      </c>
-      <c r="O55" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P55" s="85">
-        <v>0.72070000000000001</v>
-      </c>
-      <c r="Q55" s="86">
+      <c r="N55" s="68">
+        <v>11</v>
+      </c>
+      <c r="O55" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P55" s="70">
+        <v>0.80189999999999995</v>
+      </c>
+      <c r="Q55" s="71">
         <f>P55*N55</f>
-        <v>28.827999999999999</v>
-      </c>
-      <c r="R55" s="83"/>
-      <c r="S55" s="82"/>
+        <v>8.8209</v>
+      </c>
+      <c r="R55" s="68"/>
+      <c r="S55" s="67"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="48">
+      <c r="B56" s="81">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="56" t="s">
+      <c r="C56" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="38" t="s">
+      <c r="D56" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="E56" s="59" t="s">
+      <c r="E56" s="56" t="s">
         <v>145</v>
       </c>
       <c r="F56" s="39" t="s">
@@ -5686,94 +5806,94 @@
         <v>2</v>
       </c>
       <c r="M56" s="38">
-        <f t="shared" ref="M56" si="47">L56*5</f>
+        <f t="shared" ref="M56" si="46">L56*5</f>
         <v>10</v>
       </c>
       <c r="N56" s="38">
         <v>15</v>
       </c>
-      <c r="O56" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P56" s="49">
-        <v>0.1182</v>
+      <c r="O56" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P56" s="47">
+        <v>0.1227</v>
       </c>
       <c r="Q56" s="40">
-        <f t="shared" ref="Q56" si="48">P56*N56</f>
-        <v>1.7729999999999999</v>
+        <f t="shared" ref="Q56" si="47">P56*N56</f>
+        <v>1.8405</v>
       </c>
       <c r="R56" s="39"/>
       <c r="S56" s="38"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="47">
+      <c r="B57" s="78">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="81" t="s">
+      <c r="C57" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="D57" s="82" t="s">
+      <c r="D57" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="E57" s="82" t="s">
+      <c r="E57" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="F57" s="83" t="s">
+      <c r="F57" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="G57" s="82" t="s">
+      <c r="G57" s="67" t="s">
         <v>274</v>
       </c>
-      <c r="H57" s="83" t="s">
+      <c r="H57" s="68" t="s">
         <v>323</v>
       </c>
-      <c r="I57" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J57" s="83" t="s">
+      <c r="I57" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J57" s="68" t="s">
         <v>368</v>
       </c>
-      <c r="K57" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L57" s="83">
+      <c r="K57" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L57" s="68">
         <v>6</v>
       </c>
-      <c r="M57" s="82">
+      <c r="M57" s="67">
         <f>L57*5</f>
         <v>30</v>
       </c>
-      <c r="N57" s="83">
-        <v>20</v>
-      </c>
-      <c r="O57" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P57" s="85">
-        <v>3.3500000000000002E-2</v>
-      </c>
-      <c r="Q57" s="86">
+      <c r="N57" s="68">
+        <v>40</v>
+      </c>
+      <c r="O57" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P57" s="70">
+        <v>3.49E-2</v>
+      </c>
+      <c r="Q57" s="71">
         <f>P57*N57</f>
-        <v>0.67</v>
-      </c>
-      <c r="R57" s="83"/>
-      <c r="S57" s="82"/>
+        <v>1.3959999999999999</v>
+      </c>
+      <c r="R57" s="68"/>
+      <c r="S57" s="67"/>
     </row>
     <row r="58" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="48">
+      <c r="B58" s="81">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="56" t="s">
+      <c r="C58" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="38" t="s">
+      <c r="D58" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="56" t="s">
         <v>147</v>
       </c>
       <c r="F58" s="39" t="s">
@@ -5789,7 +5909,7 @@
         <v>436</v>
       </c>
       <c r="J58" s="39" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K58" s="38" t="s">
         <v>436</v>
@@ -5798,94 +5918,94 @@
         <v>10</v>
       </c>
       <c r="M58" s="38">
-        <f t="shared" ref="M58" si="49">L58*5</f>
+        <f t="shared" ref="M58" si="48">L58*5</f>
         <v>50</v>
       </c>
       <c r="N58" s="38">
         <v>60</v>
       </c>
-      <c r="O58" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P58" s="49">
-        <v>1.9099999999999999E-2</v>
+      <c r="O58" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P58" s="47">
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="Q58" s="40">
-        <f t="shared" ref="Q58" si="50">P58*N58</f>
-        <v>1.1459999999999999</v>
+        <f t="shared" ref="Q58" si="49">P58*N58</f>
+        <v>1.1640000000000001</v>
       </c>
       <c r="R58" s="39"/>
       <c r="S58" s="38"/>
     </row>
     <row r="59" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="47">
+      <c r="B59" s="78">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="81" t="s">
+      <c r="C59" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="82" t="s">
+      <c r="D59" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E59" s="82" t="s">
+      <c r="E59" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="F59" s="83" t="s">
+      <c r="F59" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="G59" s="82" t="s">
+      <c r="G59" s="67" t="s">
         <v>276</v>
       </c>
-      <c r="H59" s="83" t="s">
+      <c r="H59" s="68" t="s">
         <v>342</v>
       </c>
-      <c r="I59" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J59" s="83" t="s">
-        <v>500</v>
-      </c>
-      <c r="K59" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L59" s="83">
+      <c r="I59" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J59" s="68" t="s">
+        <v>499</v>
+      </c>
+      <c r="K59" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L59" s="68">
         <v>2</v>
       </c>
-      <c r="M59" s="82">
+      <c r="M59" s="67">
         <f>L59*5</f>
         <v>10</v>
       </c>
-      <c r="N59" s="83">
+      <c r="N59" s="68">
         <v>20</v>
       </c>
-      <c r="O59" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P59" s="85">
-        <v>2.0299999999999999E-2</v>
-      </c>
-      <c r="Q59" s="86">
+      <c r="O59" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P59" s="70">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q59" s="71">
         <f>P59*N59</f>
-        <v>0.40599999999999997</v>
-      </c>
-      <c r="R59" s="83"/>
-      <c r="S59" s="82"/>
+        <v>0.5</v>
+      </c>
+      <c r="R59" s="68"/>
+      <c r="S59" s="67"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="48">
+      <c r="B60" s="81">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="56" t="s">
+      <c r="C60" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D60" s="38" t="s">
+      <c r="D60" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="E60" s="59" t="s">
+      <c r="E60" s="56" t="s">
         <v>149</v>
       </c>
       <c r="F60" s="39" t="s">
@@ -5901,7 +6021,7 @@
         <v>436</v>
       </c>
       <c r="J60" s="39" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K60" s="38" t="s">
         <v>436</v>
@@ -5910,94 +6030,94 @@
         <v>3</v>
       </c>
       <c r="M60" s="38">
-        <f t="shared" ref="M60" si="51">L60*5</f>
+        <f t="shared" ref="M60" si="50">L60*5</f>
         <v>15</v>
       </c>
       <c r="N60" s="38">
         <v>20</v>
       </c>
-      <c r="O60" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P60" s="49">
-        <v>2.9899999999999999E-2</v>
+      <c r="O60" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P60" s="47">
+        <v>2.9700000000000001E-2</v>
       </c>
       <c r="Q60" s="40">
-        <f t="shared" ref="Q60" si="52">P60*N60</f>
-        <v>0.59799999999999998</v>
+        <f t="shared" ref="Q60" si="51">P60*N60</f>
+        <v>0.59399999999999997</v>
       </c>
       <c r="R60" s="39"/>
       <c r="S60" s="38"/>
     </row>
     <row r="61" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="47">
+      <c r="B61" s="78">
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="81" t="s">
+      <c r="C61" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="82" t="s">
+      <c r="D61" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="E61" s="82" t="s">
+      <c r="E61" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="F61" s="83" t="s">
+      <c r="F61" s="68" t="s">
         <v>440</v>
       </c>
-      <c r="G61" s="82" t="s">
+      <c r="G61" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="H61" s="83" t="s">
+      <c r="H61" s="68" t="s">
         <v>343</v>
       </c>
-      <c r="I61" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J61" s="83" t="s">
-        <v>502</v>
-      </c>
-      <c r="K61" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L61" s="83">
+      <c r="I61" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J61" s="68" t="s">
+        <v>501</v>
+      </c>
+      <c r="K61" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L61" s="68">
         <v>1</v>
       </c>
-      <c r="M61" s="82">
+      <c r="M61" s="67">
         <f>L61*5</f>
         <v>5</v>
       </c>
-      <c r="N61" s="83">
+      <c r="N61" s="68">
         <v>10</v>
       </c>
-      <c r="O61" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P61" s="85">
-        <v>0.3261</v>
-      </c>
-      <c r="Q61" s="86">
+      <c r="O61" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P61" s="70">
+        <v>0.32490000000000002</v>
+      </c>
+      <c r="Q61" s="71">
         <f>P61*N61</f>
-        <v>3.2610000000000001</v>
-      </c>
-      <c r="R61" s="83"/>
-      <c r="S61" s="82"/>
+        <v>3.2490000000000001</v>
+      </c>
+      <c r="R61" s="68"/>
+      <c r="S61" s="67"/>
     </row>
     <row r="62" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="48">
+      <c r="B62" s="81">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="56" t="s">
+      <c r="C62" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D62" s="38" t="s">
+      <c r="D62" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="E62" s="59" t="s">
+      <c r="E62" s="56" t="s">
         <v>151</v>
       </c>
       <c r="F62" s="39" t="s">
@@ -6022,94 +6142,94 @@
         <v>1</v>
       </c>
       <c r="M62" s="38">
-        <f t="shared" ref="M62" si="53">L62*5</f>
+        <f t="shared" ref="M62" si="52">L62*5</f>
         <v>5</v>
       </c>
       <c r="N62" s="38">
         <v>10</v>
       </c>
-      <c r="O62" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P62" s="49">
-        <v>4.3700000000000003E-2</v>
+      <c r="O62" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P62" s="47">
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="Q62" s="40">
-        <f t="shared" ref="Q62" si="54">P62*N62</f>
-        <v>0.43700000000000006</v>
+        <f t="shared" ref="Q62" si="53">P62*N62</f>
+        <v>0.46899999999999997</v>
       </c>
       <c r="R62" s="39"/>
       <c r="S62" s="38"/>
     </row>
     <row r="63" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="47">
+      <c r="B63" s="78">
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="81" t="s">
+      <c r="C63" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D63" s="82" t="s">
+      <c r="D63" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="E63" s="82" t="s">
+      <c r="E63" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="F63" s="83" t="s">
+      <c r="F63" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G63" s="82" t="s">
+      <c r="G63" s="67" t="s">
         <v>279</v>
       </c>
-      <c r="H63" s="83" t="s">
+      <c r="H63" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I63" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J63" s="83" t="s">
-        <v>503</v>
-      </c>
-      <c r="K63" s="82" t="s">
+      <c r="I63" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J63" s="68" t="s">
+        <v>502</v>
+      </c>
+      <c r="K63" s="67" t="s">
         <v>395</v>
       </c>
-      <c r="L63" s="83">
+      <c r="L63" s="68">
         <v>1</v>
       </c>
-      <c r="M63" s="82">
+      <c r="M63" s="67">
         <f>L63*5</f>
         <v>5</v>
       </c>
-      <c r="N63" s="83">
+      <c r="N63" s="68">
         <v>100</v>
       </c>
-      <c r="O63" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P63" s="85">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="Q63" s="86">
+      <c r="O63" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P63" s="70">
+        <v>2E-3</v>
+      </c>
+      <c r="Q63" s="71">
         <f>P63*N63</f>
-        <v>0.21</v>
-      </c>
-      <c r="R63" s="83"/>
-      <c r="S63" s="82"/>
+        <v>0.2</v>
+      </c>
+      <c r="R63" s="68"/>
+      <c r="S63" s="67"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="48">
+      <c r="B64" s="81">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="56" t="s">
+      <c r="C64" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D64" s="38" t="s">
+      <c r="D64" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="E64" s="59" t="s">
+      <c r="E64" s="56" t="s">
         <v>153</v>
       </c>
       <c r="F64" s="39" t="s">
@@ -6125,7 +6245,7 @@
         <v>436</v>
       </c>
       <c r="J64" s="39" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K64" s="38" t="s">
         <v>396</v>
@@ -6134,20 +6254,20 @@
         <v>1</v>
       </c>
       <c r="M64" s="38">
-        <f t="shared" ref="M64" si="55">L64*5</f>
+        <f t="shared" ref="M64" si="54">L64*5</f>
         <v>5</v>
       </c>
       <c r="N64" s="38">
         <v>100</v>
       </c>
-      <c r="O64" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P64" s="49">
+      <c r="O64" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P64" s="47">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q64" s="40">
-        <f t="shared" ref="Q64" si="56">P64*N64</f>
+        <f t="shared" ref="Q64" si="55">P64*N64</f>
         <v>0.12</v>
       </c>
       <c r="R64" s="39"/>
@@ -6155,74 +6275,74 @@
     </row>
     <row r="65" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="47">
+      <c r="B65" s="78">
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="81" t="s">
+      <c r="C65" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="82" t="s">
+      <c r="D65" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="E65" s="82" t="s">
+      <c r="E65" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="F65" s="83" t="s">
+      <c r="F65" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G65" s="82" t="s">
+      <c r="G65" s="67" t="s">
         <v>435</v>
       </c>
-      <c r="H65" s="83" t="s">
+      <c r="H65" s="68" t="s">
         <v>345</v>
       </c>
-      <c r="I65" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J65" s="83" t="s">
-        <v>505</v>
-      </c>
-      <c r="K65" s="82" t="s">
+      <c r="I65" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J65" s="68" t="s">
+        <v>504</v>
+      </c>
+      <c r="K65" s="67" t="s">
         <v>397</v>
       </c>
-      <c r="L65" s="83">
+      <c r="L65" s="68">
         <v>1</v>
       </c>
-      <c r="M65" s="82">
+      <c r="M65" s="67">
         <f>L65*5</f>
         <v>5</v>
       </c>
-      <c r="N65" s="83">
+      <c r="N65" s="68">
         <v>50</v>
       </c>
-      <c r="O65" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P65" s="85">
+      <c r="O65" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P65" s="70">
         <v>3.8E-3</v>
       </c>
-      <c r="Q65" s="86">
+      <c r="Q65" s="71">
         <f>P65*N65</f>
         <v>0.19</v>
       </c>
-      <c r="R65" s="83"/>
-      <c r="S65" s="82"/>
+      <c r="R65" s="68"/>
+      <c r="S65" s="67"/>
     </row>
     <row r="66" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="47">
+      <c r="B66" s="78">
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="56" t="s">
+      <c r="C66" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="38" t="s">
+      <c r="D66" s="82" t="s">
         <v>454</v>
       </c>
-      <c r="E66" s="59" t="s">
-        <v>547</v>
+      <c r="E66" s="56" t="s">
+        <v>541</v>
       </c>
       <c r="F66" s="39" t="s">
         <v>227</v>
@@ -6252,10 +6372,10 @@
       <c r="N66" s="38">
         <v>100</v>
       </c>
-      <c r="O66" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P66" s="49">
+      <c r="O66" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P66" s="47">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q66" s="40">
@@ -6267,73 +6387,73 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="48">
+      <c r="B67" s="81">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="81" t="s">
+      <c r="C67" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D67" s="82" t="s">
+      <c r="D67" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="E67" s="82" t="s">
+      <c r="E67" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="F67" s="83" t="s">
+      <c r="F67" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G67" s="82" t="s">
+      <c r="G67" s="67" t="s">
         <v>282</v>
       </c>
-      <c r="H67" s="83" t="s">
+      <c r="H67" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I67" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J67" s="83" t="s">
-        <v>506</v>
-      </c>
-      <c r="K67" s="82" t="s">
+      <c r="I67" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J67" s="68" t="s">
+        <v>505</v>
+      </c>
+      <c r="K67" s="67" t="s">
         <v>400</v>
       </c>
-      <c r="L67" s="83">
+      <c r="L67" s="68">
         <v>2</v>
       </c>
-      <c r="M67" s="82">
-        <f t="shared" ref="M67" si="57">L67*5</f>
+      <c r="M67" s="67">
+        <f t="shared" ref="M67" si="56">L67*5</f>
         <v>10</v>
       </c>
-      <c r="N67" s="83">
+      <c r="N67" s="68">
         <v>100</v>
       </c>
-      <c r="O67" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P67" s="85">
+      <c r="O67" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P67" s="70">
         <v>1.5E-3</v>
       </c>
-      <c r="Q67" s="86">
-        <f t="shared" ref="Q67" si="58">P67*N67</f>
+      <c r="Q67" s="71">
+        <f t="shared" ref="Q67" si="57">P67*N67</f>
         <v>0.15</v>
       </c>
-      <c r="R67" s="83"/>
-      <c r="S67" s="82"/>
+      <c r="R67" s="68"/>
+      <c r="S67" s="67"/>
     </row>
     <row r="68" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="47">
+      <c r="B68" s="78">
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="56" t="s">
+      <c r="C68" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D68" s="38" t="s">
+      <c r="D68" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="E68" s="59" t="s">
+      <c r="E68" s="56" t="s">
         <v>156</v>
       </c>
       <c r="F68" s="39" t="s">
@@ -6349,7 +6469,7 @@
         <v>436</v>
       </c>
       <c r="J68" s="39" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K68" s="38" t="s">
         <v>401</v>
@@ -6364,10 +6484,10 @@
       <c r="N68" s="38">
         <v>100</v>
       </c>
-      <c r="O68" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P68" s="49">
+      <c r="O68" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P68" s="47">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q68" s="40">
@@ -6379,73 +6499,73 @@
     </row>
     <row r="69" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="48">
+      <c r="B69" s="81">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="81" t="s">
+      <c r="C69" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D69" s="82" t="s">
+      <c r="D69" s="79" t="s">
         <v>448</v>
       </c>
-      <c r="E69" s="82" t="s">
+      <c r="E69" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="F69" s="83" t="s">
+      <c r="F69" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="G69" s="82" t="s">
+      <c r="G69" s="67" t="s">
         <v>284</v>
       </c>
-      <c r="H69" s="83" t="s">
+      <c r="H69" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I69" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J69" s="83" t="s">
+      <c r="I69" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J69" s="68" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="82" t="s">
+      <c r="K69" s="67" t="s">
         <v>398</v>
       </c>
-      <c r="L69" s="83">
+      <c r="L69" s="68">
         <v>20</v>
       </c>
-      <c r="M69" s="82">
-        <f t="shared" ref="M69" si="59">L69*5</f>
+      <c r="M69" s="67">
+        <f t="shared" ref="M69" si="58">L69*5</f>
         <v>100</v>
       </c>
-      <c r="N69" s="83">
+      <c r="N69" s="68">
         <v>200</v>
       </c>
-      <c r="O69" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P69" s="85">
+      <c r="O69" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P69" s="70">
         <v>1E-3</v>
       </c>
-      <c r="Q69" s="86">
-        <f t="shared" ref="Q69" si="60">P69*N69</f>
+      <c r="Q69" s="71">
+        <f t="shared" ref="Q69" si="59">P69*N69</f>
         <v>0.2</v>
       </c>
-      <c r="R69" s="83"/>
-      <c r="S69" s="82"/>
+      <c r="R69" s="68"/>
+      <c r="S69" s="67"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="47">
+      <c r="B70" s="78">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="56" t="s">
+      <c r="C70" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="38" t="s">
+      <c r="D70" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="E70" s="59" t="s">
+      <c r="E70" s="56" t="s">
         <v>158</v>
       </c>
       <c r="F70" s="39" t="s">
@@ -6461,7 +6581,7 @@
         <v>436</v>
       </c>
       <c r="J70" s="39" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K70" s="38" t="s">
         <v>402</v>
@@ -6476,88 +6596,88 @@
       <c r="N70" s="38">
         <v>100</v>
       </c>
-      <c r="O70" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P70" s="49">
-        <v>1.1999999999999999E-3</v>
+      <c r="O70" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P70" s="47">
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q70" s="40">
         <f>P70*N70</f>
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="R70" s="39"/>
       <c r="S70" s="38"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="48">
+      <c r="B71" s="81">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="81" t="s">
+      <c r="C71" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="82" t="s">
+      <c r="D71" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="E71" s="82" t="s">
+      <c r="E71" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="F71" s="83" t="s">
+      <c r="F71" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G71" s="82" t="s">
+      <c r="G71" s="67" t="s">
         <v>286</v>
       </c>
-      <c r="H71" s="83" t="s">
+      <c r="H71" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I71" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J71" s="83" t="s">
-        <v>508</v>
-      </c>
-      <c r="K71" s="82" t="s">
+      <c r="I71" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J71" s="68" t="s">
+        <v>507</v>
+      </c>
+      <c r="K71" s="67" t="s">
         <v>403</v>
       </c>
-      <c r="L71" s="83">
+      <c r="L71" s="68">
         <v>3</v>
       </c>
-      <c r="M71" s="82">
-        <f t="shared" ref="M71" si="61">L71*5</f>
+      <c r="M71" s="67">
+        <f t="shared" ref="M71" si="60">L71*5</f>
         <v>15</v>
       </c>
-      <c r="N71" s="83">
+      <c r="N71" s="68">
         <v>100</v>
       </c>
-      <c r="O71" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P71" s="85">
+      <c r="O71" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P71" s="70">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q71" s="86">
-        <f t="shared" ref="Q71" si="62">P71*N71</f>
+      <c r="Q71" s="71">
+        <f t="shared" ref="Q71" si="61">P71*N71</f>
         <v>0.12</v>
       </c>
-      <c r="R71" s="83"/>
-      <c r="S71" s="82"/>
+      <c r="R71" s="68"/>
+      <c r="S71" s="67"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="47">
+      <c r="B72" s="78">
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="56" t="s">
+      <c r="C72" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D72" s="38" t="s">
+      <c r="D72" s="82" t="s">
         <v>453</v>
       </c>
-      <c r="E72" s="59" t="s">
+      <c r="E72" s="56" t="s">
         <v>160</v>
       </c>
       <c r="F72" s="39" t="s">
@@ -6573,7 +6693,7 @@
         <v>436</v>
       </c>
       <c r="J72" s="39" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K72" s="38" t="s">
         <v>404</v>
@@ -6588,10 +6708,10 @@
       <c r="N72" s="38">
         <v>100</v>
       </c>
-      <c r="O72" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P72" s="49">
+      <c r="O72" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P72" s="47">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q72" s="40">
@@ -6603,73 +6723,73 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="B73" s="48">
+      <c r="B73" s="81">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="81" t="s">
+      <c r="C73" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="82" t="s">
+      <c r="D73" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="E73" s="82" t="s">
+      <c r="E73" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="F73" s="83" t="s">
+      <c r="F73" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G73" s="82" t="s">
+      <c r="G73" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="H73" s="83" t="s">
+      <c r="H73" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I73" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J73" s="83" t="s">
-        <v>529</v>
-      </c>
-      <c r="K73" s="82" t="s">
+      <c r="I73" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J73" s="68" t="s">
+        <v>527</v>
+      </c>
+      <c r="K73" s="67" t="s">
         <v>405</v>
       </c>
-      <c r="L73" s="83">
+      <c r="L73" s="68">
         <v>2</v>
       </c>
-      <c r="M73" s="82">
-        <f t="shared" ref="M73" si="63">L73*5</f>
+      <c r="M73" s="67">
+        <f t="shared" ref="M73" si="62">L73*5</f>
         <v>10</v>
       </c>
-      <c r="N73" s="83">
+      <c r="N73" s="68">
         <v>100</v>
       </c>
-      <c r="O73" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P73" s="85">
+      <c r="O73" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P73" s="70">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q73" s="86">
-        <f t="shared" ref="Q73" si="64">P73*N73</f>
+      <c r="Q73" s="71">
+        <f t="shared" ref="Q73" si="63">P73*N73</f>
         <v>0.12</v>
       </c>
-      <c r="R73" s="83"/>
-      <c r="S73" s="82"/>
+      <c r="R73" s="68"/>
+      <c r="S73" s="67"/>
     </row>
     <row r="74" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="47">
+      <c r="B74" s="78">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="56" t="s">
+      <c r="C74" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="38" t="s">
+      <c r="D74" s="82" t="s">
         <v>450</v>
       </c>
-      <c r="E74" s="59" t="s">
+      <c r="E74" s="56" t="s">
         <v>162</v>
       </c>
       <c r="F74" s="39" t="s">
@@ -6685,7 +6805,7 @@
         <v>436</v>
       </c>
       <c r="J74" s="39" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K74" s="38" t="s">
         <v>406</v>
@@ -6700,10 +6820,10 @@
       <c r="N74" s="38">
         <v>100</v>
       </c>
-      <c r="O74" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P74" s="49">
+      <c r="O74" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P74" s="47">
         <v>1E-3</v>
       </c>
       <c r="Q74" s="40">
@@ -6715,73 +6835,73 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="48">
+      <c r="B75" s="81">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="81" t="s">
+      <c r="C75" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="82" t="s">
-        <v>548</v>
-      </c>
-      <c r="E75" s="82" t="s">
+      <c r="D75" s="79" t="s">
+        <v>542</v>
+      </c>
+      <c r="E75" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="F75" s="83" t="s">
+      <c r="F75" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="G75" s="82" t="s">
+      <c r="G75" s="67" t="s">
         <v>290</v>
       </c>
-      <c r="H75" s="83" t="s">
+      <c r="H75" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I75" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J75" s="83" t="s">
-        <v>530</v>
-      </c>
-      <c r="K75" s="82" t="s">
+      <c r="I75" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J75" s="68" t="s">
+        <v>528</v>
+      </c>
+      <c r="K75" s="67" t="s">
         <v>408</v>
       </c>
-      <c r="L75" s="83">
+      <c r="L75" s="68">
         <v>2</v>
       </c>
-      <c r="M75" s="82">
-        <f t="shared" ref="M75" si="65">L75*5</f>
+      <c r="M75" s="67">
+        <f t="shared" ref="M75" si="64">L75*5</f>
         <v>10</v>
       </c>
-      <c r="N75" s="83">
+      <c r="N75" s="68">
         <v>20</v>
       </c>
-      <c r="O75" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P75" s="85">
+      <c r="O75" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P75" s="70">
         <v>2.92E-2</v>
       </c>
-      <c r="Q75" s="86">
-        <f t="shared" ref="Q75" si="66">P75*N75</f>
+      <c r="Q75" s="71">
+        <f t="shared" ref="Q75" si="65">P75*N75</f>
         <v>0.58399999999999996</v>
       </c>
-      <c r="R75" s="83"/>
-      <c r="S75" s="82"/>
+      <c r="R75" s="68"/>
+      <c r="S75" s="67"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="47">
+      <c r="B76" s="78">
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="56" t="s">
+      <c r="C76" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D76" s="38" t="s">
+      <c r="D76" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="E76" s="59" t="s">
+      <c r="E76" s="56" t="s">
         <v>164</v>
       </c>
       <c r="F76" s="39" t="s">
@@ -6797,7 +6917,7 @@
         <v>436</v>
       </c>
       <c r="J76" s="39" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K76" s="38" t="s">
         <v>409</v>
@@ -6812,10 +6932,10 @@
       <c r="N76" s="38">
         <v>20</v>
       </c>
-      <c r="O76" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P76" s="49">
+      <c r="O76" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P76" s="47">
         <v>0.03</v>
       </c>
       <c r="Q76" s="40">
@@ -6827,73 +6947,73 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="48">
+      <c r="B77" s="81">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="81" t="s">
+      <c r="C77" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D77" s="82" t="s">
+      <c r="D77" s="79" t="s">
         <v>451</v>
       </c>
-      <c r="E77" s="82" t="s">
+      <c r="E77" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="F77" s="83" t="s">
+      <c r="F77" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G77" s="82" t="s">
+      <c r="G77" s="67" t="s">
         <v>292</v>
       </c>
-      <c r="H77" s="83" t="s">
+      <c r="H77" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I77" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J77" s="83" t="s">
-        <v>511</v>
-      </c>
-      <c r="K77" s="82" t="s">
+      <c r="I77" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J77" s="68" t="s">
+        <v>510</v>
+      </c>
+      <c r="K77" s="67" t="s">
         <v>410</v>
       </c>
-      <c r="L77" s="83">
+      <c r="L77" s="68">
         <v>3</v>
       </c>
-      <c r="M77" s="82">
-        <f t="shared" ref="M77" si="67">L77*5</f>
+      <c r="M77" s="67">
+        <f t="shared" ref="M77" si="66">L77*5</f>
         <v>15</v>
       </c>
-      <c r="N77" s="83">
+      <c r="N77" s="68">
         <v>100</v>
       </c>
-      <c r="O77" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P77" s="85">
+      <c r="O77" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P77" s="70">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q77" s="86">
-        <f t="shared" ref="Q77" si="68">P77*N77</f>
+      <c r="Q77" s="71">
+        <f t="shared" ref="Q77" si="67">P77*N77</f>
         <v>0.12</v>
       </c>
-      <c r="R77" s="83"/>
-      <c r="S77" s="82"/>
+      <c r="R77" s="68"/>
+      <c r="S77" s="67"/>
     </row>
     <row r="78" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="47">
+      <c r="B78" s="78">
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
-      <c r="C78" s="56" t="s">
+      <c r="C78" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D78" s="38" t="s">
+      <c r="D78" s="82" t="s">
         <v>449</v>
       </c>
-      <c r="E78" s="59" t="s">
+      <c r="E78" s="56" t="s">
         <v>166</v>
       </c>
       <c r="F78" s="39" t="s">
@@ -6909,7 +7029,7 @@
         <v>436</v>
       </c>
       <c r="J78" s="39" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K78" s="38" t="s">
         <v>407</v>
@@ -6924,10 +7044,10 @@
       <c r="N78" s="38">
         <v>200</v>
       </c>
-      <c r="O78" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P78" s="49">
+      <c r="O78" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P78" s="47">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q78" s="40">
@@ -6939,73 +7059,73 @@
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="48">
+      <c r="B79" s="81">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="81" t="s">
+      <c r="C79" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="82" t="s">
+      <c r="D79" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="E79" s="82" t="s">
+      <c r="E79" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="F79" s="83" t="s">
+      <c r="F79" s="68" t="s">
         <v>228</v>
       </c>
-      <c r="G79" s="82" t="s">
+      <c r="G79" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="H79" s="83" t="s">
+      <c r="H79" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I79" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J79" s="83" t="s">
+      <c r="I79" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J79" s="68" t="s">
         <v>371</v>
       </c>
-      <c r="K79" s="82" t="s">
+      <c r="K79" s="67" t="s">
         <v>411</v>
       </c>
-      <c r="L79" s="83">
+      <c r="L79" s="68">
         <v>1</v>
       </c>
-      <c r="M79" s="82">
-        <f t="shared" ref="M79" si="69">L79*5</f>
+      <c r="M79" s="67">
+        <f t="shared" ref="M79" si="68">L79*5</f>
         <v>5</v>
       </c>
-      <c r="N79" s="83">
+      <c r="N79" s="68">
         <v>100</v>
       </c>
-      <c r="O79" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P79" s="85">
+      <c r="O79" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P79" s="70">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="Q79" s="86">
-        <f t="shared" ref="Q79" si="70">P79*N79</f>
+      <c r="Q79" s="71">
+        <f t="shared" ref="Q79" si="69">P79*N79</f>
         <v>0.22</v>
       </c>
-      <c r="R79" s="83"/>
-      <c r="S79" s="82"/>
+      <c r="R79" s="68"/>
+      <c r="S79" s="67"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="B80" s="47">
+      <c r="B80" s="78">
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
-      <c r="C80" s="56" t="s">
+      <c r="C80" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D80" s="38" t="s">
+      <c r="D80" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="E80" s="59" t="s">
+      <c r="E80" s="56" t="s">
         <v>168</v>
       </c>
       <c r="F80" s="39" t="s">
@@ -7036,10 +7156,10 @@
       <c r="N80" s="38">
         <v>50</v>
       </c>
-      <c r="O80" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P80" s="49">
+      <c r="O80" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P80" s="47">
         <v>1.6899999999999998E-2</v>
       </c>
       <c r="Q80" s="40">
@@ -7051,73 +7171,73 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="48">
+      <c r="B81" s="81">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="81" t="s">
+      <c r="C81" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D81" s="82" t="s">
+      <c r="D81" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="E81" s="82" t="s">
+      <c r="E81" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="F81" s="83" t="s">
+      <c r="F81" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="G81" s="82" t="s">
+      <c r="G81" s="67" t="s">
         <v>296</v>
       </c>
-      <c r="H81" s="83" t="s">
+      <c r="H81" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I81" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J81" s="83" t="s">
+      <c r="I81" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J81" s="68" t="s">
         <v>373</v>
       </c>
-      <c r="K81" s="82" t="s">
+      <c r="K81" s="67" t="s">
         <v>412</v>
       </c>
-      <c r="L81" s="83">
+      <c r="L81" s="68">
         <v>1</v>
       </c>
-      <c r="M81" s="82">
-        <f t="shared" ref="M81" si="71">L81*5</f>
+      <c r="M81" s="67">
+        <f t="shared" ref="M81" si="70">L81*5</f>
         <v>5</v>
       </c>
-      <c r="N81" s="83">
+      <c r="N81" s="68">
         <v>100</v>
       </c>
-      <c r="O81" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P81" s="85">
+      <c r="O81" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P81" s="70">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q81" s="86">
-        <f t="shared" ref="Q81" si="72">P81*N81</f>
+      <c r="Q81" s="71">
+        <f t="shared" ref="Q81" si="71">P81*N81</f>
         <v>0.13</v>
       </c>
-      <c r="R81" s="83"/>
-      <c r="S81" s="82"/>
+      <c r="R81" s="68"/>
+      <c r="S81" s="67"/>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
-      <c r="B82" s="47">
+      <c r="B82" s="78">
         <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
-      <c r="C82" s="56" t="s">
+      <c r="C82" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D82" s="38" t="s">
+      <c r="D82" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="E82" s="59" t="s">
+      <c r="E82" s="56" t="s">
         <v>170</v>
       </c>
       <c r="F82" s="39" t="s">
@@ -7133,7 +7253,7 @@
         <v>436</v>
       </c>
       <c r="J82" s="39" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K82" s="38" t="s">
         <v>413</v>
@@ -7148,10 +7268,10 @@
       <c r="N82" s="38">
         <v>100</v>
       </c>
-      <c r="O82" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P82" s="49">
+      <c r="O82" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P82" s="47">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q82" s="40">
@@ -7163,74 +7283,74 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="B83" s="48">
+      <c r="B83" s="81">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C83" s="81" t="s">
+      <c r="C83" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D83" s="82" t="s">
+      <c r="D83" s="79" t="s">
         <v>452</v>
       </c>
-      <c r="E83" s="82" t="s">
+      <c r="E83" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="F83" s="83" t="s">
+      <c r="F83" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G83" s="87" t="s">
+      <c r="G83" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="H83" s="83" t="s">
+      <c r="H83" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I83" s="82" t="s">
-        <v>539</v>
-      </c>
-      <c r="J83" s="83" t="s">
-        <v>538</v>
-      </c>
-      <c r="K83" s="82" t="s">
+      <c r="I83" s="67" t="s">
+        <v>537</v>
+      </c>
+      <c r="J83" s="68" t="s">
+        <v>536</v>
+      </c>
+      <c r="K83" s="67" t="s">
         <v>411</v>
       </c>
-      <c r="L83" s="83">
+      <c r="L83" s="68">
         <v>5</v>
       </c>
-      <c r="M83" s="82">
-        <f t="shared" ref="M83" si="73">L83*5</f>
+      <c r="M83" s="67">
+        <f t="shared" ref="M83" si="72">L83*5</f>
         <v>25</v>
       </c>
-      <c r="N83" s="83">
+      <c r="N83" s="68">
         <v>100</v>
       </c>
-      <c r="O83" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P83" s="85">
+      <c r="O83" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P83" s="70">
         <v>2E-3</v>
       </c>
-      <c r="Q83" s="86">
-        <f t="shared" ref="Q83" si="74">P83*N83</f>
+      <c r="Q83" s="71">
+        <f t="shared" ref="Q83" si="73">P83*N83</f>
         <v>0.2</v>
       </c>
-      <c r="R83" s="83"/>
-      <c r="S83" s="82"/>
+      <c r="R83" s="68"/>
+      <c r="S83" s="67"/>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="B84" s="47">
+      <c r="B84" s="78">
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
-      <c r="C84" s="56" t="s">
+      <c r="C84" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D84" s="38" t="s">
+      <c r="D84" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="E84" s="59" t="s">
-        <v>540</v>
+      <c r="E84" s="56" t="s">
+        <v>538</v>
       </c>
       <c r="F84" s="39" t="s">
         <v>226</v>
@@ -7245,7 +7365,7 @@
         <v>436</v>
       </c>
       <c r="J84" s="39" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K84" s="38" t="s">
         <v>414</v>
@@ -7260,10 +7380,10 @@
       <c r="N84" s="38">
         <v>100</v>
       </c>
-      <c r="O84" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P84" s="49">
+      <c r="O84" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P84" s="47">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q84" s="40">
@@ -7275,80 +7395,80 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
-      <c r="B85" s="48">
+      <c r="B85" s="81">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="81" t="s">
+      <c r="C85" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D85" s="82" t="s">
+      <c r="D85" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="E85" s="82" t="s">
+      <c r="E85" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="F85" s="83" t="s">
+      <c r="F85" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="G85" s="82" t="s">
+      <c r="G85" s="67" t="s">
         <v>300</v>
       </c>
-      <c r="H85" s="83" t="s">
+      <c r="H85" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I85" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J85" s="83" t="s">
+      <c r="I85" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J85" s="68" t="s">
         <v>374</v>
       </c>
-      <c r="K85" s="82" t="s">
+      <c r="K85" s="67" t="s">
         <v>415</v>
       </c>
-      <c r="L85" s="83">
+      <c r="L85" s="68">
         <v>2</v>
       </c>
-      <c r="M85" s="82">
-        <f t="shared" ref="M85" si="75">L85*5</f>
+      <c r="M85" s="67">
+        <f t="shared" ref="M85" si="74">L85*5</f>
         <v>10</v>
       </c>
-      <c r="N85" s="83">
+      <c r="N85" s="68">
         <v>100</v>
       </c>
-      <c r="O85" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P85" s="85">
+      <c r="O85" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P85" s="70">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q85" s="86">
-        <f t="shared" ref="Q85" si="76">P85*N85</f>
+      <c r="Q85" s="71">
+        <f t="shared" ref="Q85" si="75">P85*N85</f>
         <v>0.11</v>
       </c>
-      <c r="R85" s="83"/>
-      <c r="S85" s="82"/>
+      <c r="R85" s="68"/>
+      <c r="S85" s="67"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
-      <c r="B86" s="47">
+      <c r="B86" s="78">
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="56" t="s">
+      <c r="C86" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D86" s="38" t="s">
+      <c r="D86" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="E86" s="59" t="s">
+      <c r="E86" s="56" t="s">
         <v>173</v>
       </c>
       <c r="F86" s="39" t="s">
         <v>230</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H86" s="39" t="s">
         <v>348</v>
@@ -7357,7 +7477,7 @@
         <v>436</v>
       </c>
       <c r="J86" s="39" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K86" s="38" t="s">
         <v>416</v>
@@ -7372,10 +7492,10 @@
       <c r="N86" s="38">
         <v>50</v>
       </c>
-      <c r="O86" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P86" s="49">
+      <c r="O86" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P86" s="47">
         <v>0.01</v>
       </c>
       <c r="Q86" s="40">
@@ -7387,73 +7507,73 @@
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
-      <c r="B87" s="48">
+      <c r="B87" s="81">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="81" t="s">
+      <c r="C87" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="82" t="s">
+      <c r="D87" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="E87" s="82" t="s">
-        <v>516</v>
-      </c>
-      <c r="F87" s="83" t="s">
+      <c r="E87" s="67" t="s">
+        <v>515</v>
+      </c>
+      <c r="F87" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="G87" s="82" t="s">
+      <c r="G87" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="H87" s="83" t="s">
+      <c r="H87" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I87" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J87" s="83" t="s">
-        <v>515</v>
-      </c>
-      <c r="K87" s="82" t="s">
+      <c r="I87" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J87" s="68" t="s">
+        <v>514</v>
+      </c>
+      <c r="K87" s="67" t="s">
         <v>417</v>
       </c>
-      <c r="L87" s="83">
+      <c r="L87" s="68">
         <v>2</v>
       </c>
-      <c r="M87" s="82">
-        <f t="shared" ref="M87" si="77">L87*5</f>
+      <c r="M87" s="67">
+        <f t="shared" ref="M87" si="76">L87*5</f>
         <v>10</v>
       </c>
-      <c r="N87" s="83">
+      <c r="N87" s="68">
         <v>100</v>
       </c>
-      <c r="O87" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P87" s="85">
+      <c r="O87" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P87" s="70">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q87" s="86">
-        <f t="shared" ref="Q87" si="78">P87*N87</f>
+      <c r="Q87" s="71">
+        <f t="shared" ref="Q87" si="77">P87*N87</f>
         <v>0.12</v>
       </c>
-      <c r="R87" s="83"/>
-      <c r="S87" s="82"/>
+      <c r="R87" s="68"/>
+      <c r="S87" s="67"/>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
-      <c r="B88" s="47">
+      <c r="B88" s="78">
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="56" t="s">
+      <c r="C88" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D88" s="38" t="s">
+      <c r="D88" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="E88" s="59" t="s">
+      <c r="E88" s="56" t="s">
         <v>174</v>
       </c>
       <c r="F88" s="39" t="s">
@@ -7469,7 +7589,7 @@
         <v>436</v>
       </c>
       <c r="J88" s="39" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K88" s="38" t="s">
         <v>418</v>
@@ -7484,10 +7604,10 @@
       <c r="N88" s="38">
         <v>50</v>
       </c>
-      <c r="O88" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P88" s="49">
+      <c r="O88" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P88" s="47">
         <v>8.8000000000000005E-3</v>
       </c>
       <c r="Q88" s="40">
@@ -7499,184 +7619,184 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
-      <c r="B89" s="48">
+      <c r="B89" s="81">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C89" s="81" t="s">
+      <c r="C89" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D89" s="82" t="s">
+      <c r="D89" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="E89" s="82" t="s">
+      <c r="E89" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="F89" s="83" t="s">
+      <c r="F89" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="G89" s="82" t="s">
+      <c r="G89" s="67" t="s">
         <v>303</v>
       </c>
-      <c r="H89" s="83" t="s">
+      <c r="H89" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="I89" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J89" s="83" t="s">
-        <v>533</v>
-      </c>
-      <c r="K89" s="82" t="s">
+      <c r="I89" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J89" s="68" t="s">
+        <v>531</v>
+      </c>
+      <c r="K89" s="67" t="s">
         <v>419</v>
       </c>
-      <c r="L89" s="83">
+      <c r="L89" s="68">
         <v>1</v>
       </c>
-      <c r="M89" s="82">
-        <f t="shared" ref="M89" si="79">L89*5</f>
+      <c r="M89" s="67">
+        <f t="shared" ref="M89" si="78">L89*5</f>
         <v>5</v>
       </c>
-      <c r="N89" s="83">
+      <c r="N89" s="68">
         <v>20</v>
       </c>
-      <c r="O89" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P89" s="85">
+      <c r="O89" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P89" s="70">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="Q89" s="86">
-        <f t="shared" ref="Q89" si="80">P89*N89</f>
+      <c r="Q89" s="71">
+        <f t="shared" ref="Q89" si="79">P89*N89</f>
         <v>0.55800000000000005</v>
       </c>
-      <c r="R89" s="83"/>
-      <c r="S89" s="82"/>
+      <c r="R89" s="68"/>
+      <c r="S89" s="67"/>
     </row>
     <row r="90" spans="1:19" ht="84" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
-      <c r="B90" s="48">
+      <c r="B90" s="81">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="C90" s="65" t="s">
+      <c r="C90" s="88" t="s">
         <v>231</v>
       </c>
-      <c r="D90" s="61" t="s">
+      <c r="D90" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="E90" s="61" t="s">
+      <c r="E90" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F90" s="66" t="s">
+      <c r="F90" s="62" t="s">
         <v>425</v>
       </c>
-      <c r="G90" s="61" t="s">
+      <c r="G90" s="58" t="s">
         <v>231</v>
       </c>
-      <c r="H90" s="66" t="s">
-        <v>436</v>
-      </c>
-      <c r="I90" s="61" t="s">
-        <v>436</v>
-      </c>
-      <c r="J90" s="66" t="s">
-        <v>436</v>
-      </c>
-      <c r="K90" s="61" t="s">
-        <v>436</v>
-      </c>
-      <c r="L90" s="66">
+      <c r="H90" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="I90" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="J90" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="K90" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="L90" s="62">
         <v>42</v>
       </c>
-      <c r="M90" s="61">
-        <f t="shared" ref="M90" si="81">L90*5</f>
+      <c r="M90" s="58">
+        <f t="shared" ref="M90" si="80">L90*5</f>
         <v>210</v>
       </c>
-      <c r="N90" s="61" t="s">
-        <v>436</v>
-      </c>
-      <c r="O90" s="67" t="s">
-        <v>436</v>
-      </c>
-      <c r="P90" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="Q90" s="69" t="s">
-        <v>436</v>
-      </c>
-      <c r="R90" s="66"/>
-      <c r="S90" s="61"/>
+      <c r="N90" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="O90" s="63" t="s">
+        <v>436</v>
+      </c>
+      <c r="P90" s="64" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q90" s="65" t="s">
+        <v>436</v>
+      </c>
+      <c r="R90" s="62"/>
+      <c r="S90" s="58"/>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
-      <c r="B91" s="47">
+      <c r="B91" s="78">
         <f>ROW(B91) - ROW($B$9)</f>
         <v>82</v>
       </c>
-      <c r="C91" s="81" t="s">
-        <v>534</v>
-      </c>
-      <c r="D91" s="82" t="s">
+      <c r="C91" s="86" t="s">
+        <v>532</v>
+      </c>
+      <c r="D91" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="E91" s="82" t="s">
+      <c r="E91" s="67" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="83" t="s">
+      <c r="F91" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G91" s="82" t="s">
+      <c r="G91" s="72" t="s">
         <v>232</v>
       </c>
-      <c r="H91" s="83" t="s">
+      <c r="H91" s="68" t="s">
         <v>349</v>
       </c>
-      <c r="I91" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J91" s="83" t="s">
-        <v>517</v>
-      </c>
-      <c r="K91" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L91" s="83">
+      <c r="I91" s="67" t="s">
+        <v>569</v>
+      </c>
+      <c r="J91" s="68" t="s">
+        <v>568</v>
+      </c>
+      <c r="K91" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L91" s="68">
         <v>7</v>
       </c>
-      <c r="M91" s="82">
+      <c r="M91" s="67">
         <f>L91*5</f>
         <v>35</v>
       </c>
-      <c r="N91" s="83">
-        <v>37</v>
-      </c>
-      <c r="O91" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P91" s="85">
-        <v>0.6905</v>
-      </c>
-      <c r="Q91" s="86">
+      <c r="N91" s="68">
+        <v>40</v>
+      </c>
+      <c r="O91" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P91" s="70">
+        <v>5.5500000000000001E-2</v>
+      </c>
+      <c r="Q91" s="71">
         <f>P91*N91</f>
-        <v>25.548500000000001</v>
-      </c>
-      <c r="R91" s="83"/>
-      <c r="S91" s="82"/>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="R91" s="61"/>
+      <c r="S91" s="67"/>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
-      <c r="B92" s="48">
+      <c r="B92" s="81">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="C92" s="56" t="s">
-        <v>535</v>
-      </c>
-      <c r="D92" s="38" t="s">
+      <c r="C92" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D92" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="E92" s="59" t="s">
+      <c r="E92" s="56" t="s">
         <v>178</v>
       </c>
       <c r="F92" s="39" t="s">
@@ -7699,94 +7819,96 @@
         <v>2</v>
       </c>
       <c r="M92" s="38">
-        <f t="shared" ref="M92" si="82">L92*5</f>
+        <f t="shared" ref="M92" si="81">L92*5</f>
         <v>10</v>
       </c>
       <c r="N92" s="38">
-        <v>12</v>
-      </c>
-      <c r="O92" s="60" t="s">
-        <v>542</v>
-      </c>
-      <c r="P92" s="49">
-        <v>8.8239999999999998</v>
+        <v>11</v>
+      </c>
+      <c r="O92" s="57" t="s">
+        <v>567</v>
+      </c>
+      <c r="P92" s="47">
+        <v>3.76</v>
       </c>
       <c r="Q92" s="40">
-        <f t="shared" ref="Q92" si="83">P92*N92</f>
-        <v>105.88800000000001</v>
-      </c>
-      <c r="R92" s="39"/>
+        <f t="shared" ref="Q92" si="82">P92*N92</f>
+        <v>41.36</v>
+      </c>
+      <c r="R92" s="61" t="s">
+        <v>570</v>
+      </c>
       <c r="S92" s="38"/>
     </row>
     <row r="93" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="B93" s="47">
+      <c r="B93" s="78">
         <f>ROW(B93) - ROW($B$9)</f>
         <v>84</v>
       </c>
-      <c r="C93" s="81" t="s">
-        <v>535</v>
-      </c>
-      <c r="D93" s="82" t="s">
+      <c r="C93" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D93" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="E93" s="82" t="s">
+      <c r="E93" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="F93" s="83" t="s">
+      <c r="F93" s="68" t="s">
         <v>233</v>
       </c>
-      <c r="G93" s="82" t="s">
+      <c r="G93" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="H93" s="83" t="s">
+      <c r="H93" s="68" t="s">
         <v>351</v>
       </c>
-      <c r="I93" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J93" s="83" t="s">
-        <v>518</v>
-      </c>
-      <c r="K93" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L93" s="83">
+      <c r="I93" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J93" s="68" t="s">
+        <v>516</v>
+      </c>
+      <c r="K93" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L93" s="68">
         <v>1</v>
       </c>
-      <c r="M93" s="82">
+      <c r="M93" s="67">
         <f>L93*5</f>
         <v>5</v>
       </c>
-      <c r="N93" s="83">
+      <c r="N93" s="68">
         <v>6</v>
       </c>
-      <c r="O93" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P93" s="85">
+      <c r="O93" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P93" s="70">
         <v>0.39779999999999999</v>
       </c>
-      <c r="Q93" s="86">
+      <c r="Q93" s="71">
         <f>P93*N93</f>
         <v>2.3868</v>
       </c>
-      <c r="R93" s="83"/>
-      <c r="S93" s="82"/>
+      <c r="R93" s="68"/>
+      <c r="S93" s="67"/>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
-      <c r="B94" s="48">
+      <c r="B94" s="81">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="C94" s="56" t="s">
-        <v>535</v>
-      </c>
-      <c r="D94" s="38" t="s">
+      <c r="C94" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D94" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="E94" s="59" t="s">
+      <c r="E94" s="56" t="s">
         <v>180</v>
       </c>
       <c r="F94" s="39" t="s">
@@ -7802,7 +7924,7 @@
         <v>436</v>
       </c>
       <c r="J94" s="39" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="K94" s="38" t="s">
         <v>436</v>
@@ -7811,94 +7933,94 @@
         <v>1</v>
       </c>
       <c r="M94" s="38">
-        <f t="shared" ref="M94" si="84">L94*5</f>
+        <f t="shared" ref="M94" si="83">L94*5</f>
         <v>5</v>
       </c>
       <c r="N94" s="38">
         <v>6</v>
       </c>
-      <c r="O94" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P94" s="49">
-        <v>1.0309999999999999</v>
+      <c r="O94" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P94" s="47">
+        <v>1.0086999999999999</v>
       </c>
       <c r="Q94" s="40">
-        <f t="shared" ref="Q94" si="85">P94*N94</f>
-        <v>6.1859999999999999</v>
+        <f t="shared" ref="Q94" si="84">P94*N94</f>
+        <v>6.0521999999999991</v>
       </c>
       <c r="R94" s="39"/>
       <c r="S94" s="38"/>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
-      <c r="B95" s="47">
+      <c r="B95" s="78">
         <f>ROW(B95) - ROW($B$9)</f>
         <v>86</v>
       </c>
-      <c r="C95" s="81" t="s">
-        <v>535</v>
-      </c>
-      <c r="D95" s="82" t="s">
+      <c r="C95" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D95" s="79" t="s">
         <v>90</v>
       </c>
-      <c r="E95" s="82" t="s">
+      <c r="E95" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="F95" s="83" t="s">
+      <c r="F95" s="68" t="s">
         <v>235</v>
       </c>
-      <c r="G95" s="82" t="s">
+      <c r="G95" s="67" t="s">
         <v>307</v>
       </c>
-      <c r="H95" s="83" t="s">
+      <c r="H95" s="68" t="s">
         <v>352</v>
       </c>
-      <c r="I95" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J95" s="83" t="s">
-        <v>520</v>
-      </c>
-      <c r="K95" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L95" s="83">
+      <c r="I95" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J95" s="68" t="s">
+        <v>518</v>
+      </c>
+      <c r="K95" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L95" s="68">
         <v>1</v>
       </c>
-      <c r="M95" s="82">
+      <c r="M95" s="67">
         <f>L95*5</f>
         <v>5</v>
       </c>
-      <c r="N95" s="83">
+      <c r="N95" s="68">
         <v>6</v>
       </c>
-      <c r="O95" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P95" s="85">
-        <v>7.3596000000000004</v>
-      </c>
-      <c r="Q95" s="86">
+      <c r="O95" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P95" s="70">
+        <v>8.0723000000000003</v>
+      </c>
+      <c r="Q95" s="71">
         <f>P95*N95</f>
-        <v>44.157600000000002</v>
-      </c>
-      <c r="R95" s="83"/>
-      <c r="S95" s="82"/>
+        <v>48.433800000000005</v>
+      </c>
+      <c r="R95" s="68"/>
+      <c r="S95" s="67"/>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="B96" s="48">
+      <c r="B96" s="81">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="C96" s="56" t="s">
-        <v>535</v>
-      </c>
-      <c r="D96" s="38" t="s">
+      <c r="C96" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D96" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="E96" s="59" t="s">
+      <c r="E96" s="56" t="s">
         <v>182</v>
       </c>
       <c r="F96" s="39" t="s">
@@ -7923,94 +8045,98 @@
         <v>1</v>
       </c>
       <c r="M96" s="38">
-        <f t="shared" ref="M96" si="86">L96*5</f>
+        <f t="shared" ref="M96" si="85">L96*5</f>
         <v>5</v>
       </c>
       <c r="N96" s="38">
-        <v>8</v>
-      </c>
-      <c r="O96" s="60" t="s">
-        <v>542</v>
-      </c>
-      <c r="P96" s="49">
-        <v>6.944</v>
+        <v>6</v>
+      </c>
+      <c r="O96" s="57" t="s">
+        <v>567</v>
+      </c>
+      <c r="P96" s="47">
+        <v>1.9550000000000001</v>
       </c>
       <c r="Q96" s="40">
-        <f t="shared" ref="Q96" si="87">P96*N96</f>
-        <v>55.552</v>
-      </c>
-      <c r="R96" s="39"/>
+        <f t="shared" ref="Q96" si="86">P96*N96</f>
+        <v>11.73</v>
+      </c>
+      <c r="R96" s="61" t="s">
+        <v>570</v>
+      </c>
       <c r="S96" s="38"/>
     </row>
     <row r="97" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
-      <c r="B97" s="47">
+      <c r="B97" s="78">
         <f>ROW(B97) - ROW($B$9)</f>
         <v>88</v>
       </c>
-      <c r="C97" s="81" t="s">
-        <v>535</v>
-      </c>
-      <c r="D97" s="82" t="s">
+      <c r="C97" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D97" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="E97" s="82" t="s">
+      <c r="E97" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="F97" s="83" t="s">
+      <c r="F97" s="68" t="s">
         <v>439</v>
       </c>
-      <c r="G97" s="82" t="s">
+      <c r="G97" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="H97" s="83" t="s">
+      <c r="H97" s="68" t="s">
         <v>353</v>
       </c>
-      <c r="I97" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J97" s="83" t="s">
-        <v>436</v>
-      </c>
-      <c r="K97" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L97" s="83">
+      <c r="I97" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J97" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="K97" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L97" s="68">
         <v>1</v>
       </c>
-      <c r="M97" s="82">
+      <c r="M97" s="67">
         <f>L97*5</f>
         <v>5</v>
       </c>
-      <c r="N97" s="83">
-        <v>7</v>
-      </c>
-      <c r="O97" s="84" t="s">
-        <v>542</v>
-      </c>
-      <c r="P97" s="85">
-        <v>8.2669999999999995</v>
-      </c>
-      <c r="Q97" s="86">
+      <c r="N97" s="68">
+        <v>6</v>
+      </c>
+      <c r="O97" s="69" t="s">
+        <v>567</v>
+      </c>
+      <c r="P97" s="70">
+        <v>7.52</v>
+      </c>
+      <c r="Q97" s="71">
         <f>P97*N97</f>
-        <v>57.869</v>
-      </c>
-      <c r="R97" s="83"/>
-      <c r="S97" s="82"/>
+        <v>45.12</v>
+      </c>
+      <c r="R97" s="61" t="s">
+        <v>570</v>
+      </c>
+      <c r="S97" s="67"/>
     </row>
     <row r="98" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
-      <c r="B98" s="48">
+      <c r="B98" s="81">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="C98" s="56" t="s">
-        <v>535</v>
-      </c>
-      <c r="D98" s="38" t="s">
+      <c r="C98" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D98" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="E98" s="59" t="s">
+      <c r="E98" s="56" t="s">
         <v>184</v>
       </c>
       <c r="F98" s="39" t="s">
@@ -8026,7 +8152,7 @@
         <v>436</v>
       </c>
       <c r="J98" s="39" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K98" s="38" t="s">
         <v>436</v>
@@ -8035,20 +8161,20 @@
         <v>4</v>
       </c>
       <c r="M98" s="38">
-        <f t="shared" ref="M98" si="88">L98*5</f>
+        <f t="shared" ref="M98" si="87">L98*5</f>
         <v>20</v>
       </c>
       <c r="N98" s="38">
         <v>25</v>
       </c>
-      <c r="O98" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P98" s="49">
+      <c r="O98" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P98" s="47">
         <v>0.41510000000000002</v>
       </c>
       <c r="Q98" s="40">
-        <f t="shared" ref="Q98" si="89">P98*N98</f>
+        <f t="shared" ref="Q98" si="88">P98*N98</f>
         <v>10.377500000000001</v>
       </c>
       <c r="R98" s="39"/>
@@ -8056,73 +8182,73 @@
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
-      <c r="B99" s="47">
+      <c r="B99" s="78">
         <f>ROW(B99) - ROW($B$9)</f>
         <v>90</v>
       </c>
-      <c r="C99" s="81" t="s">
-        <v>535</v>
-      </c>
-      <c r="D99" s="82" t="s">
+      <c r="C99" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D99" s="79" t="s">
         <v>94</v>
       </c>
-      <c r="E99" s="82" t="s">
+      <c r="E99" s="67" t="s">
         <v>185</v>
       </c>
-      <c r="F99" s="83" t="s">
+      <c r="F99" s="68" t="s">
         <v>238</v>
       </c>
-      <c r="G99" s="82" t="s">
+      <c r="G99" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="H99" s="83" t="s">
+      <c r="H99" s="68" t="s">
         <v>351</v>
       </c>
-      <c r="I99" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J99" s="83" t="s">
-        <v>522</v>
-      </c>
-      <c r="K99" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L99" s="83">
+      <c r="I99" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J99" s="68" t="s">
+        <v>520</v>
+      </c>
+      <c r="K99" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L99" s="68">
         <v>3</v>
       </c>
-      <c r="M99" s="82">
+      <c r="M99" s="67">
         <f>L99*5</f>
         <v>15</v>
       </c>
-      <c r="N99" s="83">
+      <c r="N99" s="68">
         <v>20</v>
       </c>
-      <c r="O99" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P99" s="85">
-        <v>0.24310000000000001</v>
-      </c>
-      <c r="Q99" s="86">
+      <c r="O99" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P99" s="70">
+        <v>0.25240000000000001</v>
+      </c>
+      <c r="Q99" s="71">
         <f>P99*N99</f>
-        <v>4.8620000000000001</v>
-      </c>
-      <c r="R99" s="83"/>
-      <c r="S99" s="82"/>
-    </row>
-    <row r="100" spans="1:19" s="63" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A100" s="62"/>
-      <c r="B100" s="48">
+        <v>5.048</v>
+      </c>
+      <c r="R99" s="68"/>
+      <c r="S99" s="67"/>
+    </row>
+    <row r="100" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="59"/>
+      <c r="B100" s="81">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="C100" s="56" t="s">
-        <v>535</v>
-      </c>
-      <c r="D100" s="38" t="s">
+      <c r="C100" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D100" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="E100" s="59" t="s">
+      <c r="E100" s="56" t="s">
         <v>186</v>
       </c>
       <c r="F100" s="39" t="s">
@@ -8138,7 +8264,7 @@
         <v>436</v>
       </c>
       <c r="J100" s="39" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K100" s="38" t="s">
         <v>436</v>
@@ -8147,98 +8273,98 @@
         <v>1</v>
       </c>
       <c r="M100" s="38">
-        <f t="shared" ref="M100" si="90">L100*5</f>
+        <f t="shared" ref="M100" si="89">L100*5</f>
         <v>5</v>
       </c>
       <c r="N100" s="38">
-        <v>11</v>
-      </c>
-      <c r="O100" s="60" t="s">
-        <v>542</v>
-      </c>
-      <c r="P100" s="49">
-        <v>4.7060000000000004</v>
+        <v>6</v>
+      </c>
+      <c r="O100" s="57" t="s">
+        <v>567</v>
+      </c>
+      <c r="P100" s="47">
+        <v>2.56</v>
       </c>
       <c r="Q100" s="40">
-        <f t="shared" ref="Q100" si="91">P100*N100</f>
-        <v>51.766000000000005</v>
-      </c>
-      <c r="R100" s="64" t="s">
-        <v>544</v>
+        <f t="shared" ref="Q100" si="90">P100*N100</f>
+        <v>15.36</v>
+      </c>
+      <c r="R100" s="61" t="s">
+        <v>570</v>
       </c>
       <c r="S100" s="38"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
-      <c r="B101" s="47">
+      <c r="B101" s="78">
         <f>ROW(B101) - ROW($B$9)</f>
         <v>92</v>
       </c>
-      <c r="C101" s="81" t="s">
-        <v>535</v>
-      </c>
-      <c r="D101" s="82" t="s">
+      <c r="C101" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D101" s="79" t="s">
         <v>96</v>
       </c>
-      <c r="E101" s="82" t="s">
+      <c r="E101" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="F101" s="83" t="s">
+      <c r="F101" s="68" t="s">
         <v>240</v>
       </c>
-      <c r="G101" s="82" t="s">
+      <c r="G101" s="67" t="s">
         <v>311</v>
       </c>
-      <c r="H101" s="83" t="s">
+      <c r="H101" s="68" t="s">
         <v>355</v>
       </c>
-      <c r="I101" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J101" s="83" t="s">
-        <v>524</v>
-      </c>
-      <c r="K101" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L101" s="83">
+      <c r="I101" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J101" s="68" t="s">
+        <v>522</v>
+      </c>
+      <c r="K101" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L101" s="68">
         <v>1</v>
       </c>
-      <c r="M101" s="82">
+      <c r="M101" s="67">
         <f>L101*5</f>
         <v>5</v>
       </c>
-      <c r="N101" s="83">
+      <c r="N101" s="68">
         <v>6</v>
       </c>
-      <c r="O101" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P101" s="85">
-        <v>4.0076000000000001</v>
-      </c>
-      <c r="Q101" s="86">
+      <c r="O101" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P101" s="70">
+        <v>4.2176</v>
+      </c>
+      <c r="Q101" s="71">
         <f>P101*N101</f>
-        <v>24.0456</v>
-      </c>
-      <c r="R101" s="93" t="s">
-        <v>543</v>
-      </c>
-      <c r="S101" s="82"/>
+        <v>25.305599999999998</v>
+      </c>
+      <c r="R101" s="77" t="s">
+        <v>540</v>
+      </c>
+      <c r="S101" s="67"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
-      <c r="B102" s="48">
+      <c r="B102" s="81">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="C102" s="56" t="s">
-        <v>535</v>
-      </c>
-      <c r="D102" s="38" t="s">
+      <c r="C102" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D102" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="E102" s="59" t="s">
+      <c r="E102" s="56" t="s">
         <v>188</v>
       </c>
       <c r="F102" s="39" t="s">
@@ -8254,7 +8380,7 @@
         <v>436</v>
       </c>
       <c r="J102" s="39" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="K102" s="38" t="s">
         <v>436</v>
@@ -8263,94 +8389,96 @@
         <v>1</v>
       </c>
       <c r="M102" s="38">
-        <f t="shared" ref="M102" si="92">L102*5</f>
+        <f t="shared" ref="M102" si="91">L102*5</f>
         <v>5</v>
       </c>
       <c r="N102" s="38">
         <v>6</v>
       </c>
-      <c r="O102" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P102" s="49">
-        <v>0.996</v>
+      <c r="O102" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P102" s="47">
+        <v>1.0357000000000001</v>
       </c>
       <c r="Q102" s="40">
-        <f t="shared" ref="Q102" si="93">P102*N102</f>
-        <v>5.976</v>
+        <f t="shared" ref="Q102" si="92">P102*N102</f>
+        <v>6.2141999999999999</v>
       </c>
       <c r="R102" s="39"/>
       <c r="S102" s="38"/>
     </row>
     <row r="103" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
-      <c r="B103" s="47">
+      <c r="B103" s="78">
         <f>ROW(B103) - ROW($B$9)</f>
         <v>94</v>
       </c>
-      <c r="C103" s="81" t="s">
-        <v>536</v>
-      </c>
-      <c r="D103" s="82" t="s">
+      <c r="C103" s="86" t="s">
+        <v>534</v>
+      </c>
+      <c r="D103" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="E103" s="82" t="s">
+      <c r="E103" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="F103" s="83" t="s">
+      <c r="F103" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G103" s="82" t="s">
+      <c r="G103" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="H103" s="83" t="s">
+      <c r="H103" s="68" t="s">
         <v>357</v>
       </c>
-      <c r="I103" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J103" s="83" t="s">
-        <v>526</v>
-      </c>
-      <c r="K103" s="82" t="s">
+      <c r="I103" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J103" s="68" t="s">
+        <v>524</v>
+      </c>
+      <c r="K103" s="67" t="s">
         <v>420</v>
       </c>
-      <c r="L103" s="83">
+      <c r="L103" s="68">
         <v>1</v>
       </c>
-      <c r="M103" s="82">
+      <c r="M103" s="67">
         <f>L103*5</f>
         <v>5</v>
       </c>
-      <c r="N103" s="83">
+      <c r="N103" s="68">
         <v>6</v>
       </c>
-      <c r="O103" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P103" s="85">
+      <c r="O103" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P103" s="70">
         <v>0.19889999999999999</v>
       </c>
-      <c r="Q103" s="86">
+      <c r="Q103" s="71">
         <f>P103*N103</f>
         <v>1.1934</v>
       </c>
-      <c r="R103" s="83"/>
-      <c r="S103" s="82"/>
+      <c r="R103" s="77" t="s">
+        <v>571</v>
+      </c>
+      <c r="S103" s="67"/>
     </row>
     <row r="104" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
-      <c r="B104" s="48">
+      <c r="B104" s="81">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="C104" s="56" t="s">
-        <v>536</v>
-      </c>
-      <c r="D104" s="38" t="s">
+      <c r="C104" s="85" t="s">
+        <v>534</v>
+      </c>
+      <c r="D104" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="E104" s="59" t="s">
+      <c r="E104" s="56" t="s">
         <v>190</v>
       </c>
       <c r="F104" s="39" t="s">
@@ -8375,363 +8503,525 @@
         <v>1</v>
       </c>
       <c r="M104" s="38">
-        <f t="shared" ref="M104" si="94">L104*5</f>
+        <f t="shared" ref="M104" si="93">L104*5</f>
         <v>5</v>
       </c>
       <c r="N104" s="38">
         <v>10</v>
       </c>
-      <c r="O104" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="P104" s="49">
-        <v>9.9900000000000003E-2</v>
+      <c r="O104" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P104" s="47">
+        <v>0.1221</v>
       </c>
       <c r="Q104" s="40">
-        <f t="shared" ref="Q104" si="95">P104*N104</f>
-        <v>0.999</v>
+        <f t="shared" ref="Q104" si="94">P104*N104</f>
+        <v>1.2210000000000001</v>
       </c>
       <c r="R104" s="39"/>
       <c r="S104" s="38"/>
     </row>
     <row r="105" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
-      <c r="B105" s="47">
+      <c r="B105" s="78">
         <f>ROW(B105) - ROW($B$9)</f>
         <v>96</v>
       </c>
-      <c r="C105" s="81" t="s">
-        <v>536</v>
-      </c>
-      <c r="D105" s="82" t="s">
+      <c r="C105" s="86" t="s">
+        <v>534</v>
+      </c>
+      <c r="D105" s="79" t="s">
         <v>100</v>
       </c>
-      <c r="E105" s="82" t="s">
+      <c r="E105" s="67" t="s">
         <v>191</v>
       </c>
-      <c r="F105" s="83" t="s">
+      <c r="F105" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G105" s="82" t="s">
+      <c r="G105" s="67" t="s">
         <v>243</v>
       </c>
-      <c r="H105" s="83" t="s">
+      <c r="H105" s="68" t="s">
         <v>359</v>
       </c>
-      <c r="I105" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J105" s="83" t="s">
-        <v>527</v>
-      </c>
-      <c r="K105" s="82" t="s">
+      <c r="I105" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J105" s="68" t="s">
+        <v>525</v>
+      </c>
+      <c r="K105" s="67" t="s">
         <v>422</v>
       </c>
-      <c r="L105" s="83">
+      <c r="L105" s="68">
         <v>1</v>
       </c>
-      <c r="M105" s="82">
+      <c r="M105" s="67">
         <f>L105*5</f>
         <v>5</v>
       </c>
-      <c r="N105" s="83">
+      <c r="N105" s="68">
         <v>10</v>
       </c>
-      <c r="O105" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P105" s="85">
-        <v>0.2218</v>
-      </c>
-      <c r="Q105" s="86">
+      <c r="O105" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P105" s="70">
+        <v>0.22420000000000001</v>
+      </c>
+      <c r="Q105" s="71">
         <f>P105*N105</f>
-        <v>2.218</v>
-      </c>
-      <c r="R105" s="83"/>
-      <c r="S105" s="82"/>
+        <v>2.242</v>
+      </c>
+      <c r="R105" s="68"/>
+      <c r="S105" s="67"/>
     </row>
     <row r="106" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
-      <c r="B106" s="47">
-        <f t="shared" ref="B106:B109" si="96">ROW(B106) - ROW($B$9)</f>
+      <c r="B106" s="78">
+        <f t="shared" ref="B106:B112" si="95">ROW(B106) - ROW($B$9)</f>
         <v>97</v>
       </c>
-      <c r="C106" s="81" t="s">
-        <v>560</v>
-      </c>
-      <c r="D106" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="E106" s="82" t="s">
-        <v>553</v>
-      </c>
-      <c r="F106" s="83" t="s">
+      <c r="C106" s="86" t="s">
+        <v>554</v>
+      </c>
+      <c r="D106" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E106" s="67" t="s">
+        <v>547</v>
+      </c>
+      <c r="F106" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G106" s="82" t="s">
-        <v>554</v>
-      </c>
-      <c r="H106" s="83" t="s">
-        <v>555</v>
-      </c>
-      <c r="I106" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J106" s="83" t="s">
-        <v>556</v>
-      </c>
-      <c r="K106" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L106" s="83">
+      <c r="G106" s="67" t="s">
+        <v>548</v>
+      </c>
+      <c r="H106" s="68" t="s">
+        <v>549</v>
+      </c>
+      <c r="I106" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J106" s="68" t="s">
+        <v>550</v>
+      </c>
+      <c r="K106" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L106" s="68">
         <v>9</v>
       </c>
-      <c r="M106" s="82">
+      <c r="M106" s="67">
         <f>L106*5</f>
         <v>45</v>
       </c>
-      <c r="N106" s="83">
+      <c r="N106" s="68">
         <v>50</v>
       </c>
-      <c r="O106" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P106" s="85">
+      <c r="O106" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P106" s="70">
         <v>0.1595</v>
       </c>
-      <c r="Q106" s="86">
-        <f t="shared" ref="Q106:Q109" si="97">P106*N106</f>
+      <c r="Q106" s="71">
+        <f t="shared" ref="Q106:Q110" si="96">P106*N106</f>
         <v>7.9750000000000005</v>
       </c>
-      <c r="R106" s="83"/>
-      <c r="S106" s="82"/>
+      <c r="R106" s="68"/>
+      <c r="S106" s="67"/>
     </row>
     <row r="107" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
-      <c r="B107" s="47">
-        <f t="shared" si="96"/>
+      <c r="B107" s="78">
+        <f t="shared" si="95"/>
         <v>98</v>
       </c>
-      <c r="C107" s="81" t="s">
-        <v>560</v>
-      </c>
-      <c r="D107" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="E107" s="82" t="s">
-        <v>558</v>
-      </c>
-      <c r="F107" s="83" t="s">
+      <c r="C107" s="86" t="s">
+        <v>554</v>
+      </c>
+      <c r="D107" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E107" s="67" t="s">
+        <v>552</v>
+      </c>
+      <c r="F107" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G107" s="82" t="s">
-        <v>559</v>
-      </c>
-      <c r="H107" s="83" t="s">
-        <v>555</v>
-      </c>
-      <c r="I107" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J107" s="83" t="s">
-        <v>557</v>
-      </c>
-      <c r="K107" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L107" s="83">
+      <c r="G107" s="67" t="s">
+        <v>553</v>
+      </c>
+      <c r="H107" s="68" t="s">
+        <v>549</v>
+      </c>
+      <c r="I107" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J107" s="68" t="s">
+        <v>551</v>
+      </c>
+      <c r="K107" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L107" s="68">
         <v>5</v>
       </c>
-      <c r="M107" s="82">
+      <c r="M107" s="67">
         <f>L107*5</f>
         <v>25</v>
       </c>
-      <c r="N107" s="83">
+      <c r="N107" s="68">
         <v>30</v>
       </c>
-      <c r="O107" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P107" s="85">
+      <c r="O107" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P107" s="70">
         <v>0.29559999999999997</v>
       </c>
-      <c r="Q107" s="86">
-        <f t="shared" si="97"/>
+      <c r="Q107" s="71">
+        <f t="shared" si="96"/>
         <v>8.8679999999999986</v>
       </c>
-      <c r="R107" s="83"/>
-      <c r="S107" s="82"/>
+      <c r="R107" s="68"/>
+      <c r="S107" s="67"/>
     </row>
     <row r="108" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
-      <c r="B108" s="47">
-        <f t="shared" si="96"/>
+      <c r="B108" s="78">
+        <f t="shared" si="95"/>
         <v>99</v>
       </c>
-      <c r="C108" s="81" t="s">
-        <v>560</v>
-      </c>
-      <c r="D108" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="E108" s="82" t="s">
-        <v>561</v>
-      </c>
-      <c r="F108" s="83" t="s">
+      <c r="C108" s="86" t="s">
+        <v>554</v>
+      </c>
+      <c r="D108" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E108" s="67" t="s">
+        <v>555</v>
+      </c>
+      <c r="F108" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G108" s="82" t="s">
-        <v>563</v>
-      </c>
-      <c r="H108" s="83" t="s">
-        <v>555</v>
-      </c>
-      <c r="I108" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J108" s="83" t="s">
-        <v>562</v>
-      </c>
-      <c r="K108" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L108" s="83">
+      <c r="G108" s="67" t="s">
+        <v>557</v>
+      </c>
+      <c r="H108" s="68" t="s">
+        <v>549</v>
+      </c>
+      <c r="I108" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J108" s="68" t="s">
+        <v>556</v>
+      </c>
+      <c r="K108" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L108" s="68">
         <v>1</v>
       </c>
-      <c r="M108" s="82">
+      <c r="M108" s="67">
         <f>L108*5</f>
         <v>5</v>
       </c>
-      <c r="N108" s="83">
+      <c r="N108" s="68">
         <v>10</v>
       </c>
-      <c r="O108" s="84" t="s">
-        <v>456</v>
-      </c>
-      <c r="P108" s="85">
+      <c r="O108" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P108" s="70">
         <v>0.34520000000000001</v>
       </c>
-      <c r="Q108" s="86">
-        <f t="shared" si="97"/>
+      <c r="Q108" s="71">
+        <f t="shared" si="96"/>
         <v>3.452</v>
       </c>
-      <c r="R108" s="83"/>
-      <c r="S108" s="82"/>
-    </row>
-    <row r="109" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R108" s="68"/>
+      <c r="S108" s="67"/>
+    </row>
+    <row r="109" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
-      <c r="B109" s="47">
+      <c r="B109" s="78">
+        <f t="shared" si="95"/>
+        <v>100</v>
+      </c>
+      <c r="C109" s="89" t="s">
+        <v>561</v>
+      </c>
+      <c r="D109" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E109" s="67" t="s">
+        <v>563</v>
+      </c>
+      <c r="F109" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G109" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="H109" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="I109" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J109" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="K109" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L109" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="M109" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="N109" s="68">
+        <v>3</v>
+      </c>
+      <c r="O109" s="69" t="s">
+        <v>562</v>
+      </c>
+      <c r="P109" s="70">
+        <v>1.33</v>
+      </c>
+      <c r="Q109" s="71">
         <f t="shared" si="96"/>
-        <v>100</v>
-      </c>
-      <c r="C109" s="94" t="s">
-        <v>567</v>
-      </c>
-      <c r="D109" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="E109" s="82" t="s">
-        <v>569</v>
-      </c>
-      <c r="F109" s="83" t="s">
+        <v>3.99</v>
+      </c>
+      <c r="R109" s="68"/>
+      <c r="S109" s="67"/>
+    </row>
+    <row r="110" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A110" s="1"/>
+      <c r="B110" s="78">
+        <f t="shared" si="95"/>
+        <v>101</v>
+      </c>
+      <c r="C110" s="86" t="s">
+        <v>572</v>
+      </c>
+      <c r="D110" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E110" s="67" t="s">
+        <v>573</v>
+      </c>
+      <c r="F110" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="G109" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="H109" s="83" t="s">
-        <v>436</v>
-      </c>
-      <c r="I109" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="J109" s="83" t="s">
-        <v>436</v>
-      </c>
-      <c r="K109" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="L109" s="83" t="s">
-        <v>436</v>
-      </c>
-      <c r="M109" s="82" t="s">
-        <v>436</v>
-      </c>
-      <c r="N109" s="83">
-        <v>3</v>
-      </c>
-      <c r="O109" s="84" t="s">
-        <v>568</v>
-      </c>
-      <c r="P109" s="85">
-        <v>1.33</v>
-      </c>
-      <c r="Q109" s="86">
-        <f t="shared" si="97"/>
-        <v>3.99</v>
-      </c>
-      <c r="R109" s="83"/>
-      <c r="S109" s="82"/>
-    </row>
-    <row r="110" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="1"/>
-      <c r="B110" s="41"/>
-      <c r="C110" s="42"/>
-      <c r="D110" s="43"/>
-      <c r="E110" s="44"/>
-      <c r="F110" s="45"/>
-      <c r="G110" s="46"/>
-      <c r="H110" s="45"/>
-      <c r="I110" s="46"/>
-      <c r="J110" s="45"/>
-      <c r="K110" s="46"/>
-      <c r="L110" s="46"/>
-      <c r="M110" s="46"/>
-      <c r="N110" s="78" t="s">
+      <c r="G110" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="H110" s="68" t="s">
+        <v>574</v>
+      </c>
+      <c r="I110" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J110" s="68" t="s">
+        <v>575</v>
+      </c>
+      <c r="K110" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L110" s="68">
+        <v>1</v>
+      </c>
+      <c r="M110" s="67">
+        <f>L110*5</f>
         <v>5</v>
       </c>
-      <c r="O110" s="79"/>
-      <c r="P110" s="79"/>
-      <c r="Q110" s="50">
-        <f>SUM(Q10:Q105)</f>
-        <v>546.65329999999994</v>
-      </c>
-      <c r="R110" s="74"/>
-      <c r="S110" s="75"/>
-    </row>
-    <row r="111" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N110" s="68">
+        <v>5</v>
+      </c>
+      <c r="O110" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P110" s="70">
+        <v>1.23</v>
+      </c>
+      <c r="Q110" s="71">
+        <f t="shared" si="96"/>
+        <v>6.15</v>
+      </c>
+      <c r="R110" s="68"/>
+      <c r="S110" s="67"/>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="37"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
-      <c r="I111" s="10"/>
-      <c r="J111" s="10"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="10"/>
-      <c r="M111" s="10"/>
-      <c r="N111" s="78" t="s">
+      <c r="B111" s="78">
+        <f t="shared" si="95"/>
+        <v>102</v>
+      </c>
+      <c r="C111" s="89" t="s">
+        <v>578</v>
+      </c>
+      <c r="D111" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E111" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="F111" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G111" s="67" t="s">
+        <v>576</v>
+      </c>
+      <c r="H111" s="68"/>
+      <c r="I111" s="67"/>
+      <c r="J111" s="68" t="s">
+        <v>577</v>
+      </c>
+      <c r="K111" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L111" s="68">
+        <v>1</v>
+      </c>
+      <c r="M111" s="67">
+        <f>L111*5</f>
+        <v>5</v>
+      </c>
+      <c r="N111" s="68">
+        <v>5</v>
+      </c>
+      <c r="O111" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P111" s="70">
+        <v>3.2073</v>
+      </c>
+      <c r="Q111" s="80">
+        <f>P111*N111</f>
+        <v>16.0365</v>
+      </c>
+      <c r="R111" s="68"/>
+      <c r="S111" s="67"/>
+    </row>
+    <row r="112" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="1"/>
+      <c r="B112" s="78">
+        <f t="shared" si="95"/>
+        <v>103</v>
+      </c>
+      <c r="C112" s="86" t="s">
+        <v>579</v>
+      </c>
+      <c r="D112" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E112" s="67" t="s">
+        <v>580</v>
+      </c>
+      <c r="F112" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G112" s="67" t="s">
+        <v>581</v>
+      </c>
+      <c r="H112" s="68" t="s">
+        <v>582</v>
+      </c>
+      <c r="I112" s="67"/>
+      <c r="J112" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="K112" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L112" s="68">
+        <v>1</v>
+      </c>
+      <c r="M112" s="67">
+        <f>L112*5</f>
+        <v>5</v>
+      </c>
+      <c r="N112" s="68">
+        <v>5</v>
+      </c>
+      <c r="O112" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P112" s="70">
+        <v>0.1827</v>
+      </c>
+      <c r="Q112" s="80">
+        <f>P112*N112</f>
+        <v>0.91349999999999998</v>
+      </c>
+      <c r="R112" s="68"/>
+      <c r="S112" s="67"/>
+    </row>
+    <row r="113" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1"/>
+      <c r="B113" s="41"/>
+      <c r="C113" s="42"/>
+      <c r="D113" s="43"/>
+      <c r="E113" s="44"/>
+      <c r="F113" s="45"/>
+      <c r="G113" s="46"/>
+      <c r="H113" s="45"/>
+      <c r="I113" s="46"/>
+      <c r="J113" s="45"/>
+      <c r="K113" s="46"/>
+      <c r="L113" s="46"/>
+      <c r="M113" s="46"/>
+      <c r="N113" s="98" t="s">
+        <v>5</v>
+      </c>
+      <c r="O113" s="99"/>
+      <c r="P113" s="99"/>
+      <c r="Q113" s="48">
+        <f>SUM(Q10:Q112)</f>
+        <v>390.46329999999995</v>
+      </c>
+      <c r="R113" s="94"/>
+      <c r="S113" s="95"/>
+    </row>
+    <row r="114" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="37"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="10"/>
+      <c r="F114" s="10"/>
+      <c r="G114" s="10"/>
+      <c r="H114" s="10"/>
+      <c r="I114" s="10"/>
+      <c r="J114" s="10"/>
+      <c r="K114" s="10"/>
+      <c r="L114" s="10"/>
+      <c r="M114" s="10"/>
+      <c r="N114" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="O111" s="79"/>
-      <c r="P111" s="79"/>
-      <c r="Q111" s="51">
-        <f>Q110/5</f>
-        <v>109.33065999999999</v>
-      </c>
-      <c r="R111" s="76"/>
-      <c r="S111" s="77"/>
+      <c r="O114" s="99"/>
+      <c r="P114" s="99"/>
+      <c r="Q114" s="49">
+        <f>Q113/5</f>
+        <v>78.092659999999995</v>
+      </c>
+      <c r="R114" s="96"/>
+      <c r="S114" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R110:S111"/>
-    <mergeCell ref="N110:P110"/>
-    <mergeCell ref="N111:P111"/>
+    <mergeCell ref="R113:S114"/>
+    <mergeCell ref="N113:P113"/>
+    <mergeCell ref="N114:P114"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -8795,42 +9085,42 @@
     <hyperlink ref="O78" r:id="rId59"/>
     <hyperlink ref="O86" r:id="rId60"/>
     <hyperlink ref="O87" r:id="rId61"/>
-    <hyperlink ref="O91" r:id="rId62"/>
-    <hyperlink ref="O94" r:id="rId63"/>
-    <hyperlink ref="O95" r:id="rId64"/>
-    <hyperlink ref="O99" r:id="rId65"/>
-    <hyperlink ref="O101" r:id="rId66"/>
-    <hyperlink ref="O102" r:id="rId67"/>
-    <hyperlink ref="O93" r:id="rId68"/>
-    <hyperlink ref="O98" r:id="rId69"/>
-    <hyperlink ref="O103" r:id="rId70"/>
-    <hyperlink ref="O105" r:id="rId71"/>
-    <hyperlink ref="O70" r:id="rId72"/>
-    <hyperlink ref="O73" r:id="rId73"/>
-    <hyperlink ref="O75" r:id="rId74"/>
-    <hyperlink ref="O76" r:id="rId75"/>
-    <hyperlink ref="O79" r:id="rId76"/>
-    <hyperlink ref="O80" r:id="rId77"/>
-    <hyperlink ref="O88" r:id="rId78"/>
-    <hyperlink ref="O89" r:id="rId79"/>
-    <hyperlink ref="O81" r:id="rId80"/>
-    <hyperlink ref="O82" r:id="rId81"/>
-    <hyperlink ref="O83" r:id="rId82"/>
-    <hyperlink ref="O84" r:id="rId83"/>
-    <hyperlink ref="O85" r:id="rId84"/>
-    <hyperlink ref="O104" r:id="rId85"/>
-    <hyperlink ref="O92" r:id="rId86"/>
-    <hyperlink ref="O96" r:id="rId87"/>
-    <hyperlink ref="O97" r:id="rId88"/>
-    <hyperlink ref="O55" r:id="rId89"/>
-    <hyperlink ref="O32" r:id="rId90"/>
-    <hyperlink ref="O11" r:id="rId91"/>
-    <hyperlink ref="O31" r:id="rId92"/>
-    <hyperlink ref="O106" r:id="rId93"/>
-    <hyperlink ref="O107" r:id="rId94"/>
-    <hyperlink ref="O108" r:id="rId95"/>
-    <hyperlink ref="O37" r:id="rId96"/>
-    <hyperlink ref="O109" r:id="rId97"/>
+    <hyperlink ref="O94" r:id="rId62"/>
+    <hyperlink ref="O95" r:id="rId63"/>
+    <hyperlink ref="O99" r:id="rId64"/>
+    <hyperlink ref="O101" r:id="rId65"/>
+    <hyperlink ref="O102" r:id="rId66"/>
+    <hyperlink ref="O93" r:id="rId67"/>
+    <hyperlink ref="O98" r:id="rId68"/>
+    <hyperlink ref="O103" r:id="rId69"/>
+    <hyperlink ref="O105" r:id="rId70"/>
+    <hyperlink ref="O70" r:id="rId71"/>
+    <hyperlink ref="O73" r:id="rId72"/>
+    <hyperlink ref="O75" r:id="rId73"/>
+    <hyperlink ref="O76" r:id="rId74"/>
+    <hyperlink ref="O79" r:id="rId75"/>
+    <hyperlink ref="O80" r:id="rId76"/>
+    <hyperlink ref="O88" r:id="rId77"/>
+    <hyperlink ref="O89" r:id="rId78"/>
+    <hyperlink ref="O81" r:id="rId79"/>
+    <hyperlink ref="O82" r:id="rId80"/>
+    <hyperlink ref="O83" r:id="rId81"/>
+    <hyperlink ref="O84" r:id="rId82"/>
+    <hyperlink ref="O85" r:id="rId83"/>
+    <hyperlink ref="O104" r:id="rId84"/>
+    <hyperlink ref="O55" r:id="rId85"/>
+    <hyperlink ref="O11" r:id="rId86"/>
+    <hyperlink ref="O31" r:id="rId87"/>
+    <hyperlink ref="O106" r:id="rId88"/>
+    <hyperlink ref="O107" r:id="rId89"/>
+    <hyperlink ref="O108" r:id="rId90"/>
+    <hyperlink ref="O37" r:id="rId91"/>
+    <hyperlink ref="O109" r:id="rId92"/>
+    <hyperlink ref="O32" r:id="rId93"/>
+    <hyperlink ref="O91" r:id="rId94"/>
+    <hyperlink ref="O110" r:id="rId95"/>
+    <hyperlink ref="O111" r:id="rId96"/>
+    <hyperlink ref="O112" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId98"/>

--- a/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
+++ b/BOM/GTV3_Board/eSpakr-V3_Board.xlsx
@@ -9,17 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
+    <sheet name="10 Boards" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="590">
   <si>
     <t>Component list</t>
   </si>
@@ -1714,12 +1715,6 @@
     <t>Jumper Wires Male to Female 30cm 1 x 40</t>
   </si>
   <si>
-    <t>PZ127VS-12-10-H10-A38</t>
-  </si>
-  <si>
-    <t>C2935458</t>
-  </si>
-  <si>
     <t>PZ254V-11-02P</t>
   </si>
   <si>
@@ -1775,6 +1770,27 @@
   </si>
   <si>
     <t>Do NOT MOUNT</t>
+  </si>
+  <si>
+    <t>MOQ (10 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (10 Boards)</t>
+  </si>
+  <si>
+    <t>UnitCost (10 Boards)</t>
+  </si>
+  <si>
+    <t>TotalCost (10 Boards)</t>
+  </si>
+  <si>
+    <t>X1321WVS-2x05J-C40D53</t>
+  </si>
+  <si>
+    <t>C2881910</t>
+  </si>
+  <si>
+    <t>Non Stock on LCSC</t>
   </si>
 </sst>
 </file>
@@ -1786,7 +1802,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1985,6 +2001,14 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2301,7 +2325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2552,6 +2576,9 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2584,7 +2611,10 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2654,6 +2684,60 @@
         <a:xfrm>
           <a:off x="29927550" y="620017"/>
           <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18459450" y="620016"/>
+          <a:ext cx="1714500" cy="1132583"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2963,15 +3047,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
-      <c r="S1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3021,7 +3105,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="92"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3046,7 +3130,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="93"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3071,7 +3155,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="93"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3092,7 +3176,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="93"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -3113,7 +3197,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="93"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3134,7 +3218,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="93"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4448,10 +4532,10 @@
         <v>326</v>
       </c>
       <c r="I32" s="38" t="s">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="K32" s="38" t="s">
         <v>436</v>
@@ -4470,11 +4554,11 @@
         <v>456</v>
       </c>
       <c r="P32" s="47">
-        <v>0.15229999999999999</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" ref="Q32" si="24">P32*N32</f>
-        <v>1.5229999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="R32" s="39"/>
       <c r="S32" s="38"/>
@@ -4699,8 +4783,8 @@
       <c r="Q36" s="65" t="s">
         <v>436</v>
       </c>
-      <c r="R36" s="100" t="s">
-        <v>584</v>
+      <c r="R36" s="90" t="s">
+        <v>582</v>
       </c>
       <c r="S36" s="38"/>
     </row>
@@ -5514,7 +5598,7 @@
         <v>338</v>
       </c>
       <c r="I51" s="67" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J51" s="68" t="s">
         <v>489</v>
@@ -7753,10 +7837,10 @@
         <v>349</v>
       </c>
       <c r="I91" s="67" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J91" s="68" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="K91" s="67" t="s">
         <v>436</v>
@@ -7826,7 +7910,7 @@
         <v>11</v>
       </c>
       <c r="O92" s="57" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="P92" s="47">
         <v>3.76</v>
@@ -7836,7 +7920,7 @@
         <v>41.36</v>
       </c>
       <c r="R92" s="61" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="S92" s="38"/>
     </row>
@@ -8052,7 +8136,7 @@
         <v>6</v>
       </c>
       <c r="O96" s="57" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="P96" s="47">
         <v>1.9550000000000001</v>
@@ -8062,7 +8146,7 @@
         <v>11.73</v>
       </c>
       <c r="R96" s="61" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="S96" s="38"/>
     </row>
@@ -8110,7 +8194,7 @@
         <v>6</v>
       </c>
       <c r="O97" s="69" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="P97" s="70">
         <v>7.52</v>
@@ -8120,7 +8204,7 @@
         <v>45.12</v>
       </c>
       <c r="R97" s="61" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="S97" s="67"/>
     </row>
@@ -8280,7 +8364,7 @@
         <v>6</v>
       </c>
       <c r="O100" s="57" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="P100" s="47">
         <v>2.56</v>
@@ -8290,7 +8374,7 @@
         <v>15.36</v>
       </c>
       <c r="R100" s="61" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="S100" s="38"/>
     </row>
@@ -8462,7 +8546,7 @@
         <v>1.1934</v>
       </c>
       <c r="R103" s="77" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="S103" s="67"/>
     </row>
@@ -8808,13 +8892,13 @@
         <v>101</v>
       </c>
       <c r="C110" s="86" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D110" s="79" t="s">
         <v>436</v>
       </c>
       <c r="E110" s="67" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F110" s="68" t="s">
         <v>425</v>
@@ -8823,13 +8907,13 @@
         <v>436</v>
       </c>
       <c r="H110" s="68" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I110" s="67" t="s">
         <v>436</v>
       </c>
       <c r="J110" s="68" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="K110" s="67" t="s">
         <v>436</v>
@@ -8864,7 +8948,7 @@
         <v>102</v>
       </c>
       <c r="C111" s="89" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D111" s="79" t="s">
         <v>436</v>
@@ -8876,12 +8960,12 @@
         <v>425</v>
       </c>
       <c r="G111" s="67" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H111" s="68"/>
       <c r="I111" s="67"/>
       <c r="J111" s="68" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K111" s="67" t="s">
         <v>436</v>
@@ -8916,26 +9000,26 @@
         <v>103</v>
       </c>
       <c r="C112" s="86" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D112" s="79" t="s">
         <v>436</v>
       </c>
       <c r="E112" s="67" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F112" s="68" t="s">
         <v>425</v>
       </c>
       <c r="G112" s="67" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H112" s="68" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="I112" s="67"/>
       <c r="J112" s="68" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="K112" s="67" t="s">
         <v>436</v>
@@ -8977,17 +9061,17 @@
       <c r="K113" s="46"/>
       <c r="L113" s="46"/>
       <c r="M113" s="46"/>
-      <c r="N113" s="98" t="s">
+      <c r="N113" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="O113" s="99"/>
-      <c r="P113" s="99"/>
+      <c r="O113" s="100"/>
+      <c r="P113" s="100"/>
       <c r="Q113" s="48">
         <f>SUM(Q10:Q112)</f>
-        <v>390.46329999999995</v>
-      </c>
-      <c r="R113" s="94"/>
-      <c r="S113" s="95"/>
+        <v>391.76029999999997</v>
+      </c>
+      <c r="R113" s="95"/>
+      <c r="S113" s="96"/>
     </row>
     <row r="114" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
@@ -9003,17 +9087,17 @@
       <c r="K114" s="10"/>
       <c r="L114" s="10"/>
       <c r="M114" s="10"/>
-      <c r="N114" s="98" t="s">
+      <c r="N114" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="O114" s="99"/>
-      <c r="P114" s="99"/>
+      <c r="O114" s="100"/>
+      <c r="P114" s="100"/>
       <c r="Q114" s="49">
         <f>Q113/5</f>
-        <v>78.092659999999995</v>
-      </c>
-      <c r="R114" s="96"/>
-      <c r="S114" s="97"/>
+        <v>78.352059999999994</v>
+      </c>
+      <c r="R114" s="97"/>
+      <c r="S114" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9116,14 +9200,6217 @@
     <hyperlink ref="O108" r:id="rId90"/>
     <hyperlink ref="O37" r:id="rId91"/>
     <hyperlink ref="O109" r:id="rId92"/>
-    <hyperlink ref="O32" r:id="rId93"/>
-    <hyperlink ref="O91" r:id="rId94"/>
-    <hyperlink ref="O110" r:id="rId95"/>
-    <hyperlink ref="O111" r:id="rId96"/>
-    <hyperlink ref="O112" r:id="rId97"/>
+    <hyperlink ref="O91" r:id="rId93"/>
+    <hyperlink ref="O110" r:id="rId94"/>
+    <hyperlink ref="O111" r:id="rId95"/>
+    <hyperlink ref="O112" r:id="rId96"/>
+    <hyperlink ref="O32" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId98"/>
   <drawing r:id="rId99"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S114"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="50" t="s">
+        <v>545</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="51" t="s">
+        <v>546</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="93"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="52" t="s">
+        <v>546</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="94"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="94"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="94"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="94"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="94"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="H9" s="55" t="s">
+        <v>313</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>427</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>584</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>586</v>
+      </c>
+      <c r="R9" s="31" t="s">
+        <v>433</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="59"/>
+      <c r="B10" s="78">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>424</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J10" s="38" t="s">
+        <v>455</v>
+      </c>
+      <c r="K10" s="38" t="s">
+        <v>377</v>
+      </c>
+      <c r="L10" s="39">
+        <v>13</v>
+      </c>
+      <c r="M10" s="38">
+        <f>L10*10</f>
+        <v>130</v>
+      </c>
+      <c r="N10" s="38">
+        <v>140</v>
+      </c>
+      <c r="O10" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P10" s="40">
+        <v>2.81E-2</v>
+      </c>
+      <c r="Q10" s="40">
+        <f>P10*N10</f>
+        <v>3.9340000000000002</v>
+      </c>
+      <c r="R10" s="39"/>
+      <c r="S10" s="101"/>
+    </row>
+    <row r="11" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="59"/>
+      <c r="B11" s="81">
+        <f t="shared" ref="B11:B104" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>245</v>
+      </c>
+      <c r="H11" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I11" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J11" s="68" t="s">
+        <v>361</v>
+      </c>
+      <c r="K11" s="67" t="s">
+        <v>378</v>
+      </c>
+      <c r="L11" s="68">
+        <v>1</v>
+      </c>
+      <c r="M11" s="38">
+        <f t="shared" ref="M11:M74" si="1">L11*10</f>
+        <v>10</v>
+      </c>
+      <c r="N11" s="68">
+        <v>50</v>
+      </c>
+      <c r="O11" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P11" s="70">
+        <v>1.18E-2</v>
+      </c>
+      <c r="Q11" s="71">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>0.59</v>
+      </c>
+      <c r="R11" s="68"/>
+      <c r="S11" s="67"/>
+    </row>
+    <row r="12" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="59"/>
+      <c r="B12" s="78">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>446</v>
+      </c>
+      <c r="E12" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>362</v>
+      </c>
+      <c r="K12" s="38" t="s">
+        <v>379</v>
+      </c>
+      <c r="L12" s="39">
+        <v>9</v>
+      </c>
+      <c r="M12" s="38">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="N12" s="38">
+        <v>100</v>
+      </c>
+      <c r="O12" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P12" s="47">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Q12" s="40">
+        <f>P12*N12</f>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="R12" s="39"/>
+      <c r="S12" s="38"/>
+    </row>
+    <row r="13" spans="1:19" s="60" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="59"/>
+      <c r="B13" s="81">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="H13" s="68" t="s">
+        <v>316</v>
+      </c>
+      <c r="I13" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J13" s="68" t="s">
+        <v>457</v>
+      </c>
+      <c r="K13" s="67" t="s">
+        <v>380</v>
+      </c>
+      <c r="L13" s="68">
+        <v>5</v>
+      </c>
+      <c r="M13" s="38">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N13" s="68">
+        <v>52</v>
+      </c>
+      <c r="O13" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P13" s="70">
+        <v>0.27210000000000001</v>
+      </c>
+      <c r="Q13" s="71">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>14.1492</v>
+      </c>
+      <c r="R13" s="68"/>
+      <c r="S13" s="67"/>
+    </row>
+    <row r="14" spans="1:19" s="60" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="59"/>
+      <c r="B14" s="78">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>447</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J14" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="K14" s="38" t="s">
+        <v>378</v>
+      </c>
+      <c r="L14" s="39">
+        <v>37</v>
+      </c>
+      <c r="M14" s="38">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="N14" s="38">
+        <v>400</v>
+      </c>
+      <c r="O14" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P14" s="47">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q14" s="40">
+        <f>P14*N14</f>
+        <v>1.08</v>
+      </c>
+      <c r="R14" s="39"/>
+      <c r="S14" s="38"/>
+    </row>
+    <row r="15" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="59"/>
+      <c r="B15" s="81">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="67" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="H15" s="68" t="s">
+        <v>317</v>
+      </c>
+      <c r="I15" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J15" s="68" t="s">
+        <v>459</v>
+      </c>
+      <c r="K15" s="67" t="s">
+        <v>381</v>
+      </c>
+      <c r="L15" s="68">
+        <v>1</v>
+      </c>
+      <c r="M15" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N15" s="68">
+        <v>15</v>
+      </c>
+      <c r="O15" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P15" s="70">
+        <v>0.1363</v>
+      </c>
+      <c r="Q15" s="71">
+        <f t="shared" ref="Q15" si="4">P15*N15</f>
+        <v>2.0445000000000002</v>
+      </c>
+      <c r="R15" s="68"/>
+      <c r="S15" s="67"/>
+    </row>
+    <row r="16" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="59"/>
+      <c r="B16" s="78">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="56" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I16" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J16" s="39" t="s">
+        <v>460</v>
+      </c>
+      <c r="K16" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="L16" s="39">
+        <v>1</v>
+      </c>
+      <c r="M16" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N16" s="38">
+        <v>100</v>
+      </c>
+      <c r="O16" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P16" s="47">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="Q16" s="40">
+        <f>P16*N16</f>
+        <v>0.25</v>
+      </c>
+      <c r="R16" s="39"/>
+      <c r="S16" s="38"/>
+    </row>
+    <row r="17" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A17" s="59"/>
+      <c r="B17" s="81">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>318</v>
+      </c>
+      <c r="I17" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>461</v>
+      </c>
+      <c r="K17" s="67" t="s">
+        <v>379</v>
+      </c>
+      <c r="L17" s="68">
+        <v>1</v>
+      </c>
+      <c r="M17" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N17" s="68">
+        <v>11</v>
+      </c>
+      <c r="O17" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P17" s="70">
+        <v>0.15959999999999999</v>
+      </c>
+      <c r="Q17" s="71">
+        <f t="shared" ref="Q17" si="5">P17*N17</f>
+        <v>1.7555999999999998</v>
+      </c>
+      <c r="R17" s="68"/>
+      <c r="S17" s="67"/>
+    </row>
+    <row r="18" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="59"/>
+      <c r="B18" s="78">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I18" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>462</v>
+      </c>
+      <c r="K18" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="L18" s="39">
+        <v>2</v>
+      </c>
+      <c r="M18" s="38">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N18" s="38">
+        <v>100</v>
+      </c>
+      <c r="O18" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P18" s="47">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="Q18" s="40">
+        <f>P18*N18</f>
+        <v>0.26</v>
+      </c>
+      <c r="R18" s="39"/>
+      <c r="S18" s="38"/>
+    </row>
+    <row r="19" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="59"/>
+      <c r="B19" s="81">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="79" t="s">
+        <v>464</v>
+      </c>
+      <c r="E19" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>251</v>
+      </c>
+      <c r="H19" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I19" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J19" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="K19" s="67" t="s">
+        <v>384</v>
+      </c>
+      <c r="L19" s="68">
+        <v>4</v>
+      </c>
+      <c r="M19" s="38">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N19" s="68">
+        <v>100</v>
+      </c>
+      <c r="O19" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P19" s="70">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="Q19" s="71">
+        <f t="shared" ref="Q19" si="6">P19*N19</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R19" s="68"/>
+      <c r="S19" s="67"/>
+    </row>
+    <row r="20" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="59"/>
+      <c r="B20" s="78">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J20" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="K20" s="38" t="s">
+        <v>385</v>
+      </c>
+      <c r="L20" s="39">
+        <v>1</v>
+      </c>
+      <c r="M20" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N20" s="38">
+        <v>20</v>
+      </c>
+      <c r="O20" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P20" s="47">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="Q20" s="40">
+        <f>P20*N20</f>
+        <v>0.70400000000000007</v>
+      </c>
+      <c r="R20" s="39"/>
+      <c r="S20" s="38"/>
+    </row>
+    <row r="21" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="59"/>
+      <c r="B21" s="81">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>253</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>319</v>
+      </c>
+      <c r="I21" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J21" s="68" t="s">
+        <v>463</v>
+      </c>
+      <c r="K21" s="67" t="s">
+        <v>386</v>
+      </c>
+      <c r="L21" s="68">
+        <v>1</v>
+      </c>
+      <c r="M21" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N21" s="68">
+        <v>20</v>
+      </c>
+      <c r="O21" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P21" s="70">
+        <v>3.04E-2</v>
+      </c>
+      <c r="Q21" s="71">
+        <f t="shared" ref="Q21:Q22" si="7">P21*N21</f>
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="R21" s="68"/>
+      <c r="S21" s="67"/>
+    </row>
+    <row r="22" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="59"/>
+      <c r="B22" s="81">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="82" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J22" s="39" t="s">
+        <v>465</v>
+      </c>
+      <c r="K22" s="38" t="s">
+        <v>387</v>
+      </c>
+      <c r="L22" s="39">
+        <v>1</v>
+      </c>
+      <c r="M22" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N22" s="38">
+        <v>100</v>
+      </c>
+      <c r="O22" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P22" s="47">
+        <v>3.3E-3</v>
+      </c>
+      <c r="Q22" s="40">
+        <f t="shared" si="7"/>
+        <v>0.33</v>
+      </c>
+      <c r="R22" s="39"/>
+      <c r="S22" s="38"/>
+    </row>
+    <row r="23" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="59"/>
+      <c r="B23" s="78">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>255</v>
+      </c>
+      <c r="H23" s="68" t="s">
+        <v>319</v>
+      </c>
+      <c r="I23" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J23" s="68" t="s">
+        <v>466</v>
+      </c>
+      <c r="K23" s="67" t="s">
+        <v>388</v>
+      </c>
+      <c r="L23" s="68">
+        <v>1</v>
+      </c>
+      <c r="M23" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N23" s="68">
+        <v>20</v>
+      </c>
+      <c r="O23" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P23" s="70">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="Q23" s="71">
+        <f>P23*N23</f>
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="R23" s="68"/>
+      <c r="S23" s="67"/>
+    </row>
+    <row r="24" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="59"/>
+      <c r="B24" s="81">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="H24" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I24" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J24" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="K24" s="38" t="s">
+        <v>389</v>
+      </c>
+      <c r="L24" s="39">
+        <v>1</v>
+      </c>
+      <c r="M24" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N24" s="38">
+        <v>100</v>
+      </c>
+      <c r="O24" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P24" s="47">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="Q24" s="40">
+        <f t="shared" ref="Q24" si="8">P24*N24</f>
+        <v>0.31</v>
+      </c>
+      <c r="R24" s="39"/>
+      <c r="S24" s="38"/>
+    </row>
+    <row r="25" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A25" s="59"/>
+      <c r="B25" s="78">
+        <f>ROW(B25) - ROW($B$9)</f>
+        <v>16</v>
+      </c>
+      <c r="C25" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="79" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>257</v>
+      </c>
+      <c r="H25" s="68" t="s">
+        <v>320</v>
+      </c>
+      <c r="I25" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J25" s="68" t="s">
+        <v>468</v>
+      </c>
+      <c r="K25" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L25" s="68">
+        <v>1</v>
+      </c>
+      <c r="M25" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N25" s="68">
+        <v>20</v>
+      </c>
+      <c r="O25" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P25" s="70">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="Q25" s="71">
+        <f>P25*N25</f>
+        <v>0.65799999999999992</v>
+      </c>
+      <c r="R25" s="68"/>
+      <c r="S25" s="67"/>
+    </row>
+    <row r="26" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A26" s="59"/>
+      <c r="B26" s="81">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="82" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="H26" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="I26" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J26" s="39" t="s">
+        <v>469</v>
+      </c>
+      <c r="K26" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L26" s="39">
+        <v>1</v>
+      </c>
+      <c r="M26" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N26" s="38">
+        <v>11</v>
+      </c>
+      <c r="O26" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P26" s="47">
+        <v>0.17660000000000001</v>
+      </c>
+      <c r="Q26" s="40">
+        <f t="shared" ref="Q26" si="9">P26*N26</f>
+        <v>1.9426000000000001</v>
+      </c>
+      <c r="R26" s="39"/>
+      <c r="S26" s="38"/>
+    </row>
+    <row r="27" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A27" s="59"/>
+      <c r="B27" s="78">
+        <f>ROW(B27) - ROW($B$9)</f>
+        <v>18</v>
+      </c>
+      <c r="C27" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="68" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="H27" s="68" t="s">
+        <v>322</v>
+      </c>
+      <c r="I27" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J27" s="68" t="s">
+        <v>470</v>
+      </c>
+      <c r="K27" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L27" s="68">
+        <v>1</v>
+      </c>
+      <c r="M27" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N27" s="68">
+        <v>20</v>
+      </c>
+      <c r="O27" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P27" s="70">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="Q27" s="71">
+        <f>P27*N27</f>
+        <v>0.62799999999999989</v>
+      </c>
+      <c r="R27" s="68"/>
+      <c r="S27" s="67"/>
+    </row>
+    <row r="28" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="59"/>
+      <c r="B28" s="81">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="82" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="H28" s="39" t="s">
+        <v>323</v>
+      </c>
+      <c r="I28" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J28" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="K28" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L28" s="39">
+        <v>5</v>
+      </c>
+      <c r="M28" s="38">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N28" s="38">
+        <v>60</v>
+      </c>
+      <c r="O28" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P28" s="47">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="Q28" s="40">
+        <f t="shared" ref="Q28" si="10">P28*N28</f>
+        <v>1.2240000000000002</v>
+      </c>
+      <c r="R28" s="39"/>
+      <c r="S28" s="38"/>
+    </row>
+    <row r="29" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A29" s="59"/>
+      <c r="B29" s="78">
+        <f>ROW(B29) - ROW($B$9)</f>
+        <v>20</v>
+      </c>
+      <c r="C29" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="F29" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="G29" s="67" t="s">
+        <v>260</v>
+      </c>
+      <c r="H29" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="I29" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J29" s="68" t="s">
+        <v>471</v>
+      </c>
+      <c r="K29" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L29" s="68">
+        <v>1</v>
+      </c>
+      <c r="M29" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N29" s="68">
+        <v>20</v>
+      </c>
+      <c r="O29" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P29" s="70">
+        <v>6.2700000000000006E-2</v>
+      </c>
+      <c r="Q29" s="71">
+        <f>P29*N29</f>
+        <v>1.254</v>
+      </c>
+      <c r="R29" s="68"/>
+      <c r="S29" s="67"/>
+    </row>
+    <row r="30" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="59"/>
+      <c r="B30" s="81">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C30" s="85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="H30" s="39" t="s">
+        <v>325</v>
+      </c>
+      <c r="I30" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J30" s="39" t="s">
+        <v>472</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L30" s="39">
+        <v>1</v>
+      </c>
+      <c r="M30" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N30" s="38">
+        <v>15</v>
+      </c>
+      <c r="O30" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P30" s="47">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="Q30" s="40">
+        <f t="shared" ref="Q30" si="11">P30*N30</f>
+        <v>1.1625000000000001</v>
+      </c>
+      <c r="R30" s="39"/>
+      <c r="S30" s="38"/>
+    </row>
+    <row r="31" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A31" s="59"/>
+      <c r="B31" s="78">
+        <f>ROW(B31) - ROW($B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="C31" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="79" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>543</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="G31" s="67" t="s">
+        <v>261</v>
+      </c>
+      <c r="H31" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="I31" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J31" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="K31" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L31" s="68">
+        <v>1</v>
+      </c>
+      <c r="M31" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N31" s="68">
+        <v>20</v>
+      </c>
+      <c r="O31" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P31" s="70">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="Q31" s="71">
+        <f>P31*N31</f>
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="R31" s="68"/>
+      <c r="S31" s="67"/>
+    </row>
+    <row r="32" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="59"/>
+      <c r="B32" s="81">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="D32" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="G32" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="H32" s="39" t="s">
+        <v>326</v>
+      </c>
+      <c r="I32" s="38" t="s">
+        <v>587</v>
+      </c>
+      <c r="J32" s="39" t="s">
+        <v>588</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L32" s="39">
+        <v>1</v>
+      </c>
+      <c r="M32" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N32" s="38">
+        <v>15</v>
+      </c>
+      <c r="O32" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P32" s="47">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="Q32" s="40">
+        <f t="shared" ref="Q32" si="12">P32*N32</f>
+        <v>4.2299999999999995</v>
+      </c>
+      <c r="R32" s="39"/>
+      <c r="S32" s="38"/>
+    </row>
+    <row r="33" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="59"/>
+      <c r="B33" s="78">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="86" t="s">
+        <v>441</v>
+      </c>
+      <c r="D33" s="79" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G33" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="H33" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="I33" s="67" t="s">
+        <v>473</v>
+      </c>
+      <c r="J33" s="68" t="s">
+        <v>476</v>
+      </c>
+      <c r="K33" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L33" s="68">
+        <v>9</v>
+      </c>
+      <c r="M33" s="38">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="N33" s="68">
+        <v>100</v>
+      </c>
+      <c r="O33" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P33" s="70">
+        <v>6.0100000000000001E-2</v>
+      </c>
+      <c r="Q33" s="71">
+        <f>P33*N33</f>
+        <v>6.01</v>
+      </c>
+      <c r="R33" s="68"/>
+      <c r="S33" s="67"/>
+    </row>
+    <row r="34" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="59"/>
+      <c r="B34" s="81">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="85" t="s">
+        <v>441</v>
+      </c>
+      <c r="D34" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="G34" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="I34" s="38" t="s">
+        <v>474</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="K34" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L34" s="39">
+        <v>5</v>
+      </c>
+      <c r="M34" s="38">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N34" s="38">
+        <v>55</v>
+      </c>
+      <c r="O34" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P34" s="47">
+        <v>8.2400000000000001E-2</v>
+      </c>
+      <c r="Q34" s="40">
+        <f t="shared" ref="Q34" si="13">P34*N34</f>
+        <v>4.532</v>
+      </c>
+      <c r="R34" s="39"/>
+      <c r="S34" s="38"/>
+    </row>
+    <row r="35" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="59"/>
+      <c r="B35" s="78">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="86" t="s">
+        <v>441</v>
+      </c>
+      <c r="D35" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G35" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="H35" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="I35" s="67" t="s">
+        <v>475</v>
+      </c>
+      <c r="J35" s="68" t="s">
+        <v>478</v>
+      </c>
+      <c r="K35" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L35" s="68">
+        <v>1</v>
+      </c>
+      <c r="M35" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N35" s="68">
+        <v>15</v>
+      </c>
+      <c r="O35" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P35" s="70">
+        <v>0.1163</v>
+      </c>
+      <c r="Q35" s="71">
+        <f>P35*N35</f>
+        <v>1.7444999999999999</v>
+      </c>
+      <c r="R35" s="68"/>
+      <c r="S35" s="67"/>
+    </row>
+    <row r="36" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A36" s="59"/>
+      <c r="B36" s="81">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="85" t="s">
+        <v>442</v>
+      </c>
+      <c r="D36" s="84" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="62" t="s">
+        <v>425</v>
+      </c>
+      <c r="G36" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="H36" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="I36" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="J36" s="62" t="s">
+        <v>479</v>
+      </c>
+      <c r="K36" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="L36" s="62">
+        <v>1</v>
+      </c>
+      <c r="M36" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N36" s="58">
+        <v>6</v>
+      </c>
+      <c r="O36" s="63" t="s">
+        <v>456</v>
+      </c>
+      <c r="P36" s="64" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q36" s="65" t="s">
+        <v>436</v>
+      </c>
+      <c r="R36" s="90" t="s">
+        <v>582</v>
+      </c>
+      <c r="S36" s="38"/>
+    </row>
+    <row r="37" spans="1:19" s="60" customFormat="1" ht="108" x14ac:dyDescent="0.25">
+      <c r="A37" s="59"/>
+      <c r="B37" s="78">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="86" t="s">
+        <v>438</v>
+      </c>
+      <c r="D37" s="79" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="F37" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G37" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="H37" s="68" t="s">
+        <v>559</v>
+      </c>
+      <c r="I37" s="67" t="s">
+        <v>558</v>
+      </c>
+      <c r="J37" s="68" t="s">
+        <v>558</v>
+      </c>
+      <c r="K37" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L37" s="68">
+        <v>1</v>
+      </c>
+      <c r="M37" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N37" s="68">
+        <v>20</v>
+      </c>
+      <c r="O37" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P37" s="70">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="Q37" s="71">
+        <f>P37*N37</f>
+        <v>0.8640000000000001</v>
+      </c>
+      <c r="R37" s="77" t="s">
+        <v>560</v>
+      </c>
+      <c r="S37" s="67"/>
+    </row>
+    <row r="38" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A38" s="59"/>
+      <c r="B38" s="81">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="G38" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="H38" s="39" t="s">
+        <v>329</v>
+      </c>
+      <c r="I38" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J38" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="K38" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L38" s="39">
+        <v>1</v>
+      </c>
+      <c r="M38" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N38" s="38">
+        <v>11</v>
+      </c>
+      <c r="O38" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P38" s="47">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="Q38" s="40">
+        <f t="shared" ref="Q38" si="14">P38*N38</f>
+        <v>1.9415</v>
+      </c>
+      <c r="R38" s="39"/>
+      <c r="S38" s="38"/>
+    </row>
+    <row r="39" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A39" s="59"/>
+      <c r="B39" s="78">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" s="68" t="s">
+        <v>209</v>
+      </c>
+      <c r="G39" s="67" t="s">
+        <v>263</v>
+      </c>
+      <c r="H39" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="I39" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J39" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="K39" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L39" s="68">
+        <v>5</v>
+      </c>
+      <c r="M39" s="38">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N39" s="68">
+        <v>52</v>
+      </c>
+      <c r="O39" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P39" s="70">
+        <v>0.9546</v>
+      </c>
+      <c r="Q39" s="71">
+        <f>P39*N39</f>
+        <v>49.639200000000002</v>
+      </c>
+      <c r="R39" s="68"/>
+      <c r="S39" s="67"/>
+    </row>
+    <row r="40" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A40" s="59"/>
+      <c r="B40" s="81">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="85" t="s">
+        <v>443</v>
+      </c>
+      <c r="D40" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="F40" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="H40" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="I40" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J40" s="39" t="s">
+        <v>480</v>
+      </c>
+      <c r="K40" s="38" t="s">
+        <v>390</v>
+      </c>
+      <c r="L40" s="39">
+        <v>1</v>
+      </c>
+      <c r="M40" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N40" s="38">
+        <v>20</v>
+      </c>
+      <c r="O40" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P40" s="47">
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="Q40" s="40">
+        <f t="shared" ref="Q40" si="15">P40*N40</f>
+        <v>0.88600000000000001</v>
+      </c>
+      <c r="R40" s="39"/>
+      <c r="S40" s="38"/>
+    </row>
+    <row r="41" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A41" s="59"/>
+      <c r="B41" s="78">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="86" t="s">
+        <v>443</v>
+      </c>
+      <c r="D41" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G41" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="68" t="s">
+        <v>332</v>
+      </c>
+      <c r="I41" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J41" s="68" t="s">
+        <v>481</v>
+      </c>
+      <c r="K41" s="67" t="s">
+        <v>391</v>
+      </c>
+      <c r="L41" s="68">
+        <v>1</v>
+      </c>
+      <c r="M41" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N41" s="68">
+        <v>11</v>
+      </c>
+      <c r="O41" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P41" s="70">
+        <v>0.40260000000000001</v>
+      </c>
+      <c r="Q41" s="71">
+        <f>P41*N41</f>
+        <v>4.4286000000000003</v>
+      </c>
+      <c r="R41" s="68"/>
+      <c r="S41" s="67"/>
+    </row>
+    <row r="42" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A42" s="59"/>
+      <c r="B42" s="81">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="85" t="s">
+        <v>443</v>
+      </c>
+      <c r="D42" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="H42" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="I42" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J42" s="39" t="s">
+        <v>482</v>
+      </c>
+      <c r="K42" s="38" t="s">
+        <v>392</v>
+      </c>
+      <c r="L42" s="39">
+        <v>1</v>
+      </c>
+      <c r="M42" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N42" s="38">
+        <v>15</v>
+      </c>
+      <c r="O42" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P42" s="47">
+        <v>7.7700000000000005E-2</v>
+      </c>
+      <c r="Q42" s="40">
+        <f t="shared" ref="Q42" si="16">P42*N42</f>
+        <v>1.1655</v>
+      </c>
+      <c r="R42" s="39"/>
+      <c r="S42" s="38"/>
+    </row>
+    <row r="43" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A43" s="59"/>
+      <c r="B43" s="78">
+        <f>ROW(B43) - ROW($B$9)</f>
+        <v>34</v>
+      </c>
+      <c r="C43" s="86" t="s">
+        <v>443</v>
+      </c>
+      <c r="D43" s="79" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="F43" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="G43" s="67" t="s">
+        <v>266</v>
+      </c>
+      <c r="H43" s="68" t="s">
+        <v>334</v>
+      </c>
+      <c r="I43" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J43" s="68" t="s">
+        <v>483</v>
+      </c>
+      <c r="K43" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="L43" s="68">
+        <v>1</v>
+      </c>
+      <c r="M43" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N43" s="68">
+        <v>15</v>
+      </c>
+      <c r="O43" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P43" s="70">
+        <v>8.5099999999999995E-2</v>
+      </c>
+      <c r="Q43" s="71">
+        <f>P43*N43</f>
+        <v>1.2765</v>
+      </c>
+      <c r="R43" s="68"/>
+      <c r="S43" s="67"/>
+    </row>
+    <row r="44" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A44" s="59"/>
+      <c r="B44" s="81">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="85" t="s">
+        <v>444</v>
+      </c>
+      <c r="D44" s="82" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="G44" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="H44" s="39" t="s">
+        <v>335</v>
+      </c>
+      <c r="I44" s="38" t="s">
+        <v>494</v>
+      </c>
+      <c r="J44" s="39" t="s">
+        <v>484</v>
+      </c>
+      <c r="K44" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L44" s="39">
+        <v>7</v>
+      </c>
+      <c r="M44" s="38">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="N44" s="38">
+        <v>80</v>
+      </c>
+      <c r="O44" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P44" s="47">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="Q44" s="40">
+        <f t="shared" ref="Q44" si="17">P44*N44</f>
+        <v>2.9360000000000004</v>
+      </c>
+      <c r="R44" s="39"/>
+      <c r="S44" s="38"/>
+    </row>
+    <row r="45" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="59"/>
+      <c r="B45" s="78">
+        <f>ROW(B45) - ROW($B$9)</f>
+        <v>36</v>
+      </c>
+      <c r="C45" s="86" t="s">
+        <v>444</v>
+      </c>
+      <c r="D45" s="79" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="F45" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G45" s="67" t="s">
+        <v>268</v>
+      </c>
+      <c r="H45" s="68" t="s">
+        <v>336</v>
+      </c>
+      <c r="I45" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J45" s="68" t="s">
+        <v>485</v>
+      </c>
+      <c r="K45" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L45" s="68">
+        <v>1</v>
+      </c>
+      <c r="M45" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N45" s="68">
+        <v>15</v>
+      </c>
+      <c r="O45" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P45" s="70">
+        <v>0.1186</v>
+      </c>
+      <c r="Q45" s="71">
+        <f>P45*N45</f>
+        <v>1.7789999999999999</v>
+      </c>
+      <c r="R45" s="68"/>
+      <c r="S45" s="67"/>
+    </row>
+    <row r="46" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A46" s="59"/>
+      <c r="B46" s="81">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="85" t="s">
+        <v>445</v>
+      </c>
+      <c r="D46" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="E46" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="F46" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="G46" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="H46" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="I46" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J46" s="39" t="s">
+        <v>486</v>
+      </c>
+      <c r="K46" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L46" s="39">
+        <v>1</v>
+      </c>
+      <c r="M46" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N46" s="38">
+        <v>15</v>
+      </c>
+      <c r="O46" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P46" s="47">
+        <v>0.3352</v>
+      </c>
+      <c r="Q46" s="40">
+        <f t="shared" ref="Q46" si="18">P46*N46</f>
+        <v>5.0279999999999996</v>
+      </c>
+      <c r="R46" s="39"/>
+      <c r="S46" s="38"/>
+    </row>
+    <row r="47" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="59"/>
+      <c r="B47" s="78">
+        <f>ROW(B47) - ROW($B$9)</f>
+        <v>38</v>
+      </c>
+      <c r="C47" s="87" t="s">
+        <v>394</v>
+      </c>
+      <c r="D47" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="F47" s="73" t="s">
+        <v>425</v>
+      </c>
+      <c r="G47" s="72" t="s">
+        <v>216</v>
+      </c>
+      <c r="H47" s="73" t="s">
+        <v>436</v>
+      </c>
+      <c r="I47" s="72" t="s">
+        <v>436</v>
+      </c>
+      <c r="J47" s="73" t="s">
+        <v>436</v>
+      </c>
+      <c r="K47" s="72" t="s">
+        <v>436</v>
+      </c>
+      <c r="L47" s="73">
+        <v>2</v>
+      </c>
+      <c r="M47" s="38">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N47" s="73" t="s">
+        <v>436</v>
+      </c>
+      <c r="O47" s="74" t="s">
+        <v>436</v>
+      </c>
+      <c r="P47" s="75" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q47" s="76" t="s">
+        <v>436</v>
+      </c>
+      <c r="R47" s="73"/>
+      <c r="S47" s="72"/>
+    </row>
+    <row r="48" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="59"/>
+      <c r="B48" s="81">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C48" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="D48" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="G48" s="58">
+        <v>61300311121</v>
+      </c>
+      <c r="H48" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="I48" s="38" t="s">
+        <v>497</v>
+      </c>
+      <c r="J48" s="39" t="s">
+        <v>497</v>
+      </c>
+      <c r="K48" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L48" s="39">
+        <v>2</v>
+      </c>
+      <c r="M48" s="38">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N48" s="38">
+        <v>50</v>
+      </c>
+      <c r="O48" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P48" s="47">
+        <v>1.44E-2</v>
+      </c>
+      <c r="Q48" s="40">
+        <f t="shared" ref="Q48" si="19">P48*N48</f>
+        <v>0.72</v>
+      </c>
+      <c r="R48" s="39"/>
+      <c r="S48" s="38"/>
+    </row>
+    <row r="49" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="59"/>
+      <c r="B49" s="78">
+        <f>ROW(B49) - ROW($B$9)</f>
+        <v>40</v>
+      </c>
+      <c r="C49" s="86" t="s">
+        <v>438</v>
+      </c>
+      <c r="D49" s="79" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="67" t="s">
+        <v>138</v>
+      </c>
+      <c r="F49" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="G49" s="72">
+        <v>61300611121</v>
+      </c>
+      <c r="H49" s="68" t="s">
+        <v>338</v>
+      </c>
+      <c r="I49" s="67" t="s">
+        <v>495</v>
+      </c>
+      <c r="J49" s="68" t="s">
+        <v>487</v>
+      </c>
+      <c r="K49" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L49" s="68">
+        <v>4</v>
+      </c>
+      <c r="M49" s="38">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N49" s="68">
+        <v>60</v>
+      </c>
+      <c r="O49" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P49" s="70">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="Q49" s="71">
+        <f>P49*N49</f>
+        <v>1.8480000000000001</v>
+      </c>
+      <c r="R49" s="68"/>
+      <c r="S49" s="67"/>
+    </row>
+    <row r="50" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="59"/>
+      <c r="B50" s="81">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C50" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="D50" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="G50" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>339</v>
+      </c>
+      <c r="I50" s="38" t="s">
+        <v>488</v>
+      </c>
+      <c r="J50" s="39" t="s">
+        <v>488</v>
+      </c>
+      <c r="K50" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L50" s="39">
+        <v>1</v>
+      </c>
+      <c r="M50" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N50" s="38">
+        <v>15</v>
+      </c>
+      <c r="O50" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P50" s="47">
+        <v>0.11509999999999999</v>
+      </c>
+      <c r="Q50" s="40">
+        <f t="shared" ref="Q50" si="20">P50*N50</f>
+        <v>1.7264999999999999</v>
+      </c>
+      <c r="R50" s="39"/>
+      <c r="S50" s="38"/>
+    </row>
+    <row r="51" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A51" s="59"/>
+      <c r="B51" s="78">
+        <f>ROW(B51) - ROW($B$9)</f>
+        <v>42</v>
+      </c>
+      <c r="C51" s="86" t="s">
+        <v>438</v>
+      </c>
+      <c r="D51" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="G51" s="72">
+        <v>61300211121</v>
+      </c>
+      <c r="H51" s="68" t="s">
+        <v>338</v>
+      </c>
+      <c r="I51" s="67" t="s">
+        <v>564</v>
+      </c>
+      <c r="J51" s="68" t="s">
+        <v>489</v>
+      </c>
+      <c r="K51" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L51" s="68">
+        <v>3</v>
+      </c>
+      <c r="M51" s="38">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N51" s="68">
+        <v>50</v>
+      </c>
+      <c r="O51" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P51" s="70">
+        <v>1.37E-2</v>
+      </c>
+      <c r="Q51" s="71">
+        <f>P51*N51</f>
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="R51" s="68"/>
+      <c r="S51" s="67"/>
+    </row>
+    <row r="52" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A52" s="59"/>
+      <c r="B52" s="81">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C52" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="D52" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="E52" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="F52" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="G52" s="58">
+        <v>61300411121</v>
+      </c>
+      <c r="H52" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="I52" s="38" t="s">
+        <v>496</v>
+      </c>
+      <c r="J52" s="39" t="s">
+        <v>490</v>
+      </c>
+      <c r="K52" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L52" s="39">
+        <v>1</v>
+      </c>
+      <c r="M52" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N52" s="38">
+        <v>20</v>
+      </c>
+      <c r="O52" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P52" s="47">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="Q52" s="40">
+        <f t="shared" ref="Q52" si="21">P52*N52</f>
+        <v>0.44200000000000006</v>
+      </c>
+      <c r="R52" s="39"/>
+      <c r="S52" s="38"/>
+    </row>
+    <row r="53" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A53" s="59"/>
+      <c r="B53" s="78">
+        <f>ROW(B53) - ROW($B$9)</f>
+        <v>44</v>
+      </c>
+      <c r="C53" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="F53" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="G53" s="67" t="s">
+        <v>270</v>
+      </c>
+      <c r="H53" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="I53" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J53" s="68" t="s">
+        <v>491</v>
+      </c>
+      <c r="K53" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L53" s="68">
+        <v>9</v>
+      </c>
+      <c r="M53" s="38">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="N53" s="68">
+        <v>92</v>
+      </c>
+      <c r="O53" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P53" s="70">
+        <v>0.31269999999999998</v>
+      </c>
+      <c r="Q53" s="71">
+        <f>P53*N53</f>
+        <v>28.7684</v>
+      </c>
+      <c r="R53" s="68"/>
+      <c r="S53" s="67"/>
+    </row>
+    <row r="54" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A54" s="59"/>
+      <c r="B54" s="81">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C54" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="82" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="F54" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="G54" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="H54" s="39" t="s">
+        <v>340</v>
+      </c>
+      <c r="I54" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J54" s="39" t="s">
+        <v>492</v>
+      </c>
+      <c r="K54" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L54" s="39">
+        <v>1</v>
+      </c>
+      <c r="M54" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N54" s="38">
+        <v>15</v>
+      </c>
+      <c r="O54" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P54" s="47">
+        <v>7.3599999999999999E-2</v>
+      </c>
+      <c r="Q54" s="40">
+        <f t="shared" ref="Q54" si="22">P54*N54</f>
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="R54" s="39"/>
+      <c r="S54" s="38"/>
+    </row>
+    <row r="55" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="59"/>
+      <c r="B55" s="78">
+        <f>ROW(B55) - ROW($B$9)</f>
+        <v>46</v>
+      </c>
+      <c r="C55" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F55" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="G55" s="67" t="s">
+        <v>272</v>
+      </c>
+      <c r="H55" s="68" t="s">
+        <v>341</v>
+      </c>
+      <c r="I55" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J55" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="K55" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L55" s="68">
+        <v>2</v>
+      </c>
+      <c r="M55" s="38">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N55" s="68">
+        <v>21</v>
+      </c>
+      <c r="O55" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P55" s="70">
+        <v>0.80349999999999999</v>
+      </c>
+      <c r="Q55" s="71">
+        <f>P55*N55</f>
+        <v>16.8735</v>
+      </c>
+      <c r="R55" s="68"/>
+      <c r="S55" s="67"/>
+    </row>
+    <row r="56" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A56" s="59"/>
+      <c r="B56" s="81">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C56" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="E56" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="F56" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="G56" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="H56" s="39" t="s">
+        <v>340</v>
+      </c>
+      <c r="I56" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J56" s="39" t="s">
+        <v>493</v>
+      </c>
+      <c r="K56" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L56" s="39">
+        <v>2</v>
+      </c>
+      <c r="M56" s="38">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N56" s="38">
+        <v>25</v>
+      </c>
+      <c r="O56" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P56" s="47">
+        <v>0.1227</v>
+      </c>
+      <c r="Q56" s="40">
+        <f t="shared" ref="Q56" si="23">P56*N56</f>
+        <v>3.0674999999999999</v>
+      </c>
+      <c r="R56" s="39"/>
+      <c r="S56" s="38"/>
+    </row>
+    <row r="57" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A57" s="59"/>
+      <c r="B57" s="78">
+        <f>ROW(B57) - ROW($B$9)</f>
+        <v>48</v>
+      </c>
+      <c r="C57" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="79" t="s">
+        <v>60</v>
+      </c>
+      <c r="E57" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="F57" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="G57" s="67" t="s">
+        <v>274</v>
+      </c>
+      <c r="H57" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="I57" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J57" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="K57" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L57" s="68">
+        <v>6</v>
+      </c>
+      <c r="M57" s="38">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="N57" s="68">
+        <v>80</v>
+      </c>
+      <c r="O57" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P57" s="70">
+        <v>3.49E-2</v>
+      </c>
+      <c r="Q57" s="71">
+        <f>P57*N57</f>
+        <v>2.7919999999999998</v>
+      </c>
+      <c r="R57" s="68"/>
+      <c r="S57" s="67"/>
+    </row>
+    <row r="58" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A58" s="59"/>
+      <c r="B58" s="81">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C58" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F58" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="G58" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="H58" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="I58" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J58" s="39" t="s">
+        <v>498</v>
+      </c>
+      <c r="K58" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L58" s="39">
+        <v>10</v>
+      </c>
+      <c r="M58" s="38">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N58" s="38">
+        <v>120</v>
+      </c>
+      <c r="O58" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P58" s="47">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="Q58" s="40">
+        <f t="shared" ref="Q58" si="24">P58*N58</f>
+        <v>2.3039999999999998</v>
+      </c>
+      <c r="R58" s="39"/>
+      <c r="S58" s="38"/>
+    </row>
+    <row r="59" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A59" s="59"/>
+      <c r="B59" s="78">
+        <f>ROW(B59) - ROW($B$9)</f>
+        <v>50</v>
+      </c>
+      <c r="C59" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="79" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="F59" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="G59" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="H59" s="68" t="s">
+        <v>342</v>
+      </c>
+      <c r="I59" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J59" s="68" t="s">
+        <v>499</v>
+      </c>
+      <c r="K59" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L59" s="68">
+        <v>2</v>
+      </c>
+      <c r="M59" s="38">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N59" s="68">
+        <v>40</v>
+      </c>
+      <c r="O59" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P59" s="70">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="Q59" s="71">
+        <f>P59*N59</f>
+        <v>0.95600000000000007</v>
+      </c>
+      <c r="R59" s="68"/>
+      <c r="S59" s="67"/>
+    </row>
+    <row r="60" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A60" s="59"/>
+      <c r="B60" s="81">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="C60" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="E60" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="F60" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="G60" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="H60" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="I60" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J60" s="39" t="s">
+        <v>500</v>
+      </c>
+      <c r="K60" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L60" s="39">
+        <v>3</v>
+      </c>
+      <c r="M60" s="38">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N60" s="38">
+        <v>40</v>
+      </c>
+      <c r="O60" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P60" s="47">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="Q60" s="40">
+        <f t="shared" ref="Q60" si="25">P60*N60</f>
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="R60" s="39"/>
+      <c r="S60" s="38"/>
+    </row>
+    <row r="61" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A61" s="59"/>
+      <c r="B61" s="78">
+        <f>ROW(B61) - ROW($B$9)</f>
+        <v>52</v>
+      </c>
+      <c r="C61" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="F61" s="68" t="s">
+        <v>440</v>
+      </c>
+      <c r="G61" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H61" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="I61" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J61" s="68" t="s">
+        <v>501</v>
+      </c>
+      <c r="K61" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L61" s="68">
+        <v>1</v>
+      </c>
+      <c r="M61" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N61" s="68">
+        <v>15</v>
+      </c>
+      <c r="O61" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P61" s="70">
+        <v>0.32490000000000002</v>
+      </c>
+      <c r="Q61" s="71">
+        <f>P61*N61</f>
+        <v>4.8734999999999999</v>
+      </c>
+      <c r="R61" s="68"/>
+      <c r="S61" s="67"/>
+    </row>
+    <row r="62" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A62" s="59"/>
+      <c r="B62" s="81">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C62" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="F62" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="G62" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="H62" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="I62" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J62" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="K62" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L62" s="39">
+        <v>1</v>
+      </c>
+      <c r="M62" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N62" s="38">
+        <v>20</v>
+      </c>
+      <c r="O62" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P62" s="47">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="Q62" s="40">
+        <f t="shared" ref="Q62" si="26">P62*N62</f>
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="R62" s="39"/>
+      <c r="S62" s="38"/>
+    </row>
+    <row r="63" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A63" s="59"/>
+      <c r="B63" s="78">
+        <f>ROW(B63) - ROW($B$9)</f>
+        <v>54</v>
+      </c>
+      <c r="C63" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="E63" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="F63" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G63" s="67" t="s">
+        <v>279</v>
+      </c>
+      <c r="H63" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I63" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J63" s="68" t="s">
+        <v>502</v>
+      </c>
+      <c r="K63" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="L63" s="68">
+        <v>1</v>
+      </c>
+      <c r="M63" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N63" s="68">
+        <v>100</v>
+      </c>
+      <c r="O63" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P63" s="70">
+        <v>2E-3</v>
+      </c>
+      <c r="Q63" s="71">
+        <f>P63*N63</f>
+        <v>0.2</v>
+      </c>
+      <c r="R63" s="68"/>
+      <c r="S63" s="67"/>
+    </row>
+    <row r="64" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="59"/>
+      <c r="B64" s="81">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C64" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="E64" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="F64" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="G64" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="H64" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I64" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J64" s="39" t="s">
+        <v>503</v>
+      </c>
+      <c r="K64" s="38" t="s">
+        <v>396</v>
+      </c>
+      <c r="L64" s="39">
+        <v>1</v>
+      </c>
+      <c r="M64" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N64" s="38">
+        <v>100</v>
+      </c>
+      <c r="O64" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P64" s="47">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q64" s="40">
+        <f t="shared" ref="Q64" si="27">P64*N64</f>
+        <v>0.12</v>
+      </c>
+      <c r="R64" s="39"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A65" s="59"/>
+      <c r="B65" s="78">
+        <f>ROW(B65) - ROW($B$9)</f>
+        <v>56</v>
+      </c>
+      <c r="C65" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="79" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="F65" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G65" s="67" t="s">
+        <v>435</v>
+      </c>
+      <c r="H65" s="68" t="s">
+        <v>345</v>
+      </c>
+      <c r="I65" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J65" s="68" t="s">
+        <v>504</v>
+      </c>
+      <c r="K65" s="67" t="s">
+        <v>397</v>
+      </c>
+      <c r="L65" s="68">
+        <v>1</v>
+      </c>
+      <c r="M65" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N65" s="68">
+        <v>50</v>
+      </c>
+      <c r="O65" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P65" s="70">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q65" s="71">
+        <f>P65*N65</f>
+        <v>0.19</v>
+      </c>
+      <c r="R65" s="68"/>
+      <c r="S65" s="67"/>
+    </row>
+    <row r="66" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A66" s="59"/>
+      <c r="B66" s="78">
+        <f>ROW(B66) - ROW($B$9)</f>
+        <v>57</v>
+      </c>
+      <c r="C66" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="82" t="s">
+        <v>454</v>
+      </c>
+      <c r="E66" s="56" t="s">
+        <v>541</v>
+      </c>
+      <c r="F66" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="G66" s="38" t="s">
+        <v>281</v>
+      </c>
+      <c r="H66" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I66" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J66" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="K66" s="38" t="s">
+        <v>399</v>
+      </c>
+      <c r="L66" s="39">
+        <v>15</v>
+      </c>
+      <c r="M66" s="38">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="N66" s="38">
+        <v>200</v>
+      </c>
+      <c r="O66" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P66" s="47">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q66" s="40">
+        <f>P66*N66</f>
+        <v>0.24</v>
+      </c>
+      <c r="R66" s="39"/>
+      <c r="S66" s="38"/>
+    </row>
+    <row r="67" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A67" s="59"/>
+      <c r="B67" s="81">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C67" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="F67" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G67" s="67" t="s">
+        <v>282</v>
+      </c>
+      <c r="H67" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I67" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J67" s="68" t="s">
+        <v>505</v>
+      </c>
+      <c r="K67" s="67" t="s">
+        <v>400</v>
+      </c>
+      <c r="L67" s="68">
+        <v>2</v>
+      </c>
+      <c r="M67" s="38">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N67" s="68">
+        <v>100</v>
+      </c>
+      <c r="O67" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P67" s="70">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q67" s="71">
+        <f t="shared" ref="Q67" si="28">P67*N67</f>
+        <v>0.15</v>
+      </c>
+      <c r="R67" s="68"/>
+      <c r="S67" s="67"/>
+    </row>
+    <row r="68" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A68" s="59"/>
+      <c r="B68" s="78">
+        <f>ROW(B68) - ROW($B$9)</f>
+        <v>59</v>
+      </c>
+      <c r="C68" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="E68" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="G68" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="H68" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="I68" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J68" s="39" t="s">
+        <v>506</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="L68" s="39">
+        <v>1</v>
+      </c>
+      <c r="M68" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N68" s="38">
+        <v>100</v>
+      </c>
+      <c r="O68" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P68" s="47">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="Q68" s="40">
+        <f>P68*N68</f>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="R68" s="39"/>
+      <c r="S68" s="38"/>
+    </row>
+    <row r="69" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A69" s="59"/>
+      <c r="B69" s="81">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="C69" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="79" t="s">
+        <v>448</v>
+      </c>
+      <c r="E69" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="F69" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="G69" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="H69" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I69" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J69" s="68" t="s">
+        <v>370</v>
+      </c>
+      <c r="K69" s="67" t="s">
+        <v>398</v>
+      </c>
+      <c r="L69" s="68">
+        <v>20</v>
+      </c>
+      <c r="M69" s="38">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="N69" s="68">
+        <v>300</v>
+      </c>
+      <c r="O69" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P69" s="70">
+        <v>1E-3</v>
+      </c>
+      <c r="Q69" s="71">
+        <f t="shared" ref="Q69" si="29">P69*N69</f>
+        <v>0.3</v>
+      </c>
+      <c r="R69" s="68"/>
+      <c r="S69" s="67"/>
+    </row>
+    <row r="70" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="59"/>
+      <c r="B70" s="78">
+        <f>ROW(B70) - ROW($B$9)</f>
+        <v>61</v>
+      </c>
+      <c r="C70" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="82" t="s">
+        <v>71</v>
+      </c>
+      <c r="E70" s="56" t="s">
+        <v>158</v>
+      </c>
+      <c r="F70" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="G70" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="H70" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I70" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J70" s="39" t="s">
+        <v>526</v>
+      </c>
+      <c r="K70" s="38" t="s">
+        <v>402</v>
+      </c>
+      <c r="L70" s="39">
+        <v>1</v>
+      </c>
+      <c r="M70" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N70" s="38">
+        <v>100</v>
+      </c>
+      <c r="O70" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P70" s="47">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q70" s="40">
+        <f>P70*N70</f>
+        <v>0.13</v>
+      </c>
+      <c r="R70" s="39"/>
+      <c r="S70" s="38"/>
+    </row>
+    <row r="71" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A71" s="59"/>
+      <c r="B71" s="81">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C71" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="E71" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="F71" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G71" s="67" t="s">
+        <v>286</v>
+      </c>
+      <c r="H71" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I71" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J71" s="68" t="s">
+        <v>507</v>
+      </c>
+      <c r="K71" s="67" t="s">
+        <v>403</v>
+      </c>
+      <c r="L71" s="68">
+        <v>3</v>
+      </c>
+      <c r="M71" s="38">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N71" s="68">
+        <v>100</v>
+      </c>
+      <c r="O71" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P71" s="70">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q71" s="71">
+        <f t="shared" ref="Q71" si="30">P71*N71</f>
+        <v>0.12</v>
+      </c>
+      <c r="R71" s="68"/>
+      <c r="S71" s="67"/>
+    </row>
+    <row r="72" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A72" s="59"/>
+      <c r="B72" s="78">
+        <f>ROW(B72) - ROW($B$9)</f>
+        <v>63</v>
+      </c>
+      <c r="C72" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="82" t="s">
+        <v>453</v>
+      </c>
+      <c r="E72" s="56" t="s">
+        <v>160</v>
+      </c>
+      <c r="F72" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="G72" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="H72" s="39" t="s">
+        <v>347</v>
+      </c>
+      <c r="I72" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J72" s="39" t="s">
+        <v>508</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="L72" s="39">
+        <v>8</v>
+      </c>
+      <c r="M72" s="38">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N72" s="38">
+        <v>100</v>
+      </c>
+      <c r="O72" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P72" s="47">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q72" s="40">
+        <f>P72*N72</f>
+        <v>0.12</v>
+      </c>
+      <c r="R72" s="39"/>
+      <c r="S72" s="38"/>
+    </row>
+    <row r="73" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="59"/>
+      <c r="B73" s="81">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="C73" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="E73" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="F73" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G73" s="67" t="s">
+        <v>288</v>
+      </c>
+      <c r="H73" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I73" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J73" s="68" t="s">
+        <v>527</v>
+      </c>
+      <c r="K73" s="67" t="s">
+        <v>405</v>
+      </c>
+      <c r="L73" s="68">
+        <v>2</v>
+      </c>
+      <c r="M73" s="38">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N73" s="68">
+        <v>100</v>
+      </c>
+      <c r="O73" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P73" s="70">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q73" s="71">
+        <f t="shared" ref="Q73" si="31">P73*N73</f>
+        <v>0.12</v>
+      </c>
+      <c r="R73" s="68"/>
+      <c r="S73" s="67"/>
+    </row>
+    <row r="74" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A74" s="59"/>
+      <c r="B74" s="78">
+        <f>ROW(B74) - ROW($B$9)</f>
+        <v>65</v>
+      </c>
+      <c r="C74" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="E74" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="F74" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="G74" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="H74" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I74" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J74" s="39" t="s">
+        <v>509</v>
+      </c>
+      <c r="K74" s="38" t="s">
+        <v>406</v>
+      </c>
+      <c r="L74" s="39">
+        <v>13</v>
+      </c>
+      <c r="M74" s="38">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="N74" s="38">
+        <v>200</v>
+      </c>
+      <c r="O74" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P74" s="47">
+        <v>1E-3</v>
+      </c>
+      <c r="Q74" s="40">
+        <f>P74*N74</f>
+        <v>0.2</v>
+      </c>
+      <c r="R74" s="39"/>
+      <c r="S74" s="38"/>
+    </row>
+    <row r="75" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A75" s="59"/>
+      <c r="B75" s="81">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="C75" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="79" t="s">
+        <v>542</v>
+      </c>
+      <c r="E75" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="F75" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="G75" s="67" t="s">
+        <v>290</v>
+      </c>
+      <c r="H75" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I75" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J75" s="68" t="s">
+        <v>528</v>
+      </c>
+      <c r="K75" s="67" t="s">
+        <v>408</v>
+      </c>
+      <c r="L75" s="68">
+        <v>2</v>
+      </c>
+      <c r="M75" s="38">
+        <f t="shared" ref="M75:M112" si="32">L75*10</f>
+        <v>20</v>
+      </c>
+      <c r="N75" s="68">
+        <v>40</v>
+      </c>
+      <c r="O75" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P75" s="70">
+        <v>2.92E-2</v>
+      </c>
+      <c r="Q75" s="71">
+        <f t="shared" ref="Q75" si="33">P75*N75</f>
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="R75" s="68"/>
+      <c r="S75" s="67"/>
+    </row>
+    <row r="76" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A76" s="59"/>
+      <c r="B76" s="78">
+        <f>ROW(B76) - ROW($B$9)</f>
+        <v>67</v>
+      </c>
+      <c r="C76" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="82" t="s">
+        <v>74</v>
+      </c>
+      <c r="E76" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="F76" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="G76" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="H76" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I76" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J76" s="39" t="s">
+        <v>529</v>
+      </c>
+      <c r="K76" s="38" t="s">
+        <v>409</v>
+      </c>
+      <c r="L76" s="39">
+        <v>1</v>
+      </c>
+      <c r="M76" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N76" s="38">
+        <v>20</v>
+      </c>
+      <c r="O76" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P76" s="47">
+        <v>0.03</v>
+      </c>
+      <c r="Q76" s="40">
+        <f>P76*N76</f>
+        <v>0.6</v>
+      </c>
+      <c r="R76" s="39"/>
+      <c r="S76" s="38"/>
+    </row>
+    <row r="77" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="59"/>
+      <c r="B77" s="81">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="C77" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" s="79" t="s">
+        <v>451</v>
+      </c>
+      <c r="E77" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="F77" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G77" s="67" t="s">
+        <v>292</v>
+      </c>
+      <c r="H77" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I77" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J77" s="68" t="s">
+        <v>510</v>
+      </c>
+      <c r="K77" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="L77" s="68">
+        <v>3</v>
+      </c>
+      <c r="M77" s="38">
+        <f t="shared" si="32"/>
+        <v>30</v>
+      </c>
+      <c r="N77" s="68">
+        <v>100</v>
+      </c>
+      <c r="O77" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P77" s="70">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q77" s="71">
+        <f t="shared" ref="Q77" si="34">P77*N77</f>
+        <v>0.12</v>
+      </c>
+      <c r="R77" s="68"/>
+      <c r="S77" s="67"/>
+    </row>
+    <row r="78" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A78" s="59"/>
+      <c r="B78" s="78">
+        <f>ROW(B78) - ROW($B$9)</f>
+        <v>69</v>
+      </c>
+      <c r="C78" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="82" t="s">
+        <v>449</v>
+      </c>
+      <c r="E78" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="F78" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="G78" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="H78" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I78" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J78" s="39" t="s">
+        <v>511</v>
+      </c>
+      <c r="K78" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="L78" s="39">
+        <v>24</v>
+      </c>
+      <c r="M78" s="38">
+        <f t="shared" si="32"/>
+        <v>240</v>
+      </c>
+      <c r="N78" s="38">
+        <v>300</v>
+      </c>
+      <c r="O78" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P78" s="47">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q78" s="40">
+        <f>P78*N78</f>
+        <v>0.36</v>
+      </c>
+      <c r="R78" s="39"/>
+      <c r="S78" s="38"/>
+    </row>
+    <row r="79" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="59"/>
+      <c r="B79" s="81">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="C79" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="79" t="s">
+        <v>75</v>
+      </c>
+      <c r="E79" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="G79" s="67" t="s">
+        <v>294</v>
+      </c>
+      <c r="H79" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I79" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J79" s="68" t="s">
+        <v>371</v>
+      </c>
+      <c r="K79" s="67" t="s">
+        <v>411</v>
+      </c>
+      <c r="L79" s="68">
+        <v>1</v>
+      </c>
+      <c r="M79" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N79" s="68">
+        <v>100</v>
+      </c>
+      <c r="O79" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P79" s="70">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="Q79" s="71">
+        <f t="shared" ref="Q79" si="35">P79*N79</f>
+        <v>0.22</v>
+      </c>
+      <c r="R79" s="68"/>
+      <c r="S79" s="67"/>
+    </row>
+    <row r="80" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="59"/>
+      <c r="B80" s="78">
+        <f>ROW(B80) - ROW($B$9)</f>
+        <v>71</v>
+      </c>
+      <c r="C80" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" s="82" t="s">
+        <v>76</v>
+      </c>
+      <c r="E80" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="F80" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="G80" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="H80" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I80" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J80" s="39" t="s">
+        <v>372</v>
+      </c>
+      <c r="K80" s="38" t="s">
+        <v>406</v>
+      </c>
+      <c r="L80" s="39">
+        <v>1</v>
+      </c>
+      <c r="M80" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N80" s="38">
+        <v>50</v>
+      </c>
+      <c r="O80" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P80" s="47">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="Q80" s="40">
+        <f>P80*N80</f>
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="R80" s="39"/>
+      <c r="S80" s="38"/>
+    </row>
+    <row r="81" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="59"/>
+      <c r="B81" s="81">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="C81" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="E81" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="F81" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="G81" s="67" t="s">
+        <v>296</v>
+      </c>
+      <c r="H81" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I81" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J81" s="68" t="s">
+        <v>373</v>
+      </c>
+      <c r="K81" s="67" t="s">
+        <v>412</v>
+      </c>
+      <c r="L81" s="68">
+        <v>1</v>
+      </c>
+      <c r="M81" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N81" s="68">
+        <v>100</v>
+      </c>
+      <c r="O81" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P81" s="70">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q81" s="71">
+        <f t="shared" ref="Q81" si="36">P81*N81</f>
+        <v>0.13</v>
+      </c>
+      <c r="R81" s="68"/>
+      <c r="S81" s="67"/>
+    </row>
+    <row r="82" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A82" s="59"/>
+      <c r="B82" s="78">
+        <f>ROW(B82) - ROW($B$9)</f>
+        <v>73</v>
+      </c>
+      <c r="C82" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" s="82" t="s">
+        <v>78</v>
+      </c>
+      <c r="E82" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="F82" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="G82" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="H82" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I82" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J82" s="39" t="s">
+        <v>535</v>
+      </c>
+      <c r="K82" s="38" t="s">
+        <v>413</v>
+      </c>
+      <c r="L82" s="39">
+        <v>2</v>
+      </c>
+      <c r="M82" s="38">
+        <f t="shared" si="32"/>
+        <v>20</v>
+      </c>
+      <c r="N82" s="38">
+        <v>100</v>
+      </c>
+      <c r="O82" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P82" s="47">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q82" s="40">
+        <f>P82*N82</f>
+        <v>0.12</v>
+      </c>
+      <c r="R82" s="39"/>
+      <c r="S82" s="38"/>
+    </row>
+    <row r="83" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="59"/>
+      <c r="B83" s="81">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="C83" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" s="79" t="s">
+        <v>452</v>
+      </c>
+      <c r="E83" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="F83" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G83" s="72" t="s">
+        <v>298</v>
+      </c>
+      <c r="H83" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I83" s="67" t="s">
+        <v>537</v>
+      </c>
+      <c r="J83" s="68" t="s">
+        <v>536</v>
+      </c>
+      <c r="K83" s="67" t="s">
+        <v>411</v>
+      </c>
+      <c r="L83" s="68">
+        <v>5</v>
+      </c>
+      <c r="M83" s="38">
+        <f t="shared" si="32"/>
+        <v>50</v>
+      </c>
+      <c r="N83" s="68">
+        <v>100</v>
+      </c>
+      <c r="O83" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P83" s="70">
+        <v>2E-3</v>
+      </c>
+      <c r="Q83" s="71">
+        <f t="shared" ref="Q83" si="37">P83*N83</f>
+        <v>0.2</v>
+      </c>
+      <c r="R83" s="68"/>
+      <c r="S83" s="67"/>
+    </row>
+    <row r="84" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="59"/>
+      <c r="B84" s="78">
+        <f>ROW(B84) - ROW($B$9)</f>
+        <v>75</v>
+      </c>
+      <c r="C84" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="82" t="s">
+        <v>79</v>
+      </c>
+      <c r="E84" s="56" t="s">
+        <v>538</v>
+      </c>
+      <c r="F84" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="G84" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="H84" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I84" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J84" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="K84" s="38" t="s">
+        <v>414</v>
+      </c>
+      <c r="L84" s="39">
+        <v>2</v>
+      </c>
+      <c r="M84" s="38">
+        <f t="shared" si="32"/>
+        <v>20</v>
+      </c>
+      <c r="N84" s="38">
+        <v>100</v>
+      </c>
+      <c r="O84" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P84" s="47">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q84" s="40">
+        <f>P84*N84</f>
+        <v>0.13</v>
+      </c>
+      <c r="R84" s="39"/>
+      <c r="S84" s="38"/>
+    </row>
+    <row r="85" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="59"/>
+      <c r="B85" s="81">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="C85" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="E85" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="F85" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="G85" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="H85" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I85" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J85" s="68" t="s">
+        <v>374</v>
+      </c>
+      <c r="K85" s="67" t="s">
+        <v>415</v>
+      </c>
+      <c r="L85" s="68">
+        <v>2</v>
+      </c>
+      <c r="M85" s="38">
+        <f t="shared" si="32"/>
+        <v>20</v>
+      </c>
+      <c r="N85" s="68">
+        <v>100</v>
+      </c>
+      <c r="O85" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P85" s="70">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q85" s="71">
+        <f t="shared" ref="Q85" si="38">P85*N85</f>
+        <v>0.11</v>
+      </c>
+      <c r="R85" s="68"/>
+      <c r="S85" s="67"/>
+    </row>
+    <row r="86" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A86" s="59"/>
+      <c r="B86" s="78">
+        <f>ROW(B86) - ROW($B$9)</f>
+        <v>77</v>
+      </c>
+      <c r="C86" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="82" t="s">
+        <v>81</v>
+      </c>
+      <c r="E86" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="F86" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="G86" s="38" t="s">
+        <v>513</v>
+      </c>
+      <c r="H86" s="39" t="s">
+        <v>348</v>
+      </c>
+      <c r="I86" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J86" s="39" t="s">
+        <v>512</v>
+      </c>
+      <c r="K86" s="38" t="s">
+        <v>416</v>
+      </c>
+      <c r="L86" s="39">
+        <v>2</v>
+      </c>
+      <c r="M86" s="38">
+        <f t="shared" si="32"/>
+        <v>20</v>
+      </c>
+      <c r="N86" s="38">
+        <v>50</v>
+      </c>
+      <c r="O86" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P86" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="Q86" s="40">
+        <f>P86*N86</f>
+        <v>0.5</v>
+      </c>
+      <c r="R86" s="39"/>
+      <c r="S86" s="38"/>
+    </row>
+    <row r="87" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="59"/>
+      <c r="B87" s="81">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="C87" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="E87" s="67" t="s">
+        <v>515</v>
+      </c>
+      <c r="F87" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G87" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="H87" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I87" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J87" s="68" t="s">
+        <v>514</v>
+      </c>
+      <c r="K87" s="67" t="s">
+        <v>417</v>
+      </c>
+      <c r="L87" s="68">
+        <v>2</v>
+      </c>
+      <c r="M87" s="38">
+        <f t="shared" si="32"/>
+        <v>20</v>
+      </c>
+      <c r="N87" s="68">
+        <v>100</v>
+      </c>
+      <c r="O87" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P87" s="70">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q87" s="71">
+        <f t="shared" ref="Q87" si="39">P87*N87</f>
+        <v>0.12</v>
+      </c>
+      <c r="R87" s="68"/>
+      <c r="S87" s="67"/>
+    </row>
+    <row r="88" spans="1:19" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="59"/>
+      <c r="B88" s="78">
+        <f>ROW(B88) - ROW($B$9)</f>
+        <v>79</v>
+      </c>
+      <c r="C88" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="82" t="s">
+        <v>83</v>
+      </c>
+      <c r="E88" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="F88" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="G88" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="H88" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I88" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J88" s="39" t="s">
+        <v>530</v>
+      </c>
+      <c r="K88" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="L88" s="39">
+        <v>1</v>
+      </c>
+      <c r="M88" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N88" s="38">
+        <v>50</v>
+      </c>
+      <c r="O88" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P88" s="47">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="Q88" s="40">
+        <f>P88*N88</f>
+        <v>0.44</v>
+      </c>
+      <c r="R88" s="39"/>
+      <c r="S88" s="38"/>
+    </row>
+    <row r="89" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A89" s="59"/>
+      <c r="B89" s="81">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="C89" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="E89" s="67" t="s">
+        <v>175</v>
+      </c>
+      <c r="F89" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="G89" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="H89" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I89" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J89" s="68" t="s">
+        <v>531</v>
+      </c>
+      <c r="K89" s="67" t="s">
+        <v>419</v>
+      </c>
+      <c r="L89" s="68">
+        <v>1</v>
+      </c>
+      <c r="M89" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N89" s="68">
+        <v>20</v>
+      </c>
+      <c r="O89" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P89" s="70">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="Q89" s="71">
+        <f t="shared" ref="Q89" si="40">P89*N89</f>
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="R89" s="68"/>
+      <c r="S89" s="67"/>
+    </row>
+    <row r="90" spans="1:19" s="60" customFormat="1" ht="84" x14ac:dyDescent="0.25">
+      <c r="A90" s="59"/>
+      <c r="B90" s="81">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C90" s="88" t="s">
+        <v>231</v>
+      </c>
+      <c r="D90" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E90" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="F90" s="62" t="s">
+        <v>425</v>
+      </c>
+      <c r="G90" s="58" t="s">
+        <v>231</v>
+      </c>
+      <c r="H90" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="I90" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="J90" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="K90" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="L90" s="62">
+        <v>42</v>
+      </c>
+      <c r="M90" s="38">
+        <f t="shared" si="32"/>
+        <v>420</v>
+      </c>
+      <c r="N90" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="O90" s="63" t="s">
+        <v>436</v>
+      </c>
+      <c r="P90" s="64" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q90" s="65" t="s">
+        <v>436</v>
+      </c>
+      <c r="R90" s="62"/>
+      <c r="S90" s="58"/>
+    </row>
+    <row r="91" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A91" s="59"/>
+      <c r="B91" s="78">
+        <f>ROW(B91) - ROW($B$9)</f>
+        <v>82</v>
+      </c>
+      <c r="C91" s="86" t="s">
+        <v>532</v>
+      </c>
+      <c r="D91" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="E91" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="F91" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G91" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="H91" s="68" t="s">
+        <v>349</v>
+      </c>
+      <c r="I91" s="67" t="s">
+        <v>567</v>
+      </c>
+      <c r="J91" s="68" t="s">
+        <v>566</v>
+      </c>
+      <c r="K91" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L91" s="68">
+        <v>7</v>
+      </c>
+      <c r="M91" s="38">
+        <f t="shared" si="32"/>
+        <v>70</v>
+      </c>
+      <c r="N91" s="68">
+        <v>75</v>
+      </c>
+      <c r="O91" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P91" s="70">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="Q91" s="71">
+        <f>P91*N91</f>
+        <v>2.5724999999999998</v>
+      </c>
+      <c r="R91" s="61"/>
+      <c r="S91" s="67"/>
+    </row>
+    <row r="92" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A92" s="59"/>
+      <c r="B92" s="81">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="C92" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D92" s="82" t="s">
+        <v>87</v>
+      </c>
+      <c r="E92" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="F92" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="G92" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="H92" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="I92" s="38"/>
+      <c r="J92" s="39" t="s">
+        <v>436</v>
+      </c>
+      <c r="K92" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L92" s="39">
+        <v>2</v>
+      </c>
+      <c r="M92" s="38">
+        <f t="shared" si="32"/>
+        <v>20</v>
+      </c>
+      <c r="N92" s="38">
+        <v>21</v>
+      </c>
+      <c r="O92" s="57" t="s">
+        <v>565</v>
+      </c>
+      <c r="P92" s="47">
+        <v>3.76</v>
+      </c>
+      <c r="Q92" s="40">
+        <f t="shared" ref="Q92" si="41">P92*N92</f>
+        <v>78.959999999999994</v>
+      </c>
+      <c r="R92" s="61" t="s">
+        <v>568</v>
+      </c>
+      <c r="S92" s="38"/>
+    </row>
+    <row r="93" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A93" s="59"/>
+      <c r="B93" s="78">
+        <f>ROW(B93) - ROW($B$9)</f>
+        <v>84</v>
+      </c>
+      <c r="C93" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D93" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="E93" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="F93" s="68" t="s">
+        <v>233</v>
+      </c>
+      <c r="G93" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="H93" s="68" t="s">
+        <v>351</v>
+      </c>
+      <c r="I93" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J93" s="68" t="s">
+        <v>516</v>
+      </c>
+      <c r="K93" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L93" s="68">
+        <v>1</v>
+      </c>
+      <c r="M93" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N93" s="68">
+        <v>15</v>
+      </c>
+      <c r="O93" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P93" s="70">
+        <v>0.3463</v>
+      </c>
+      <c r="Q93" s="71">
+        <f>P93*N93</f>
+        <v>5.1944999999999997</v>
+      </c>
+      <c r="R93" s="68"/>
+      <c r="S93" s="67"/>
+    </row>
+    <row r="94" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A94" s="59"/>
+      <c r="B94" s="81">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C94" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D94" s="82" t="s">
+        <v>89</v>
+      </c>
+      <c r="E94" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="F94" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="G94" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="H94" s="39" t="s">
+        <v>351</v>
+      </c>
+      <c r="I94" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J94" s="39" t="s">
+        <v>517</v>
+      </c>
+      <c r="K94" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L94" s="39">
+        <v>1</v>
+      </c>
+      <c r="M94" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N94" s="38">
+        <v>11</v>
+      </c>
+      <c r="O94" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P94" s="47">
+        <v>0.85440000000000005</v>
+      </c>
+      <c r="Q94" s="40">
+        <f t="shared" ref="Q94" si="42">P94*N94</f>
+        <v>9.3984000000000005</v>
+      </c>
+      <c r="R94" s="39"/>
+      <c r="S94" s="38"/>
+    </row>
+    <row r="95" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A95" s="59"/>
+      <c r="B95" s="78">
+        <f>ROW(B95) - ROW($B$9)</f>
+        <v>86</v>
+      </c>
+      <c r="C95" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D95" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="E95" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="F95" s="68" t="s">
+        <v>235</v>
+      </c>
+      <c r="G95" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="H95" s="68" t="s">
+        <v>352</v>
+      </c>
+      <c r="I95" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J95" s="68" t="s">
+        <v>518</v>
+      </c>
+      <c r="K95" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L95" s="68">
+        <v>1</v>
+      </c>
+      <c r="M95" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N95" s="68">
+        <v>11</v>
+      </c>
+      <c r="O95" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P95" s="70">
+        <v>7.4375999999999998</v>
+      </c>
+      <c r="Q95" s="71">
+        <f>P95*N95</f>
+        <v>81.813599999999994</v>
+      </c>
+      <c r="R95" s="68"/>
+      <c r="S95" s="67"/>
+    </row>
+    <row r="96" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A96" s="59"/>
+      <c r="B96" s="81">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="C96" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D96" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="E96" s="56" t="s">
+        <v>182</v>
+      </c>
+      <c r="F96" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="G96" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="H96" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="I96" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J96" s="39" t="s">
+        <v>436</v>
+      </c>
+      <c r="K96" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L96" s="39">
+        <v>1</v>
+      </c>
+      <c r="M96" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N96" s="38">
+        <v>11</v>
+      </c>
+      <c r="O96" s="57" t="s">
+        <v>565</v>
+      </c>
+      <c r="P96" s="47">
+        <v>1.9550000000000001</v>
+      </c>
+      <c r="Q96" s="40">
+        <f t="shared" ref="Q96" si="43">P96*N96</f>
+        <v>21.505000000000003</v>
+      </c>
+      <c r="R96" s="61" t="s">
+        <v>568</v>
+      </c>
+      <c r="S96" s="38"/>
+    </row>
+    <row r="97" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A97" s="59"/>
+      <c r="B97" s="78">
+        <f>ROW(B97) - ROW($B$9)</f>
+        <v>88</v>
+      </c>
+      <c r="C97" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D97" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="E97" s="67" t="s">
+        <v>183</v>
+      </c>
+      <c r="F97" s="68" t="s">
+        <v>439</v>
+      </c>
+      <c r="G97" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="H97" s="68" t="s">
+        <v>353</v>
+      </c>
+      <c r="I97" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J97" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="K97" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L97" s="68">
+        <v>1</v>
+      </c>
+      <c r="M97" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N97" s="68">
+        <v>11</v>
+      </c>
+      <c r="O97" s="69" t="s">
+        <v>565</v>
+      </c>
+      <c r="P97" s="70">
+        <v>7.52</v>
+      </c>
+      <c r="Q97" s="71">
+        <f>P97*N97</f>
+        <v>82.72</v>
+      </c>
+      <c r="R97" s="61" t="s">
+        <v>568</v>
+      </c>
+      <c r="S97" s="67"/>
+    </row>
+    <row r="98" spans="1:19" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A98" s="59"/>
+      <c r="B98" s="81">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="C98" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D98" s="82" t="s">
+        <v>93</v>
+      </c>
+      <c r="E98" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="F98" s="39" t="s">
+        <v>437</v>
+      </c>
+      <c r="G98" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="H98" s="39" t="s">
+        <v>354</v>
+      </c>
+      <c r="I98" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J98" s="39" t="s">
+        <v>519</v>
+      </c>
+      <c r="K98" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L98" s="39">
+        <v>4</v>
+      </c>
+      <c r="M98" s="38">
+        <f t="shared" si="32"/>
+        <v>40</v>
+      </c>
+      <c r="N98" s="38">
+        <v>45</v>
+      </c>
+      <c r="O98" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P98" s="47">
+        <v>0.41510000000000002</v>
+      </c>
+      <c r="Q98" s="40">
+        <f t="shared" ref="Q98" si="44">P98*N98</f>
+        <v>18.679500000000001</v>
+      </c>
+      <c r="R98" s="39"/>
+      <c r="S98" s="38"/>
+    </row>
+    <row r="99" spans="1:19" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A99" s="59"/>
+      <c r="B99" s="78">
+        <f>ROW(B99) - ROW($B$9)</f>
+        <v>90</v>
+      </c>
+      <c r="C99" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D99" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="E99" s="67" t="s">
+        <v>185</v>
+      </c>
+      <c r="F99" s="68" t="s">
+        <v>238</v>
+      </c>
+      <c r="G99" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="H99" s="68" t="s">
+        <v>351</v>
+      </c>
+      <c r="I99" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J99" s="68" t="s">
+        <v>520</v>
+      </c>
+      <c r="K99" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L99" s="68">
+        <v>3</v>
+      </c>
+      <c r="M99" s="38">
+        <f t="shared" si="32"/>
+        <v>30</v>
+      </c>
+      <c r="N99" s="68">
+        <v>35</v>
+      </c>
+      <c r="O99" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P99" s="70">
+        <v>0.25240000000000001</v>
+      </c>
+      <c r="Q99" s="71">
+        <f>P99*N99</f>
+        <v>8.8339999999999996</v>
+      </c>
+      <c r="R99" s="102" t="s">
+        <v>589</v>
+      </c>
+      <c r="S99" s="67"/>
+    </row>
+    <row r="100" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A100" s="59"/>
+      <c r="B100" s="81">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="C100" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D100" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="E100" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="F100" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="G100" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="H100" s="39" t="s">
+        <v>351</v>
+      </c>
+      <c r="I100" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J100" s="39" t="s">
+        <v>521</v>
+      </c>
+      <c r="K100" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L100" s="39">
+        <v>1</v>
+      </c>
+      <c r="M100" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N100" s="38">
+        <v>11</v>
+      </c>
+      <c r="O100" s="57" t="s">
+        <v>565</v>
+      </c>
+      <c r="P100" s="47">
+        <v>2.56</v>
+      </c>
+      <c r="Q100" s="40">
+        <f t="shared" ref="Q100" si="45">P100*N100</f>
+        <v>28.16</v>
+      </c>
+      <c r="R100" s="61" t="s">
+        <v>568</v>
+      </c>
+      <c r="S100" s="38"/>
+    </row>
+    <row r="101" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A101" s="59"/>
+      <c r="B101" s="78">
+        <f>ROW(B101) - ROW($B$9)</f>
+        <v>92</v>
+      </c>
+      <c r="C101" s="86" t="s">
+        <v>533</v>
+      </c>
+      <c r="D101" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="E101" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="F101" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G101" s="67" t="s">
+        <v>311</v>
+      </c>
+      <c r="H101" s="68" t="s">
+        <v>355</v>
+      </c>
+      <c r="I101" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J101" s="68" t="s">
+        <v>522</v>
+      </c>
+      <c r="K101" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L101" s="68">
+        <v>1</v>
+      </c>
+      <c r="M101" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N101" s="68">
+        <v>11</v>
+      </c>
+      <c r="O101" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P101" s="70">
+        <v>3.7244000000000002</v>
+      </c>
+      <c r="Q101" s="71">
+        <f>P101*N101</f>
+        <v>40.968400000000003</v>
+      </c>
+      <c r="R101" s="77" t="s">
+        <v>540</v>
+      </c>
+      <c r="S101" s="67"/>
+    </row>
+    <row r="102" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A102" s="59"/>
+      <c r="B102" s="81">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="C102" s="85" t="s">
+        <v>533</v>
+      </c>
+      <c r="D102" s="82" t="s">
+        <v>97</v>
+      </c>
+      <c r="E102" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="F102" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="G102" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="H102" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="I102" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J102" s="39" t="s">
+        <v>523</v>
+      </c>
+      <c r="K102" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L102" s="39">
+        <v>1</v>
+      </c>
+      <c r="M102" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N102" s="38">
+        <v>11</v>
+      </c>
+      <c r="O102" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P102" s="47">
+        <v>0.89249999999999996</v>
+      </c>
+      <c r="Q102" s="40">
+        <f t="shared" ref="Q102" si="46">P102*N102</f>
+        <v>9.817499999999999</v>
+      </c>
+      <c r="R102" s="39"/>
+      <c r="S102" s="38"/>
+    </row>
+    <row r="103" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A103" s="59"/>
+      <c r="B103" s="78">
+        <f>ROW(B103) - ROW($B$9)</f>
+        <v>94</v>
+      </c>
+      <c r="C103" s="86" t="s">
+        <v>534</v>
+      </c>
+      <c r="D103" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="E103" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="F103" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G103" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="H103" s="68" t="s">
+        <v>357</v>
+      </c>
+      <c r="I103" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J103" s="68" t="s">
+        <v>524</v>
+      </c>
+      <c r="K103" s="67" t="s">
+        <v>420</v>
+      </c>
+      <c r="L103" s="68">
+        <v>1</v>
+      </c>
+      <c r="M103" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N103" s="68">
+        <v>15</v>
+      </c>
+      <c r="O103" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P103" s="70">
+        <v>0.19889999999999999</v>
+      </c>
+      <c r="Q103" s="71">
+        <f>P103*N103</f>
+        <v>2.9834999999999998</v>
+      </c>
+      <c r="R103" s="77" t="s">
+        <v>569</v>
+      </c>
+      <c r="S103" s="67"/>
+    </row>
+    <row r="104" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A104" s="59"/>
+      <c r="B104" s="81">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="C104" s="85" t="s">
+        <v>534</v>
+      </c>
+      <c r="D104" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="E104" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="F104" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="G104" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="H104" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="I104" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="J104" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="K104" s="38" t="s">
+        <v>421</v>
+      </c>
+      <c r="L104" s="39">
+        <v>1</v>
+      </c>
+      <c r="M104" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N104" s="38">
+        <v>15</v>
+      </c>
+      <c r="O104" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P104" s="47">
+        <v>0.1221</v>
+      </c>
+      <c r="Q104" s="40">
+        <f t="shared" ref="Q104" si="47">P104*N104</f>
+        <v>1.8314999999999999</v>
+      </c>
+      <c r="R104" s="39"/>
+      <c r="S104" s="38"/>
+    </row>
+    <row r="105" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A105" s="59"/>
+      <c r="B105" s="78">
+        <f>ROW(B105) - ROW($B$9)</f>
+        <v>96</v>
+      </c>
+      <c r="C105" s="86" t="s">
+        <v>534</v>
+      </c>
+      <c r="D105" s="79" t="s">
+        <v>100</v>
+      </c>
+      <c r="E105" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="F105" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G105" s="67" t="s">
+        <v>243</v>
+      </c>
+      <c r="H105" s="68" t="s">
+        <v>359</v>
+      </c>
+      <c r="I105" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J105" s="68" t="s">
+        <v>525</v>
+      </c>
+      <c r="K105" s="67" t="s">
+        <v>422</v>
+      </c>
+      <c r="L105" s="68">
+        <v>1</v>
+      </c>
+      <c r="M105" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N105" s="68">
+        <v>15</v>
+      </c>
+      <c r="O105" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P105" s="70">
+        <v>0.22420000000000001</v>
+      </c>
+      <c r="Q105" s="71">
+        <f>P105*N105</f>
+        <v>3.363</v>
+      </c>
+      <c r="R105" s="68"/>
+      <c r="S105" s="67"/>
+    </row>
+    <row r="106" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A106" s="59"/>
+      <c r="B106" s="78">
+        <f t="shared" ref="B106:B112" si="48">ROW(B106) - ROW($B$9)</f>
+        <v>97</v>
+      </c>
+      <c r="C106" s="86" t="s">
+        <v>554</v>
+      </c>
+      <c r="D106" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E106" s="67" t="s">
+        <v>547</v>
+      </c>
+      <c r="F106" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G106" s="67" t="s">
+        <v>548</v>
+      </c>
+      <c r="H106" s="68" t="s">
+        <v>549</v>
+      </c>
+      <c r="I106" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J106" s="68" t="s">
+        <v>550</v>
+      </c>
+      <c r="K106" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L106" s="68">
+        <v>9</v>
+      </c>
+      <c r="M106" s="38">
+        <f t="shared" si="32"/>
+        <v>90</v>
+      </c>
+      <c r="N106" s="68">
+        <v>95</v>
+      </c>
+      <c r="O106" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P106" s="70">
+        <v>0.1656</v>
+      </c>
+      <c r="Q106" s="71">
+        <f t="shared" ref="Q106:Q110" si="49">P106*N106</f>
+        <v>15.731999999999999</v>
+      </c>
+      <c r="R106" s="68"/>
+      <c r="S106" s="67"/>
+    </row>
+    <row r="107" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A107" s="59"/>
+      <c r="B107" s="78">
+        <f t="shared" si="48"/>
+        <v>98</v>
+      </c>
+      <c r="C107" s="86" t="s">
+        <v>554</v>
+      </c>
+      <c r="D107" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E107" s="67" t="s">
+        <v>552</v>
+      </c>
+      <c r="F107" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G107" s="67" t="s">
+        <v>553</v>
+      </c>
+      <c r="H107" s="68" t="s">
+        <v>549</v>
+      </c>
+      <c r="I107" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J107" s="68" t="s">
+        <v>551</v>
+      </c>
+      <c r="K107" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L107" s="68">
+        <v>5</v>
+      </c>
+      <c r="M107" s="38">
+        <f t="shared" si="32"/>
+        <v>50</v>
+      </c>
+      <c r="N107" s="68">
+        <v>55</v>
+      </c>
+      <c r="O107" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P107" s="70">
+        <v>0.2515</v>
+      </c>
+      <c r="Q107" s="71">
+        <f t="shared" si="49"/>
+        <v>13.8325</v>
+      </c>
+      <c r="R107" s="68"/>
+      <c r="S107" s="67"/>
+    </row>
+    <row r="108" spans="1:19" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A108" s="59"/>
+      <c r="B108" s="78">
+        <f t="shared" si="48"/>
+        <v>99</v>
+      </c>
+      <c r="C108" s="86" t="s">
+        <v>554</v>
+      </c>
+      <c r="D108" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E108" s="67" t="s">
+        <v>555</v>
+      </c>
+      <c r="F108" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G108" s="67" t="s">
+        <v>557</v>
+      </c>
+      <c r="H108" s="68" t="s">
+        <v>549</v>
+      </c>
+      <c r="I108" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J108" s="68" t="s">
+        <v>556</v>
+      </c>
+      <c r="K108" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L108" s="68">
+        <v>1</v>
+      </c>
+      <c r="M108" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N108" s="68">
+        <v>15</v>
+      </c>
+      <c r="O108" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P108" s="70">
+        <v>0.3553</v>
+      </c>
+      <c r="Q108" s="71">
+        <f t="shared" si="49"/>
+        <v>5.3295000000000003</v>
+      </c>
+      <c r="R108" s="68"/>
+      <c r="S108" s="67"/>
+    </row>
+    <row r="109" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A109" s="59"/>
+      <c r="B109" s="78">
+        <f t="shared" si="48"/>
+        <v>100</v>
+      </c>
+      <c r="C109" s="89" t="s">
+        <v>561</v>
+      </c>
+      <c r="D109" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E109" s="67" t="s">
+        <v>563</v>
+      </c>
+      <c r="F109" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G109" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="H109" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="I109" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J109" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="K109" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L109" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="M109" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="N109" s="68">
+        <v>5</v>
+      </c>
+      <c r="O109" s="69" t="s">
+        <v>562</v>
+      </c>
+      <c r="P109" s="70">
+        <v>1.33</v>
+      </c>
+      <c r="Q109" s="71">
+        <f t="shared" si="49"/>
+        <v>6.65</v>
+      </c>
+      <c r="R109" s="68"/>
+      <c r="S109" s="67"/>
+    </row>
+    <row r="110" spans="1:19" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A110" s="59"/>
+      <c r="B110" s="78">
+        <f t="shared" si="48"/>
+        <v>101</v>
+      </c>
+      <c r="C110" s="86" t="s">
+        <v>570</v>
+      </c>
+      <c r="D110" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E110" s="67" t="s">
+        <v>571</v>
+      </c>
+      <c r="F110" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G110" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="H110" s="68" t="s">
+        <v>572</v>
+      </c>
+      <c r="I110" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J110" s="68" t="s">
+        <v>573</v>
+      </c>
+      <c r="K110" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L110" s="68">
+        <v>1</v>
+      </c>
+      <c r="M110" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N110" s="68">
+        <v>10</v>
+      </c>
+      <c r="O110" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P110" s="70">
+        <v>1.0610999999999999</v>
+      </c>
+      <c r="Q110" s="71">
+        <f t="shared" si="49"/>
+        <v>10.610999999999999</v>
+      </c>
+      <c r="R110" s="68"/>
+      <c r="S110" s="67"/>
+    </row>
+    <row r="111" spans="1:19" s="60" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="59"/>
+      <c r="B111" s="78">
+        <f t="shared" si="48"/>
+        <v>102</v>
+      </c>
+      <c r="C111" s="89" t="s">
+        <v>576</v>
+      </c>
+      <c r="D111" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E111" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="F111" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G111" s="67" t="s">
+        <v>574</v>
+      </c>
+      <c r="H111" s="68"/>
+      <c r="I111" s="67"/>
+      <c r="J111" s="68" t="s">
+        <v>575</v>
+      </c>
+      <c r="K111" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L111" s="68">
+        <v>1</v>
+      </c>
+      <c r="M111" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N111" s="68">
+        <v>10</v>
+      </c>
+      <c r="O111" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P111" s="70">
+        <v>2.8001</v>
+      </c>
+      <c r="Q111" s="80">
+        <f>P111*N111</f>
+        <v>28.001000000000001</v>
+      </c>
+      <c r="R111" s="68"/>
+      <c r="S111" s="67"/>
+    </row>
+    <row r="112" spans="1:19" s="60" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="59"/>
+      <c r="B112" s="78">
+        <f t="shared" si="48"/>
+        <v>103</v>
+      </c>
+      <c r="C112" s="86" t="s">
+        <v>577</v>
+      </c>
+      <c r="D112" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="E112" s="67" t="s">
+        <v>578</v>
+      </c>
+      <c r="F112" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="G112" s="67" t="s">
+        <v>579</v>
+      </c>
+      <c r="H112" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="I112" s="67"/>
+      <c r="J112" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="K112" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="L112" s="68">
+        <v>1</v>
+      </c>
+      <c r="M112" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="N112" s="68">
+        <v>10</v>
+      </c>
+      <c r="O112" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="P112" s="70">
+        <v>0.1734</v>
+      </c>
+      <c r="Q112" s="80">
+        <f>P112*N112</f>
+        <v>1.734</v>
+      </c>
+      <c r="R112" s="68"/>
+      <c r="S112" s="67"/>
+    </row>
+    <row r="113" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1"/>
+      <c r="B113" s="41"/>
+      <c r="C113" s="42"/>
+      <c r="D113" s="43"/>
+      <c r="E113" s="44"/>
+      <c r="F113" s="45"/>
+      <c r="G113" s="46"/>
+      <c r="H113" s="45"/>
+      <c r="I113" s="46"/>
+      <c r="J113" s="45"/>
+      <c r="K113" s="46"/>
+      <c r="L113" s="46"/>
+      <c r="M113" s="46"/>
+      <c r="N113" s="99" t="s">
+        <v>5</v>
+      </c>
+      <c r="O113" s="100"/>
+      <c r="P113" s="100"/>
+      <c r="Q113" s="48">
+        <f>SUM(Q10:Q112)</f>
+        <v>676.12400000000002</v>
+      </c>
+      <c r="R113" s="95"/>
+      <c r="S113" s="96"/>
+    </row>
+    <row r="114" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="37"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="10"/>
+      <c r="F114" s="10"/>
+      <c r="G114" s="10"/>
+      <c r="H114" s="10"/>
+      <c r="I114" s="10"/>
+      <c r="J114" s="10"/>
+      <c r="K114" s="10"/>
+      <c r="L114" s="10"/>
+      <c r="M114" s="10"/>
+      <c r="N114" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="O114" s="100"/>
+      <c r="P114" s="100"/>
+      <c r="Q114" s="49">
+        <f>Q113/10</f>
+        <v>67.612400000000008</v>
+      </c>
+      <c r="R114" s="97"/>
+      <c r="S114" s="98"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N113:P113"/>
+    <mergeCell ref="R113:S114"/>
+    <mergeCell ref="N114:P114"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O17" r:id="rId8"/>
+    <hyperlink ref="O19" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O20" r:id="rId11"/>
+    <hyperlink ref="O22" r:id="rId12"/>
+    <hyperlink ref="O23" r:id="rId13"/>
+    <hyperlink ref="O24" r:id="rId14"/>
+    <hyperlink ref="O25" r:id="rId15"/>
+    <hyperlink ref="O26" r:id="rId16"/>
+    <hyperlink ref="O27" r:id="rId17"/>
+    <hyperlink ref="O30" r:id="rId18"/>
+    <hyperlink ref="O29" r:id="rId19"/>
+    <hyperlink ref="O33" r:id="rId20"/>
+    <hyperlink ref="O34" r:id="rId21"/>
+    <hyperlink ref="O35" r:id="rId22"/>
+    <hyperlink ref="O36" r:id="rId23"/>
+    <hyperlink ref="O38" r:id="rId24"/>
+    <hyperlink ref="O41" r:id="rId25"/>
+    <hyperlink ref="O42" r:id="rId26"/>
+    <hyperlink ref="O43" r:id="rId27"/>
+    <hyperlink ref="O45" r:id="rId28"/>
+    <hyperlink ref="O46" r:id="rId29"/>
+    <hyperlink ref="O53" r:id="rId30"/>
+    <hyperlink ref="O40" r:id="rId31"/>
+    <hyperlink ref="O49" r:id="rId32"/>
+    <hyperlink ref="O52" r:id="rId33"/>
+    <hyperlink ref="O54" r:id="rId34"/>
+    <hyperlink ref="O56" r:id="rId35"/>
+    <hyperlink ref="O44" r:id="rId36"/>
+    <hyperlink ref="O50" r:id="rId37"/>
+    <hyperlink ref="O51" r:id="rId38"/>
+    <hyperlink ref="O28" r:id="rId39"/>
+    <hyperlink ref="O39" r:id="rId40"/>
+    <hyperlink ref="O48" r:id="rId41"/>
+    <hyperlink ref="O57" r:id="rId42"/>
+    <hyperlink ref="O58" r:id="rId43"/>
+    <hyperlink ref="O59" r:id="rId44"/>
+    <hyperlink ref="O60" r:id="rId45"/>
+    <hyperlink ref="O61" r:id="rId46"/>
+    <hyperlink ref="O62" r:id="rId47"/>
+    <hyperlink ref="O63" r:id="rId48"/>
+    <hyperlink ref="O64" r:id="rId49"/>
+    <hyperlink ref="O65" r:id="rId50"/>
+    <hyperlink ref="O66" r:id="rId51"/>
+    <hyperlink ref="O67" r:id="rId52"/>
+    <hyperlink ref="O68" r:id="rId53"/>
+    <hyperlink ref="O69" r:id="rId54"/>
+    <hyperlink ref="O71" r:id="rId55"/>
+    <hyperlink ref="O72" r:id="rId56"/>
+    <hyperlink ref="O74" r:id="rId57"/>
+    <hyperlink ref="O77" r:id="rId58"/>
+    <hyperlink ref="O78" r:id="rId59"/>
+    <hyperlink ref="O86" r:id="rId60"/>
+    <hyperlink ref="O87" r:id="rId61"/>
+    <hyperlink ref="O94" r:id="rId62"/>
+    <hyperlink ref="O95" r:id="rId63"/>
+    <hyperlink ref="O99" r:id="rId64"/>
+    <hyperlink ref="O101" r:id="rId65"/>
+    <hyperlink ref="O102" r:id="rId66"/>
+    <hyperlink ref="O93" r:id="rId67"/>
+    <hyperlink ref="O98" r:id="rId68"/>
+    <hyperlink ref="O103" r:id="rId69"/>
+    <hyperlink ref="O105" r:id="rId70"/>
+    <hyperlink ref="O70" r:id="rId71"/>
+    <hyperlink ref="O73" r:id="rId72"/>
+    <hyperlink ref="O75" r:id="rId73"/>
+    <hyperlink ref="O76" r:id="rId74"/>
+    <hyperlink ref="O79" r:id="rId75"/>
+    <hyperlink ref="O80" r:id="rId76"/>
+    <hyperlink ref="O88" r:id="rId77"/>
+    <hyperlink ref="O89" r:id="rId78"/>
+    <hyperlink ref="O81" r:id="rId79"/>
+    <hyperlink ref="O82" r:id="rId80"/>
+    <hyperlink ref="O83" r:id="rId81"/>
+    <hyperlink ref="O84" r:id="rId82"/>
+    <hyperlink ref="O85" r:id="rId83"/>
+    <hyperlink ref="O104" r:id="rId84"/>
+    <hyperlink ref="O55" r:id="rId85"/>
+    <hyperlink ref="O11" r:id="rId86"/>
+    <hyperlink ref="O31" r:id="rId87"/>
+    <hyperlink ref="O106" r:id="rId88"/>
+    <hyperlink ref="O107" r:id="rId89"/>
+    <hyperlink ref="O108" r:id="rId90"/>
+    <hyperlink ref="O37" r:id="rId91"/>
+    <hyperlink ref="O109" r:id="rId92"/>
+    <hyperlink ref="O91" r:id="rId93"/>
+    <hyperlink ref="O110" r:id="rId94"/>
+    <hyperlink ref="O111" r:id="rId95"/>
+    <hyperlink ref="O112" r:id="rId96"/>
+    <hyperlink ref="O32" r:id="rId97"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId98"/>
+</worksheet>
 </file>